--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -541,14 +541,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : Kamis, 18 Juli 2026</t>
+          <t>Hari/Tanggal : 18 Juli 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15:21 WITA</t>
+          <t>Pukul        : 06.55 WITA</t>
         </is>
       </c>
     </row>
@@ -1807,14 +1807,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : Kamis, 18 Juli 2026</t>
+          <t>Hari/Tanggal : 18 Juli 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15:21 WITA</t>
+          <t>Pukul        : 06.55 WITA</t>
         </is>
       </c>
     </row>
@@ -8036,14 +8036,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : Kamis, 18 Juli 2026</t>
+          <t>Hari/Tanggal : 18 Juli 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15:21 WITA</t>
+          <t>Pukul        : 06.55 WITA</t>
         </is>
       </c>
     </row>
@@ -9227,14 +9227,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : Kamis, 18 Juli 2026</t>
+          <t>Hari/Tanggal : 18 Juli 2026</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15:21 WITA</t>
+          <t>Pukul        : 06.55 WITA</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,16 +49,8 @@
     <font>
       <color rgb="00595959"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00006100"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -81,18 +73,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -122,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -139,8 +119,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.55 WITA</t>
+          <t>Pukul        : 17.53 WITA</t>
         </is>
       </c>
     </row>
@@ -657,62 +635,62 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4125</v>
+        <v>4127</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1235</v>
+        <v>1214</v>
       </c>
       <c r="E7" s="4">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="3" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="G7" s="4">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="3" t="n">
-        <v>282</v>
+        <v>191</v>
       </c>
       <c r="I7" s="4">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K7" s="4">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2564</v>
+        <v>2664</v>
       </c>
       <c r="M7" s="4">
         <f>L7/B7</f>
         <v/>
       </c>
       <c r="N7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O7" s="4">
         <f>N7/B7</f>
         <v/>
       </c>
       <c r="P7" s="3" t="n">
-        <v>2857</v>
+        <v>2872</v>
       </c>
       <c r="Q7" s="4">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="3" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="S7" s="4">
         <f>R7/B7</f>
@@ -732,21 +710,21 @@
         <v>24</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E8" s="4">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="3" t="n">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="G8" s="4">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I8" s="4">
         <f>H8/B8</f>
@@ -760,7 +738,7 @@
         <v/>
       </c>
       <c r="L8" s="3" t="n">
-        <v>658</v>
+        <v>672</v>
       </c>
       <c r="M8" s="4">
         <f>L8/B8</f>
@@ -774,14 +752,14 @@
         <v/>
       </c>
       <c r="P8" s="3" t="n">
-        <v>679</v>
+        <v>689</v>
       </c>
       <c r="Q8" s="4">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S8" s="4">
         <f>R8/B8</f>
@@ -795,41 +773,41 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>6198</v>
+        <v>6217</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1724</v>
+        <v>1673</v>
       </c>
       <c r="E9" s="4">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="3" t="n">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="G9" s="4">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="3" t="n">
-        <v>337</v>
+        <v>279</v>
       </c>
       <c r="I9" s="4">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K9" s="4">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="3" t="n">
-        <v>4003</v>
+        <v>4085</v>
       </c>
       <c r="M9" s="4">
         <f>L9/B9</f>
@@ -843,14 +821,14 @@
         <v/>
       </c>
       <c r="P9" s="3" t="n">
-        <v>4407</v>
+        <v>4435</v>
       </c>
       <c r="Q9" s="4">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="3" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="S9" s="4">
         <f>R9/B9</f>
@@ -864,13 +842,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3135</v>
+        <v>3145</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>856</v>
+        <v>839</v>
       </c>
       <c r="E10" s="4">
         <f>D10/B10</f>
@@ -884,21 +862,21 @@
         <v/>
       </c>
       <c r="H10" s="3" t="n">
-        <v>98</v>
+        <v>44</v>
       </c>
       <c r="I10" s="4">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K10" s="4">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="3" t="n">
-        <v>2165</v>
+        <v>2240</v>
       </c>
       <c r="M10" s="4">
         <f>L10/B10</f>
@@ -912,14 +890,14 @@
         <v/>
       </c>
       <c r="P10" s="3" t="n">
-        <v>2279</v>
+        <v>2306</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="3" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="S10" s="4">
         <f>R10/B10</f>
@@ -933,27 +911,27 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="E11" s="4">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G11" s="4">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" s="4">
         <f>H11/B11</f>
@@ -967,7 +945,7 @@
         <v/>
       </c>
       <c r="L11" s="3" t="n">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M11" s="4">
         <f>L11/B11</f>
@@ -981,14 +959,14 @@
         <v/>
       </c>
       <c r="P11" s="3" t="n">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="Q11" s="4">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="4">
         <f>R11/B11</f>
@@ -1002,13 +980,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="E12" s="4">
         <f>D12/B12</f>
@@ -1022,7 +1000,7 @@
         <v/>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I12" s="4">
         <f>H12/B12</f>
@@ -1050,14 +1028,14 @@
         <v/>
       </c>
       <c r="P12" s="3" t="n">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="Q12" s="4">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" s="4">
         <f>R12/B12</f>
@@ -1071,13 +1049,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>4580</v>
+        <v>4583</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2082</v>
+        <v>2076</v>
       </c>
       <c r="E13" s="4">
         <f>D13/B13</f>
@@ -1091,21 +1069,21 @@
         <v/>
       </c>
       <c r="H13" s="3" t="n">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="I13" s="4">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K13" s="4">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="3" t="n">
-        <v>2198</v>
+        <v>2215</v>
       </c>
       <c r="M13" s="4">
         <f>L13/B13</f>
@@ -1119,14 +1097,14 @@
         <v/>
       </c>
       <c r="P13" s="3" t="n">
-        <v>2463</v>
+        <v>2472</v>
       </c>
       <c r="Q13" s="4">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S13" s="4">
         <f>R13/B13</f>
@@ -1140,27 +1118,27 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5976</v>
+        <v>5984</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2875</v>
+        <v>2852</v>
       </c>
       <c r="E14" s="4">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="3" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G14" s="4">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="3" t="n">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="I14" s="4">
         <f>H14/B14</f>
@@ -1174,7 +1152,7 @@
         <v/>
       </c>
       <c r="L14" s="3" t="n">
-        <v>2841</v>
+        <v>2861</v>
       </c>
       <c r="M14" s="4">
         <f>L14/B14</f>
@@ -1188,14 +1166,14 @@
         <v/>
       </c>
       <c r="P14" s="3" t="n">
-        <v>3066</v>
+        <v>3093</v>
       </c>
       <c r="Q14" s="4">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="3" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S14" s="4">
         <f>R14/B14</f>
@@ -1209,27 +1187,27 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>8021</v>
+        <v>8031</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3624</v>
+        <v>3608</v>
       </c>
       <c r="E15" s="4">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G15" s="4">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="3" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I15" s="4">
         <f>H15/B15</f>
@@ -1243,7 +1221,7 @@
         <v/>
       </c>
       <c r="L15" s="3" t="n">
-        <v>4235</v>
+        <v>4245</v>
       </c>
       <c r="M15" s="4">
         <f>L15/B15</f>
@@ -1257,14 +1235,14 @@
         <v/>
       </c>
       <c r="P15" s="3" t="n">
-        <v>4259</v>
+        <v>4283</v>
       </c>
       <c r="Q15" s="4">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="3" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S15" s="4">
         <f>R15/B15</f>
@@ -1278,41 +1256,41 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5164</v>
+        <v>5168</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2135</v>
+        <v>2100</v>
       </c>
       <c r="E16" s="4">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="3" t="n">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G16" s="4">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="3" t="n">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="I16" s="4">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="3" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K16" s="4">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="3" t="n">
-        <v>2804</v>
+        <v>2812</v>
       </c>
       <c r="M16" s="4">
         <f>L16/B16</f>
@@ -1326,14 +1304,14 @@
         <v/>
       </c>
       <c r="P16" s="3" t="n">
-        <v>2910</v>
+        <v>2941</v>
       </c>
       <c r="Q16" s="4">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="S16" s="4">
         <f>R16/B16</f>
@@ -1347,41 +1325,41 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>2398</v>
+        <v>2402</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="E17" s="4">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G17" s="4">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="3" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I17" s="4">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K17" s="4">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="3" t="n">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="M17" s="4">
         <f>L17/B17</f>
@@ -1395,14 +1373,14 @@
         <v/>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1243</v>
+        <v>1248</v>
       </c>
       <c r="Q17" s="4">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S17" s="4">
         <f>R17/B17</f>
@@ -1416,41 +1394,41 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>9113</v>
+        <v>9133</v>
       </c>
       <c r="C18" s="3" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2839</v>
+        <v>2800</v>
       </c>
       <c r="E18" s="4">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="3" t="n">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="G18" s="4">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="3" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I18" s="4">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K18" s="4">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="3" t="n">
-        <v>5991</v>
+        <v>6025</v>
       </c>
       <c r="M18" s="4">
         <f>L18/B18</f>
@@ -1464,14 +1442,14 @@
         <v/>
       </c>
       <c r="P18" s="3" t="n">
-        <v>6153</v>
+        <v>6191</v>
       </c>
       <c r="Q18" s="4">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="3" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="S18" s="4">
         <f>R18/B18</f>
@@ -1491,7 +1469,7 @@
         <v>26</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="E19" s="4">
         <f>D19/B19</f>
@@ -1505,21 +1483,21 @@
         <v/>
       </c>
       <c r="H19" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I19" s="4">
         <f>H19/B19</f>
         <v/>
       </c>
       <c r="J19" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K19" s="4">
         <f>J19/B19</f>
         <v/>
       </c>
       <c r="L19" s="3" t="n">
-        <v>834</v>
+        <v>845</v>
       </c>
       <c r="M19" s="4">
         <f>L19/B19</f>
@@ -1533,14 +1511,14 @@
         <v/>
       </c>
       <c r="P19" s="3" t="n">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="Q19" s="4">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S19" s="4">
         <f>R19/B19</f>
@@ -1623,13 +1601,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2788</v>
+        <v>2793</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1210</v>
+        <v>1195</v>
       </c>
       <c r="E21" s="4">
         <f>D21/B21</f>
@@ -1643,21 +1621,21 @@
         <v/>
       </c>
       <c r="H21" s="3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I21" s="4">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K21" s="4">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="3" t="n">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="M21" s="4">
         <f>L21/B21</f>
@@ -1671,14 +1649,14 @@
         <v/>
       </c>
       <c r="P21" s="3" t="n">
-        <v>1574</v>
+        <v>1594</v>
       </c>
       <c r="Q21" s="4">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="3" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="S21" s="4">
         <f>R21/B21</f>
@@ -1814,7 +1792,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.55 WITA</t>
+          <t>Pukul        : 17.53 WITA</t>
         </is>
       </c>
     </row>
@@ -2050,10 +2028,10 @@
         <v>544</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0</v>
@@ -2080,45 +2058,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Merry Christiani Lano</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>508</v>
+        <v>364</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>118</v>
+      </c>
+      <c r="I11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" s="3" t="n">
-        <v>409</v>
+        <v>196</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>430</v>
+        <v>318</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.8464566929133859</v>
+        <v>0.8736263736263736</v>
       </c>
     </row>
     <row r="12">
@@ -2127,45 +2105,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Alfred Jonathan</t>
+          <t>Merry Christiani Lano</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>377</v>
+        <v>514</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>303</v>
+        <v>430</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>311</v>
+        <v>431</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.8249336870026525</v>
+        <v>0.8385214007782102</v>
       </c>
     </row>
     <row r="13">
@@ -2174,45 +2152,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Fitria Rianti Gorosita</t>
+          <t>Alfred Jonathan</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.8176943699731903</v>
+        <v>0.8381962864721486</v>
       </c>
     </row>
     <row r="14">
@@ -2235,31 +2213,31 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.8097826086956522</v>
+        <v>0.8333333333333335</v>
       </c>
     </row>
     <row r="15">
@@ -2268,45 +2246,45 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Fitria Rianti Gorosita</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>425</v>
+        <v>373</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>343</v>
+        <v>305</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.8070588235294117</v>
+        <v>0.8176943699731903</v>
       </c>
     </row>
     <row r="16">
@@ -2315,45 +2293,45 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>481</v>
+        <v>426</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>105</v>
+        <v>74</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>374</v>
+        <v>260</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.7796257796257797</v>
+        <v>0.812206572769953</v>
       </c>
     </row>
     <row r="17">
@@ -2376,31 +2354,31 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>106</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>7</v>
-      </c>
       <c r="J17" s="3" t="n">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.7784552845528455</v>
+        <v>0.7813765182186235</v>
       </c>
     </row>
     <row r="18">
@@ -2409,45 +2387,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>395</v>
+        <v>481</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>294</v>
+        <v>373</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>307</v>
+        <v>374</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7772151898734179</v>
+        <v>0.7775467775467776</v>
       </c>
     </row>
     <row r="19">
@@ -2456,45 +2434,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>475</v>
+        <v>395</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>368</v>
+        <v>307</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.7747368421052632</v>
+        <v>0.7772151898734179</v>
       </c>
     </row>
     <row r="20">
@@ -2503,7 +2481,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -2517,31 +2495,31 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>360</v>
+        <v>475</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>193</v>
+        <v>362</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>274</v>
+        <v>368</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7611111111111112</v>
+        <v>0.7747368421052632</v>
       </c>
     </row>
     <row r="21">
@@ -2550,45 +2528,45 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>428</v>
+        <v>365</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>325</v>
+        <v>278</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.7593457943925234</v>
+        <v>0.7616438356164383</v>
       </c>
     </row>
     <row r="22">
@@ -2597,45 +2575,45 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>365</v>
+        <v>410</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>276</v>
+        <v>310</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>276</v>
+        <v>312</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.7561643835616438</v>
+        <v>0.7609756097560976</v>
       </c>
     </row>
     <row r="23">
@@ -2644,7 +2622,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2658,7 +2636,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>103</v>
@@ -2667,22 +2645,22 @@
         <v>0</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.7541766109785203</v>
+        <v>0.7593457943925234</v>
       </c>
     </row>
     <row r="24">
@@ -2705,16 +2683,16 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>12</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>0</v>
@@ -2726,10 +2704,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.75</v>
+        <v>0.7590822179732314</v>
       </c>
     </row>
     <row r="25">
@@ -2738,45 +2716,45 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J25" s="3" t="n">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.7408312958435208</v>
+        <v>0.7541766109785203</v>
       </c>
     </row>
     <row r="26">
@@ -2785,45 +2763,45 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>385</v>
+        <v>493</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>276</v>
+        <v>357</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>284</v>
+        <v>370</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.7376623376623377</v>
+        <v>0.7505070993914807</v>
       </c>
     </row>
     <row r="27">
@@ -2832,45 +2810,45 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>493</v>
+        <v>385</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>351</v>
+        <v>285</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>361</v>
+        <v>286</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.7322515212981745</v>
+        <v>0.7428571428571429</v>
       </c>
     </row>
     <row r="28">
@@ -2893,31 +2871,31 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.722567287784679</v>
+        <v>0.7252066115702479</v>
       </c>
     </row>
     <row r="29">
@@ -2943,28 +2921,28 @@
         <v>382</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.7225130890052356</v>
+        <v>0.725130890052356</v>
       </c>
     </row>
     <row r="30">
@@ -2987,13 +2965,13 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>138</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0</v>
@@ -3011,7 +2989,7 @@
         <v>354</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.7137096774193549</v>
+        <v>0.7122736418511066</v>
       </c>
     </row>
     <row r="31">
@@ -3020,45 +2998,45 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E31" s="3" t="n">
-        <v>551</v>
+        <v>406</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>357</v>
+        <v>274</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>389</v>
+        <v>287</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.705989110707804</v>
+        <v>0.7068965517241379</v>
       </c>
     </row>
     <row r="32">
@@ -3067,45 +3045,45 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>414</v>
+        <v>551</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>287</v>
+        <v>357</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>291</v>
+        <v>389</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.7028985507246377</v>
+        <v>0.705989110707804</v>
       </c>
     </row>
     <row r="33">
@@ -3114,45 +3092,45 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>346</v>
+        <v>420</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="G33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.7023121387283237</v>
+        <v>0.7047619047619048</v>
       </c>
     </row>
     <row r="34">
@@ -3161,45 +3139,45 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>416</v>
+        <v>489</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>291</v>
+        <v>344</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.6995192307692306</v>
+        <v>0.7034764826175869</v>
       </c>
     </row>
     <row r="35">
@@ -3208,45 +3186,45 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E35" s="3" t="n">
-        <v>489</v>
+        <v>414</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>311</v>
+        <v>287</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>342</v>
+        <v>291</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.6993865030674846</v>
+        <v>0.7028985507246377</v>
       </c>
     </row>
     <row r="36">
@@ -3255,45 +3233,45 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>404</v>
+        <v>346</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>267</v>
+        <v>242</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="M36" s="4" t="n">
-        <v>0.6905940594059404</v>
+        <v>0.7023121387283237</v>
       </c>
     </row>
     <row r="37">
@@ -3316,31 +3294,31 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="M37" s="4" t="n">
-        <v>0.6892655367231639</v>
+        <v>0.6985018726591761</v>
       </c>
     </row>
     <row r="38">
@@ -3363,31 +3341,31 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M38" s="4" t="n">
-        <v>0.6863905325443787</v>
+        <v>0.6895874263261297</v>
       </c>
     </row>
     <row r="39">
@@ -3413,13 +3391,13 @@
         <v>388</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>0</v>
@@ -3431,10 +3409,10 @@
         <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M39" s="4" t="n">
-        <v>0.6804123711340206</v>
+        <v>0.6829896907216495</v>
       </c>
     </row>
     <row r="40">
@@ -3460,7 +3438,7 @@
         <v>374</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>1</v>
@@ -3475,13 +3453,13 @@
         <v>252</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M40" s="4" t="n">
-        <v>0.6764705882352942</v>
+        <v>0.679144385026738</v>
       </c>
     </row>
     <row r="41">
@@ -3504,7 +3482,7 @@
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>131</v>
@@ -3513,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>2</v>
@@ -3525,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>0.6700251889168766</v>
+        <v>0.6708542713567839</v>
       </c>
     </row>
     <row r="42">
@@ -3645,7 +3623,7 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F44" s="3" t="n">
         <v>175</v>
@@ -3654,7 +3632,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" s="3" t="n">
         <v>2</v>
@@ -3666,10 +3644,10 @@
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M44" s="4" t="n">
-        <v>0.6641074856046064</v>
+        <v>0.664750957854406</v>
       </c>
     </row>
     <row r="45">
@@ -3678,45 +3656,45 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>415</v>
+        <v>495</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>249</v>
+        <v>325</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>275</v>
+        <v>329</v>
       </c>
       <c r="M45" s="4" t="n">
-        <v>0.6626506024096386</v>
+        <v>0.6646464646464646</v>
       </c>
     </row>
     <row r="46">
@@ -3725,45 +3703,45 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>495</v>
+        <v>415</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="I46" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="n">
-        <v>319</v>
+        <v>249</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="M46" s="4" t="n">
-        <v>0.6565656565656566</v>
+        <v>0.6626506024096386</v>
       </c>
     </row>
     <row r="47">
@@ -3772,45 +3750,45 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>444</v>
+        <v>499</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>282</v>
+        <v>310</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>284</v>
+        <v>328</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>0.6396396396396397</v>
+        <v>0.657314629258517</v>
       </c>
     </row>
     <row r="48">
@@ -3819,45 +3797,45 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>498</v>
+        <v>444</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="M48" s="4" t="n">
-        <v>0.6345381526104418</v>
+        <v>0.6396396396396397</v>
       </c>
     </row>
     <row r="49">
@@ -3866,45 +3844,45 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>129</v>
+        <v>168</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="K49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="M49" s="4" t="n">
-        <v>0.6339285714285714</v>
+        <v>0.6314655172413793</v>
       </c>
     </row>
     <row r="50">
@@ -3913,45 +3891,45 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>464</v>
+        <v>405</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>293</v>
+        <v>193</v>
       </c>
       <c r="K50" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>293</v>
+        <v>255</v>
       </c>
       <c r="M50" s="4" t="n">
-        <v>0.6314655172413793</v>
+        <v>0.6296296296296297</v>
       </c>
     </row>
     <row r="51">
@@ -3960,45 +3938,45 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>405</v>
+        <v>452</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>193</v>
+        <v>283</v>
       </c>
       <c r="K51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>255</v>
+        <v>284</v>
       </c>
       <c r="M51" s="4" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.6283185840707964</v>
       </c>
     </row>
     <row r="52">
@@ -4030,13 +4008,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="K52" s="3" t="n">
         <v>0</v>
@@ -4101,45 +4079,45 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>434</v>
+        <v>367</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>269</v>
+        <v>227</v>
       </c>
       <c r="K54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="M54" s="4" t="n">
-        <v>0.6221198156682027</v>
+        <v>0.6267029972752044</v>
       </c>
     </row>
     <row r="55">
@@ -4162,31 +4140,31 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="K55" s="3" t="n">
         <v>2</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M55" s="4" t="n">
-        <v>0.6220095693779905</v>
+        <v>0.6261904761904762</v>
       </c>
     </row>
     <row r="56">
@@ -4195,45 +4173,45 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>367</v>
+        <v>435</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="K56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="M56" s="4" t="n">
-        <v>0.6212534059945504</v>
+        <v>0.6206896551724138</v>
       </c>
     </row>
     <row r="57">
@@ -4289,45 +4267,45 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="K58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="M58" s="4" t="n">
-        <v>0.62</v>
+        <v>0.613682092555332</v>
       </c>
     </row>
     <row r="59">
@@ -4336,45 +4314,45 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>497</v>
+        <v>452</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>295</v>
+        <v>238</v>
       </c>
       <c r="K59" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>305</v>
+        <v>277</v>
       </c>
       <c r="M59" s="4" t="n">
-        <v>0.613682092555332</v>
+        <v>0.6128318584070797</v>
       </c>
     </row>
     <row r="60">
@@ -4383,45 +4361,45 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>452</v>
+        <v>500</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="M60" s="4" t="n">
-        <v>0.6061946902654868</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="61">
@@ -4430,45 +4408,45 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>429</v>
+        <v>509</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="K61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="M61" s="4" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.6090373280943026</v>
       </c>
     </row>
     <row r="62">
@@ -4477,45 +4455,45 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E62" s="3" t="n">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="M62" s="4" t="n">
-        <v>0.6059225512528473</v>
+        <v>0.6060606060606061</v>
       </c>
     </row>
     <row r="63">
@@ -4524,45 +4502,45 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>496</v>
+        <v>439</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="K63" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="M63" s="4" t="n">
-        <v>0.6048387096774194</v>
+        <v>0.6059225512528473</v>
       </c>
     </row>
     <row r="64">
@@ -4571,45 +4549,45 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E64" s="3" t="n">
-        <v>427</v>
+        <v>504</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>172</v>
+        <v>200</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I64" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="I64" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J64" s="3" t="n">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="K64" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="M64" s="4" t="n">
-        <v>0.5971896955503513</v>
+        <v>0.6031746031746031</v>
       </c>
     </row>
     <row r="65">
@@ -4638,25 +4616,25 @@
         <v>163</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="K65" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M65" s="4" t="n">
-        <v>0.5970873786407767</v>
+        <v>0.5995145631067961</v>
       </c>
     </row>
     <row r="66">
@@ -4665,45 +4643,45 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>503</v>
+        <v>427</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="G66" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>286</v>
+        <v>249</v>
       </c>
       <c r="K66" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>300</v>
+        <v>255</v>
       </c>
       <c r="M66" s="4" t="n">
-        <v>0.5964214711729622</v>
+        <v>0.5971896955503513</v>
       </c>
     </row>
     <row r="67">
@@ -4712,45 +4690,45 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>400</v>
+        <v>449</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>203</v>
+        <v>262</v>
       </c>
       <c r="K67" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="M67" s="4" t="n">
-        <v>0.5925</v>
+        <v>0.5946547884187082</v>
       </c>
     </row>
     <row r="68">
@@ -4759,45 +4737,45 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>449</v>
+        <v>371</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>183</v>
+        <v>131</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>262</v>
+        <v>216</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>266</v>
+        <v>220</v>
       </c>
       <c r="M68" s="4" t="n">
-        <v>0.5924276169265034</v>
+        <v>0.5929919137466307</v>
       </c>
     </row>
     <row r="69">
@@ -4806,45 +4784,45 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>466</v>
+        <v>400</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H69" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I69" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I69" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="J69" s="3" t="n">
-        <v>272</v>
+        <v>203</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>275</v>
+        <v>237</v>
       </c>
       <c r="M69" s="4" t="n">
-        <v>0.5901287553648069</v>
+        <v>0.5925</v>
       </c>
     </row>
     <row r="70">
@@ -4853,45 +4831,45 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>345</v>
+        <v>468</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>195</v>
+        <v>272</v>
       </c>
       <c r="K70" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>203</v>
+        <v>276</v>
       </c>
       <c r="M70" s="4" t="n">
-        <v>0.5884057971014492</v>
+        <v>0.5897435897435898</v>
       </c>
     </row>
     <row r="71">
@@ -4900,45 +4878,45 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="M71" s="4" t="n">
-        <v>0.587431693989071</v>
+        <v>0.5894736842105263</v>
       </c>
     </row>
     <row r="72">
@@ -4947,33 +4925,33 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="G72" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J72" s="3" t="n">
         <v>201</v>
@@ -4982,10 +4960,10 @@
         <v>0</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="M72" s="4" t="n">
-        <v>0.5872576177285319</v>
+        <v>0.5884057971014492</v>
       </c>
     </row>
     <row r="73">
@@ -4994,45 +4972,45 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>458</v>
+        <v>361</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>263</v>
+        <v>201</v>
       </c>
       <c r="K73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>267</v>
+        <v>212</v>
       </c>
       <c r="M73" s="4" t="n">
-        <v>0.5829694323144105</v>
+        <v>0.5872576177285319</v>
       </c>
     </row>
     <row r="74">
@@ -5041,45 +5019,45 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>377</v>
+        <v>462</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>208</v>
+        <v>263</v>
       </c>
       <c r="K74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>217</v>
+        <v>271</v>
       </c>
       <c r="M74" s="4" t="n">
-        <v>0.5755968169761273</v>
+        <v>0.5865800865800865</v>
       </c>
     </row>
     <row r="75">
@@ -5102,16 +5080,16 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0</v>
@@ -5123,10 +5101,10 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="M75" s="4" t="n">
-        <v>0.569620253164557</v>
+        <v>0.5747747747747748</v>
       </c>
     </row>
     <row r="76">
@@ -5135,45 +5113,45 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>433</v>
+        <v>498</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>232</v>
+        <v>279</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>246</v>
+        <v>285</v>
       </c>
       <c r="M76" s="4" t="n">
-        <v>0.5681293302540416</v>
+        <v>0.572289156626506</v>
       </c>
     </row>
     <row r="77">
@@ -5182,45 +5160,45 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E77" s="3" t="n">
-        <v>394</v>
+        <v>455</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>212</v>
+        <v>254</v>
       </c>
       <c r="K77" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>223</v>
+        <v>260</v>
       </c>
       <c r="M77" s="4" t="n">
-        <v>0.565989847715736</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="78">
@@ -5229,7 +5207,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -5243,31 +5221,31 @@
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>232</v>
+      </c>
+      <c r="K78" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J78" s="3" t="n">
-        <v>243</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L78" s="3" t="n">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="M78" s="4" t="n">
-        <v>0.5638766519823789</v>
+        <v>0.5681293302540416</v>
       </c>
     </row>
     <row r="79">
@@ -5276,45 +5254,45 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>237</v>
+        <v>221</v>
       </c>
       <c r="K79" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="M79" s="4" t="n">
-        <v>0.5633802816901409</v>
+        <v>0.565989847715736</v>
       </c>
     </row>
     <row r="80">
@@ -5323,45 +5301,45 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>532</v>
+        <v>462</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>289</v>
+        <v>249</v>
       </c>
       <c r="K80" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>299</v>
+        <v>261</v>
       </c>
       <c r="M80" s="4" t="n">
-        <v>0.5620300751879699</v>
+        <v>0.564935064935065</v>
       </c>
     </row>
     <row r="81">
@@ -5370,45 +5348,45 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E81" s="3" t="n">
-        <v>462</v>
+        <v>426</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>195</v>
+        <v>176</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="K81" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="M81" s="4" t="n">
-        <v>0.5606060606060606</v>
+        <v>0.5633802816901409</v>
       </c>
     </row>
     <row r="82">
@@ -5417,45 +5395,45 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E82" s="3" t="n">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="G82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K82" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="M82" s="4" t="n">
-        <v>0.5591939546599496</v>
+        <v>0.5631868131868132</v>
       </c>
     </row>
     <row r="83">
@@ -5464,45 +5442,45 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E83" s="3" t="n">
-        <v>470</v>
+        <v>532</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>180</v>
+        <v>233</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="K83" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>262</v>
+        <v>299</v>
       </c>
       <c r="M83" s="4" t="n">
-        <v>0.5574468085106383</v>
+        <v>0.5620300751879699</v>
       </c>
     </row>
     <row r="84">
@@ -5511,45 +5489,45 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E84" s="3" t="n">
-        <v>497</v>
+        <v>445</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>272</v>
+        <v>246</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="M84" s="4" t="n">
-        <v>0.5573440643863179</v>
+        <v>0.5595505617977528</v>
       </c>
     </row>
     <row r="85">
@@ -5558,45 +5536,45 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E85" s="3" t="n">
-        <v>501</v>
+        <v>397</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H85" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I85" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I85" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="J85" s="3" t="n">
-        <v>271</v>
+        <v>202</v>
       </c>
       <c r="K85" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="M85" s="4" t="n">
-        <v>0.5548902195608783</v>
+        <v>0.5591939546599496</v>
       </c>
     </row>
     <row r="86">
@@ -5605,7 +5583,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -5619,31 +5597,31 @@
         </is>
       </c>
       <c r="E86" s="3" t="n">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I86" s="3" t="n">
         <v>3</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="K86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="M86" s="4" t="n">
-        <v>0.5528455284552846</v>
+        <v>0.5574468085106383</v>
       </c>
     </row>
     <row r="87">
@@ -5652,45 +5630,45 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E87" s="3" t="n">
-        <v>445</v>
+        <v>501</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>245</v>
+        <v>271</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="M87" s="4" t="n">
-        <v>0.5528089887640449</v>
+        <v>0.5548902195608783</v>
       </c>
     </row>
     <row r="88">
@@ -5699,45 +5677,45 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E88" s="3" t="n">
-        <v>363</v>
+        <v>492</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>199</v>
+        <v>269</v>
       </c>
       <c r="K88" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>199</v>
+        <v>272</v>
       </c>
       <c r="M88" s="4" t="n">
-        <v>0.5482093663911846</v>
+        <v>0.5528455284552846</v>
       </c>
     </row>
     <row r="89">
@@ -5910,13 +5888,13 @@
         <v>2</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>1</v>
@@ -6028,24 +6006,24 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="G95" s="3" t="n">
         <v>1</v>
@@ -6054,19 +6032,19 @@
         <v>9</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="K95" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="M95" s="4" t="n">
-        <v>0.5331807780320366</v>
+        <v>0.5333333333333333</v>
       </c>
     </row>
     <row r="96">
@@ -6075,45 +6053,45 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>402</v>
+        <v>437</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="G96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H96" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="H96" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="I96" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="M96" s="4" t="n">
-        <v>0.5323383084577115</v>
+        <v>0.5331807780320366</v>
       </c>
     </row>
     <row r="97">
@@ -6122,7 +6100,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -6136,13 +6114,13 @@
         </is>
       </c>
       <c r="E97" s="3" t="n">
-        <v>530</v>
+        <v>402</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>230</v>
+        <v>186</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H97" s="3" t="n">
         <v>0</v>
@@ -6151,16 +6129,16 @@
         <v>0</v>
       </c>
       <c r="J97" s="3" t="n">
-        <v>281</v>
+        <v>214</v>
       </c>
       <c r="K97" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="3" t="n">
-        <v>281</v>
+        <v>214</v>
       </c>
       <c r="M97" s="4" t="n">
-        <v>0.530188679245283</v>
+        <v>0.5323383084577115</v>
       </c>
     </row>
     <row r="98">
@@ -6169,45 +6147,45 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E98" s="3" t="n">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="G98" s="3" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I98" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J98" s="3" t="n">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="K98" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="3" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="M98" s="4" t="n">
-        <v>0.5286343612334802</v>
+        <v>0.5306553911205074</v>
       </c>
     </row>
     <row r="99">
@@ -6216,45 +6194,45 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E99" s="3" t="n">
-        <v>451</v>
+        <v>530</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>208</v>
+        <v>281</v>
       </c>
       <c r="K99" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="M99" s="4" t="n">
-        <v>0.5254988913525499</v>
+        <v>0.530188679245283</v>
       </c>
     </row>
     <row r="100">
@@ -6263,45 +6241,45 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E100" s="3" t="n">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="M100" s="4" t="n">
-        <v>0.5225806451612903</v>
+        <v>0.5286343612334802</v>
       </c>
     </row>
     <row r="101">
@@ -6310,45 +6288,45 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E101" s="3" t="n">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="M101" s="4" t="n">
-        <v>0.5213270142180095</v>
+        <v>0.5254988913525499</v>
       </c>
     </row>
     <row r="102">
@@ -6357,45 +6335,45 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E102" s="3" t="n">
         <v>422</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G102" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I102" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J102" s="3" t="n">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="K102" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="3" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M102" s="4" t="n">
-        <v>0.518957345971564</v>
+        <v>0.5213270142180095</v>
       </c>
     </row>
     <row r="103">
@@ -6404,45 +6382,45 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="H103" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I103" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="I103" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="J103" s="3" t="n">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="K103" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="M103" s="4" t="n">
-        <v>0.5169491525423728</v>
+        <v>0.5212765957446809</v>
       </c>
     </row>
     <row r="104">
@@ -6451,7 +6429,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -6465,16 +6443,16 @@
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="G104" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H104" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I104" s="3" t="n">
         <v>0</v>
@@ -6483,13 +6461,13 @@
         <v>219</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="3" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="M104" s="4" t="n">
-        <v>0.5127020785219399</v>
+        <v>0.518957345971564</v>
       </c>
     </row>
     <row r="105">
@@ -6498,45 +6476,45 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E105" s="3" t="n">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="F105" s="3" t="n">
+        <v>201</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J105" s="3" t="n">
         <v>198</v>
       </c>
-      <c r="G105" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H105" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="3" t="n">
-        <v>206</v>
-      </c>
       <c r="K105" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="3" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="M105" s="4" t="n">
-        <v>0.5122549019607843</v>
+        <v>0.5179856115107914</v>
       </c>
     </row>
     <row r="106">
@@ -6545,45 +6523,45 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="M106" s="4" t="n">
-        <v>0.5096153846153846</v>
+        <v>0.516209476309227</v>
       </c>
     </row>
     <row r="107">
@@ -6592,45 +6570,45 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J107" s="3" t="n">
         <v>248</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="M107" s="4" t="n">
-        <v>0.5040650406504065</v>
+        <v>0.5146771037181996</v>
       </c>
     </row>
     <row r="108">
@@ -6639,45 +6617,45 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E108" s="3" t="n">
-        <v>389</v>
+        <v>433</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J108" s="3" t="n">
-        <v>187</v>
+        <v>219</v>
       </c>
       <c r="K108" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="3" t="n">
-        <v>196</v>
+        <v>222</v>
       </c>
       <c r="M108" s="4" t="n">
-        <v>0.5038560411311054</v>
+        <v>0.5127020785219399</v>
       </c>
     </row>
     <row r="109">
@@ -6686,45 +6664,45 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E109" s="3" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G109" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J109" s="3" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K109" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="3" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M109" s="4" t="n">
-        <v>0.5036496350364964</v>
+        <v>0.5122549019607843</v>
       </c>
     </row>
     <row r="110">
@@ -6733,45 +6711,45 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E110" s="3" t="n">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J110" s="3" t="n">
         <v>248</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="M110" s="4" t="n">
-        <v>0.5029469548133595</v>
+        <v>0.5040650406504065</v>
       </c>
     </row>
     <row r="111">
@@ -6780,45 +6758,45 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E111" s="3" t="n">
-        <v>470</v>
+        <v>389</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>224</v>
+        <v>186</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="M111" s="4" t="n">
-        <v>0.5</v>
+        <v>0.5038560411311054</v>
       </c>
     </row>
     <row r="112">
@@ -6827,45 +6805,45 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E112" s="3" t="n">
-        <v>450</v>
+        <v>411</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="K112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="M112" s="4" t="n">
-        <v>0.4977777777777778</v>
+        <v>0.5036496350364964</v>
       </c>
     </row>
     <row r="113">
@@ -6874,45 +6852,45 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E113" s="3" t="n">
-        <v>399</v>
+        <v>346</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>192</v>
+        <v>173</v>
       </c>
       <c r="G113" s="3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I113" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="3" t="n">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="K113" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="3" t="n">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="M113" s="4" t="n">
-        <v>0.4962406015037594</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="114">
@@ -6921,45 +6899,45 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E114" s="3" t="n">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H114" s="3" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="J114" s="3" t="n">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="K114" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="3" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="M114" s="4" t="n">
-        <v>0.4957805907172996</v>
+        <v>0.4977777777777778</v>
       </c>
     </row>
     <row r="115">
@@ -6968,45 +6946,45 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E115" s="3" t="n">
-        <v>346</v>
+        <v>399</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="M115" s="4" t="n">
-        <v>0.4942196531791908</v>
+        <v>0.4962406015037594</v>
       </c>
     </row>
     <row r="116">
@@ -7015,45 +6993,45 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E116" s="3" t="n">
-        <v>361</v>
+        <v>474</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="K116" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="M116" s="4" t="n">
-        <v>0.4930747922437673</v>
+        <v>0.4957805907172996</v>
       </c>
     </row>
     <row r="117">
@@ -7062,45 +7040,45 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E117" s="3" t="n">
-        <v>418</v>
+        <v>323</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>212</v>
+        <v>116</v>
       </c>
       <c r="G117" s="3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I117" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J117" s="3" t="n">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="K117" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="3" t="n">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="M117" s="4" t="n">
-        <v>0.4928229665071771</v>
+        <v>0.4953560371517028</v>
       </c>
     </row>
     <row r="118">
@@ -7126,28 +7104,28 @@
         <v>402</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>1</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M118" s="4" t="n">
-        <v>0.4900497512437811</v>
+        <v>0.4950248756218906</v>
       </c>
     </row>
     <row r="119">
@@ -7156,45 +7134,45 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E119" s="3" t="n">
-        <v>425</v>
+        <v>361</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="G119" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H119" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J119" s="3" t="n">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="K119" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="3" t="n">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="M119" s="4" t="n">
-        <v>0.4847058823529412</v>
+        <v>0.4930747922437673</v>
       </c>
     </row>
     <row r="120">
@@ -7203,7 +7181,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -7217,31 +7195,31 @@
         </is>
       </c>
       <c r="E120" s="3" t="n">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="G120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="3" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J120" s="3" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="K120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="3" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="M120" s="4" t="n">
-        <v>0.4804597701149425</v>
+        <v>0.4928229665071771</v>
       </c>
     </row>
     <row r="121">
@@ -7250,27 +7228,27 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E121" s="3" t="n">
-        <v>323</v>
+        <v>425</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>119</v>
+        <v>219</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -7279,16 +7257,16 @@
         <v>0</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="K121" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="M121" s="4" t="n">
-        <v>0.4798761609907121</v>
+        <v>0.4847058823529412</v>
       </c>
     </row>
     <row r="122">
@@ -7297,45 +7275,45 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E122" s="3" t="n">
-        <v>501</v>
+        <v>437</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="G122" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H122" s="3" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="I122" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J122" s="3" t="n">
-        <v>234</v>
+        <v>175</v>
       </c>
       <c r="K122" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="3" t="n">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="M122" s="4" t="n">
-        <v>0.471057884231537</v>
+        <v>0.482837528604119</v>
       </c>
     </row>
     <row r="123">
@@ -7344,7 +7322,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -7358,31 +7336,31 @@
         </is>
       </c>
       <c r="E123" s="3" t="n">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="G123" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H123" s="3" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J123" s="3" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="K123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="3" t="n">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="M123" s="4" t="n">
-        <v>0.4691075514874142</v>
+        <v>0.4806763285024155</v>
       </c>
     </row>
     <row r="124">
@@ -7391,45 +7369,45 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E124" s="3" t="n">
-        <v>413</v>
+        <v>503</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>220</v>
+        <v>262</v>
       </c>
       <c r="G124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="3" t="n">
+        <v>234</v>
+      </c>
+      <c r="K124" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="H124" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="I124" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J124" s="3" t="n">
-        <v>168</v>
-      </c>
-      <c r="K124" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L124" s="3" t="n">
-        <v>192</v>
+        <v>241</v>
       </c>
       <c r="M124" s="4" t="n">
-        <v>0.4648910411622276</v>
+        <v>0.4791252485089463</v>
       </c>
     </row>
     <row r="125">
@@ -7438,7 +7416,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -7452,31 +7430,31 @@
         </is>
       </c>
       <c r="E125" s="3" t="n">
-        <v>407</v>
+        <v>437</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="K125" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="M125" s="4" t="n">
-        <v>0.4619164619164619</v>
+        <v>0.4759725400457666</v>
       </c>
     </row>
     <row r="126">
@@ -7485,7 +7463,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -7499,31 +7477,31 @@
         </is>
       </c>
       <c r="E126" s="3" t="n">
-        <v>447</v>
+        <v>407</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="K126" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="M126" s="4" t="n">
-        <v>0.4563758389261745</v>
+        <v>0.4619164619164619</v>
       </c>
     </row>
     <row r="127">
@@ -7532,45 +7510,45 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E127" s="3" t="n">
-        <v>391</v>
+        <v>447</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="G127" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H127" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J127" s="3" t="n">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="K127" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="3" t="n">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="M127" s="4" t="n">
-        <v>0.4526854219948849</v>
+        <v>0.4563758389261745</v>
       </c>
     </row>
     <row r="128">
@@ -7596,28 +7574,28 @@
         <v>437</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G128" s="3" t="n">
         <v>18</v>
       </c>
       <c r="H128" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I128" s="3" t="n">
         <v>19</v>
       </c>
       <c r="J128" s="3" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K128" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="3" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="M128" s="4" t="n">
-        <v>0.448512585812357</v>
+        <v>0.4530892448512586</v>
       </c>
     </row>
     <row r="129">
@@ -7626,7 +7604,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -7640,31 +7618,31 @@
         </is>
       </c>
       <c r="E129" s="3" t="n">
-        <v>440</v>
+        <v>391</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H129" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J129" s="3" t="n">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="K129" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="3" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="M129" s="4" t="n">
-        <v>0.4454545454545455</v>
+        <v>0.4526854219948849</v>
       </c>
     </row>
     <row r="130">
@@ -7673,45 +7651,45 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E130" s="3" t="n">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>235</v>
+        <v>222</v>
       </c>
       <c r="G130" s="3" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J130" s="3" t="n">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="K130" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" s="3" t="n">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="M130" s="4" t="n">
-        <v>0.4326923076923077</v>
+        <v>0.4454545454545455</v>
       </c>
     </row>
     <row r="131">
@@ -7720,45 +7698,45 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E131" s="3" t="n">
-        <v>512</v>
+        <v>417</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="G131" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H131" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="J131" s="3" t="n">
-        <v>192</v>
+        <v>142</v>
       </c>
       <c r="K131" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L131" s="3" t="n">
-        <v>221</v>
+        <v>180</v>
       </c>
       <c r="M131" s="4" t="n">
-        <v>0.431640625</v>
+        <v>0.4316546762589928</v>
       </c>
     </row>
     <row r="132">
@@ -7767,45 +7745,45 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E132" s="3" t="n">
-        <v>459</v>
+        <v>512</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>234</v>
+        <v>286</v>
       </c>
       <c r="G132" s="3" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J132" s="3" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K132" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="3" t="n">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="M132" s="4" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.431640625</v>
       </c>
     </row>
     <row r="133">
@@ -7814,45 +7792,45 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E133" s="3" t="n">
-        <v>413</v>
+        <v>459</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="G133" s="3" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J133" s="3" t="n">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="K133" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="3" t="n">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="M133" s="4" t="n">
-        <v>0.4285714285714285</v>
+        <v>0.4313725490196079</v>
       </c>
     </row>
     <row r="134">
@@ -7861,45 +7839,45 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E134" s="3" t="n">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="M134" s="4" t="n">
-        <v>0.4229828850855746</v>
+        <v>0.4313253012048193</v>
       </c>
     </row>
     <row r="135">
@@ -7908,45 +7886,45 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E135" s="3" t="n">
-        <v>332</v>
+        <v>409</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>8</v>
+        <v>235</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>123</v>
+        <v>174</v>
       </c>
       <c r="M135" s="4" t="n">
-        <v>0.3704819277108434</v>
+        <v>0.4254278728606357</v>
       </c>
     </row>
     <row r="136">
@@ -7955,45 +7933,45 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>Fitrianti Tadete</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E136" s="3" t="n">
-        <v>355</v>
+        <v>332</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>268</v>
+        <v>8</v>
       </c>
       <c r="G136" s="3" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="H136" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="J136" s="3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="K136" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="3" t="n">
-        <v>87</v>
+        <v>132</v>
       </c>
       <c r="M136" s="4" t="n">
-        <v>0.2450704225352113</v>
+        <v>0.3975903614457831</v>
       </c>
     </row>
   </sheetData>
@@ -8043,7 +8021,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.55 WITA</t>
+          <t>Pukul        : 17.53 WITA</t>
         </is>
       </c>
     </row>
@@ -8135,31 +8113,31 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2326</v>
+        <v>2322</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.8175746924428823</v>
+        <v>0.8158819395643008</v>
       </c>
     </row>
     <row r="8">
@@ -8182,31 +8160,31 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2767</v>
+        <v>2773</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>1916</v>
+        <v>1941</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1932</v>
+        <v>1958</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.6982291290206</v>
+        <v>0.706094482509917</v>
       </c>
     </row>
     <row r="9">
@@ -8215,45 +8193,45 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Nusa Tabukan, Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Alfi, Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2446</v>
+        <v>2026</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>769</v>
+        <v>473</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="I9" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>1386</v>
+      </c>
+      <c r="K9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="J9" s="3" t="n">
-        <v>1664</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" s="3" t="n">
-        <v>1670</v>
+        <v>1401</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.6827473426001636</v>
+        <v>0.6915103652517274</v>
       </c>
     </row>
     <row r="10">
@@ -8262,45 +8240,45 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan, Tabukan Utara</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi, Hendri</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2812</v>
+        <v>2446</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>869</v>
+        <v>755</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>1816</v>
+        <v>1676</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1833</v>
+        <v>1678</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.6518492176386913</v>
+        <v>0.6860179885527393</v>
       </c>
     </row>
     <row r="11">
@@ -8309,7 +8287,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Charly Angel Tatontos</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -8323,31 +8301,31 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2866</v>
+        <v>2814</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>737</v>
+        <v>865</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>214</v>
+        <v>67</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>1814</v>
+        <v>1861</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1864</v>
+        <v>1879</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.650383810188416</v>
+        <v>0.6677327647476902</v>
       </c>
     </row>
     <row r="12">
@@ -8356,45 +8334,45 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Charly Angel Tatontos</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2024</v>
+        <v>2880</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>492</v>
+        <v>694</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>212</v>
+        <v>188</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>1285</v>
+        <v>1851</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>1295</v>
+        <v>1904</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.6398221343873518</v>
+        <v>0.6611111111111111</v>
       </c>
     </row>
     <row r="13">
@@ -8420,22 +8398,22 @@
         <v>2101</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>1280</v>
@@ -8464,31 +8442,31 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>2140</v>
+        <v>2146</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>841</v>
+        <v>828</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>3</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.5995327102803738</v>
+        <v>0.5987884436160298</v>
       </c>
     </row>
     <row r="15">
@@ -8511,31 +8489,31 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2372</v>
+        <v>2378</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>21</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>1404</v>
+        <v>1410</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.5919055649241147</v>
+        <v>0.5929352396972245</v>
       </c>
     </row>
     <row r="16">
@@ -8558,31 +8536,31 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2872</v>
+        <v>2880</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1677</v>
+        <v>1689</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1683</v>
+        <v>1697</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.5860027855153204</v>
+        <v>0.5892361111111111</v>
       </c>
     </row>
     <row r="17">
@@ -8591,45 +8569,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2872</v>
+        <v>2737</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1134</v>
+        <v>992</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>59</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>1632</v>
+        <v>1578</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>1654</v>
+        <v>1592</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5759052924791086</v>
+        <v>0.5816587504567045</v>
       </c>
     </row>
     <row r="18">
@@ -8638,45 +8616,45 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2726</v>
+        <v>2874</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1013</v>
+        <v>1110</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>1556</v>
+        <v>1631</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>1564</v>
+        <v>1652</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5737344093910491</v>
+        <v>0.5748086290883786</v>
       </c>
     </row>
     <row r="19">
@@ -8699,22 +8677,22 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2788</v>
+        <v>2793</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1210</v>
+        <v>1195</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>4</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>1534</v>
+        <v>1532</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>7</v>
@@ -8723,7 +8701,7 @@
         <v>1548</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5552367288378766</v>
+        <v>0.5542427497314716</v>
       </c>
     </row>
     <row r="20">
@@ -8746,31 +8724,31 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>2665</v>
+        <v>2672</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1425</v>
+        <v>1435</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>1429</v>
+        <v>1439</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.5362101313320825</v>
+        <v>0.5385479041916168</v>
       </c>
     </row>
     <row r="21">
@@ -8793,16 +8771,16 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2652</v>
+        <v>2654</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -8817,7 +8795,7 @@
         <v>1422</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5361990950226244</v>
+        <v>0.5357950263752826</v>
       </c>
     </row>
     <row r="22">
@@ -8826,45 +8804,45 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2292</v>
+        <v>2428</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1001</v>
+        <v>938</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>34</v>
+        <v>166</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>1172</v>
+        <v>1289</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>1197</v>
+        <v>1296</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.5222513089005235</v>
+        <v>0.5337726523887973</v>
       </c>
     </row>
     <row r="23">
@@ -8873,45 +8851,45 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2704</v>
+        <v>2294</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1244</v>
+        <v>990</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1389</v>
+        <v>1181</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>1395</v>
+        <v>1206</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.5159023668639053</v>
+        <v>0.5257192676547515</v>
       </c>
     </row>
     <row r="24">
@@ -8920,45 +8898,45 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2423</v>
+        <v>2705</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>952</v>
+        <v>1242</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>213</v>
+        <v>9</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>1228</v>
+        <v>1389</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>1230</v>
+        <v>1395</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5076351630210483</v>
+        <v>0.5157116451016636</v>
       </c>
     </row>
     <row r="25">
@@ -8967,45 +8945,45 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Olfira Sicilia Budiman</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2525</v>
+        <v>2072</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1200</v>
+        <v>1020</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>1219</v>
+        <v>935</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>1227</v>
+        <v>1012</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4859405940594059</v>
+        <v>0.4884169884169884</v>
       </c>
     </row>
     <row r="26">
@@ -9014,45 +8992,45 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Olfira Sicilia Budiman</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2068</v>
+        <v>2527</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1030</v>
+        <v>1200</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>78</v>
+        <v>5</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>923</v>
+        <v>1225</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>1002</v>
+        <v>1232</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.4845261121856866</v>
+        <v>0.4875346260387812</v>
       </c>
     </row>
     <row r="27">
@@ -9078,28 +9056,28 @@
         <v>1410</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>658</v>
+        <v>672</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.4673758865248228</v>
+        <v>0.4773049645390071</v>
       </c>
     </row>
     <row r="28">
@@ -9122,31 +9100,31 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>2398</v>
+        <v>2402</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="K28" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.4603836530442035</v>
+        <v>0.4600333055786844</v>
       </c>
     </row>
     <row r="29">
@@ -9169,31 +9147,31 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>896</v>
+        <v>901</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.4494163424124514</v>
+        <v>0.4511424404472533</v>
       </c>
     </row>
   </sheetData>
@@ -9212,7 +9190,7 @@
   <cols>
     <col width="66" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -9234,7 +9212,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.55 WITA</t>
+          <t>Pukul        : 17.53 WITA</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9249,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.7322357019064125</v>
+        <v>0.7426343154246101</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
@@ -9289,7 +9267,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.7269537480063797</v>
+        <v>0.7332273449920508</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
@@ -9307,7 +9285,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.7110358180058083</v>
+        <v>0.7133665755187389</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
@@ -9325,7 +9303,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6926060606060606</v>
+        <v>0.6959050157499395</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
@@ -9343,7 +9321,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.6751892900252386</v>
+        <v>0.6778714551625972</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
@@ -9379,7 +9357,7 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.6129666011787819</v>
+        <v>0.620215897939156</v>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
@@ -9397,7 +9375,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5900621118012422</v>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
@@ -9415,11 +9393,11 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.5645624103299857</v>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.5707124955245256</v>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9433,11 +9411,11 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.5635166537567777</v>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.569078947368421</v>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9451,7 +9429,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5377729257641921</v>
+        <v>0.5393846825223653</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
@@ -9469,7 +9447,7 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.530981174417155</v>
+        <v>0.5333084298343918</v>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
@@ -9487,7 +9465,7 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.518348623853211</v>
+        <v>0.5195670274771024</v>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
@@ -9505,7 +9483,7 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.5130522088353414</v>
+        <v>0.5168783422459893</v>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
@@ -9523,7 +9501,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.4815602836879432</v>
+        <v>0.4886524822695036</v>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.53 WITA</t>
+          <t>Pukul        : 17.54 WITA</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.53 WITA</t>
+          <t>Pukul        : 17.54 WITA</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.53 WITA</t>
+          <t>Pukul        : 17.54 WITA</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.53 WITA</t>
+          <t>Pukul        : 17.54 WITA</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.54 WITA</t>
+          <t>Pukul        : 17.53 WITA</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
         <v/>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S7" s="4">
         <f>R7/B7</f>
@@ -759,7 +759,7 @@
         <v/>
       </c>
       <c r="R8" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S8" s="4">
         <f>R8/B8</f>
@@ -828,7 +828,7 @@
         <v/>
       </c>
       <c r="R9" s="3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S9" s="4">
         <f>R9/B9</f>
@@ -897,7 +897,7 @@
         <v/>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S10" s="4">
         <f>R10/B10</f>
@@ -966,7 +966,7 @@
         <v/>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S11" s="4">
         <f>R11/B11</f>
@@ -1035,7 +1035,7 @@
         <v/>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S12" s="4">
         <f>R12/B12</f>
@@ -1104,7 +1104,7 @@
         <v/>
       </c>
       <c r="R13" s="3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S13" s="4">
         <f>R13/B13</f>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="R14" s="3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S14" s="4">
         <f>R14/B14</f>
@@ -1242,7 +1242,7 @@
         <v/>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S15" s="4">
         <f>R15/B15</f>
@@ -1311,7 +1311,7 @@
         <v/>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S16" s="4">
         <f>R16/B16</f>
@@ -1380,7 +1380,7 @@
         <v/>
       </c>
       <c r="R17" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S17" s="4">
         <f>R17/B17</f>
@@ -1449,7 +1449,7 @@
         <v/>
       </c>
       <c r="R18" s="3" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S18" s="4">
         <f>R18/B18</f>
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="R19" s="3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S19" s="4">
         <f>R19/B19</f>
@@ -1656,7 +1656,7 @@
         <v/>
       </c>
       <c r="R21" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S21" s="4">
         <f>R21/B21</f>
@@ -1792,7 +1792,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.54 WITA</t>
+          <t>Pukul        : 17.53 WITA</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.54 WITA</t>
+          <t>Pukul        : 17.53 WITA</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.54 WITA</t>
+          <t>Pukul        : 17.53 WITA</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +526,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.53 WITA</t>
+          <t>Pukul        : 18.10 WITA</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.53 WITA</t>
+          <t>Pukul        : 18.10 WITA</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.53 WITA</t>
+          <t>Pukul        : 18.10 WITA</t>
         </is>
       </c>
     </row>
@@ -9212,7 +9212,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.53 WITA</t>
+          <t>Pukul        : 18.10 WITA</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.54 WITA</t>
+          <t>Pukul        : 19.00 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.54 WITA</t>
+          <t>Pukul        : 19.00 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.54 WITA</t>
+          <t>Pukul        : 19.00 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 17.54 WITA</t>
+          <t>Pukul        : 19.00 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -588,7 +588,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 18 Juli 2026</t>
+          <t>Hari/Tanggal : 19 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 19.00 WITA</t>
+          <t>Pukul        : 11.52 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -744,27 +744,27 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4127</v>
+        <v>4129</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1214</v>
+        <v>1176</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
@@ -778,7 +778,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2664</v>
+        <v>2737</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -792,14 +792,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2872</v>
+        <v>2916</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -813,27 +813,27 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -847,28 +847,28 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>672</v>
+        <v>698</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
         <v/>
       </c>
       <c r="N8" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O8" s="10">
         <f>N8/B8</f>
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>689</v>
+        <v>717</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -882,41 +882,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6217</v>
+        <v>6234</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1673</v>
+        <v>1616</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>279</v>
+        <v>142</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4085</v>
+        <v>4283</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -930,14 +930,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4435</v>
+        <v>4524</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3145</v>
+        <v>3157</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>839</v>
+        <v>813</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -971,21 +971,21 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2240</v>
+        <v>2319</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -999,14 +999,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2306</v>
+        <v>2344</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1020,27 +1020,27 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1068,14 +1068,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1095,7 +1095,7 @@
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
@@ -1109,42 +1109,42 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="M12" s="10">
         <f>L12/B12</f>
         <v/>
       </c>
       <c r="N12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" s="10">
         <f>N12/B12</f>
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="Q12" s="11">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1158,41 +1158,41 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4583</v>
+        <v>4591</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2076</v>
+        <v>2063</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2215</v>
+        <v>2258</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1206,14 +1206,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2472</v>
+        <v>2494</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1227,41 +1227,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>5984</v>
+        <v>5995</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2852</v>
+        <v>2832</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2861</v>
+        <v>2912</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1275,14 +1275,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3093</v>
+        <v>3127</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1296,27 +1296,27 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8031</v>
+        <v>8049</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3608</v>
+        <v>3577</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
@@ -1330,7 +1330,7 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4245</v>
+        <v>4283</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1344,14 +1344,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4283</v>
+        <v>4333</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1365,62 +1365,62 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5168</v>
+        <v>5177</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2100</v>
+        <v>2085</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2812</v>
+        <v>2835</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
         <v/>
       </c>
       <c r="N16" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O16" s="10">
         <f>N16/B16</f>
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>2941</v>
+        <v>2968</v>
       </c>
       <c r="Q16" s="11">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,56 +1440,56 @@
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1248</v>
+        <v>1256</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1503,41 +1503,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9133</v>
+        <v>9181</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2800</v>
+        <v>2717</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>139</v>
+        <v>243</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6025</v>
+        <v>6104</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1551,14 +1551,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6191</v>
+        <v>6365</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1592,21 +1592,21 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
         <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="10">
         <f>J19/B19</f>
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1620,14 +1620,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>857</v>
+        <v>873</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1647,7 +1647,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E20" s="10">
         <f>D20/B20</f>
@@ -1661,14 +1661,14 @@
         <v/>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I20" s="10">
         <f>H20/B20</f>
         <v/>
       </c>
       <c r="J20" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K20" s="10">
         <f>J20/B20</f>
@@ -1689,7 +1689,7 @@
         <v/>
       </c>
       <c r="P20" s="9" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Q20" s="11">
         <f>P20/B20</f>
@@ -1710,13 +1710,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2793</v>
+        <v>2796</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1195</v>
+        <v>1176</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1730,21 +1730,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1532</v>
+        <v>1559</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1758,14 +1758,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1594</v>
+        <v>1616</v>
       </c>
       <c r="Q21" s="11">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1894,7 +1894,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 18 Juli 2026</t>
+          <t>Hari/Tanggal : 19 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 19.00 WITA</t>
+          <t>Pukul        : 11.52 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Regina Mahoro</t>
+          <t>Syamsia Makaminan</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -2107,31 +2107,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>413</v>
+        <v>551</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>370</v>
+        <v>486</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.910411622276029</v>
+        <v>0.911070780399274</v>
       </c>
     </row>
     <row r="10">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Syamsia Makaminan</t>
+          <t>Regina Mahoro</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>544</v>
+        <v>413</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>1</v>
@@ -2169,16 +2169,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>486</v>
+        <v>370</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>486</v>
+        <v>376</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.8933823529411765</v>
+        <v>0.910411622276029</v>
       </c>
     </row>
     <row r="11">
@@ -2210,13 +2210,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>196</v>
+        <v>249</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>3</v>
@@ -2251,28 +2251,28 @@
         <v>514</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>15</v>
       </c>
       <c r="H12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J12" s="9" t="n">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8385214007782102</v>
+        <v>0.8638132295719845</v>
       </c>
     </row>
     <row r="13">
@@ -2298,28 +2298,28 @@
         <v>377</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.8381962864721486</v>
+        <v>0.8541114058355439</v>
       </c>
     </row>
     <row r="14">
@@ -2389,31 +2389,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.8176943699731903</v>
+        <v>0.8324468085106383</v>
       </c>
     </row>
     <row r="16">
@@ -2442,25 +2442,25 @@
         <v>74</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.812206572769953</v>
+        <v>0.8215962441314554</v>
       </c>
     </row>
     <row r="17">
@@ -2469,45 +2469,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>494</v>
+        <v>397</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="J17" s="9" t="n">
-        <v>385</v>
+        <v>313</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>386</v>
+        <v>315</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.7813765182186235</v>
+        <v>0.7934508816120907</v>
       </c>
     </row>
     <row r="18">
@@ -2516,45 +2516,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>374</v>
+      </c>
+      <c r="K18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="9" t="n">
-        <v>373</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" s="9" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.7775467775467776</v>
+        <v>0.7894736842105263</v>
       </c>
     </row>
     <row r="19">
@@ -2563,45 +2563,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>395</v>
+        <v>372</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.7772151898734179</v>
+        <v>0.7849462365591396</v>
       </c>
     </row>
     <row r="20">
@@ -2610,45 +2610,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.7747368421052632</v>
+        <v>0.7797979797979798</v>
       </c>
     </row>
     <row r="21">
@@ -2657,45 +2657,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>365</v>
+        <v>421</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>277</v>
+        <v>314</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.7616438356164383</v>
+        <v>0.7790973871733968</v>
       </c>
     </row>
     <row r="22">
@@ -2704,45 +2704,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>410</v>
+        <v>481</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>310</v>
+        <v>373</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>312</v>
+        <v>374</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.7609756097560976</v>
+        <v>0.7775467775467776</v>
       </c>
     </row>
     <row r="23">
@@ -2751,45 +2751,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.7593457943925234</v>
+        <v>0.7712895377128953</v>
       </c>
     </row>
     <row r="24">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>523</v>
+        <v>430</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H24" s="9" t="n">
         <v>24</v>
@@ -2827,16 +2827,16 @@
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>373</v>
+        <v>305</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>397</v>
+        <v>329</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.7590822179732314</v>
+        <v>0.7651162790697674</v>
       </c>
     </row>
     <row r="25">
@@ -2845,45 +2845,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>419</v>
+        <v>493</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>314</v>
+        <v>367</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>316</v>
+        <v>375</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7541766109785203</v>
+        <v>0.7606490872210954</v>
       </c>
     </row>
     <row r="26">
@@ -2892,45 +2892,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>493</v>
+        <v>523</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>357</v>
+        <v>388</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.7505070993914807</v>
+        <v>0.7590822179732314</v>
       </c>
     </row>
     <row r="27">
@@ -3003,28 +3003,28 @@
         <v>484</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>240</v>
+        <v>321</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.7252066115702479</v>
+        <v>0.7417355371900827</v>
       </c>
     </row>
     <row r="29">
@@ -3050,13 +3050,13 @@
         <v>382</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>1</v>
@@ -3068,10 +3068,10 @@
         <v>1</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.725130890052356</v>
+        <v>0.7356020942408377</v>
       </c>
     </row>
     <row r="30">
@@ -3080,45 +3080,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>497</v>
+        <v>552</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>354</v>
+        <v>399</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7122736418511066</v>
+        <v>0.7228260869565217</v>
       </c>
     </row>
     <row r="31">
@@ -3127,45 +3127,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>287</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7068965517241379</v>
+        <v>0.7139303482587064</v>
       </c>
     </row>
     <row r="32">
@@ -3174,45 +3174,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>551</v>
+        <v>496</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.705989110707804</v>
+        <v>0.7137096774193549</v>
       </c>
     </row>
     <row r="33">
@@ -3221,45 +3221,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>420</v>
+        <v>509</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>289</v>
+        <v>361</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>296</v>
+        <v>362</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7047619047619048</v>
+        <v>0.7111984282907662</v>
       </c>
     </row>
     <row r="34">
@@ -3268,45 +3268,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>489</v>
+        <v>407</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="G34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H34" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I34" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>335</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" s="9" t="n">
-        <v>344</v>
+        <v>289</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7034764826175869</v>
+        <v>0.71007371007371</v>
       </c>
     </row>
     <row r="35">
@@ -3315,27 +3315,27 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>414</v>
+        <v>499</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H35" s="9" t="n">
         <v>0</v>
@@ -3344,16 +3344,16 @@
         <v>4</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>287</v>
+        <v>349</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>291</v>
+        <v>354</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7028985507246377</v>
+        <v>0.7094188376753507</v>
       </c>
     </row>
     <row r="36">
@@ -3362,45 +3362,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>346</v>
+        <v>420</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>242</v>
+        <v>289</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7023121387283237</v>
+        <v>0.7047619047619048</v>
       </c>
     </row>
     <row r="37">
@@ -3409,45 +3409,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>534</v>
+        <v>414</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>161</v>
+        <v>123</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>367</v>
+        <v>287</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>373</v>
+        <v>291</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.6985018726591761</v>
+        <v>0.7028985507246377</v>
       </c>
     </row>
     <row r="38">
@@ -3456,45 +3456,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>509</v>
+        <v>346</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="I38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>242</v>
+      </c>
+      <c r="K38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="9" t="n">
-        <v>313</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" s="9" t="n">
-        <v>351</v>
+        <v>243</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.6895874263261297</v>
+        <v>0.7023121387283237</v>
       </c>
     </row>
     <row r="39">
@@ -3503,45 +3503,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>388</v>
+        <v>534</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>216</v>
+        <v>367</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>265</v>
+        <v>373</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.6829896907216495</v>
+        <v>0.6985018726591761</v>
       </c>
     </row>
     <row r="40">
@@ -3550,45 +3550,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.679144385026738</v>
+        <v>0.6829896907216495</v>
       </c>
     </row>
     <row r="41">
@@ -3597,45 +3597,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.6708542713567839</v>
+        <v>0.679144385026738</v>
       </c>
     </row>
     <row r="42">
@@ -3644,45 +3644,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>289</v>
+        <v>417</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>191</v>
+        <v>252</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>193</v>
+        <v>282</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.6678200692041523</v>
+        <v>0.6762589928057554</v>
       </c>
     </row>
     <row r="43">
@@ -3691,45 +3691,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>438</v>
+        <v>499</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>292</v>
+        <v>337</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6753507014028056</v>
       </c>
     </row>
     <row r="44">
@@ -3738,45 +3738,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>522</v>
+        <v>501</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.664750957854406</v>
+        <v>0.6686626746506987</v>
       </c>
     </row>
     <row r="45">
@@ -3785,45 +3785,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>495</v>
+        <v>289</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>165</v>
+        <v>96</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>325</v>
+        <v>191</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>329</v>
+        <v>193</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.6646464646464646</v>
+        <v>0.6678200692041523</v>
       </c>
     </row>
     <row r="46">
@@ -3832,45 +3832,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>415</v>
+        <v>522</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>249</v>
+        <v>344</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>275</v>
+        <v>348</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.6626506024096386</v>
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="47">
@@ -3879,45 +3879,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>499</v>
+        <v>438</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>328</v>
+        <v>292</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.657314629258517</v>
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="48">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -3940,31 +3940,31 @@
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>444</v>
+        <v>345</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>282</v>
+        <v>214</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>284</v>
+        <v>222</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6396396396396397</v>
+        <v>0.6434782608695652</v>
       </c>
     </row>
     <row r="49">
@@ -3973,45 +3973,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6314655172413793</v>
+        <v>0.6396396396396397</v>
       </c>
     </row>
     <row r="50">
@@ -4020,45 +4020,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>405</v>
+        <v>367</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="I50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>193</v>
+        <v>232</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6296296296296297</v>
+        <v>0.6376021798365122</v>
       </c>
     </row>
     <row r="51">
@@ -4067,27 +4067,27 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="H51" s="9" t="n">
         <v>0</v>
@@ -4096,16 +4096,16 @@
         <v>1</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6283185840707964</v>
+        <v>0.6344827586206897</v>
       </c>
     </row>
     <row r="52">
@@ -4114,45 +4114,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>457</v>
+        <v>409</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="I52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>262</v>
+        <v>193</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6280087527352297</v>
+        <v>0.6332518337408313</v>
       </c>
     </row>
     <row r="53">
@@ -4161,45 +4161,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>622</v>
+        <v>421</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>227</v>
+        <v>155</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>385</v>
+        <v>247</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>390</v>
+        <v>266</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6270096463022508</v>
+        <v>0.6318289786223278</v>
       </c>
     </row>
     <row r="54">
@@ -4208,45 +4208,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>367</v>
+        <v>513</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>227</v>
+        <v>314</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>230</v>
+        <v>324</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6267029972752044</v>
+        <v>0.631578947368421</v>
       </c>
     </row>
     <row r="55">
@@ -4255,45 +4255,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>245</v>
+        <v>293</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6261904761904762</v>
+        <v>0.6314655172413793</v>
       </c>
     </row>
     <row r="56">
@@ -4302,45 +4302,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.6305309734513275</v>
       </c>
     </row>
     <row r="57">
@@ -4349,45 +4349,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>345</v>
+        <v>458</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>131</v>
+        <v>170</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>214</v>
+        <v>288</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.6202898550724638</v>
+        <v>0.62882096069869</v>
       </c>
     </row>
     <row r="58">
@@ -4396,45 +4396,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>497</v>
+        <v>429</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="K58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.613682092555332</v>
+        <v>0.627039627039627</v>
       </c>
     </row>
     <row r="59">
@@ -4443,45 +4443,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>452</v>
+        <v>622</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>238</v>
+        <v>385</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>277</v>
+        <v>390</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6128318584070797</v>
+        <v>0.6270096463022508</v>
       </c>
     </row>
     <row r="60">
@@ -4490,45 +4490,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>500</v>
+        <v>452</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.61</v>
+        <v>0.6238938053097345</v>
       </c>
     </row>
     <row r="61">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
@@ -4551,31 +4551,31 @@
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>509</v>
+        <v>441</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>310</v>
+        <v>274</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6090373280943026</v>
+        <v>0.6213151927437641</v>
       </c>
     </row>
     <row r="62">
@@ -4584,45 +4584,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>429</v>
+        <v>498</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>259</v>
+        <v>305</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6060606060606061</v>
+        <v>0.6164658634538153</v>
       </c>
     </row>
     <row r="63">
@@ -4631,45 +4631,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>439</v>
+        <v>371</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>167</v>
+        <v>130</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.6059225512528473</v>
+        <v>0.6118598382749326</v>
       </c>
     </row>
     <row r="64">
@@ -4678,45 +4678,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>504</v>
+        <v>450</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="K64" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6031746031746031</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="65">
@@ -4725,45 +4725,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>412</v>
+        <v>500</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>247</v>
+        <v>305</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.5995145631067961</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="66">
@@ -4786,31 +4786,31 @@
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.5971896955503513</v>
+        <v>0.6098130841121495</v>
       </c>
     </row>
     <row r="67">
@@ -4819,45 +4819,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>449</v>
+        <v>413</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" s="9" t="n">
         <v>4</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.5946547884187082</v>
+        <v>0.6053268765133172</v>
       </c>
     </row>
     <row r="68">
@@ -4866,45 +4866,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>371</v>
+        <v>505</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>216</v>
+        <v>299</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>220</v>
+        <v>305</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.5929919137466307</v>
+        <v>0.6039603960396039</v>
       </c>
     </row>
     <row r="69">
@@ -4913,45 +4913,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>400</v>
+        <v>347</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>237</v>
+        <v>209</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.5925</v>
+        <v>0.6023054755043228</v>
       </c>
     </row>
     <row r="70">
@@ -4960,45 +4960,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="K70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.5939524838012959</v>
       </c>
     </row>
     <row r="71">
@@ -5007,45 +5007,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.5894736842105263</v>
+        <v>0.5925</v>
       </c>
     </row>
     <row r="72">
@@ -5054,45 +5054,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>345</v>
+        <v>468</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>201</v>
+        <v>273</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>203</v>
+        <v>276</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>0.5884057971014492</v>
+        <v>0.5897435897435898</v>
       </c>
     </row>
     <row r="73">
@@ -5101,45 +5101,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="M73" s="11" t="n">
-        <v>0.5872576177285319</v>
+        <v>0.5894736842105263</v>
       </c>
     </row>
     <row r="74">
@@ -5148,45 +5148,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>462</v>
+        <v>557</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>263</v>
+        <v>328</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>271</v>
+        <v>328</v>
       </c>
       <c r="M74" s="11" t="n">
-        <v>0.5865800865800865</v>
+        <v>0.5888689407540395</v>
       </c>
     </row>
     <row r="75">
@@ -5195,45 +5195,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>555</v>
+        <v>361</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>315</v>
+        <v>201</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>319</v>
+        <v>212</v>
       </c>
       <c r="M75" s="11" t="n">
-        <v>0.5747747747747748</v>
+        <v>0.5872576177285319</v>
       </c>
     </row>
     <row r="76">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -5256,31 +5256,31 @@
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>498</v>
+        <v>426</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>279</v>
+        <v>237</v>
       </c>
       <c r="K76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="M76" s="11" t="n">
-        <v>0.572289156626506</v>
+        <v>0.5845070422535211</v>
       </c>
     </row>
     <row r="77">
@@ -5289,45 +5289,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>455</v>
+        <v>533</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>254</v>
+        <v>291</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>260</v>
+        <v>311</v>
       </c>
       <c r="M77" s="11" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5834896810506567</v>
       </c>
     </row>
     <row r="78">
@@ -5336,45 +5336,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>433</v>
+        <v>463</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="M78" s="11" t="n">
-        <v>0.5681293302540416</v>
+        <v>0.5788336933045356</v>
       </c>
     </row>
     <row r="79">
@@ -5383,45 +5383,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>394</v>
+        <v>456</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="K79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>223</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>0.565989847715736</v>
+        <v>262</v>
+      </c>
+      <c r="M79" s="11" t="n">
+        <v>0.5745614035087719</v>
       </c>
     </row>
     <row r="80">
@@ -5430,45 +5430,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>462</v>
+        <v>498</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>249</v>
+        <v>286</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>261</v>
-      </c>
-      <c r="M80" s="12" t="n">
-        <v>0.564935064935065</v>
+        <v>286</v>
+      </c>
+      <c r="M80" s="11" t="n">
+        <v>0.5742971887550201</v>
       </c>
     </row>
     <row r="81">
@@ -5477,45 +5477,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>240</v>
-      </c>
-      <c r="M81" s="12" t="n">
-        <v>0.5633802816901409</v>
+        <v>248</v>
+      </c>
+      <c r="M81" s="11" t="n">
+        <v>0.5727482678983834</v>
       </c>
     </row>
     <row r="82">
@@ -5524,45 +5524,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>364</v>
+        <v>445</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>205</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>0.5631868131868132</v>
+        <v>253</v>
+      </c>
+      <c r="M82" s="11" t="n">
+        <v>0.5685393258426966</v>
       </c>
     </row>
     <row r="83">
@@ -5571,45 +5571,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>532</v>
+        <v>501</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.5620300751879699</v>
+        <v>0.5668662674650699</v>
       </c>
     </row>
     <row r="84">
@@ -5618,45 +5618,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>178</v>
+        <v>127</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.5595505617977528</v>
+        <v>0.565989847715736</v>
       </c>
     </row>
     <row r="85">
@@ -5665,45 +5665,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>397</v>
+        <v>364</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.5591939546599496</v>
+        <v>0.5631868131868132</v>
       </c>
     </row>
     <row r="86">
@@ -5712,45 +5712,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>256</v>
+        <v>238</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="9" t="n">
         <v>262</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.5574468085106383</v>
+        <v>0.5622317596566524</v>
       </c>
     </row>
     <row r="87">
@@ -5759,45 +5759,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>501</v>
+        <v>397</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H87" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I87" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="J87" s="9" t="n">
-        <v>271</v>
+        <v>202</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.5548902195608783</v>
+        <v>0.5591939546599496</v>
       </c>
     </row>
     <row r="88">
@@ -5806,45 +5806,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.5528455284552846</v>
+        <v>0.5584677419354839</v>
       </c>
     </row>
     <row r="89">
@@ -5853,45 +5853,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>437</v>
+        <v>470</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>237</v>
+        <v>256</v>
       </c>
       <c r="K89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>238</v>
+        <v>262</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.5446224256292906</v>
+        <v>0.5574468085106383</v>
       </c>
     </row>
     <row r="90">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
@@ -5914,31 +5914,31 @@
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.5413043478260869</v>
+        <v>0.5528455284552846</v>
       </c>
     </row>
     <row r="91">
@@ -5947,27 +5947,27 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>403</v>
+        <v>440</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H91" s="9" t="n">
         <v>0</v>
@@ -5976,16 +5976,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="92">
@@ -5994,45 +5994,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.5376344086021505</v>
+        <v>0.5454545454545454</v>
       </c>
     </row>
     <row r="93">
@@ -6041,27 +6041,27 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>489</v>
+        <v>460</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" s="9" t="n">
         <v>0</v>
@@ -6070,16 +6070,16 @@
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>262</v>
+        <v>249</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.5357873210633947</v>
+        <v>0.5413043478260869</v>
       </c>
     </row>
     <row r="94">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
@@ -6102,31 +6102,31 @@
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>399</v>
+        <v>532</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>213</v>
+        <v>282</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>213</v>
+        <v>287</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5338345864661654</v>
+        <v>0.5394736842105263</v>
       </c>
     </row>
     <row r="95">
@@ -6135,45 +6135,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>465</v>
+        <v>412</v>
       </c>
       <c r="F95" s="9" t="n">
+        <v>170</v>
+      </c>
+      <c r="G95" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="9" t="n">
         <v>216</v>
-      </c>
-      <c r="G95" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="9" t="n">
-        <v>238</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5388349514563107</v>
       </c>
     </row>
     <row r="96">
@@ -6182,45 +6182,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>437</v>
+        <v>465</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="K96" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5331807780320366</v>
+        <v>0.5376344086021505</v>
       </c>
     </row>
     <row r="97">
@@ -6229,7 +6229,7 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
@@ -6243,13 +6243,13 @@
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" s="9" t="n">
         <v>0</v>
@@ -6258,16 +6258,16 @@
         <v>0</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5323383084577115</v>
+        <v>0.5338345864661654</v>
       </c>
     </row>
     <row r="98">
@@ -6276,45 +6276,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>473</v>
+        <v>437</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="H98" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I98" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I98" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J98" s="9" t="n">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>251</v>
+        <v>233</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5306553911205074</v>
+        <v>0.5331807780320366</v>
       </c>
     </row>
     <row r="99">
@@ -6323,45 +6323,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>530</v>
+        <v>426</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>281</v>
+        <v>213</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>281</v>
+        <v>227</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.530188679245283</v>
+        <v>0.5328638497652582</v>
       </c>
     </row>
     <row r="100">
@@ -6370,45 +6370,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>454</v>
+        <v>402</v>
       </c>
       <c r="F100" s="9" t="n">
+        <v>186</v>
+      </c>
+      <c r="G100" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="9" t="n">
         <v>214</v>
       </c>
-      <c r="G100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="I100" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="9" t="n">
-        <v>227</v>
-      </c>
       <c r="K100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.5286343612334802</v>
+        <v>0.5323383084577115</v>
       </c>
     </row>
     <row r="101">
@@ -6417,45 +6417,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>208</v>
+        <v>237</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5254988913525499</v>
+        <v>0.5286343612334802</v>
       </c>
     </row>
     <row r="102">
@@ -6464,45 +6464,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>422</v>
+        <v>451</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5213270142180095</v>
+        <v>0.5254988913525499</v>
       </c>
     </row>
     <row r="103">
@@ -6528,19 +6528,19 @@
         <v>470</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I103" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K103" s="9" t="n">
         <v>0</v>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
@@ -6572,10 +6572,10 @@
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="G104" s="9" t="n">
         <v>0</v>
@@ -6587,16 +6587,16 @@
         <v>0</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.518957345971564</v>
+        <v>0.5205479452054794</v>
       </c>
     </row>
     <row r="105">
@@ -6605,45 +6605,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>417</v>
+        <v>498</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="G105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5179856115107914</v>
+        <v>0.5200803212851406</v>
       </c>
     </row>
     <row r="106">
@@ -6652,45 +6652,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>401</v>
+        <v>364</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="G106" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H106" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H106" s="9" t="n">
-        <v>8</v>
-      </c>
       <c r="I106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.516209476309227</v>
+        <v>0.5192307692307693</v>
       </c>
     </row>
     <row r="107">
@@ -6699,45 +6699,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>511</v>
+        <v>422</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5146771037181996</v>
+        <v>0.518957345971564</v>
       </c>
     </row>
     <row r="108">
@@ -6746,45 +6746,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>433</v>
+        <v>511</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H108" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I108" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I108" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J108" s="9" t="n">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>222</v>
+        <v>265</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5127020785219399</v>
+        <v>0.5185909980430529</v>
       </c>
     </row>
     <row r="109">
@@ -6793,45 +6793,45 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="F109" s="9" t="n">
+        <v>201</v>
+      </c>
+      <c r="G109" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I109" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J109" s="9" t="n">
         <v>198</v>
       </c>
-      <c r="G109" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="9" t="n">
-        <v>206</v>
-      </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5122549019607843</v>
+        <v>0.5179856115107914</v>
       </c>
     </row>
     <row r="110">
@@ -6840,27 +6840,27 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>492</v>
+        <v>323</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>244</v>
+        <v>114</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="H110" s="9" t="n">
         <v>0</v>
@@ -6869,16 +6869,16 @@
         <v>0</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>248</v>
+        <v>167</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5040650406504065</v>
+        <v>0.5170278637770898</v>
       </c>
     </row>
     <row r="111">
@@ -6887,45 +6887,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5038560411311054</v>
+        <v>0.516209476309227</v>
       </c>
     </row>
     <row r="112">
@@ -6934,45 +6934,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5036496350364964</v>
+        <v>0.5122549019607843</v>
       </c>
     </row>
     <row r="113">
@@ -6981,45 +6981,45 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>346</v>
+        <v>414</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>173</v>
+        <v>211</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5</v>
+        <v>0.5096618357487923</v>
       </c>
     </row>
     <row r="114">
@@ -7028,45 +7028,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.4977777777777778</v>
+        <v>0.5063291139240507</v>
       </c>
     </row>
     <row r="115">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
@@ -7089,31 +7089,31 @@
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.4962406015037594</v>
+        <v>0.5038560411311054</v>
       </c>
     </row>
     <row r="116">
@@ -7122,45 +7122,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>194</v>
+        <v>222</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.4957805907172996</v>
+        <v>0.5022222222222222</v>
       </c>
     </row>
     <row r="117">
@@ -7169,45 +7169,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.4953560371517028</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="118">
@@ -7216,45 +7216,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="G118" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H118" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="I118" s="9" t="n">
-        <v>10</v>
-      </c>
       <c r="J118" s="9" t="n">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.4950248756218906</v>
+        <v>0.4962406015037594</v>
       </c>
     </row>
     <row r="119">
@@ -7263,45 +7263,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J119" s="9" t="n">
         <v>176</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.4930747922437673</v>
+        <v>0.4950248756218906</v>
       </c>
     </row>
     <row r="120">
@@ -7404,45 +7404,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>437</v>
+        <v>503</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="G122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.482837528604119</v>
+        <v>0.4831013916500994</v>
       </c>
     </row>
     <row r="123">
@@ -7468,13 +7468,13 @@
         <v>414</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I123" s="9" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.4806763285024155</v>
+        <v>0.4830917874396136</v>
       </c>
     </row>
     <row r="124">
@@ -7498,45 +7498,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>503</v>
+        <v>437</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="G124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="I124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>234</v>
+        <v>175</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>241</v>
+        <v>211</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.4791252485089463</v>
+        <v>0.482837528604119</v>
       </c>
     </row>
     <row r="125">
@@ -7559,31 +7559,31 @@
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F125" s="9" t="n">
         <v>224</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H125" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="I125" s="9" t="n">
-        <v>15</v>
-      </c>
       <c r="J125" s="9" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.4759725400457666</v>
+        <v>0.4794520547945205</v>
       </c>
     </row>
     <row r="126">
@@ -7592,45 +7592,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.4619164619164619</v>
+        <v>0.4629156010230179</v>
       </c>
     </row>
     <row r="127">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7653,31 +7653,31 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>447</v>
+        <v>407</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.4563758389261745</v>
+        <v>0.4619164619164619</v>
       </c>
     </row>
     <row r="128">
@@ -7686,45 +7686,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4530892448512586</v>
+        <v>0.4608501118568233</v>
       </c>
     </row>
     <row r="129">
@@ -7733,45 +7733,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>391</v>
+        <v>437</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4526854219948849</v>
+        <v>0.4599542334096111</v>
       </c>
     </row>
     <row r="130">
@@ -7794,16 +7794,16 @@
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I130" s="9" t="n">
         <v>0</v>
@@ -7815,10 +7815,10 @@
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4454545454545455</v>
+        <v>0.4557823129251701</v>
       </c>
     </row>
     <row r="131">
@@ -7827,45 +7827,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4316546762589928</v>
+        <v>0.4514563106796117</v>
       </c>
     </row>
     <row r="132">
@@ -7874,45 +7874,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>512</v>
+        <v>459</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>286</v>
+        <v>227</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="K132" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>221</v>
+        <v>203</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.431640625</v>
+        <v>0.4422657952069716</v>
       </c>
     </row>
     <row r="133">
@@ -7921,45 +7921,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>459</v>
+        <v>512</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>234</v>
+        <v>283</v>
       </c>
       <c r="G133" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H133" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="H133" s="9" t="n">
-        <v>7</v>
-      </c>
       <c r="I133" s="9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>198</v>
+        <v>224</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4313725490196079</v>
+        <v>0.4375</v>
       </c>
     </row>
     <row r="134">
@@ -7985,13 +7985,13 @@
         <v>415</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I134" s="9" t="n">
         <v>27</v>
@@ -8003,10 +8003,10 @@
         <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.4313253012048193</v>
+        <v>0.436144578313253</v>
       </c>
     </row>
     <row r="135">
@@ -8015,45 +8015,45 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="I135" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>143</v>
+      </c>
+      <c r="K135" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J135" s="9" t="n">
-        <v>137</v>
-      </c>
-      <c r="K135" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L135" s="9" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4254278728606357</v>
+        <v>0.434052757793765</v>
       </c>
     </row>
     <row r="136">
@@ -8082,25 +8082,25 @@
         <v>8</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.3975903614457831</v>
+        <v>0.4216867469879519</v>
       </c>
     </row>
   </sheetData>
@@ -8143,7 +8143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 18 Juli 2026</t>
+          <t>Hari/Tanggal : 19 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 19.00 WITA</t>
+          <t>Pukul        : 11.52 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8262,19 +8262,19 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2846</v>
+        <v>2869</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>502</v>
+        <v>454</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>9</v>
+        <v>94</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>2312</v>
@@ -8283,10 +8283,10 @@
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2322</v>
+        <v>2319</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8158819395643008</v>
+        <v>0.8082955733705124</v>
       </c>
     </row>
     <row r="8">
@@ -8295,45 +8295,45 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Simson Petiunaung</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2773</v>
+        <v>2026</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>777</v>
+        <v>462</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1941</v>
+        <v>1459</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1958</v>
+        <v>1474</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.706094482509917</v>
+        <v>0.7275419545903258</v>
       </c>
     </row>
     <row r="9">
@@ -8342,45 +8342,45 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Simson Petiunaung</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2026</v>
+        <v>2784</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>473</v>
+        <v>752</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1386</v>
+        <v>2012</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1401</v>
+        <v>2022</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.6915103652517274</v>
+        <v>0.7262931034482759</v>
       </c>
     </row>
     <row r="10">
@@ -8389,45 +8389,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Charly Angel Tatontos</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan, Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Alfi, Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2446</v>
+        <v>2884</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>755</v>
+        <v>669</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>11</v>
+        <v>61</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1676</v>
+        <v>2003</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>1678</v>
+        <v>2076</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.6860179885527393</v>
+        <v>0.7198335644937586</v>
       </c>
     </row>
     <row r="11">
@@ -8436,45 +8436,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan, Tabukan Utara</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi, Hendri</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2814</v>
+        <v>2461</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>865</v>
+        <v>727</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1861</v>
+        <v>1696</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1879</v>
+        <v>1697</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.6677327647476902</v>
+        <v>0.6895570906135717</v>
       </c>
     </row>
     <row r="12">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Charly Angel Tatontos</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -8497,31 +8497,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2880</v>
+        <v>2827</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>694</v>
+        <v>833</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>94</v>
+        <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>188</v>
+        <v>81</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1851</v>
+        <v>1892</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1904</v>
+        <v>1909</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.6611111111111111</v>
+        <v>0.6752741422002121</v>
       </c>
     </row>
     <row r="13">
@@ -8530,45 +8530,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Manganitu, Tamako</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike, Mega</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2101</v>
+        <v>2381</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>741</v>
+        <v>903</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>73</v>
+        <v>3</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1278</v>
+        <v>1438</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1280</v>
+        <v>1455</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6092336982389338</v>
+        <v>0.6110877782444352</v>
       </c>
     </row>
     <row r="14">
@@ -8577,45 +8577,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2146</v>
+        <v>2103</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>828</v>
+        <v>714</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>12</v>
+        <v>102</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1281</v>
+        <v>1278</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.5987884436160298</v>
+        <v>0.6086543033761294</v>
       </c>
     </row>
     <row r="15">
@@ -8624,45 +8624,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Manganitu, Tamako</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Erike, Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2378</v>
+        <v>2148</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>912</v>
+        <v>821</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1398</v>
+        <v>1278</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1410</v>
+        <v>1285</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.5929352396972245</v>
+        <v>0.5982309124767226</v>
       </c>
     </row>
     <row r="16">
@@ -8671,45 +8671,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore, Tabukan Utara</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Hendri, Michael</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2880</v>
+        <v>2747</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>1075</v>
+        <v>979</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1689</v>
+        <v>1633</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1697</v>
+        <v>1642</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.5892361111111111</v>
+        <v>0.5977429923552967</v>
       </c>
     </row>
     <row r="17">
@@ -8718,45 +8718,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kepulauan Marore, Tabukan Utara</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Hendri, Michael</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2737</v>
+        <v>2881</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>992</v>
+        <v>1062</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1578</v>
+        <v>1701</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1592</v>
+        <v>1704</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.5816587504567045</v>
+        <v>0.591461298160361</v>
       </c>
     </row>
     <row r="18">
@@ -8779,31 +8779,31 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2874</v>
+        <v>2878</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1631</v>
+        <v>1640</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1652</v>
+        <v>1663</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.5748086290883786</v>
+        <v>0.5778318276580959</v>
       </c>
     </row>
     <row r="19">
@@ -8826,31 +8826,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2793</v>
+        <v>2796</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1195</v>
+        <v>1176</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1532</v>
+        <v>1559</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1548</v>
+        <v>1578</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.5542427497314716</v>
+        <v>0.5643776824034334</v>
       </c>
     </row>
     <row r="20">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -8873,31 +8873,31 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2672</v>
+        <v>2657</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>1450</v>
+      </c>
+      <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="9" t="n">
-        <v>1435</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="L20" s="9" t="n">
-        <v>1439</v>
+        <v>1451</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5385479041916168</v>
+        <v>0.5461046292811441</v>
       </c>
     </row>
     <row r="21">
@@ -8906,45 +8906,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2654</v>
+        <v>2437</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1191</v>
+        <v>928</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="H21" s="9" t="n">
+        <v>155</v>
+      </c>
+      <c r="I21" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" s="9" t="n">
-        <v>1421</v>
+        <v>1317</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1422</v>
+        <v>1327</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5357950263752826</v>
+        <v>0.5445219532211736</v>
       </c>
     </row>
     <row r="22">
@@ -8953,45 +8953,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2428</v>
+        <v>2681</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>938</v>
+        <v>1164</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1289</v>
+        <v>1444</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1296</v>
+        <v>1448</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5337726523887973</v>
+        <v>0.5400969787392764</v>
       </c>
     </row>
     <row r="23">
@@ -9014,31 +9014,31 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2294</v>
+        <v>2299</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>990</v>
+        <v>982</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>23</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1181</v>
+        <v>1195</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1206</v>
+        <v>1220</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5257192676547515</v>
+        <v>0.5306655067420618</v>
       </c>
     </row>
     <row r="24">
@@ -9061,16 +9061,16 @@
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2705</v>
+        <v>2711</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>6</v>
@@ -9085,7 +9085,7 @@
         <v>1395</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5157116451016636</v>
+        <v>0.5145702692733308</v>
       </c>
     </row>
     <row r="25">
@@ -9094,45 +9094,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Olfira Sicilia Budiman</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2072</v>
+        <v>1413</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1020</v>
+        <v>422</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>23</v>
+        <v>274</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>935</v>
+        <v>698</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1012</v>
+        <v>702</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.4884169884169884</v>
+        <v>0.4968152866242038</v>
       </c>
     </row>
     <row r="26">
@@ -9158,28 +9158,28 @@
         <v>2527</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1225</v>
+        <v>1248</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1232</v>
+        <v>1253</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.4875346260387812</v>
+        <v>0.4958448753462604</v>
       </c>
     </row>
     <row r="27">
@@ -9188,45 +9188,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Olfira Sicilia Budiman</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>1410</v>
+        <v>2076</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>433</v>
+        <v>1016</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>288</v>
+        <v>22</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>672</v>
+        <v>938</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>673</v>
+        <v>1011</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.4773049645390071</v>
+        <v>0.4869942196531792</v>
       </c>
     </row>
     <row r="28">
@@ -9235,45 +9235,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2402</v>
+        <v>2061</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1128</v>
+        <v>1027</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>143</v>
+        <v>77</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1063</v>
+        <v>924</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1105</v>
+        <v>951</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.4600333055786844</v>
+        <v>0.4614264919941775</v>
       </c>
     </row>
     <row r="29">
@@ -9282,45 +9282,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2057</v>
+        <v>2402</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1034</v>
+        <v>1122</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>901</v>
+        <v>1066</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>928</v>
+        <v>1108</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.4511424404472533</v>
+        <v>0.4612822647793505</v>
       </c>
     </row>
   </sheetData>
@@ -9354,7 +9354,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 18 Juli 2026</t>
+          <t>Hari/Tanggal : 19 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 19.00 WITA</t>
+          <t>Pukul        : 11.52 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.7426343154246101</v>
+        <v>0.7558441558441558</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7332273449920508</v>
+        <v>0.7424770351599619</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7133665755187389</v>
+        <v>0.7256977863330125</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.6959050157499395</v>
+        <v>0.7062242673770889</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.6778714551625972</v>
+        <v>0.6932795991722035</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.6270096463022508</v>
+        <v>0.6334405144694534</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.620215897939156</v>
+        <v>0.6221786064769381</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.5900621118012422</v>
+        <v>0.6005314437555359</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0.5707124955245256</v>
+        <v>0.5779685264663805</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="C16" s="11" t="n">
-        <v>0.569078947368421</v>
+        <v>0.5733050028974309</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5393846825223653</v>
+        <v>0.5432367675887606</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5333084298343918</v>
+        <v>0.5383277425767176</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5195670274771024</v>
+        <v>0.5228975853455454</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5168783422459893</v>
+        <v>0.5216013344453712</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.4886524822695036</v>
+        <v>0.5074309978768577</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.52 WITA</t>
+          <t>Pukul        : 11.58 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.52 WITA</t>
+          <t>Pukul        : 11.58 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.52 WITA</t>
+          <t>Pukul        : 11.58 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.52 WITA</t>
+          <t>Pukul        : 11.58 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -610,32 +610,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.58 WITA</t>
+          <t>Pukul        : 06.29 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-34):</t>
+          <t>Target Hari Ini (H-35):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>56.78%</t>
+          <t>58.45%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 56.78%</t>
+          <t>Hijau &gt;= 58.45%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 28.39% - 56.78%</t>
+          <t>Kuning 29.22% - 58.45%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 28.39%</t>
+          <t>Merah &lt; 29.22%</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       <c r="P16" s="9" t="n">
         <v>2968</v>
       </c>
-      <c r="Q16" s="11">
+      <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
@@ -1760,7 +1760,7 @@
       <c r="P21" s="9" t="n">
         <v>1616</v>
       </c>
-      <c r="Q21" s="11">
+      <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
@@ -1911,17 +1911,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.58 WITA</t>
+          <t>Pukul        : 06.29 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-34):</t>
+          <t>Target Hari Ini (H-35):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>56.78%</t>
+          <t>58.45%</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5326,7 @@
       <c r="L77" s="9" t="n">
         <v>311</v>
       </c>
-      <c r="M77" s="11" t="n">
+      <c r="M77" s="12" t="n">
         <v>0.5834896810506567</v>
       </c>
     </row>
@@ -5373,7 +5373,7 @@
       <c r="L78" s="9" t="n">
         <v>268</v>
       </c>
-      <c r="M78" s="11" t="n">
+      <c r="M78" s="12" t="n">
         <v>0.5788336933045356</v>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
       <c r="L79" s="9" t="n">
         <v>262</v>
       </c>
-      <c r="M79" s="11" t="n">
+      <c r="M79" s="12" t="n">
         <v>0.5745614035087719</v>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       <c r="L80" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="M80" s="11" t="n">
+      <c r="M80" s="12" t="n">
         <v>0.5742971887550201</v>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       <c r="L81" s="9" t="n">
         <v>248</v>
       </c>
-      <c r="M81" s="11" t="n">
+      <c r="M81" s="12" t="n">
         <v>0.5727482678983834</v>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
       <c r="L82" s="9" t="n">
         <v>253</v>
       </c>
-      <c r="M82" s="11" t="n">
+      <c r="M82" s="12" t="n">
         <v>0.5685393258426966</v>
       </c>
     </row>
@@ -8160,17 +8160,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.58 WITA</t>
+          <t>Pukul        : 06.29 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-34):</t>
+          <t>Target Hari Ini (H-35):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>56.78%</t>
+          <t>58.45%</t>
         </is>
       </c>
     </row>
@@ -8802,7 +8802,7 @@
       <c r="L18" s="9" t="n">
         <v>1663</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="12" t="n">
         <v>0.5778318276580959</v>
       </c>
     </row>
@@ -9371,17 +9371,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.58 WITA</t>
+          <t>Pukul        : 06.29 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-34):</t>
+          <t>Target Hari Ini (H-35):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>56.78%</t>
+          <t>58.45%</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9561,7 @@
           <t>Kendahe</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>0.5779685264663805</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -9579,7 +9579,7 @@
           <t>Tahuna Timur</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="12" t="n">
         <v>0.5733050028974309</v>
       </c>
       <c r="D16" s="17" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -799,7 +799,7 @@
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -868,7 +868,7 @@
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -937,7 +937,7 @@
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -1006,7 +1006,7 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1075,7 +1075,7 @@
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1213,7 +1213,7 @@
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1282,7 +1282,7 @@
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1351,7 +1351,7 @@
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1489,7 +1489,7 @@
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1558,7 +1558,7 @@
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1627,7 +1627,7 @@
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1696,7 +1696,7 @@
         <v/>
       </c>
       <c r="R20" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S20" s="10">
         <f>R20/B20</f>
@@ -1765,7 +1765,7 @@
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.29 WITA</t>
+          <t>Pukul        : 18.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -744,13 +744,13 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4129</v>
+        <v>4130</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1176</v>
+        <v>1169</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
@@ -764,7 +764,7 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
@@ -778,28 +778,28 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2737</v>
+        <v>2833</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
         <v/>
       </c>
       <c r="N7" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O7" s="10">
         <f>N7/B7</f>
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2916</v>
+        <v>2924</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -813,27 +813,27 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1413</v>
+        <v>1420</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -847,7 +847,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>698</v>
+        <v>712</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -861,14 +861,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>717</v>
+        <v>744</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -882,41 +882,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6234</v>
+        <v>6240</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1616</v>
+        <v>1605</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4283</v>
+        <v>4333</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -930,14 +930,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4524</v>
+        <v>4550</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>117</v>
+        <v>26</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -971,7 +971,7 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
@@ -985,7 +985,7 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2319</v>
+        <v>2334</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -999,14 +999,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2344</v>
+        <v>2352</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1020,27 +1020,27 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1068,14 +1068,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>678</v>
+        <v>692</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1144,7 +1144,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1158,41 +1158,41 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4591</v>
+        <v>4596</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2063</v>
+        <v>2049</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2258</v>
+        <v>2276</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1206,14 +1206,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2494</v>
+        <v>2510</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1227,62 +1227,62 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>5995</v>
+        <v>5997</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2832</v>
+        <v>2808</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2912</v>
+        <v>2955</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
         <v/>
       </c>
       <c r="N14" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="10">
         <f>N14/B14</f>
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3127</v>
+        <v>3152</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1296,41 +1296,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8049</v>
+        <v>8064</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3577</v>
+        <v>3560</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4283</v>
+        <v>4329</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1344,14 +1344,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4333</v>
+        <v>4368</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,21 +1371,21 @@
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2085</v>
+        <v>2077</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
@@ -1399,7 +1399,7 @@
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2835</v>
+        <v>2862</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1413,14 +1413,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>2968</v>
+        <v>2983</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1434,20 +1434,20 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2402</v>
+        <v>2406</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
@@ -1461,14 +1461,14 @@
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1066</v>
+        <v>1087</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
@@ -1482,14 +1482,14 @@
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1256</v>
+        <v>1266</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1503,41 +1503,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9181</v>
+        <v>9203</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2717</v>
+        <v>2682</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>243</v>
+        <v>112</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6104</v>
+        <v>6293</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1551,14 +1551,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6365</v>
+        <v>6424</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>212</v>
+        <v>59</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,7 +1578,7 @@
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1592,7 +1592,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1606,7 +1606,7 @@
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>853</v>
+        <v>877</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1620,14 +1620,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1661,21 +1661,21 @@
         <v/>
       </c>
       <c r="H20" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I20" s="10">
         <f>H20/B20</f>
         <v/>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="10">
         <f>J20/B20</f>
         <v/>
       </c>
       <c r="L20" s="9" t="n">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="M20" s="10">
         <f>L20/B20</f>
@@ -1696,7 +1696,7 @@
         <v/>
       </c>
       <c r="R20" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S20" s="10">
         <f>R20/B20</f>
@@ -1710,27 +1710,27 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2796</v>
+        <v>2804</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1176</v>
+        <v>1163</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
         <v/>
       </c>
       <c r="F21" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G21" s="10">
         <f>F21/B21</f>
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
@@ -1744,28 +1744,28 @@
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1559</v>
+        <v>1605</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
         <v/>
       </c>
       <c r="N21" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O21" s="10">
         <f>N21/B21</f>
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1616</v>
+        <v>1638</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.29 WITA</t>
+          <t>Pukul        : 18.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2046,27 +2046,27 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Ayu Lestari Areros</t>
+          <t>Regina Mahoro</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>308</v>
+        <v>417</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>0</v>
@@ -2075,16 +2075,16 @@
         <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>279</v>
+        <v>393</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>281</v>
+        <v>399</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.9123376623376623</v>
+        <v>0.9568345323741008</v>
       </c>
     </row>
     <row r="9">
@@ -2093,45 +2093,45 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Syamsia Makaminan</t>
+          <t>Ayu Lestari Areros</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>551</v>
+        <v>308</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>486</v>
+        <v>279</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>502</v>
+        <v>281</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.911070780399274</v>
+        <v>0.9123376623376623</v>
       </c>
     </row>
     <row r="10">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Regina Mahoro</t>
+          <t>Syamsia Makaminan</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>413</v>
+        <v>551</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>1</v>
@@ -2169,16 +2169,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>370</v>
+        <v>502</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>376</v>
+        <v>502</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.910411622276029</v>
+        <v>0.911070780399274</v>
       </c>
     </row>
     <row r="11">
@@ -2187,45 +2187,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Merry Christiani Lano</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>364</v>
+        <v>516</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>249</v>
+        <v>443</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>318</v>
+        <v>458</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.8736263736263736</v>
+        <v>0.8875968992248062</v>
       </c>
     </row>
     <row r="12">
@@ -2234,45 +2234,45 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Merry Christiani Lano</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>514</v>
+        <v>364</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>443</v>
+        <v>286</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>444</v>
+        <v>319</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8638132295719845</v>
+        <v>0.8763736263736264</v>
       </c>
     </row>
     <row r="13">
@@ -2298,28 +2298,28 @@
         <v>377</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.8541114058355439</v>
+        <v>0.8647214854111405</v>
       </c>
     </row>
     <row r="14">
@@ -2342,31 +2342,31 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>5</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.8333333333333335</v>
+        <v>0.836461126005362</v>
       </c>
     </row>
     <row r="15">
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
@@ -2445,13 +2445,13 @@
         <v>2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
@@ -2469,24 +2469,24 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>397</v>
+        <v>488</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
@@ -2495,19 +2495,19 @@
         <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>313</v>
+        <v>392</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.7934508816120907</v>
+        <v>0.8032786885245902</v>
       </c>
     </row>
     <row r="18">
@@ -2516,24 +2516,24 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>475</v>
+        <v>397</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
@@ -2542,19 +2542,19 @@
         <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>374</v>
+        <v>313</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>375</v>
+        <v>315</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7934508816120907</v>
       </c>
     </row>
     <row r="19">
@@ -2563,45 +2563,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>372</v>
+        <v>475</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>374</v>
+      </c>
+      <c r="K19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J19" s="9" t="n">
-        <v>279</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" s="9" t="n">
-        <v>292</v>
+        <v>375</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.7849462365591396</v>
+        <v>0.7894736842105263</v>
       </c>
     </row>
     <row r="20">
@@ -2624,31 +2624,31 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.7797979797979798</v>
+        <v>0.7875751503006012</v>
       </c>
     </row>
     <row r="21">
@@ -2657,45 +2657,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>328</v>
+        <v>295</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.7790973871733968</v>
+        <v>0.7866666666666666</v>
       </c>
     </row>
     <row r="22">
@@ -2704,45 +2704,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>481</v>
+        <v>411</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>373</v>
+        <v>323</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>374</v>
+        <v>323</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.7775467775467776</v>
+        <v>0.7858880778588808</v>
       </c>
     </row>
     <row r="23">
@@ -2751,45 +2751,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.7712895377128953</v>
+        <v>0.7790973871733968</v>
       </c>
     </row>
     <row r="24">
@@ -2798,45 +2798,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>430</v>
+        <v>387</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>329</v>
+        <v>298</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.7651162790697674</v>
+        <v>0.7700258397932817</v>
       </c>
     </row>
     <row r="25">
@@ -2845,45 +2845,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>493</v>
+        <v>430</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>367</v>
+        <v>309</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>375</v>
+        <v>329</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7606490872210954</v>
+        <v>0.7651162790697674</v>
       </c>
     </row>
     <row r="26">
@@ -2892,45 +2892,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>523</v>
+        <v>494</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.7590822179732314</v>
+        <v>0.7631578947368421</v>
       </c>
     </row>
     <row r="27">
@@ -2939,45 +2939,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>385</v>
+        <v>524</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>285</v>
+        <v>388</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>286</v>
+        <v>399</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7428571428571429</v>
+        <v>0.7614503816793892</v>
       </c>
     </row>
     <row r="28">
@@ -3056,16 +3056,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
         <v>281</v>
@@ -3103,13 +3103,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>357</v>
+        <v>386</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
@@ -3127,21 +3127,21 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>115</v>
@@ -3150,22 +3150,22 @@
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7139303482587064</v>
+        <v>0.7181372549019608</v>
       </c>
     </row>
     <row r="32">
@@ -3174,45 +3174,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>349</v>
+      </c>
+      <c r="K32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>342</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" s="9" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7137096774193549</v>
+        <v>0.717434869739479</v>
       </c>
     </row>
     <row r="33">
@@ -3221,45 +3221,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>509</v>
+        <v>421</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>361</v>
+        <v>299</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>362</v>
+        <v>301</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7111984282907662</v>
+        <v>0.7149643705463185</v>
       </c>
     </row>
     <row r="34">
@@ -3268,24 +3268,24 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>407</v>
+        <v>535</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
@@ -3294,19 +3294,19 @@
         <v>0</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>288</v>
+        <v>381</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>289</v>
+        <v>382</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.71007371007371</v>
+        <v>0.7140186915887852</v>
       </c>
     </row>
     <row r="35">
@@ -3315,45 +3315,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>499</v>
+        <v>416</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>349</v>
+        <v>297</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>354</v>
+        <v>297</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7094188376753507</v>
+        <v>0.7139423076923077</v>
       </c>
     </row>
     <row r="36">
@@ -3362,45 +3362,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7047619047619048</v>
+        <v>0.7139303482587064</v>
       </c>
     </row>
     <row r="37">
@@ -3409,45 +3409,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>414</v>
+        <v>496</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>287</v>
+        <v>349</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>291</v>
+        <v>354</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7028985507246377</v>
+        <v>0.7137096774193549</v>
       </c>
     </row>
     <row r="38">
@@ -3456,45 +3456,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>346</v>
+        <v>509</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>103</v>
+        <v>138</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>242</v>
+        <v>361</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>243</v>
+        <v>362</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7023121387283237</v>
+        <v>0.7111984282907662</v>
       </c>
     </row>
     <row r="39">
@@ -3503,45 +3503,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>534</v>
+        <v>346</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>367</v>
+        <v>242</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>373</v>
+        <v>243</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.6985018726591761</v>
+        <v>0.7023121387283237</v>
       </c>
     </row>
     <row r="40">
@@ -3597,45 +3597,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>374</v>
+        <v>501</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>254</v>
+        <v>342</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.679144385026738</v>
+        <v>0.6826347305389223</v>
       </c>
     </row>
     <row r="42">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -3658,31 +3658,31 @@
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="I42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>252</v>
+        <v>292</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.6762589928057554</v>
+        <v>0.6824324324324325</v>
       </c>
     </row>
     <row r="43">
@@ -3691,24 +3691,24 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>499</v>
+        <v>374</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>161</v>
+        <v>119</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>1</v>
@@ -3717,19 +3717,19 @@
         <v>0</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>332</v>
+        <v>251</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>337</v>
+        <v>254</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.6753507014028056</v>
+        <v>0.679144385026738</v>
       </c>
     </row>
     <row r="44">
@@ -3738,45 +3738,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>501</v>
+        <v>526</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.6686626746506987</v>
+        <v>0.6768060836501901</v>
       </c>
     </row>
     <row r="45">
@@ -3785,45 +3785,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>289</v>
+        <v>417</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>193</v>
+        <v>282</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.6678200692041523</v>
+        <v>0.6762589928057554</v>
       </c>
     </row>
     <row r="46">
@@ -3832,45 +3832,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>522</v>
+        <v>499</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6753507014028056</v>
       </c>
     </row>
     <row r="47">
@@ -3879,24 +3879,24 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>438</v>
+        <v>289</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
@@ -3905,19 +3905,19 @@
         <v>0</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>292</v>
+        <v>190</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>292</v>
+        <v>193</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6678200692041523</v>
       </c>
     </row>
     <row r="48">
@@ -3926,45 +3926,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>345</v>
+        <v>459</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>214</v>
+        <v>287</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>222</v>
+        <v>301</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6434782608695652</v>
+        <v>0.6557734204793029</v>
       </c>
     </row>
     <row r="49">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
@@ -3987,31 +3987,31 @@
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>444</v>
+        <v>345</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>282</v>
+        <v>222</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>284</v>
+        <v>226</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6396396396396397</v>
+        <v>0.6550724637681159</v>
       </c>
     </row>
     <row r="50">
@@ -4037,28 +4037,28 @@
         <v>367</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6376021798365122</v>
+        <v>0.6457765667574933</v>
       </c>
     </row>
     <row r="51">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -4081,31 +4081,31 @@
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6344827586206897</v>
+        <v>0.6426966292134831</v>
       </c>
     </row>
     <row r="52">
@@ -4114,45 +4114,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>409</v>
+        <v>464</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="I52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>193</v>
+        <v>292</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>259</v>
+        <v>296</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6332518337408313</v>
+        <v>0.6379310344827587</v>
       </c>
     </row>
     <row r="53">
@@ -4161,45 +4161,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>155</v>
+        <v>129</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>247</v>
+        <v>275</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6318289786223278</v>
+        <v>0.6344827586206897</v>
       </c>
     </row>
     <row r="54">
@@ -4208,45 +4208,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>513</v>
+        <v>622</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>151</v>
+        <v>223</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>314</v>
+        <v>391</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>324</v>
+        <v>394</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6334405144694534</v>
       </c>
     </row>
     <row r="55">
@@ -4255,45 +4255,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>464</v>
+        <v>409</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>293</v>
+        <v>197</v>
       </c>
       <c r="K55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>293</v>
+        <v>259</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6314655172413793</v>
+        <v>0.6332518337408313</v>
       </c>
     </row>
     <row r="56">
@@ -4319,13 +4319,13 @@
         <v>452</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I56" s="9" t="n">
         <v>1</v>
@@ -4337,10 +4337,10 @@
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6305309734513275</v>
+        <v>0.6327433628318584</v>
       </c>
     </row>
     <row r="57">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
@@ -4363,31 +4363,31 @@
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>458</v>
+        <v>514</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>262</v>
+        <v>317</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>288</v>
+        <v>325</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.62882096069869</v>
+        <v>0.632295719844358</v>
       </c>
     </row>
     <row r="58">
@@ -4396,45 +4396,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.627039627039627</v>
+        <v>0.6318289786223278</v>
       </c>
     </row>
     <row r="59">
@@ -4443,45 +4443,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>622</v>
+        <v>429</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>227</v>
+        <v>160</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>385</v>
+        <v>269</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>390</v>
+        <v>269</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6270096463022508</v>
+        <v>0.627039627039627</v>
       </c>
     </row>
     <row r="60">
@@ -4490,45 +4490,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>452</v>
+        <v>374</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>282</v>
+        <v>234</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6238938053097345</v>
+        <v>0.6256684491978609</v>
       </c>
     </row>
     <row r="61">
@@ -4537,45 +4537,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6213151927437641</v>
+        <v>0.6238938053097345</v>
       </c>
     </row>
     <row r="62">
@@ -4584,45 +4584,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>498</v>
+        <v>441</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>305</v>
+        <v>273</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>307</v>
+        <v>274</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6164658634538153</v>
+        <v>0.6213151927437641</v>
       </c>
     </row>
     <row r="63">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
@@ -4645,31 +4645,31 @@
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="9" t="n">
+        <v>201</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="9" t="n">
         <v>216</v>
       </c>
-      <c r="K63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="9" t="n">
-        <v>227</v>
-      </c>
       <c r="M63" s="11" t="n">
-        <v>0.6118598382749326</v>
+        <v>0.6189111747851003</v>
       </c>
     </row>
     <row r="64">
@@ -4678,45 +4678,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>450</v>
+        <v>498</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6164658634538153</v>
       </c>
     </row>
     <row r="65">
@@ -4725,45 +4725,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>500</v>
+        <v>428</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>305</v>
+        <v>262</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.61</v>
+        <v>0.6121495327102804</v>
       </c>
     </row>
     <row r="66">
@@ -4772,45 +4772,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6098130841121495</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="67">
@@ -4819,45 +4819,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>413</v>
+        <v>509</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>304</v>
+      </c>
+      <c r="K67" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="9" t="n">
-        <v>245</v>
-      </c>
-      <c r="K67" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L67" s="9" t="n">
-        <v>250</v>
+        <v>311</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6053268765133172</v>
+        <v>0.6110019646365422</v>
       </c>
     </row>
     <row r="68">
@@ -4866,45 +4866,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
         <v>305</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.6039603960396039</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="69">
@@ -4913,45 +4913,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>347</v>
+        <v>413</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>209</v>
+        <v>251</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6023054755043228</v>
+        <v>0.6077481840193705</v>
       </c>
     </row>
     <row r="70">
@@ -4960,45 +4960,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>463</v>
+        <v>399</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>187</v>
+        <v>115</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>275</v>
+        <v>240</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.5939524838012959</v>
+        <v>0.6015037593984962</v>
       </c>
     </row>
     <row r="71">
@@ -5007,45 +5007,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>400</v>
+        <v>557</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>224</v>
+        <v>332</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>237</v>
+        <v>332</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.5925</v>
+        <v>0.5960502692998204</v>
       </c>
     </row>
     <row r="72">
@@ -5054,45 +5054,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.5939524838012959</v>
       </c>
     </row>
     <row r="73">
@@ -5101,45 +5101,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="M73" s="11" t="n">
-        <v>0.5894736842105263</v>
+        <v>0.5925</v>
       </c>
     </row>
     <row r="74">
@@ -5148,45 +5148,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>557</v>
+        <v>468</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>328</v>
+        <v>274</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="M74" s="11" t="n">
-        <v>0.5888689407540395</v>
+        <v>0.5918803418803419</v>
       </c>
     </row>
     <row r="75">
@@ -5195,45 +5195,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="M75" s="11" t="n">
-        <v>0.5872576177285319</v>
+        <v>0.5894736842105263</v>
       </c>
     </row>
     <row r="76">
@@ -5259,28 +5259,28 @@
         <v>426</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G76" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H76" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="H76" s="9" t="n">
-        <v>12</v>
-      </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="K76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M76" s="11" t="n">
-        <v>0.5845070422535211</v>
+        <v>0.5892018779342723</v>
       </c>
     </row>
     <row r="77">
@@ -5289,45 +5289,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>533</v>
+        <v>361</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>222</v>
+        <v>149</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>291</v>
+        <v>201</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>311</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>0.5834896810506567</v>
+        <v>212</v>
+      </c>
+      <c r="M77" s="11" t="n">
+        <v>0.5872576177285319</v>
       </c>
     </row>
     <row r="78">
@@ -5336,45 +5336,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>463</v>
+        <v>533</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>188</v>
+        <v>220</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>268</v>
-      </c>
-      <c r="M78" s="12" t="n">
-        <v>0.5788336933045356</v>
+        <v>313</v>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>0.5872420262664165</v>
       </c>
     </row>
     <row r="79">
@@ -5383,45 +5383,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="K79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.5745614035087719</v>
+        <v>0.5809935205183585</v>
       </c>
     </row>
     <row r="80">
@@ -5430,45 +5430,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>498</v>
+        <v>434</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>286</v>
+        <v>252</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.5742971887550201</v>
+        <v>0.5806451612903226</v>
       </c>
     </row>
     <row r="81">
@@ -5477,45 +5477,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.5727482678983834</v>
+        <v>0.5775</v>
       </c>
     </row>
     <row r="82">
@@ -5524,45 +5524,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>445</v>
+        <v>498</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>177</v>
+        <v>205</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>250</v>
+        <v>286</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>253</v>
+        <v>286</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.5685393258426966</v>
+        <v>0.5742971887550201</v>
       </c>
     </row>
     <row r="83">
@@ -5571,45 +5571,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>501</v>
+        <v>458</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>204</v>
+        <v>176</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.5668662674650699</v>
+        <v>0.5720524017467249</v>
       </c>
     </row>
     <row r="84">
@@ -5618,45 +5618,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>394</v>
+        <v>501</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>127</v>
+        <v>216</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>219</v>
+        <v>279</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>223</v>
+        <v>285</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.565989847715736</v>
+        <v>0.5688622754491018</v>
       </c>
     </row>
     <row r="85">
@@ -5682,13 +5682,13 @@
         <v>364</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I85" s="9" t="n">
         <v>0</v>
@@ -5700,10 +5700,10 @@
         <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.5631868131868132</v>
+        <v>0.5686813186813187</v>
       </c>
     </row>
     <row r="86">
@@ -5712,45 +5712,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="K86" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.5622317596566524</v>
+        <v>0.5672645739910314</v>
       </c>
     </row>
     <row r="87">
@@ -5759,45 +5759,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>397</v>
+        <v>501</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>175</v>
+        <v>204</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>202</v>
+        <v>271</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>222</v>
+        <v>284</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.5591939546599496</v>
+        <v>0.5668662674650699</v>
       </c>
     </row>
     <row r="88">
@@ -5806,45 +5806,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.5584677419354839</v>
+        <v>0.5643776824034334</v>
       </c>
     </row>
     <row r="89">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
@@ -5867,31 +5867,31 @@
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>470</v>
+        <v>492</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>180</v>
+        <v>212</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I89" s="9" t="n">
         <v>3</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="K89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.5574468085106383</v>
+        <v>0.5630081300813008</v>
       </c>
     </row>
     <row r="90">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
@@ -5914,31 +5914,31 @@
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>214</v>
+        <v>180</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.5528455284552846</v>
+        <v>0.5595744680851064</v>
       </c>
     </row>
     <row r="91">
@@ -5947,45 +5947,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5548523206751055</v>
       </c>
     </row>
     <row r="92">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -6008,31 +6008,31 @@
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>473</v>
+        <v>407</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5528255528255528</v>
       </c>
     </row>
     <row r="93">
@@ -6041,24 +6041,24 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>0</v>
@@ -6070,16 +6070,16 @@
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.5413043478260869</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="94">
@@ -6102,31 +6102,31 @@
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5394736842105263</v>
+        <v>0.5496323529411765</v>
       </c>
     </row>
     <row r="95">
@@ -6135,30 +6135,30 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>412</v>
+        <v>466</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>170</v>
+        <v>208</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="I95" s="9" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>1</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.5388349514563107</v>
+        <v>0.5493562231759657</v>
       </c>
     </row>
     <row r="96">
@@ -6182,45 +6182,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>465</v>
+        <v>438</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>213</v>
+        <v>197</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="K96" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5376344086021505</v>
+        <v>0.547945205479452</v>
       </c>
     </row>
     <row r="97">
@@ -6246,7 +6246,7 @@
         <v>399</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>1</v>
@@ -6258,16 +6258,16 @@
         <v>0</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5338345864661654</v>
+        <v>0.5463659147869674</v>
       </c>
     </row>
     <row r="98">
@@ -6276,45 +6276,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>437</v>
+        <v>460</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5331807780320366</v>
+        <v>0.5413043478260869</v>
       </c>
     </row>
     <row r="99">
@@ -6323,45 +6323,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5328638497652582</v>
+        <v>0.5388349514563107</v>
       </c>
     </row>
     <row r="100">
@@ -6370,45 +6370,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>402</v>
+        <v>511</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>186</v>
+        <v>236</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>214</v>
+        <v>261</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.5323383084577115</v>
+        <v>0.5342465753424658</v>
       </c>
     </row>
     <row r="101">
@@ -6417,45 +6417,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
         <v>454</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5286343612334802</v>
+        <v>0.5330396475770925</v>
       </c>
     </row>
     <row r="102">
@@ -6464,45 +6464,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>451</v>
+        <v>424</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="K102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5254988913525499</v>
+        <v>0.5330188679245284</v>
       </c>
     </row>
     <row r="103">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
@@ -6525,31 +6525,31 @@
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>470</v>
+        <v>426</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>217</v>
+        <v>199</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>223</v>
+      </c>
+      <c r="K103" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J103" s="9" t="n">
-        <v>233</v>
-      </c>
-      <c r="K103" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L103" s="9" t="n">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5212765957446809</v>
+        <v>0.5328638497652582</v>
       </c>
     </row>
     <row r="104">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
@@ -6572,13 +6572,13 @@
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>438</v>
+        <v>402</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>210</v>
+        <v>186</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H104" s="9" t="n">
         <v>0</v>
@@ -6587,16 +6587,16 @@
         <v>0</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.5205479452054794</v>
+        <v>0.5323383084577115</v>
       </c>
     </row>
     <row r="105">
@@ -6605,45 +6605,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>498</v>
+        <v>454</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="G105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5200803212851406</v>
+        <v>0.5286343612334802</v>
       </c>
     </row>
     <row r="106">
@@ -6652,45 +6652,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>364</v>
+        <v>470</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="G106" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H106" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H106" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="I106" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J106" s="9" t="n">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5234042553191489</v>
       </c>
     </row>
     <row r="107">
@@ -6699,45 +6699,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>422</v>
+        <v>366</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.518957345971564</v>
+        <v>0.5218579234972678</v>
       </c>
     </row>
     <row r="108">
@@ -6746,45 +6746,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>511</v>
+        <v>438</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5185909980430529</v>
+        <v>0.5205479452054794</v>
       </c>
     </row>
     <row r="109">
@@ -6793,45 +6793,45 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>417</v>
+        <v>498</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>198</v>
+        <v>248</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>216</v>
+        <v>259</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5179856115107914</v>
+        <v>0.5200803212851406</v>
       </c>
     </row>
     <row r="110">
@@ -6840,45 +6840,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>323</v>
+        <v>417</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>114</v>
+        <v>201</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5170278637770898</v>
+        <v>0.5179856115107914</v>
       </c>
     </row>
     <row r="111">
@@ -6887,45 +6887,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>401</v>
+        <v>323</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>182</v>
+        <v>114</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.516209476309227</v>
+        <v>0.5170278637770898</v>
       </c>
     </row>
     <row r="112">
@@ -6934,45 +6934,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5122549019607843</v>
+        <v>0.5169082125603864</v>
       </c>
     </row>
     <row r="113">
@@ -6981,45 +6981,45 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5096618357487923</v>
+        <v>0.5122549019607843</v>
       </c>
     </row>
     <row r="114">
@@ -7028,45 +7028,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>474</v>
+        <v>389</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>240</v>
+        <v>196</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5063291139240507</v>
+        <v>0.5038560411311054</v>
       </c>
     </row>
     <row r="115">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
@@ -7089,31 +7089,31 @@
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>389</v>
+        <v>450</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>186</v>
+        <v>224</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>196</v>
+        <v>226</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5038560411311054</v>
+        <v>0.5022222222222222</v>
       </c>
     </row>
     <row r="116">
@@ -7122,45 +7122,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>450</v>
+        <v>346</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>224</v>
+        <v>173</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>222</v>
+        <v>170</v>
       </c>
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>226</v>
+        <v>173</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5022222222222222</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="117">
@@ -7169,42 +7169,42 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>346</v>
+        <v>474</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>173</v>
+        <v>229</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I117" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>194</v>
+      </c>
+      <c r="K117" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J117" s="9" t="n">
-        <v>170</v>
-      </c>
-      <c r="K117" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L117" s="9" t="n">
-        <v>173</v>
+        <v>237</v>
       </c>
       <c r="M117" s="12" t="n">
         <v>0.5</v>
@@ -7233,13 +7233,13 @@
         <v>399</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G118" s="9" t="n">
         <v>9</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I118" s="9" t="n">
         <v>1</v>
@@ -7251,10 +7251,10 @@
         <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.4962406015037594</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="119">
@@ -7286,13 +7286,13 @@
         <v>1</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I119" s="9" t="n">
         <v>11</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
@@ -7418,7 +7418,7 @@
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F122" s="9" t="n">
         <v>260</v>
@@ -7427,22 +7427,22 @@
         <v>0</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K122" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.4831013916500994</v>
+        <v>0.4841269841269841</v>
       </c>
     </row>
     <row r="123">
@@ -7474,13 +7474,13 @@
         <v>1</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
@@ -7521,13 +7521,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
@@ -7562,28 +7562,28 @@
         <v>438</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H125" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.4794520547945205</v>
+        <v>0.4817351598173516</v>
       </c>
     </row>
     <row r="126">
@@ -7592,45 +7592,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>391</v>
+        <v>414</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="G126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.4629156010230179</v>
+        <v>0.4758454106280193</v>
       </c>
     </row>
     <row r="127">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7653,31 +7653,31 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.4619164619164619</v>
+        <v>0.465324384787472</v>
       </c>
     </row>
     <row r="128">
@@ -7686,45 +7686,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4608501118568233</v>
+        <v>0.4645308924485125</v>
       </c>
     </row>
     <row r="129">
@@ -7733,45 +7733,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>437</v>
+        <v>391</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4599542334096111</v>
+        <v>0.4629156010230179</v>
       </c>
     </row>
     <row r="130">
@@ -7780,45 +7780,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="F130" s="9" t="n">
         <v>219</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4557823129251701</v>
+        <v>0.4619164619164619</v>
       </c>
     </row>
     <row r="131">
@@ -7827,45 +7827,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>412</v>
+        <v>441</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>137</v>
+        <v>196</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4514563106796117</v>
+        <v>0.4557823129251701</v>
       </c>
     </row>
     <row r="132">
@@ -7874,45 +7874,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>459</v>
+        <v>417</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>180</v>
+        <v>144</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4422657952069716</v>
+        <v>0.4460431654676259</v>
       </c>
     </row>
     <row r="133">
@@ -7921,45 +7921,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>512</v>
+        <v>459</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4375</v>
+        <v>0.4422657952069716</v>
       </c>
     </row>
     <row r="134">
@@ -7968,45 +7968,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Suharsi</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>415</v>
+        <v>512</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>216</v>
+        <v>281</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>181</v>
+        <v>226</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.436144578313253</v>
+        <v>0.44140625</v>
       </c>
     </row>
     <row r="135">
@@ -8015,45 +8015,45 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>417</v>
+        <v>332</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>234</v>
+        <v>8</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>2</v>
+        <v>178</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.434052757793765</v>
+        <v>0.4397590361445783</v>
       </c>
     </row>
     <row r="136">
@@ -8062,45 +8062,45 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>332</v>
+        <v>415</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>8</v>
+        <v>216</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>184</v>
+        <v>18</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>140</v>
+        <v>181</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4216867469879519</v>
+        <v>0.436144578313253</v>
       </c>
     </row>
   </sheetData>
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.29 WITA</t>
+          <t>Pukul        : 18.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8265,28 +8265,28 @@
         <v>2869</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2312</v>
+        <v>2401</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2319</v>
+        <v>2408</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8082955733705124</v>
+        <v>0.839316835134193</v>
       </c>
     </row>
     <row r="8">
@@ -8309,31 +8309,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>30</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1459</v>
+        <v>1496</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1474</v>
+        <v>1510</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7275419545903258</v>
+        <v>0.7449432659102121</v>
       </c>
     </row>
     <row r="9">
@@ -8356,31 +8356,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2784</v>
+        <v>2785</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>8</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2012</v>
+        <v>2027</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2022</v>
+        <v>2037</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7262931034482759</v>
+        <v>0.7314183123877918</v>
       </c>
     </row>
     <row r="10">
@@ -8403,31 +8403,31 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2076</v>
+        <v>2097</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7198335644937586</v>
+        <v>0.7268630849220103</v>
       </c>
     </row>
     <row r="11">
@@ -8450,31 +8450,31 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2461</v>
+        <v>2475</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>727</v>
+        <v>706</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1696</v>
+        <v>1736</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1697</v>
+        <v>1737</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.6895570906135717</v>
+        <v>0.7018181818181817</v>
       </c>
     </row>
     <row r="12">
@@ -8497,31 +8497,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2827</v>
+        <v>2831</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1892</v>
+        <v>1937</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1909</v>
+        <v>1953</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.6752741422002121</v>
+        <v>0.6898622394913458</v>
       </c>
     </row>
     <row r="13">
@@ -8530,45 +8530,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Manganitu, Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Erike, Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2381</v>
+        <v>2103</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>903</v>
+        <v>709</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1438</v>
+        <v>1337</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1455</v>
+        <v>1339</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6110877782444352</v>
+        <v>0.6367094626723728</v>
       </c>
     </row>
     <row r="14">
@@ -8577,45 +8577,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Manganitu, Tamako</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike, Mega</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2103</v>
+        <v>2384</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>714</v>
+        <v>890</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>102</v>
+        <v>11</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1278</v>
+        <v>1447</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1280</v>
+        <v>1464</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6086543033761294</v>
+        <v>0.6140939597315436</v>
       </c>
     </row>
     <row r="15">
@@ -8624,45 +8624,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Kepulauan Marore, Tabukan Utara</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Hendri, Michael</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2148</v>
+        <v>2886</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>821</v>
+        <v>1052</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1278</v>
+        <v>1758</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1285</v>
+        <v>1764</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.5982309124767226</v>
+        <v>0.6112266112266113</v>
       </c>
     </row>
     <row r="16">
@@ -8685,31 +8685,31 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2747</v>
+        <v>2750</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>979</v>
+        <v>965</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1633</v>
+        <v>1666</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1642</v>
+        <v>1674</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.5977429923552967</v>
+        <v>0.6087272727272727</v>
       </c>
     </row>
     <row r="17">
@@ -8718,45 +8718,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore, Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Hendri, Michael</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2881</v>
+        <v>2153</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>1062</v>
+        <v>806</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1701</v>
+        <v>1278</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1704</v>
+        <v>1285</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.591461298160361</v>
+        <v>0.5968416163492801</v>
       </c>
     </row>
     <row r="18">
@@ -8765,45 +8765,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2878</v>
+        <v>2804</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1103</v>
+        <v>1163</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>63</v>
+        <v>3</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1640</v>
+        <v>1605</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1663</v>
+        <v>1625</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.5778318276580959</v>
+        <v>0.5795292439372325</v>
       </c>
     </row>
     <row r="19">
@@ -8812,45 +8812,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2796</v>
+        <v>2878</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1176</v>
+        <v>1099</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1559</v>
+        <v>1640</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1578</v>
+        <v>1663</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.5643776824034334</v>
+        <v>0.5778318276580959</v>
       </c>
     </row>
     <row r="20">
@@ -8873,13 +8873,13 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2657</v>
+        <v>2659</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1177</v>
+        <v>1166</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>0</v>
@@ -8888,16 +8888,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1450</v>
+        <v>1467</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1451</v>
+        <v>1468</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5461046292811441</v>
+        <v>0.5520872508461828</v>
       </c>
     </row>
     <row r="21">
@@ -8906,45 +8906,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2437</v>
+        <v>2694</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>928</v>
+        <v>1160</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1317</v>
+        <v>1473</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1327</v>
+        <v>1477</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5445219532211736</v>
+        <v>0.5482553823311062</v>
       </c>
     </row>
     <row r="22">
@@ -8953,45 +8953,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2681</v>
+        <v>2441</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1164</v>
+        <v>917</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>17</v>
+        <v>162</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1444</v>
+        <v>1321</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1448</v>
+        <v>1332</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5400969787392764</v>
+        <v>0.5456780008193364</v>
       </c>
     </row>
     <row r="23">
@@ -9017,28 +9017,28 @@
         <v>2299</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>61</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>23</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1195</v>
+        <v>1222</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1220</v>
+        <v>1247</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5306655067420618</v>
+        <v>0.5424097433666811</v>
       </c>
     </row>
     <row r="24">
@@ -9064,16 +9064,16 @@
         <v>2711</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" s="9" t="n">
         <v>1389</v>
@@ -9082,10 +9082,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5145702692733308</v>
+        <v>0.5142014016967908</v>
       </c>
     </row>
     <row r="25">
@@ -9108,31 +9108,31 @@
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1413</v>
+        <v>1420</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>698</v>
+        <v>712</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>702</v>
+        <v>716</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.4968152866242038</v>
+        <v>0.5042253521126761</v>
       </c>
     </row>
     <row r="26">
@@ -9155,31 +9155,31 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1248</v>
+        <v>1262</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1253</v>
+        <v>1268</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.4958448753462604</v>
+        <v>0.5015822784810127</v>
       </c>
     </row>
     <row r="27">
@@ -9205,28 +9205,28 @@
         <v>2076</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1016</v>
+        <v>1007</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>938</v>
+        <v>943</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.4869942196531792</v>
+        <v>0.4845857418111754</v>
       </c>
     </row>
     <row r="28">
@@ -9252,28 +9252,28 @@
         <v>2061</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>924</v>
+        <v>953</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>951</v>
+        <v>975</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.4614264919941775</v>
+        <v>0.4730713245997089</v>
       </c>
     </row>
     <row r="29">
@@ -9296,31 +9296,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2402</v>
+        <v>2406</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H29" s="9" t="n">
         <v>148</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1066</v>
+        <v>1087</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1108</v>
+        <v>1118</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.4612822647793505</v>
+        <v>0.4646716541978387</v>
       </c>
     </row>
   </sheetData>
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 06.29 WITA</t>
+          <t>Pukul        : 18.25 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.7558441558441558</v>
+        <v>0.7670995670995669</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7424770351599619</v>
+        <v>0.7447751741608613</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7256977863330125</v>
+        <v>0.7291666666666665</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7062242673770889</v>
+        <v>0.7079903147699756</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.6932795991722035</v>
+        <v>0.6980332500271651</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.6005314437555359</v>
+        <v>0.6102292768959435</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.5779685264663805</v>
+        <v>0.5841654778887304</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.5733050028974309</v>
+        <v>0.5762024338419934</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5432367675887606</v>
+        <v>0.5461270670147955</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5383277425767176</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5228975853455454</v>
+        <v>0.5261845386533666</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5216013344453712</v>
+        <v>0.5255961313990328</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.5074309978768577</v>
+        <v>0.523943661971831</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 18.00 WITA</t>
+          <t>Pukul        : 18.47 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 18.00 WITA</t>
+          <t>Pukul        : 18.47 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 18.00 WITA</t>
+          <t>Pukul        : 18.47 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 18.00 WITA</t>
+          <t>Pukul        : 18.47 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 18.47 WITA</t>
+          <t>Pukul        : 19.58 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 18.47 WITA</t>
+          <t>Pukul        : 19.58 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
@@ -6145,7 +6145,7 @@
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 18.47 WITA</t>
+          <t>Pukul        : 19.58 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 18.47 WITA</t>
+          <t>Pukul        : 19.58 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +91,10 @@
     </font>
     <font>
       <color rgb="00595959"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="8">
@@ -163,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -188,6 +192,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -588,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 19 Juli 2026</t>
+          <t>Hari/Tanggal : 20 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -610,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 19.58 WITA</t>
+          <t>Pukul        : 05.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -744,41 +750,41 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4130</v>
+        <v>4131</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1169</v>
+        <v>1162</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2833</v>
+        <v>2884</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -792,14 +798,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2924</v>
+        <v>2935</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -813,27 +819,27 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -847,28 +853,28 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>712</v>
+        <v>745</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
         <v/>
       </c>
       <c r="N8" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O8" s="10">
         <f>N8/B8</f>
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -882,41 +888,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6240</v>
+        <v>6244</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1605</v>
+        <v>1583</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4333</v>
+        <v>4413</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -930,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4550</v>
+        <v>4588</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -951,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3158</v>
+        <v>3171</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>806</v>
+        <v>768</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -971,21 +977,21 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2334</v>
+        <v>2380</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -999,14 +1005,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2352</v>
+        <v>2403</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1020,27 +1026,27 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1054,7 +1060,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1068,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>692</v>
+        <v>701</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1095,42 +1101,42 @@
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
         <v/>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="10">
         <f>F12/B12</f>
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
         <v/>
       </c>
       <c r="L12" s="9" t="n">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="M12" s="10">
         <f>L12/B12</f>
         <v/>
       </c>
       <c r="N12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="10">
         <f>N12/B12</f>
@@ -1158,27 +1164,27 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4596</v>
+        <v>4604</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2049</v>
+        <v>2034</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
@@ -1192,7 +1198,7 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2276</v>
+        <v>2329</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1206,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2510</v>
+        <v>2537</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1227,41 +1233,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>5997</v>
+        <v>6005</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2808</v>
+        <v>2798</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2955</v>
+        <v>3021</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1275,14 +1281,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3152</v>
+        <v>3183</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1296,41 +1302,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8064</v>
+        <v>8066</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3560</v>
+        <v>3540</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4329</v>
+        <v>4342</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1344,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4368</v>
+        <v>4399</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1365,62 +1371,62 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5177</v>
+        <v>5180</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2077</v>
+        <v>2067</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2862</v>
+        <v>2918</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
         <v/>
       </c>
       <c r="N16" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16" s="10">
         <f>N16/B16</f>
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>2983</v>
+        <v>2999</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1434,41 +1440,41 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1115</v>
+        <v>1104</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1087</v>
+        <v>1133</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
@@ -1482,14 +1488,14 @@
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1266</v>
+        <v>1275</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1503,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9203</v>
+        <v>9227</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2682</v>
+        <v>2628</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6293</v>
+        <v>6435</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1551,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6424</v>
+        <v>6513</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>59</v>
+        <v>148</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,7 +1584,7 @@
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1592,21 +1598,21 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
         <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" s="10">
         <f>J19/B19</f>
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>877</v>
+        <v>887</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1620,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>886</v>
+        <v>896</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1710,13 +1716,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2804</v>
+        <v>2809</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1163</v>
+        <v>1149</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1730,21 +1736,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1605</v>
+        <v>1636</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1758,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1638</v>
-      </c>
-      <c r="Q21" s="12">
+        <v>1657</v>
+      </c>
+      <c r="Q21" s="11">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1894,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 19 Juli 2026</t>
+          <t>Hari/Tanggal : 20 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1911,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 19.58 WITA</t>
+          <t>Pukul        : 05.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2093,24 +2099,24 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Ayu Lestari Areros</t>
+          <t>Syamsia Makaminan</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>308</v>
+        <v>552</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
@@ -2122,16 +2128,16 @@
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>279</v>
+        <v>519</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>281</v>
+        <v>519</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.9123376623376623</v>
+        <v>0.9402173913043478</v>
       </c>
     </row>
     <row r="10">
@@ -2140,27 +2146,27 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Syamsia Makaminan</t>
+          <t>Ayu Lestari Areros</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>551</v>
+        <v>308</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>0</v>
@@ -2169,16 +2175,16 @@
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>502</v>
+        <v>279</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>502</v>
+        <v>281</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.911070780399274</v>
+        <v>0.9123376623376623</v>
       </c>
     </row>
     <row r="11">
@@ -2257,13 +2263,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>3</v>
@@ -2298,28 +2304,28 @@
         <v>377</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.8647214854111405</v>
+        <v>0.8726790450928382</v>
       </c>
     </row>
     <row r="14">
@@ -2328,7 +2334,7 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Clara Patricia Pangandaheng</t>
+          <t>Fitria Rianti Gorosita</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -2342,10 +2348,10 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
@@ -2354,19 +2360,19 @@
         <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.836461126005362</v>
+        <v>0.8496042216358839</v>
       </c>
     </row>
     <row r="15">
@@ -2375,7 +2381,7 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Fitria Rianti Gorosita</t>
+          <t>Clara Patricia Pangandaheng</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -2389,31 +2395,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.8324468085106383</v>
+        <v>0.841823056300268</v>
       </c>
     </row>
     <row r="16">
@@ -2469,24 +2475,24 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>488</v>
+        <v>397</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
@@ -2495,19 +2501,19 @@
         <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>392</v>
+        <v>320</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>392</v>
+        <v>322</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8032786885245902</v>
+        <v>0.8110831234256927</v>
       </c>
     </row>
     <row r="18">
@@ -2516,24 +2522,24 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>397</v>
+        <v>488</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
@@ -2542,19 +2548,19 @@
         <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>313</v>
+        <v>392</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>315</v>
+        <v>392</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.7934508816120907</v>
+        <v>0.8032786885245902</v>
       </c>
     </row>
     <row r="19">
@@ -2563,24 +2569,24 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>475</v>
+        <v>421</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
@@ -2589,19 +2595,19 @@
         <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>374</v>
+        <v>324</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>375</v>
+        <v>335</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7957244655581949</v>
       </c>
     </row>
     <row r="20">
@@ -2610,45 +2616,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>499</v>
+        <v>476</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>391</v>
+        <v>377</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.7875751503006012</v>
+        <v>0.7941176470588235</v>
       </c>
     </row>
     <row r="21">
@@ -2657,45 +2663,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.7866666666666666</v>
+        <v>0.7931873479318735</v>
       </c>
     </row>
     <row r="22">
@@ -2704,45 +2710,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>411</v>
+        <v>376</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>323</v>
+        <v>295</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.7858880778588808</v>
+        <v>0.7898936170212765</v>
       </c>
     </row>
     <row r="23">
@@ -2751,7 +2757,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -2765,31 +2771,31 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>421</v>
+        <v>499</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>314</v>
+        <v>393</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>328</v>
+        <v>393</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.7790973871733968</v>
+        <v>0.7875751503006012</v>
       </c>
     </row>
     <row r="24">
@@ -2798,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>387</v>
+        <v>495</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>294</v>
+        <v>384</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>298</v>
+        <v>384</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.7700258397932817</v>
+        <v>0.7757575757575758</v>
       </c>
     </row>
     <row r="25">
@@ -2862,28 +2868,28 @@
         <v>430</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7651162790697674</v>
+        <v>0.7744186046511627</v>
       </c>
     </row>
     <row r="26">
@@ -2892,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>494</v>
+        <v>388</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>377</v>
+        <v>297</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>377</v>
+        <v>300</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7731958762886599</v>
       </c>
     </row>
     <row r="27">
@@ -2956,28 +2962,28 @@
         <v>524</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="G27" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H27" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="H27" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="I27" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7614503816793892</v>
+        <v>0.7690839694656488</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J28" s="9" t="n">
         <v>321</v>
@@ -3033,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7356020942408377</v>
+        <v>0.7386091127098321</v>
       </c>
     </row>
     <row r="30">
@@ -3080,7 +3086,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -3094,31 +3100,31 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>552</v>
+        <v>382</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>386</v>
+        <v>279</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>399</v>
+        <v>281</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7228260869565217</v>
+        <v>0.7356020942408377</v>
       </c>
     </row>
     <row r="31">
@@ -3141,31 +3147,31 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7181372549019608</v>
+        <v>0.7294685990338166</v>
       </c>
     </row>
     <row r="32">
@@ -3174,45 +3180,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>499</v>
+        <v>422</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>349</v>
+        <v>306</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>358</v>
+        <v>307</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.717434869739479</v>
+        <v>0.7274881516587678</v>
       </c>
     </row>
     <row r="33">
@@ -3221,45 +3227,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>421</v>
+        <v>498</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>299</v>
+        <v>355</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>301</v>
+        <v>361</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7149643705463185</v>
+        <v>0.7248995983935742</v>
       </c>
     </row>
     <row r="34">
@@ -3268,21 +3274,21 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>535</v>
+        <v>552</v>
       </c>
       <c r="F34" s="9" t="n">
         <v>153</v>
@@ -3291,22 +3297,22 @@
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7140186915887852</v>
+        <v>0.7228260869565217</v>
       </c>
     </row>
     <row r="35">
@@ -3315,24 +3321,24 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>416</v>
+        <v>535</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>119</v>
+        <v>151</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>0</v>
@@ -3344,16 +3350,16 @@
         <v>0</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>297</v>
+        <v>384</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>297</v>
+        <v>384</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7139423076923077</v>
+        <v>0.7177570093457943</v>
       </c>
     </row>
     <row r="36">
@@ -3362,45 +3368,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>402</v>
+        <v>499</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>287</v>
+        <v>353</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>287</v>
+        <v>358</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7139303482587064</v>
+        <v>0.717434869739479</v>
       </c>
     </row>
     <row r="37">
@@ -3409,45 +3415,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>496</v>
+        <v>402</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>349</v>
+        <v>287</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>354</v>
+        <v>287</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7137096774193549</v>
+        <v>0.7139303482587064</v>
       </c>
     </row>
     <row r="38">
@@ -3517,16 +3523,16 @@
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>0</v>
@@ -3538,10 +3544,10 @@
         <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7023121387283237</v>
+        <v>0.7089337175792507</v>
       </c>
     </row>
     <row r="40">
@@ -3550,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>388</v>
+        <v>447</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>223</v>
+        <v>312</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>265</v>
+        <v>312</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.6829896907216495</v>
+        <v>0.697986577181208</v>
       </c>
     </row>
     <row r="41">
@@ -3597,45 +3603,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>501</v>
+        <v>417</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>311</v>
+        <v>272</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>342</v>
+        <v>286</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.6826347305389223</v>
+        <v>0.6858513189448441</v>
       </c>
     </row>
     <row r="42">
@@ -3644,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>444</v>
+        <v>389</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>292</v>
+        <v>223</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.6824324324324325</v>
+        <v>0.6838046272493572</v>
       </c>
     </row>
     <row r="43">
@@ -3691,45 +3697,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>374</v>
+        <v>501</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>251</v>
+        <v>341</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>254</v>
+        <v>342</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.679144385026738</v>
+        <v>0.6826347305389223</v>
       </c>
     </row>
     <row r="44">
@@ -3752,7 +3758,7 @@
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F44" s="9" t="n">
         <v>170</v>
@@ -3767,16 +3773,16 @@
         <v>3</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.6768060836501901</v>
+        <v>0.6774193548387096</v>
       </c>
     </row>
     <row r="45">
@@ -3785,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>417</v>
+        <v>374</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.6762589928057554</v>
+        <v>0.6764705882352942</v>
       </c>
     </row>
     <row r="46">
@@ -3926,45 +3932,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>459</v>
+        <v>345</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>158</v>
+        <v>115</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>287</v>
+        <v>230</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>301</v>
+        <v>230</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6557734204793029</v>
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="49">
@@ -3973,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>345</v>
+        <v>459</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>222</v>
+        <v>303</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>226</v>
+        <v>303</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6550724637681159</v>
+        <v>0.6601307189542482</v>
       </c>
     </row>
     <row r="50">
@@ -4037,28 +4043,28 @@
         <v>367</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6457765667574933</v>
+        <v>0.6566757493188011</v>
       </c>
     </row>
     <row r="51">
@@ -4067,45 +4073,45 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6426966292134831</v>
+        <v>0.652654867256637</v>
       </c>
     </row>
     <row r="52">
@@ -4114,45 +4120,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H52" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I52" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="I52" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J52" s="9" t="n">
-        <v>292</v>
+        <v>254</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6379310344827587</v>
+        <v>0.6462264150943396</v>
       </c>
     </row>
     <row r="53">
@@ -4161,7 +4167,7 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
@@ -4175,31 +4181,31 @@
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6344827586206897</v>
+        <v>0.6426966292134831</v>
       </c>
     </row>
     <row r="54">
@@ -4208,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>622</v>
+        <v>445</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>223</v>
+        <v>158</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>391</v>
+        <v>281</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>394</v>
+        <v>286</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6334405144694534</v>
+        <v>0.6426966292134831</v>
       </c>
     </row>
     <row r="55">
@@ -4255,45 +4261,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>197</v>
+        <v>278</v>
       </c>
       <c r="K55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6332518337408313</v>
+        <v>0.6413793103448274</v>
       </c>
     </row>
     <row r="56">
@@ -4302,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>452</v>
+        <v>514</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>283</v>
+        <v>317</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>286</v>
+        <v>329</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6327433628318584</v>
+        <v>0.6400778210116731</v>
       </c>
     </row>
     <row r="57">
@@ -4349,45 +4355,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>514</v>
+        <v>464</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>317</v>
+        <v>292</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.632295719844358</v>
+        <v>0.6379310344827587</v>
       </c>
     </row>
     <row r="58">
@@ -4396,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>421</v>
+        <v>374</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6318289786223278</v>
+        <v>0.6336898395721925</v>
       </c>
     </row>
     <row r="59">
@@ -4443,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>429</v>
+        <v>622</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>269</v>
+        <v>391</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>269</v>
+        <v>394</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.627039627039627</v>
+        <v>0.6334405144694534</v>
       </c>
     </row>
     <row r="60">
@@ -4490,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>374</v>
+        <v>409</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6256684491978609</v>
+        <v>0.6332518337408313</v>
       </c>
     </row>
     <row r="61">
@@ -4537,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>452</v>
+        <v>429</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="G61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6238938053097345</v>
+        <v>0.6317016317016317</v>
       </c>
     </row>
     <row r="62">
@@ -4584,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>441</v>
+        <v>498</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>273</v>
+        <v>307</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>274</v>
+        <v>311</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6213151927437641</v>
+        <v>0.6244979919678715</v>
       </c>
     </row>
     <row r="63">
@@ -4645,31 +4651,31 @@
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I63" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.6189111747851003</v>
+        <v>0.6239316239316239</v>
       </c>
     </row>
     <row r="64">
@@ -4678,45 +4684,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>498</v>
+        <v>452</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="K64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>307</v>
+        <v>282</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6164658634538153</v>
+        <v>0.6238938053097345</v>
       </c>
     </row>
     <row r="65">
@@ -4725,24 +4731,24 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>428</v>
+        <v>511</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
@@ -4751,19 +4757,19 @@
         <v>0</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>261</v>
+        <v>312</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.6121495327102804</v>
+        <v>0.6144814090019569</v>
       </c>
     </row>
     <row r="66">
@@ -4772,45 +4778,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.6121495327102804</v>
       </c>
     </row>
     <row r="67">
@@ -4819,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>509</v>
+        <v>450</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="K67" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6110019646365422</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="68">
@@ -4927,7 +4933,7 @@
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F69" s="9" t="n">
         <v>161</v>
@@ -4936,7 +4942,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I69" s="9" t="n">
         <v>1</v>
@@ -4948,10 +4954,10 @@
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6077481840193705</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="70">
@@ -4983,16 +4989,16 @@
         <v>44</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
         <v>240</v>
@@ -5007,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>557</v>
+        <v>400</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>332</v>
+        <v>237</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>332</v>
+        <v>240</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.5960502692998204</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="72">
@@ -5068,10 +5074,10 @@
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>1</v>
@@ -5080,19 +5086,19 @@
         <v>0</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>0.5939524838012959</v>
+        <v>0.5991379310344828</v>
       </c>
     </row>
     <row r="73">
@@ -5101,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J73" s="9" t="n">
         <v>224</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M73" s="11" t="n">
-        <v>0.5925</v>
+        <v>0.5984251968503937</v>
       </c>
     </row>
     <row r="74">
@@ -5162,31 +5168,31 @@
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H74" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I74" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="J74" s="9" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="M74" s="11" t="n">
-        <v>0.5918803418803419</v>
+        <v>0.5966029723991507</v>
       </c>
     </row>
     <row r="75">
@@ -5195,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>380</v>
+        <v>557</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>220</v>
+        <v>332</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>224</v>
+        <v>332</v>
       </c>
       <c r="M75" s="11" t="n">
-        <v>0.5894736842105263</v>
+        <v>0.5960502692998204</v>
       </c>
     </row>
     <row r="76">
@@ -5259,28 +5265,28 @@
         <v>426</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="K76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M76" s="11" t="n">
-        <v>0.5892018779342723</v>
+        <v>0.5938967136150235</v>
       </c>
     </row>
     <row r="77">
@@ -5312,13 +5318,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>0</v>
@@ -5359,13 +5365,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I78" s="9" t="n">
         <v>5</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>0</v>
@@ -5383,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>463</v>
+        <v>435</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.5809935205183585</v>
+        <v>0.5839080459770115</v>
       </c>
     </row>
     <row r="80">
@@ -5430,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.5831533477321814</v>
       </c>
     </row>
     <row r="81">
@@ -5477,45 +5483,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>231</v>
+        <v>267</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.5775</v>
+        <v>0.5804347826086956</v>
       </c>
     </row>
     <row r="82">
@@ -5524,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>498</v>
+        <v>400</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>286</v>
+        <v>216</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>286</v>
+        <v>232</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.5742971887550201</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="83">
@@ -5571,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>176</v>
+        <v>204</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H83" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.5720524017467249</v>
+        <v>0.5791583166332666</v>
       </c>
     </row>
     <row r="84">
@@ -5632,31 +5638,31 @@
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.5688622754491018</v>
+        <v>0.5734126984126984</v>
       </c>
     </row>
     <row r="85">
@@ -5665,45 +5671,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>364</v>
+        <v>466</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>207</v>
+        <v>267</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.5686813186813187</v>
+        <v>0.572961373390558</v>
       </c>
     </row>
     <row r="86">
@@ -5712,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>446</v>
+        <v>364</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>252</v>
+        <v>207</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.5672645739910314</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="87">
@@ -5759,45 +5765,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>501</v>
+        <v>440</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.5668662674650699</v>
+        <v>0.5704545454545454</v>
       </c>
     </row>
     <row r="88">
@@ -5806,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H88" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I88" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I88" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="J88" s="9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.5643776824034334</v>
+        <v>0.5680851063829787</v>
       </c>
     </row>
     <row r="89">
@@ -5853,7 +5859,7 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
@@ -5867,31 +5873,31 @@
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>492</v>
+        <v>446</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.5630081300813008</v>
+        <v>0.5672645739910314</v>
       </c>
     </row>
     <row r="90">
@@ -5900,45 +5906,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>470</v>
+        <v>501</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.5595744680851064</v>
+        <v>0.5668662674650699</v>
       </c>
     </row>
     <row r="91">
@@ -5947,45 +5953,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I91" s="9" t="n">
         <v>3</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.5548523206751055</v>
+        <v>0.5650406504065041</v>
       </c>
     </row>
     <row r="92">
@@ -5994,7 +6000,7 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -6008,31 +6014,31 @@
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>407</v>
+        <v>477</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>213</v>
+        <v>264</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.5528255528255528</v>
+        <v>0.559748427672956</v>
       </c>
     </row>
     <row r="93">
@@ -6041,45 +6047,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5536480686695279</v>
       </c>
     </row>
     <row r="94">
@@ -6088,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>544</v>
+        <v>407</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>224</v>
+        <v>174</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>298</v>
+        <v>213</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>299</v>
+        <v>225</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5496323529411765</v>
+        <v>0.5528255528255528</v>
       </c>
     </row>
     <row r="95">
@@ -6135,45 +6141,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>466</v>
+        <v>544</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="G95" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H95" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H95" s="9" t="n">
-        <v>39</v>
-      </c>
       <c r="I95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>216</v>
+        <v>298</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.5493562231759657</v>
+        <v>0.5514705882352942</v>
       </c>
     </row>
     <row r="96">
@@ -6182,45 +6188,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.547945205479452</v>
+        <v>0.5492957746478874</v>
       </c>
     </row>
     <row r="97">
@@ -6229,24 +6235,24 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>399</v>
+        <v>438</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>1</v>
@@ -6255,19 +6261,19 @@
         <v>0</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.547945205479452</v>
       </c>
     </row>
     <row r="98">
@@ -6276,7 +6282,7 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
@@ -6290,13 +6296,13 @@
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>460</v>
+        <v>399</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="9" t="n">
         <v>0</v>
@@ -6305,16 +6311,16 @@
         <v>0</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5413043478260869</v>
+        <v>0.5463659147869674</v>
       </c>
     </row>
     <row r="99">
@@ -6323,7 +6329,7 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
@@ -6337,13 +6343,13 @@
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>412</v>
+        <v>460</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H99" s="9" t="n">
         <v>0</v>
@@ -6352,16 +6358,16 @@
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>222</v>
+        <v>251</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5388349514563107</v>
+        <v>0.5456521739130434</v>
       </c>
     </row>
     <row r="100">
@@ -6370,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>511</v>
+        <v>426</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="G100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>223</v>
+      </c>
+      <c r="K100" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H100" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I100" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J100" s="9" t="n">
-        <v>261</v>
-      </c>
-      <c r="K100" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="L100" s="9" t="n">
-        <v>273</v>
+        <v>230</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.5342465753424658</v>
+        <v>0.539906103286385</v>
       </c>
     </row>
     <row r="101">
@@ -6417,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>454</v>
+        <v>412</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5330396475770925</v>
+        <v>0.5388349514563107</v>
       </c>
     </row>
     <row r="102">
@@ -6464,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>424</v>
+        <v>511</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>198</v>
+        <v>235</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>226</v>
+        <v>269</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5330188679245284</v>
+        <v>0.5362035225048923</v>
       </c>
     </row>
     <row r="103">
@@ -6511,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>426</v>
+        <v>394</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5328638497652582</v>
+        <v>0.5355329949238579</v>
       </c>
     </row>
     <row r="104">
@@ -6558,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="G104" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.5323383084577115</v>
+        <v>0.5353260869565217</v>
       </c>
     </row>
     <row r="105">
@@ -6605,45 +6611,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
         <v>454</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5286343612334802</v>
+        <v>0.5330396475770925</v>
       </c>
     </row>
     <row r="106">
@@ -6652,45 +6658,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="K106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5234042553191489</v>
+        <v>0.5323383084577115</v>
       </c>
     </row>
     <row r="107">
@@ -6699,45 +6705,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>366</v>
+        <v>454</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>187</v>
+        <v>240</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>191</v>
+        <v>240</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5218579234972678</v>
+        <v>0.5286343612334802</v>
       </c>
     </row>
     <row r="108">
@@ -6746,45 +6752,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5205479452054794</v>
+        <v>0.5234042553191489</v>
       </c>
     </row>
     <row r="109">
@@ -6793,7 +6799,7 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
@@ -6807,31 +6813,31 @@
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>498</v>
+        <v>438</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5200803212851406</v>
+        <v>0.5205479452054794</v>
       </c>
     </row>
     <row r="110">
@@ -6854,7 +6860,7 @@
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F110" s="9" t="n">
         <v>201</v>
@@ -6863,10 +6869,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J110" s="9" t="n">
         <v>198</v>
@@ -6875,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5179856115107914</v>
+        <v>0.5202863961813843</v>
       </c>
     </row>
     <row r="111">
@@ -6887,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>323</v>
+        <v>498</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>114</v>
+        <v>239</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>167</v>
+        <v>248</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>167</v>
+        <v>259</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5170278637770898</v>
+        <v>0.5200803212851406</v>
       </c>
     </row>
     <row r="112">
@@ -6948,7 +6954,7 @@
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F112" s="9" t="n">
         <v>200</v>
@@ -6957,7 +6963,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I112" s="9" t="n">
         <v>0</v>
@@ -6969,10 +6975,10 @@
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5169082125603864</v>
+        <v>0.5180722891566265</v>
       </c>
     </row>
     <row r="113">
@@ -6981,45 +6987,45 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>408</v>
+        <v>323</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>198</v>
+        <v>114</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>209</v>
+        <v>167</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5122549019607843</v>
+        <v>0.5170278637770898</v>
       </c>
     </row>
     <row r="114">
@@ -7028,45 +7034,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>389</v>
+        <v>408</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="K114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5038560411311054</v>
+        <v>0.5122549019607843</v>
       </c>
     </row>
     <row r="115">
@@ -7098,13 +7104,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I115" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
@@ -7122,45 +7128,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>346</v>
+        <v>425</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>173</v>
+        <v>212</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>173</v>
+        <v>213</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5</v>
+        <v>0.5011764705882353</v>
       </c>
     </row>
     <row r="117">
@@ -7169,42 +7175,42 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>474</v>
+        <v>404</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>229</v>
+        <v>201</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="M117" s="12" t="n">
         <v>0.5</v>
@@ -7216,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>399</v>
+        <v>474</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H118" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="I118" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>194</v>
+      </c>
+      <c r="K118" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I118" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J118" s="9" t="n">
-        <v>197</v>
-      </c>
-      <c r="K118" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L118" s="9" t="n">
-        <v>199</v>
+        <v>237</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.4987468671679198</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="119">
@@ -7263,45 +7269,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>402</v>
+        <v>346</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="G119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H119" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I119" s="9" t="n">
-        <v>11</v>
-      </c>
       <c r="J119" s="9" t="n">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.4950248756218906</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="120">
@@ -7310,45 +7316,45 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>418</v>
+        <v>505</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="G120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>200</v>
+        <v>247</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>206</v>
+        <v>252</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.4928229665071771</v>
+        <v>0.499009900990099</v>
       </c>
     </row>
     <row r="121">
@@ -7357,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>219</v>
+        <v>191</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.4847058823529412</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="122">
@@ -7404,45 +7410,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>504</v>
+        <v>418</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>260</v>
+        <v>212</v>
       </c>
       <c r="G122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>244</v>
+        <v>206</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.4841269841269841</v>
+        <v>0.4928229665071771</v>
       </c>
     </row>
     <row r="123">
@@ -7451,7 +7457,7 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
@@ -7465,31 +7471,31 @@
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="F123" s="9" t="n">
+        <v>221</v>
+      </c>
+      <c r="G123" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H123" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>202</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="9" t="n">
         <v>213</v>
       </c>
-      <c r="G123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H123" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="I123" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J123" s="9" t="n">
-        <v>178</v>
-      </c>
-      <c r="K123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="9" t="n">
-        <v>200</v>
-      </c>
       <c r="M123" s="12" t="n">
-        <v>0.4830917874396136</v>
+        <v>0.4863013698630138</v>
       </c>
     </row>
     <row r="124">
@@ -7498,45 +7504,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>437</v>
+        <v>414</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.482837528604119</v>
+        <v>0.4830917874396136</v>
       </c>
     </row>
     <row r="125">
@@ -7545,36 +7551,36 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
@@ -7583,7 +7589,7 @@
         <v>211</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.4817351598173516</v>
+        <v>0.482837528604119</v>
       </c>
     </row>
     <row r="126">
@@ -7609,13 +7615,13 @@
         <v>414</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I126" s="9" t="n">
         <v>1</v>
@@ -7627,10 +7633,10 @@
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.4758454106280193</v>
+        <v>0.4806763285024155</v>
       </c>
     </row>
     <row r="127">
@@ -7653,13 +7659,13 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H127" s="9" t="n">
         <v>1</v>
@@ -7668,16 +7674,16 @@
         <v>6</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.465324384787472</v>
+        <v>0.4776785714285715</v>
       </c>
     </row>
     <row r="128">
@@ -7686,45 +7692,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4645308924485125</v>
+        <v>0.4716553287981859</v>
       </c>
     </row>
     <row r="129">
@@ -7733,45 +7739,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>391</v>
+        <v>437</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4629156010230179</v>
+        <v>0.4668192219679634</v>
       </c>
     </row>
     <row r="130">
@@ -7780,45 +7786,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4619164619164619</v>
+        <v>0.4629156010230179</v>
       </c>
     </row>
     <row r="131">
@@ -7827,45 +7833,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>441</v>
+        <v>407</v>
       </c>
       <c r="F131" s="9" t="n">
         <v>219</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>201</v>
+        <v>188</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4557823129251701</v>
+        <v>0.4619164619164619</v>
       </c>
     </row>
     <row r="132">
@@ -7874,7 +7880,7 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
@@ -7888,31 +7894,31 @@
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="K132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4460431654676259</v>
+        <v>0.4506024096385542</v>
       </c>
     </row>
     <row r="133">
@@ -7921,45 +7927,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4422657952069716</v>
+        <v>0.4473684210526316</v>
       </c>
     </row>
     <row r="134">
@@ -7982,31 +7988,31 @@
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G134" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="K134" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.44140625</v>
+        <v>0.4463937621832358</v>
       </c>
     </row>
     <row r="135">
@@ -8035,25 +8041,25 @@
         <v>8</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4397590361445783</v>
+        <v>0.4427710843373494</v>
       </c>
     </row>
     <row r="136">
@@ -8062,45 +8068,45 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>415</v>
+        <v>459</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.436144578313253</v>
+        <v>0.4422657952069716</v>
       </c>
     </row>
   </sheetData>
@@ -8143,7 +8149,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 19 Juli 2026</t>
+          <t>Hari/Tanggal : 20 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8160,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 19.58 WITA</t>
+          <t>Pukul        : 05.55 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8262,31 +8268,31 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2869</v>
+        <v>2872</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2401</v>
+        <v>2426</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2408</v>
+        <v>2433</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.839316835134193</v>
+        <v>0.8471448467966574</v>
       </c>
     </row>
     <row r="8">
@@ -8309,31 +8315,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1496</v>
+        <v>1526</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1510</v>
+        <v>1542</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7449432659102121</v>
+        <v>0.7603550295857988</v>
       </c>
     </row>
     <row r="9">
@@ -8356,31 +8362,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2785</v>
+        <v>2798</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>745</v>
+        <v>709</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2027</v>
+        <v>2073</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2037</v>
+        <v>2084</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7314183123877918</v>
+        <v>0.74481772694782</v>
       </c>
     </row>
     <row r="10">
@@ -8403,31 +8409,31 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2885</v>
+        <v>2887</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2008</v>
+        <v>2037</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2097</v>
+        <v>2124</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7268630849220103</v>
+        <v>0.735711811569103</v>
       </c>
     </row>
     <row r="11">
@@ -8450,31 +8456,31 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2475</v>
+        <v>2482</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>706</v>
+        <v>688</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1736</v>
+        <v>1780</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1737</v>
+        <v>1781</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7018181818181817</v>
+        <v>0.7175664786462531</v>
       </c>
     </row>
     <row r="12">
@@ -8497,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2831</v>
+        <v>2833</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>828</v>
+        <v>812</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1937</v>
+        <v>1985</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>1953</v>
+        <v>2010</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.6898622394913458</v>
+        <v>0.7094952347334982</v>
       </c>
     </row>
     <row r="13">
@@ -8547,28 +8553,28 @@
         <v>2103</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="I13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1337</v>
+        <v>1358</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1339</v>
+        <v>1360</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6367094626723728</v>
+        <v>0.6466951973371374</v>
       </c>
     </row>
     <row r="14">
@@ -8577,45 +8583,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Manganitu, Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Erike, Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2384</v>
+        <v>2758</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>890</v>
+        <v>949</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1447</v>
+        <v>1711</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1464</v>
+        <v>1722</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6140939597315436</v>
+        <v>0.6243654822335025</v>
       </c>
     </row>
     <row r="15">
@@ -8638,31 +8644,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1052</v>
+        <v>1040</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1758</v>
+        <v>1796</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1764</v>
+        <v>1803</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6112266112266113</v>
+        <v>0.6234439834024896</v>
       </c>
     </row>
     <row r="16">
@@ -8671,45 +8677,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu, Tamako</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike, Mega</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2750</v>
+        <v>2385</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>965</v>
+        <v>879</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1666</v>
+        <v>1467</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1674</v>
+        <v>1475</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6087272727272727</v>
+        <v>0.6184486373165619</v>
       </c>
     </row>
     <row r="17">
@@ -8732,31 +8738,31 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1278</v>
+        <v>1321</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1285</v>
+        <v>1326</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.5968416163492801</v>
+        <v>0.6150278293135436</v>
       </c>
     </row>
     <row r="18">
@@ -8765,45 +8771,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2804</v>
+        <v>2878</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1163</v>
+        <v>1099</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1605</v>
+        <v>1697</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1625</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>0.5795292439372325</v>
+        <v>1726</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0.5997220291869354</v>
       </c>
     </row>
     <row r="19">
@@ -8812,45 +8818,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2878</v>
+        <v>2809</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1099</v>
+        <v>1149</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1663</v>
-      </c>
-      <c r="M19" s="12" t="n">
-        <v>0.5778318276580959</v>
+        <v>1652</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>0.5881096475614097</v>
       </c>
     </row>
     <row r="20">
@@ -8873,10 +8879,10 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2659</v>
+        <v>2661</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1166</v>
+        <v>1158</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>25</v>
@@ -8888,16 +8894,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1467</v>
+        <v>1477</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1468</v>
+        <v>1478</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5520872508461828</v>
+        <v>0.5554302893649005</v>
       </c>
     </row>
     <row r="21">
@@ -8923,28 +8929,28 @@
         <v>2694</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1160</v>
+        <v>1152</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1473</v>
+        <v>1476</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5482553823311062</v>
+        <v>0.5489977728285078</v>
       </c>
     </row>
     <row r="22">
@@ -8967,16 +8973,16 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>30</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>11</v>
@@ -8991,7 +8997,7 @@
         <v>1332</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5456780008193364</v>
+        <v>0.5452312730249693</v>
       </c>
     </row>
     <row r="23">
@@ -9014,31 +9020,31 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2299</v>
+        <v>2302</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5424097433666811</v>
+        <v>0.5408340573414422</v>
       </c>
     </row>
     <row r="24">
@@ -9047,45 +9053,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2711</v>
+        <v>1422</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1234</v>
+        <v>406</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>54</v>
+        <v>265</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1389</v>
+        <v>745</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1394</v>
+        <v>747</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5142014016967908</v>
+        <v>0.5253164556962026</v>
       </c>
     </row>
     <row r="25">
@@ -9094,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1420</v>
+        <v>2534</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>410</v>
+        <v>1183</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>266</v>
+        <v>3</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>712</v>
+        <v>1315</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>716</v>
+        <v>1321</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5042253521126761</v>
+        <v>0.521310181531176</v>
       </c>
     </row>
     <row r="26">
@@ -9141,45 +9147,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2528</v>
+        <v>2711</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1193</v>
+        <v>1230</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1262</v>
+        <v>1389</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1268</v>
+        <v>1394</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5015822784810127</v>
+        <v>0.5142014016967908</v>
       </c>
     </row>
     <row r="27">
@@ -9188,7 +9194,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Olfira Sicilia Budiman</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -9202,31 +9208,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2076</v>
+        <v>2063</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1007</v>
+        <v>1022</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>943</v>
+        <v>987</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.4845857418111754</v>
+        <v>0.4910324769752787</v>
       </c>
     </row>
     <row r="28">
@@ -9235,7 +9241,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Olfira Sicilia Budiman</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -9249,31 +9255,31 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2061</v>
+        <v>2081</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1024</v>
+        <v>1007</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>953</v>
+        <v>958</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>975</v>
+        <v>1014</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.4730713245997089</v>
+        <v>0.4872657376261413</v>
       </c>
     </row>
     <row r="29">
@@ -9296,31 +9302,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1115</v>
+        <v>1104</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1087</v>
+        <v>1133</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1118</v>
+        <v>1169</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.4646716541978387</v>
+        <v>0.4856668051516411</v>
       </c>
     </row>
   </sheetData>
@@ -9354,7 +9360,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 19 Juli 2026</t>
+          <t>Hari/Tanggal : 20 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9371,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 19.58 WITA</t>
+          <t>Pukul        : 05.55 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9418,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.7670995670995669</v>
+        <v>0.7757575757575758</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9436,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7447751741608613</v>
+        <v>0.7578051087984864</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9454,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7291666666666665</v>
+        <v>0.7347853939782191</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9472,7 +9478,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7079903147699756</v>
+        <v>0.7104817235536189</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9490,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.6980332500271651</v>
+        <v>0.7058632274845561</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9544,7 +9550,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.6102292768959435</v>
+        <v>0.6165347405452947</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -9561,8 +9567,8 @@
           <t>Kendahe</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
-        <v>0.5841654778887304</v>
+      <c r="C15" s="11" t="n">
+        <v>0.5898896404414382</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9580,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.5762024338419934</v>
+        <v>0.5789575289575289</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9598,7 +9604,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5461270670147955</v>
+        <v>0.5510425716768028</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -9616,7 +9622,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.545375650880238</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9630,15 +9636,15 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5261845386533666</v>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5300582847626978</v>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9648,15 +9654,15 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5255961313990328</v>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.52970502700457</v>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9676,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.523943661971831</v>
+        <v>0.5281293952180028</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -616,32 +616,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 05.55 WITA</t>
+          <t>Pukul        : 20.34 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-35):</t>
+          <t>Target Hari Ini (H-36):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>58.45%</t>
+          <t>60.12%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 58.45%</t>
+          <t>Hijau &gt;= 60.12%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 29.22% - 58.45%</t>
+          <t>Kuning 30.06% - 60.12%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 29.22%</t>
+          <t>Merah &lt; 30.06%</t>
         </is>
       </c>
     </row>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4131</v>
+        <v>4134</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1162</v>
+        <v>1149</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
@@ -770,21 +770,21 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -798,14 +798,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2935</v>
+        <v>2951</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -819,27 +819,27 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1422</v>
+        <v>1429</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>406</v>
+        <v>368</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -867,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>751</v>
+        <v>767</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -888,41 +888,41 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6244</v>
+        <v>6266</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1583</v>
+        <v>1511</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4413</v>
+        <v>4442</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -936,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4588</v>
+        <v>4651</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3171</v>
+        <v>3172</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,21 +977,21 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2380</v>
+        <v>2379</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -1005,14 +1005,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2403</v>
+        <v>2411</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1026,27 +1026,27 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1060,7 +1060,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1074,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1095,34 +1095,34 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
         <v/>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10">
         <f>F12/B12</f>
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
@@ -1143,14 +1143,14 @@
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="Q12" s="11">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1164,13 +1164,13 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4604</v>
+        <v>4615</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2034</v>
+        <v>2023</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
@@ -1184,21 +1184,21 @@
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2329</v>
+        <v>2341</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1212,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2537</v>
+        <v>2559</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,62 +1233,62 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6005</v>
+        <v>6015</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2798</v>
+        <v>2779</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3021</v>
+        <v>3041</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
         <v/>
       </c>
       <c r="N14" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="10">
         <f>N14/B14</f>
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3183</v>
+        <v>3207</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8066</v>
+        <v>8069</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3540</v>
+        <v>3529</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
@@ -1322,7 +1322,7 @@
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
@@ -1336,7 +1336,7 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4342</v>
+        <v>4359</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1350,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4399</v>
+        <v>4413</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,41 +1371,41 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5180</v>
+        <v>5190</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2067</v>
+        <v>2059</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2918</v>
+        <v>2932</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1419,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>2999</v>
+        <v>3003</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,62 +1440,62 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2407</v>
+        <v>2410</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1104</v>
+        <v>1095</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1133</v>
+        <v>1179</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1275</v>
+        <v>1285</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9227</v>
+        <v>9265</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2628</v>
+        <v>2563</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6435</v>
+        <v>6539</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6513</v>
+        <v>6611</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,21 +1598,21 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
         <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" s="10">
         <f>J19/B19</f>
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1626,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1647,20 +1647,20 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>8</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E20" s="10">
         <f>D20/B20</f>
         <v/>
       </c>
       <c r="F20" s="9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G20" s="10">
         <f>F20/B20</f>
@@ -1766,12 +1766,12 @@
       <c r="P21" s="9" t="n">
         <v>1657</v>
       </c>
-      <c r="Q21" s="11">
+      <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1917,17 +1917,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 05.55 WITA</t>
+          <t>Pukul        : 20.34 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-35):</t>
+          <t>Target Hari Ini (H-36):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>58.45%</t>
+          <t>60.12%</t>
         </is>
       </c>
     </row>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>1</v>
@@ -2081,16 +2081,16 @@
         <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.9568345323741008</v>
+        <v>0.964200477326969</v>
       </c>
     </row>
     <row r="9">
@@ -2113,16 +2113,16 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.9402173913043478</v>
+        <v>0.9551971326164874</v>
       </c>
     </row>
     <row r="10">
@@ -2146,45 +2146,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Ayu Lestari Areros</t>
+          <t>Merry Christiani Lano</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>308</v>
+        <v>520</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>279</v>
+        <v>462</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>281</v>
+        <v>480</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.9123376623376623</v>
+        <v>0.923076923076923</v>
       </c>
     </row>
     <row r="11">
@@ -2193,45 +2193,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Merry Christiani Lano</t>
+          <t>Ayu Lestari Areros</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>516</v>
+        <v>309</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>443</v>
+        <v>279</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>458</v>
+        <v>283</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.8875968992248062</v>
+        <v>0.9158576051779935</v>
       </c>
     </row>
     <row r="12">
@@ -2257,28 +2257,28 @@
         <v>364</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8763736263736264</v>
+        <v>0.8818681318681318</v>
       </c>
     </row>
     <row r="13">
@@ -2313,10 +2313,10 @@
         <v>5</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
@@ -2445,19 +2445,19 @@
         <v>426</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H16" s="9" t="n">
         <v>38</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
@@ -2475,45 +2475,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8110831234256927</v>
+        <v>0.8131578947368421</v>
       </c>
     </row>
     <row r="18">
@@ -2522,24 +2522,24 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>488</v>
+        <v>397</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
@@ -2548,19 +2548,19 @@
         <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>392</v>
+        <v>320</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>392</v>
+        <v>322</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8032786885245902</v>
+        <v>0.8110831234256927</v>
       </c>
     </row>
     <row r="19">
@@ -2569,45 +2569,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>421</v>
+        <v>477</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>324</v>
+        <v>377</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>335</v>
+        <v>385</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.7957244655581949</v>
+        <v>0.8071278825995808</v>
       </c>
     </row>
     <row r="20">
@@ -2616,24 +2616,24 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
@@ -2645,16 +2645,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.8032786885245902</v>
       </c>
     </row>
     <row r="21">
@@ -2663,45 +2663,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.7931873479318735</v>
+        <v>0.7957244655581949</v>
       </c>
     </row>
     <row r="22">
@@ -2710,45 +2710,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.7898936170212765</v>
+        <v>0.7931873479318735</v>
       </c>
     </row>
     <row r="23">
@@ -2804,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>495</v>
+        <v>530</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>384</v>
+        <v>413</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>384</v>
+        <v>416</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.7757575757575758</v>
+        <v>0.7849056603773586</v>
       </c>
     </row>
     <row r="25">
@@ -2851,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>430</v>
+        <v>495</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>325</v>
+        <v>387</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>333</v>
+        <v>387</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7744186046511627</v>
+        <v>0.7818181818181819</v>
       </c>
     </row>
     <row r="26">
@@ -2898,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>300</v>
+        <v>333</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.7731958762886599</v>
+        <v>0.7744186046511627</v>
       </c>
     </row>
     <row r="27">
@@ -2945,45 +2945,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>524</v>
+        <v>388</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>391</v>
+        <v>297</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>403</v>
+        <v>300</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7690839694656488</v>
+        <v>0.7731958762886599</v>
       </c>
     </row>
     <row r="28">
@@ -2992,45 +2992,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>484</v>
+        <v>384</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>321</v>
+        <v>280</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>359</v>
+        <v>296</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.7417355371900827</v>
+        <v>0.7708333333333335</v>
       </c>
     </row>
     <row r="29">
@@ -3039,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>417</v>
+        <v>485</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>308</v>
+        <v>362</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7386091127098321</v>
+        <v>0.7463917525773196</v>
       </c>
     </row>
     <row r="30">
@@ -3086,45 +3086,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>382</v>
+        <v>417</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7356020942408377</v>
+        <v>0.7386091127098321</v>
       </c>
     </row>
     <row r="31">
@@ -3133,45 +3133,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>414</v>
+        <v>556</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>301</v>
+        <v>398</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7294685990338166</v>
+        <v>0.7302158273381295</v>
       </c>
     </row>
     <row r="32">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
@@ -3206,19 +3206,19 @@
         <v>0</v>
       </c>
       <c r="I32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>301</v>
+      </c>
+      <c r="K32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="9" t="n">
-        <v>306</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" s="9" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7274881516587678</v>
+        <v>0.7294685990338166</v>
       </c>
     </row>
     <row r="33">
@@ -3241,31 +3241,31 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7248995983935742</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="34">
@@ -3274,45 +3274,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>552</v>
+        <v>422</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J34" s="9" t="n">
-        <v>398</v>
+        <v>306</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>399</v>
+        <v>307</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7228260869565217</v>
+        <v>0.7274881516587678</v>
       </c>
     </row>
     <row r="35">
@@ -3321,45 +3321,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>535</v>
+        <v>402</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>384</v>
+        <v>287</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>384</v>
+        <v>290</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7177570093457943</v>
+        <v>0.7213930348258707</v>
       </c>
     </row>
     <row r="36">
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F36" s="9" t="n">
         <v>136</v>
@@ -3391,7 +3391,7 @@
         <v>5</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I36" s="9" t="n">
         <v>4</v>
@@ -3403,10 +3403,10 @@
         <v>1</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.717434869739479</v>
+        <v>0.718562874251497</v>
       </c>
     </row>
     <row r="37">
@@ -3415,24 +3415,24 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>402</v>
+        <v>536</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
@@ -3444,16 +3444,16 @@
         <v>0</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>287</v>
+        <v>385</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>287</v>
+        <v>385</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7139303482587064</v>
+        <v>0.7182835820895522</v>
       </c>
     </row>
     <row r="38">
@@ -3476,31 +3476,31 @@
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I38" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7111984282907662</v>
+        <v>0.7109375</v>
       </c>
     </row>
     <row r="39">
@@ -3532,13 +3532,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>1</v>
@@ -3570,16 +3570,16 @@
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I40" s="9" t="n">
         <v>0</v>
@@ -3591,10 +3591,10 @@
         <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.697986577181208</v>
+        <v>0.7044444444444444</v>
       </c>
     </row>
     <row r="41">
@@ -3603,45 +3603,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.6858513189448441</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="42">
@@ -3650,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="9" t="n">
-        <v>42</v>
-      </c>
       <c r="I42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>288</v>
+      </c>
+      <c r="K42" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="9" t="n">
-        <v>223</v>
-      </c>
-      <c r="K42" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" s="9" t="n">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.6838046272493572</v>
+        <v>0.6954436450839329</v>
       </c>
     </row>
     <row r="43">
@@ -3711,16 +3711,16 @@
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I43" s="9" t="n">
         <v>0</v>
@@ -3732,10 +3732,10 @@
         <v>1</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.6826347305389223</v>
+        <v>0.6904761904761905</v>
       </c>
     </row>
     <row r="44">
@@ -3744,45 +3744,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>527</v>
+        <v>503</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.6858846918489065</v>
       </c>
     </row>
     <row r="45">
@@ -3791,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="I45" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.6764705882352942</v>
+        <v>0.6838046272493572</v>
       </c>
     </row>
     <row r="46">
@@ -3838,45 +3838,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>499</v>
+        <v>527</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="G46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H46" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="I46" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>337</v>
+        <v>357</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.6753507014028056</v>
+        <v>0.6774193548387096</v>
       </c>
     </row>
     <row r="47">
@@ -3902,7 +3902,7 @@
         <v>289</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
@@ -3914,16 +3914,16 @@
         <v>1</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.6678200692041523</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="48">
@@ -3932,45 +3932,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.6711956521739131</v>
       </c>
     </row>
     <row r="49">
@@ -3979,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>459</v>
+        <v>345</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>303</v>
+        <v>230</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>303</v>
+        <v>231</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6601307189542482</v>
+        <v>0.6695652173913044</v>
       </c>
     </row>
     <row r="50">
@@ -4026,45 +4026,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>367</v>
+        <v>455</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>241</v>
+        <v>303</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6566757493188011</v>
+        <v>0.6659340659340658</v>
       </c>
     </row>
     <row r="51">
@@ -4073,45 +4073,45 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>452</v>
+        <v>515</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>294</v>
+        <v>340</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>295</v>
+        <v>342</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.652654867256637</v>
+        <v>0.6640776699029126</v>
       </c>
     </row>
     <row r="52">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -4134,31 +4134,31 @@
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>424</v>
+        <v>460</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>254</v>
+        <v>304</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6462264150943396</v>
+        <v>0.6608695652173913</v>
       </c>
     </row>
     <row r="53">
@@ -4181,16 +4181,16 @@
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I53" s="9" t="n">
         <v>2</v>
@@ -4202,10 +4202,10 @@
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6426966292134831</v>
+        <v>0.6547085201793722</v>
       </c>
     </row>
     <row r="54">
@@ -4214,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>158</v>
+        <v>98</v>
       </c>
       <c r="G54" s="9" t="n">
+        <v>59</v>
+      </c>
+      <c r="H54" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H54" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="I54" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6426966292134831</v>
+        <v>0.6534216335540839</v>
       </c>
     </row>
     <row r="55">
@@ -4261,45 +4261,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6413793103448274</v>
+        <v>0.6533018867924528</v>
       </c>
     </row>
     <row r="56">
@@ -4308,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>514</v>
+        <v>411</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>317</v>
+        <v>217</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>329</v>
+        <v>266</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6400778210116731</v>
+        <v>0.6472019464720195</v>
       </c>
     </row>
     <row r="57">
@@ -4375,25 +4375,25 @@
         <v>163</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.6379310344827587</v>
+        <v>0.646551724137931</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>374</v>
+        <v>447</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H58" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J58" s="9" t="n">
-        <v>235</v>
+        <v>284</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>237</v>
+        <v>287</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6336898395721925</v>
+        <v>0.6420581655480985</v>
       </c>
     </row>
     <row r="59">
@@ -4449,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>622</v>
+        <v>435</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>223</v>
+        <v>129</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>391</v>
+        <v>278</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>394</v>
+        <v>279</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6334405144694534</v>
+        <v>0.6413793103448274</v>
       </c>
     </row>
     <row r="60">
@@ -4496,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>409</v>
+        <v>376</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6332518337408313</v>
+        <v>0.6409574468085107</v>
       </c>
     </row>
     <row r="61">
@@ -4543,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>271</v>
+        <v>238</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>271</v>
+        <v>257</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6317016317016317</v>
+        <v>0.6361386138613861</v>
       </c>
     </row>
     <row r="62">
@@ -4590,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>498</v>
+        <v>622</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>307</v>
+        <v>391</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>311</v>
+        <v>394</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6244979919678715</v>
+        <v>0.6334405144694534</v>
       </c>
     </row>
     <row r="63">
@@ -4637,45 +4637,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>351</v>
+        <v>429</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>214</v>
+        <v>271</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.6239316239316239</v>
+        <v>0.6317016317016317</v>
       </c>
     </row>
     <row r="64">
@@ -4684,45 +4684,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>452</v>
+        <v>498</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>275</v>
+        <v>311</v>
       </c>
       <c r="K64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>282</v>
+        <v>312</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6238938053097345</v>
+        <v>0.6265060240963856</v>
       </c>
     </row>
     <row r="65">
@@ -4731,45 +4731,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>511</v>
+        <v>453</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>312</v>
+        <v>274</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.6144814090019569</v>
+        <v>0.6247240618101545</v>
       </c>
     </row>
     <row r="66">
@@ -4778,45 +4778,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>428</v>
+        <v>351</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6121495327102804</v>
+        <v>0.6239316239316239</v>
       </c>
     </row>
     <row r="67">
@@ -4825,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.618</v>
       </c>
     </row>
     <row r="68">
@@ -4872,45 +4872,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>280</v>
+        <v>308</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.61</v>
+        <v>0.6179337231968811</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>261</v>
+      </c>
+      <c r="K69" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H69" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="9" t="n">
-        <v>245</v>
-      </c>
-      <c r="K69" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L69" s="9" t="n">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6121495327102804</v>
       </c>
     </row>
     <row r="70">
@@ -4966,45 +4966,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>115</v>
+        <v>161</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.6015037593984962</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="71">
@@ -5013,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>400</v>
+        <v>467</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>237</v>
+        <v>280</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>240</v>
+        <v>281</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.6</v>
+        <v>0.6017130620985011</v>
       </c>
     </row>
     <row r="72">
@@ -5060,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I72" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>261</v>
+      </c>
+      <c r="K72" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J72" s="9" t="n">
-        <v>277</v>
-      </c>
-      <c r="K72" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L72" s="9" t="n">
-        <v>278</v>
-      </c>
-      <c r="M72" s="11" t="n">
-        <v>0.5991379310344828</v>
+        <v>281</v>
+      </c>
+      <c r="M72" s="12" t="n">
+        <v>0.6004273504273504</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>381</v>
+        <v>558</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>153</v>
+        <v>199</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>224</v>
+        <v>335</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>228</v>
-      </c>
-      <c r="M73" s="11" t="n">
-        <v>0.5984251968503937</v>
+        <v>335</v>
+      </c>
+      <c r="M73" s="12" t="n">
+        <v>0.600358422939068</v>
       </c>
     </row>
     <row r="74">
@@ -5154,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>471</v>
+        <v>400</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I74" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>281</v>
-      </c>
-      <c r="M74" s="11" t="n">
-        <v>0.5966029723991507</v>
+        <v>240</v>
+      </c>
+      <c r="M74" s="12" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="75">
@@ -5201,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>557</v>
+        <v>360</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>201</v>
+        <v>144</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>332</v>
+        <v>210</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>332</v>
-      </c>
-      <c r="M75" s="11" t="n">
-        <v>0.5960502692998204</v>
+        <v>216</v>
+      </c>
+      <c r="M75" s="12" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="76">
@@ -5248,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H76" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I76" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="K76" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I76" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="9" t="n">
-        <v>252</v>
-      </c>
-      <c r="K76" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L76" s="9" t="n">
-        <v>253</v>
-      </c>
-      <c r="M76" s="11" t="n">
-        <v>0.5938967136150235</v>
+        <v>263</v>
+      </c>
+      <c r="M76" s="12" t="n">
+        <v>0.5990888382687927</v>
       </c>
     </row>
     <row r="77">
@@ -5295,45 +5295,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>212</v>
-      </c>
-      <c r="M77" s="11" t="n">
-        <v>0.5872576177285319</v>
+        <v>228</v>
+      </c>
+      <c r="M77" s="12" t="n">
+        <v>0.5984251968503937</v>
       </c>
     </row>
     <row r="78">
@@ -5342,45 +5342,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>533</v>
+        <v>475</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>313</v>
-      </c>
-      <c r="M78" s="11" t="n">
-        <v>0.5872420262664165</v>
+        <v>283</v>
+      </c>
+      <c r="M78" s="12" t="n">
+        <v>0.5957894736842105</v>
       </c>
     </row>
     <row r="79">
@@ -5389,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.5839080459770115</v>
+        <v>0.5942028985507246</v>
       </c>
     </row>
     <row r="80">
@@ -5436,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.5831533477321814</v>
+        <v>0.5938967136150235</v>
       </c>
     </row>
     <row r="81">
@@ -5483,45 +5483,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.5804347826086956</v>
+        <v>0.5913978494623656</v>
       </c>
     </row>
     <row r="82">
@@ -5530,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>400</v>
+        <v>533</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>216</v>
+        <v>308</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>232</v>
+        <v>315</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.58</v>
+        <v>0.5909943714821764</v>
       </c>
     </row>
     <row r="83">
@@ -5577,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.5791583166332666</v>
+        <v>0.5856573705179283</v>
       </c>
     </row>
     <row r="84">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
@@ -5641,28 +5641,28 @@
         <v>504</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.5734126984126984</v>
+        <v>0.5853174603174603</v>
       </c>
     </row>
     <row r="85">
@@ -5671,45 +5671,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>466</v>
+        <v>511</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.572961373390558</v>
+        <v>0.5831702544031311</v>
       </c>
     </row>
     <row r="86">
@@ -5718,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>364</v>
+        <v>462</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H86" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I86" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I86" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J86" s="9" t="n">
-        <v>207</v>
+        <v>260</v>
       </c>
       <c r="K86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>208</v>
+        <v>269</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5822510822510822</v>
       </c>
     </row>
     <row r="87">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
@@ -5779,31 +5779,31 @@
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>440</v>
+        <v>400</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.5704545454545454</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="88">
@@ -5812,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.5680851063829787</v>
+        <v>0.5727272727272728</v>
       </c>
     </row>
     <row r="89">
@@ -5859,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>446</v>
+        <v>364</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>252</v>
+        <v>207</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.5672645739910314</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="90">
@@ -5906,45 +5906,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>501</v>
+        <v>475</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H90" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I90" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.5668662674650699</v>
+        <v>0.5705263157894737</v>
       </c>
     </row>
     <row r="91">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -5967,31 +5967,31 @@
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.5650406504065041</v>
+        <v>0.5680851063829787</v>
       </c>
     </row>
     <row r="92">
@@ -6000,45 +6000,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>477</v>
+        <v>446</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="H92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.559748427672956</v>
+        <v>0.5672645739910314</v>
       </c>
     </row>
     <row r="93">
@@ -6047,45 +6047,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>216</v>
+        <v>269</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.5536480686695279</v>
+        <v>0.565922920892495</v>
       </c>
     </row>
     <row r="94">
@@ -6094,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>407</v>
+        <v>546</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>174</v>
+        <v>219</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>213</v>
+        <v>306</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>225</v>
+        <v>307</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5528255528255528</v>
+        <v>0.5622710622710623</v>
       </c>
     </row>
     <row r="95">
@@ -6141,45 +6141,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>544</v>
+        <v>466</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>298</v>
+        <v>237</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.5514705882352942</v>
+        <v>0.5536480686695279</v>
       </c>
     </row>
     <row r="96">
@@ -6202,16 +6202,16 @@
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I96" s="9" t="n">
         <v>0</v>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5492957746478874</v>
+        <v>0.5526932084309133</v>
       </c>
     </row>
     <row r="97">
@@ -6249,31 +6249,31 @@
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.547945205479452</v>
+        <v>0.55125284738041</v>
       </c>
     </row>
     <row r="98">
@@ -6282,36 +6282,36 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
@@ -6320,7 +6320,7 @@
         <v>218</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.5505050505050505</v>
       </c>
     </row>
     <row r="99">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
@@ -6343,13 +6343,13 @@
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>460</v>
+        <v>399</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="9" t="n">
         <v>0</v>
@@ -6358,16 +6358,16 @@
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5456521739130434</v>
+        <v>0.5463659147869674</v>
       </c>
     </row>
     <row r="100">
@@ -6376,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>426</v>
+        <v>460</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.539906103286385</v>
+        <v>0.5456521739130434</v>
       </c>
     </row>
     <row r="101">
@@ -6423,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5388349514563107</v>
+        <v>0.539906103286385</v>
       </c>
     </row>
     <row r="102">
@@ -6470,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>511</v>
+        <v>412</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>221</v>
+      </c>
+      <c r="K102" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I102" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="9" t="n">
-        <v>269</v>
-      </c>
-      <c r="K102" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="L102" s="9" t="n">
-        <v>274</v>
+        <v>222</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5362035225048923</v>
+        <v>0.5388349514563107</v>
       </c>
     </row>
     <row r="103">
@@ -6517,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>394</v>
+        <v>325</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>180</v>
+        <v>79</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="K103" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>211</v>
+        <v>175</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5355329949238579</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="104">
@@ -6564,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>368</v>
+        <v>455</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="G104" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H104" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H104" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="I104" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>197</v>
+        <v>244</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.5353260869565217</v>
+        <v>0.5362637362637362</v>
       </c>
     </row>
     <row r="105">
@@ -6611,45 +6611,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>454</v>
+        <v>511</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>216</v>
+        <v>264</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>242</v>
+        <v>274</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5330396475770925</v>
+        <v>0.5362035225048923</v>
       </c>
     </row>
     <row r="106">
@@ -6658,45 +6658,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>402</v>
+        <v>368</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5323383084577115</v>
+        <v>0.5353260869565217</v>
       </c>
     </row>
     <row r="107">
@@ -6722,16 +6722,16 @@
         <v>454</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107" s="9" t="n">
         <v>240</v>
@@ -6740,10 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5286343612334802</v>
+        <v>0.5352422907488987</v>
       </c>
     </row>
     <row r="108">
@@ -6752,45 +6752,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>470</v>
+        <v>402</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="K108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5234042553191489</v>
+        <v>0.5323383084577115</v>
       </c>
     </row>
     <row r="109">
@@ -6799,45 +6799,45 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5205479452054794</v>
+        <v>0.5264423076923077</v>
       </c>
     </row>
     <row r="110">
@@ -6860,31 +6860,31 @@
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5202863961813843</v>
+        <v>0.5238095238095238</v>
       </c>
     </row>
     <row r="111">
@@ -6893,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>498</v>
+        <v>471</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5200803212851406</v>
+        <v>0.5222929936305732</v>
       </c>
     </row>
     <row r="112">
@@ -6940,45 +6940,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>415</v>
+        <v>498</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>200</v>
+        <v>238</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5180722891566265</v>
+        <v>0.5220883534136547</v>
       </c>
     </row>
     <row r="113">
@@ -6987,27 +6987,27 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D113" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>323</v>
+        <v>438</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>114</v>
+        <v>210</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H113" s="9" t="n">
         <v>0</v>
@@ -7016,16 +7016,16 @@
         <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>167</v>
+        <v>227</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>167</v>
+        <v>228</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5170278637770898</v>
+        <v>0.5205479452054794</v>
       </c>
     </row>
     <row r="114">
@@ -7081,45 +7081,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>450</v>
+        <v>508</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="G115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I115" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>253</v>
+      </c>
+      <c r="K115" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J115" s="9" t="n">
-        <v>225</v>
-      </c>
-      <c r="K115" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L115" s="9" t="n">
-        <v>226</v>
+        <v>260</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5022222222222222</v>
+        <v>0.5118110236220472</v>
       </c>
     </row>
     <row r="116">
@@ -7128,24 +7128,24 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>0</v>
@@ -7157,16 +7157,16 @@
         <v>0</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5011764705882353</v>
+        <v>0.5088105726872246</v>
       </c>
     </row>
     <row r="117">
@@ -7175,45 +7175,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5</v>
+        <v>0.5011764705882353</v>
       </c>
     </row>
     <row r="118">
@@ -7236,16 +7236,16 @@
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F118" s="9" t="n">
         <v>229</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I118" s="9" t="n">
         <v>15</v>
@@ -7257,7 +7257,7 @@
         <v>1</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M118" s="12" t="n">
         <v>0.5</v>
@@ -7269,42 +7269,42 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>346</v>
+        <v>404</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>173</v>
+        <v>201</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>173</v>
+        <v>202</v>
       </c>
       <c r="M119" s="12" t="n">
         <v>0.5</v>
@@ -7316,45 +7316,45 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>505</v>
+        <v>346</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>253</v>
+        <v>173</v>
       </c>
       <c r="G120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I120" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>247</v>
+        <v>172</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>252</v>
+        <v>173</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.499009900990099</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="121">
@@ -7471,31 +7471,31 @@
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F123" s="9" t="n">
         <v>221</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I123" s="9" t="n">
         <v>10</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.4863013698630138</v>
+        <v>0.4920273348519363</v>
       </c>
     </row>
     <row r="124">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
@@ -7518,31 +7518,31 @@
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>414</v>
+        <v>450</v>
       </c>
       <c r="F124" s="9" t="n">
+        <v>229</v>
+      </c>
+      <c r="G124" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H124" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J124" s="9" t="n">
         <v>213</v>
       </c>
-      <c r="G124" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" s="9" t="n">
-        <v>200</v>
-      </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.4830917874396136</v>
+        <v>0.4866666666666667</v>
       </c>
     </row>
     <row r="125">
@@ -7565,7 +7565,7 @@
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F125" s="9" t="n">
         <v>226</v>
@@ -7574,22 +7574,22 @@
         <v>0</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.482837528604119</v>
+        <v>0.4840182648401827</v>
       </c>
     </row>
     <row r="126">
@@ -7598,45 +7598,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
         <v>414</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.4806763285024155</v>
+        <v>0.4830917874396136</v>
       </c>
     </row>
     <row r="127">
@@ -7645,45 +7645,45 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>448</v>
+        <v>414</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H127" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="I127" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I127" s="9" t="n">
-        <v>6</v>
-      </c>
       <c r="J127" s="9" t="n">
-        <v>207</v>
+        <v>147</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.4776785714285715</v>
+        <v>0.4806763285024155</v>
       </c>
     </row>
     <row r="128">
@@ -7709,13 +7709,13 @@
         <v>441</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I128" s="9" t="n">
         <v>0</v>
@@ -7727,10 +7727,10 @@
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4716553287981859</v>
+        <v>0.4784580498866213</v>
       </c>
     </row>
     <row r="129">
@@ -7753,31 +7753,31 @@
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4668192219679634</v>
+        <v>0.4660633484162895</v>
       </c>
     </row>
     <row r="130">
@@ -7786,45 +7786,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4629156010230179</v>
+        <v>0.4643734643734644</v>
       </c>
     </row>
     <row r="131">
@@ -7833,45 +7833,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4619164619164619</v>
+        <v>0.4629156010230179</v>
       </c>
     </row>
     <row r="132">
@@ -7880,45 +7880,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>415</v>
+        <v>513</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>216</v>
+        <v>272</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>149</v>
+        <v>215</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>187</v>
+        <v>236</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4506024096385542</v>
+        <v>0.4600389863547758</v>
       </c>
     </row>
     <row r="133">
@@ -7927,7 +7927,7 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
@@ -7941,31 +7941,31 @@
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.4556354916067146</v>
       </c>
     </row>
     <row r="134">
@@ -7974,45 +7974,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>513</v>
+        <v>420</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>279</v>
+        <v>228</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>202</v>
+        <v>159</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>229</v>
+        <v>190</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.4463937621832358</v>
+        <v>0.4523809523809524</v>
       </c>
     </row>
     <row r="135">
@@ -8021,45 +8021,45 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>332</v>
+        <v>459</v>
       </c>
       <c r="F135" s="9" t="n">
+        <v>227</v>
+      </c>
+      <c r="G135" s="9" t="n">
+        <v>27</v>
+      </c>
+      <c r="H135" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="G135" s="9" t="n">
-        <v>177</v>
-      </c>
-      <c r="H135" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="I135" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>147</v>
+        <v>205</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4427710843373494</v>
+        <v>0.4466230936819172</v>
       </c>
     </row>
     <row r="136">
@@ -8068,45 +8068,45 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>459</v>
+        <v>332</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>227</v>
+        <v>8</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>29</v>
+        <v>177</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>203</v>
+        <v>147</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4422657952069716</v>
+        <v>0.4427710843373494</v>
       </c>
     </row>
   </sheetData>
@@ -8166,17 +8166,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 05.55 WITA</t>
+          <t>Pukul        : 20.34 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-35):</t>
+          <t>Target Hari Ini (H-36):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>58.45%</t>
+          <t>60.12%</t>
         </is>
       </c>
     </row>
@@ -8268,31 +8268,31 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2872</v>
+        <v>2881</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8471448467966574</v>
+        <v>0.8448455397431447</v>
       </c>
     </row>
     <row r="8">
@@ -8315,31 +8315,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>27</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7603550295857988</v>
+        <v>0.7597242737567701</v>
       </c>
     </row>
     <row r="9">
@@ -8362,31 +8362,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2798</v>
+        <v>2799</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.74481772694782</v>
+        <v>0.7438370846730975</v>
       </c>
     </row>
     <row r="10">
@@ -8409,22 +8409,22 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2887</v>
+        <v>2898</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>661</v>
+        <v>612</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
@@ -8433,7 +8433,7 @@
         <v>2124</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.735711811569103</v>
+        <v>0.7329192546583851</v>
       </c>
     </row>
     <row r="11">
@@ -8456,31 +8456,31 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2482</v>
+        <v>2496</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1780</v>
+        <v>1791</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1781</v>
+        <v>1791</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7175664786462531</v>
+        <v>0.717548076923077</v>
       </c>
     </row>
     <row r="12">
@@ -8503,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2833</v>
+        <v>2838</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>812</v>
+        <v>793</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1985</v>
+        <v>1994</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7094952347334982</v>
+        <v>0.7068357998590556</v>
       </c>
     </row>
     <row r="13">
@@ -8536,45 +8536,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2103</v>
+        <v>2767</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>704</v>
+        <v>928</v>
       </c>
       <c r="G13" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H13" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="J13" s="9" t="n">
-        <v>1358</v>
+        <v>1780</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1360</v>
+        <v>1791</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6466951973371374</v>
+        <v>0.6472714130827611</v>
       </c>
     </row>
     <row r="14">
@@ -8583,45 +8583,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2758</v>
+        <v>2103</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>949</v>
+        <v>704</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1711</v>
+        <v>1358</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1722</v>
+        <v>1360</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6243654822335025</v>
+        <v>0.6466951973371374</v>
       </c>
     </row>
     <row r="15">
@@ -8644,31 +8644,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2892</v>
+        <v>2902</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1040</v>
+        <v>1014</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1796</v>
+        <v>1823</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1803</v>
+        <v>1831</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6234439834024896</v>
+        <v>0.6309441764300483</v>
       </c>
     </row>
     <row r="16">
@@ -8691,31 +8691,31 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2385</v>
+        <v>2395</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>7</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1467</v>
+        <v>1502</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1475</v>
+        <v>1509</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6184486373165619</v>
+        <v>0.630062630480167</v>
       </c>
     </row>
     <row r="17">
@@ -8738,31 +8738,31 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2156</v>
+        <v>2164</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1321</v>
+        <v>1325</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.6150278293135436</v>
+        <v>0.6141404805914972</v>
       </c>
     </row>
     <row r="18">
@@ -8808,7 +8808,7 @@
       <c r="L18" s="9" t="n">
         <v>1726</v>
       </c>
-      <c r="M18" s="11" t="n">
+      <c r="M18" s="12" t="n">
         <v>0.5997220291869354</v>
       </c>
     </row>
@@ -8855,7 +8855,7 @@
       <c r="L19" s="9" t="n">
         <v>1652</v>
       </c>
-      <c r="M19" s="11" t="n">
+      <c r="M19" s="12" t="n">
         <v>0.5881096475614097</v>
       </c>
     </row>
@@ -8879,13 +8879,13 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>0</v>
@@ -8894,16 +8894,16 @@
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1477</v>
+        <v>1480</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1478</v>
+        <v>1481</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5554302893649005</v>
+        <v>0.5563486100676184</v>
       </c>
     </row>
     <row r="21">
@@ -8926,31 +8926,31 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2694</v>
+        <v>2695</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1152</v>
+        <v>1147</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1476</v>
+        <v>1490</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1479</v>
+        <v>1493</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5489977728285078</v>
+        <v>0.5539888682745826</v>
       </c>
     </row>
     <row r="22">
@@ -8959,45 +8959,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2443</v>
+        <v>2312</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>910</v>
+        <v>960</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1321</v>
+        <v>1235</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1332</v>
+        <v>1261</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5452312730249693</v>
+        <v>0.5454152249134948</v>
       </c>
     </row>
     <row r="23">
@@ -9006,45 +9006,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2302</v>
+        <v>2443</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>968</v>
+        <v>910</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1221</v>
+        <v>1321</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1245</v>
+        <v>1332</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5408340573414422</v>
+        <v>0.5452312730249693</v>
       </c>
     </row>
     <row r="24">
@@ -9067,31 +9067,31 @@
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>1422</v>
+        <v>1429</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>406</v>
+        <v>368</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>265</v>
+        <v>294</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5253164556962026</v>
+        <v>0.523442967109867</v>
       </c>
     </row>
     <row r="25">
@@ -9114,31 +9114,31 @@
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2534</v>
+        <v>2545</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1183</v>
+        <v>1172</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1315</v>
+        <v>1327</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1321</v>
+        <v>1331</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.521310181531176</v>
+        <v>0.5229862475442043</v>
       </c>
     </row>
     <row r="26">
@@ -9161,16 +9161,16 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1230</v>
+        <v>1227</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>46</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>5</v>
@@ -9185,7 +9185,7 @@
         <v>1394</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5142014016967908</v>
+        <v>0.5140117994100295</v>
       </c>
     </row>
     <row r="27">
@@ -9194,45 +9194,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2063</v>
+        <v>2410</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1022</v>
+        <v>1095</v>
       </c>
       <c r="G27" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>1179</v>
+      </c>
+      <c r="K27" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="H27" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="I27" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>987</v>
-      </c>
-      <c r="K27" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" s="9" t="n">
-        <v>1013</v>
+        <v>1229</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.4910324769752787</v>
+        <v>0.5099585062240664</v>
       </c>
     </row>
     <row r="28">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Olfira Sicilia Budiman</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -9255,31 +9255,31 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2081</v>
+        <v>2064</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1007</v>
+        <v>1019</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>958</v>
+        <v>990</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.4872657376261413</v>
+        <v>0.4917635658914728</v>
       </c>
     </row>
     <row r="29">
@@ -9288,45 +9288,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Olfira Sicilia Budiman</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2407</v>
+        <v>2086</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>1104</v>
+        <v>996</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1133</v>
+        <v>962</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1169</v>
+        <v>1022</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.4856668051516411</v>
+        <v>0.4899328859060403</v>
       </c>
     </row>
   </sheetData>
@@ -9377,17 +9377,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 05.55 WITA</t>
+          <t>Pukul        : 20.34 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-35):</t>
+          <t>Target Hari Ini (H-36):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>58.45%</t>
+          <t>60.12%</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.7757575757575758</v>
+        <v>0.7802768166089965</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7578051087984864</v>
+        <v>0.7600882723833543</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7347853939782191</v>
+        <v>0.7422598148739228</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7104817235536189</v>
+        <v>0.7138364779874213</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7058632274845561</v>
+        <v>0.7135456017269293</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9510,15 +9510,15 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.6334405144694534</v>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.631219512195122</v>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9528,15 +9528,15 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tenggara</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.6221786064769381</v>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6304</v>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.6165347405452947</v>
+        <v>0.6180860403863038</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
           <t>Kendahe</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="12" t="n">
         <v>0.5898896404414382</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.5789575289575289</v>
+        <v>0.5786127167630057</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5510425716768028</v>
+        <v>0.5544962080173348</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.545375650880238</v>
+        <v>0.5469079191969265</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9636,15 +9636,15 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5300582847626978</v>
+        <v>0.5367389783065081</v>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
     </row>
@@ -9658,11 +9658,11 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.52970502700457</v>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.533195020746888</v>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9672,15 +9672,15 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.5281293952180028</v>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5331670822942643</v>
+      </c>
+      <c r="D21" s="19" t="inlineStr">
+        <is>
+          <t>-2</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.34 WITA</t>
+          <t>Pukul        : 21.08 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4134</v>
+        <v>4142</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1149</v>
+        <v>1123</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
@@ -770,7 +770,7 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
@@ -784,7 +784,7 @@
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2886</v>
+        <v>2908</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -798,14 +798,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2951</v>
+        <v>2985</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -825,7 +825,7 @@
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
@@ -839,7 +839,7 @@
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>746</v>
+        <v>760</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -867,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>767</v>
+        <v>776</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -888,27 +888,27 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6266</v>
+        <v>6268</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1511</v>
+        <v>1501</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
@@ -922,7 +922,7 @@
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4442</v>
+        <v>4443</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -936,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4651</v>
+        <v>4668</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3172</v>
+        <v>3174</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,7 +977,7 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
@@ -1005,14 +1005,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2411</v>
+        <v>2415</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1039,14 +1039,14 @@
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1074,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1164,27 +1164,27 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4615</v>
+        <v>4620</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
@@ -1198,7 +1198,7 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2341</v>
+        <v>2370</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1212,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2559</v>
+        <v>2569</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6015</v>
+        <v>6016</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2779</v>
+        <v>2778</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
@@ -1253,21 +1253,21 @@
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1281,14 +1281,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3207</v>
+        <v>3209</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,27 +1302,27 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8069</v>
+        <v>8072</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3529</v>
+        <v>3525</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
@@ -1350,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4413</v>
+        <v>4421</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,13 +1371,13 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5190</v>
+        <v>5196</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2059</v>
+        <v>2040</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
@@ -1391,14 +1391,14 @@
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
@@ -1419,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3003</v>
+        <v>3028</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1509,27 +1509,27 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9265</v>
+        <v>9267</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2563</v>
+        <v>2552</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6539</v>
+        <v>6540</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6611</v>
+        <v>6626</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1660,14 +1660,14 @@
         <v/>
       </c>
       <c r="F20" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20" s="10">
         <f>F20/B20</f>
         <v/>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="10">
         <f>H20/B20</f>
@@ -1695,14 +1695,14 @@
         <v/>
       </c>
       <c r="P20" s="9" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q20" s="11">
         <f>P20/B20</f>
         <v/>
       </c>
       <c r="R20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="10">
         <f>R20/B20</f>
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2809</v>
+        <v>2816</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1149</v>
+        <v>1130</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1736,21 +1736,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1764,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1657</v>
+        <v>1683</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.34 WITA</t>
+          <t>Pukul        : 21.08 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2116,13 +2116,13 @@
         <v>558</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.9551971326164874</v>
+        <v>0.956989247311828</v>
       </c>
     </row>
     <row r="10">
@@ -2166,10 +2166,10 @@
         <v>33</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>0</v>
@@ -2181,10 +2181,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.923076923076923</v>
+        <v>0.926923076923077</v>
       </c>
     </row>
     <row r="11">
@@ -2351,13 +2351,13 @@
         <v>379</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>0</v>
@@ -2369,10 +2369,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.8496042216358839</v>
+        <v>0.854881266490765</v>
       </c>
     </row>
     <row r="15">
@@ -2448,10 +2448,10 @@
         <v>67</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>47</v>
@@ -2463,10 +2463,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.8215962441314554</v>
+        <v>0.8262910798122065</v>
       </c>
     </row>
     <row r="17">
@@ -2475,45 +2475,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8131578947368421</v>
+        <v>0.8170426065162907</v>
       </c>
     </row>
     <row r="18">
@@ -2522,45 +2522,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>320</v>
+        <v>297</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8110831234256927</v>
+        <v>0.8136482939632547</v>
       </c>
     </row>
     <row r="19">
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
@@ -2651,10 +2651,10 @@
         <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8032786885245902</v>
+        <v>0.8061224489795918</v>
       </c>
     </row>
     <row r="21">
@@ -2677,16 +2677,16 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>2</v>
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.7957244655581949</v>
+        <v>0.8009478672985783</v>
       </c>
     </row>
     <row r="22">
@@ -2777,10 +2777,10 @@
         <v>103</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
@@ -2792,10 +2792,10 @@
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.7875751503006012</v>
+        <v>0.7895791583166333</v>
       </c>
     </row>
     <row r="24">
@@ -2827,13 +2827,13 @@
         <v>8</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>0</v>
@@ -2851,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>495</v>
+        <v>389</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>387</v>
+        <v>296</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>387</v>
+        <v>305</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7818181818181819</v>
+        <v>0.7840616966580977</v>
       </c>
     </row>
     <row r="26">
@@ -2898,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>430</v>
+        <v>495</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>327</v>
+        <v>387</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>333</v>
+        <v>388</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.7744186046511627</v>
+        <v>0.783838383838384</v>
       </c>
     </row>
     <row r="27">
@@ -2945,45 +2945,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>388</v>
+        <v>430</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>300</v>
+        <v>335</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7731958762886599</v>
+        <v>0.7790697674418605</v>
       </c>
     </row>
     <row r="28">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>109</v>
@@ -3109,22 +3109,22 @@
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7386091127098321</v>
+        <v>0.7417061611374407</v>
       </c>
     </row>
     <row r="31">
@@ -3133,45 +3133,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>556</v>
+        <v>419</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>398</v>
+        <v>303</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>406</v>
+        <v>310</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7302158273381295</v>
+        <v>0.7398568019093079</v>
       </c>
     </row>
     <row r="32">
@@ -3180,45 +3180,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>414</v>
+        <v>500</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>301</v>
+        <v>356</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>302</v>
+        <v>366</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7294685990338166</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="33">
@@ -3227,45 +3227,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>500</v>
+        <v>556</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>356</v>
+        <v>398</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>364</v>
+        <v>406</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.728</v>
+        <v>0.7302158273381295</v>
       </c>
     </row>
     <row r="34">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -3288,10 +3288,10 @@
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
@@ -3300,19 +3300,19 @@
         <v>0</v>
       </c>
       <c r="I34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>301</v>
+      </c>
+      <c r="K34" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="9" t="n">
-        <v>306</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" s="9" t="n">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7274881516587678</v>
+        <v>0.7294685990338166</v>
       </c>
     </row>
     <row r="35">
@@ -3462,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>512</v>
+        <v>452</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>360</v>
+        <v>312</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>364</v>
+        <v>322</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7109375</v>
+        <v>0.7123893805309734</v>
       </c>
     </row>
     <row r="39">
@@ -3509,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>347</v>
+        <v>512</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H39" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" s="9" t="n">
-        <v>244</v>
+        <v>360</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>246</v>
+        <v>364</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7089337175792507</v>
+        <v>0.7109375</v>
       </c>
     </row>
     <row r="40">
@@ -3556,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>450</v>
+        <v>347</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>312</v>
+        <v>244</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>317</v>
+        <v>246</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7044444444444444</v>
+        <v>0.7089337175792507</v>
       </c>
     </row>
     <row r="41">
@@ -3697,45 +3697,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
         <v>348</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.6904761904761905</v>
+        <v>0.6918489065606361</v>
       </c>
     </row>
     <row r="44">
@@ -3744,45 +3744,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G44" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="H44" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>341</v>
+      </c>
+      <c r="K44" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I44" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" s="9" t="n">
-        <v>333</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" s="9" t="n">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.6858846918489065</v>
+        <v>0.6904761904761905</v>
       </c>
     </row>
     <row r="45">
@@ -4026,45 +4026,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>455</v>
+        <v>515</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6659340659340658</v>
+        <v>0.6660194174757281</v>
       </c>
     </row>
     <row r="51">
@@ -4073,45 +4073,45 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>515</v>
+        <v>455</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>340</v>
+        <v>280</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>342</v>
+        <v>303</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6640776699029126</v>
+        <v>0.6659340659340658</v>
       </c>
     </row>
     <row r="52">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F53" s="9" t="n">
         <v>154</v>
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I53" s="9" t="n">
         <v>2</v>
@@ -4202,10 +4202,10 @@
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6547085201793722</v>
+        <v>0.6554809843400448</v>
       </c>
     </row>
     <row r="54">
@@ -4308,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>411</v>
+        <v>464</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>217</v>
+        <v>300</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6472019464720195</v>
+        <v>0.6508620689655173</v>
       </c>
     </row>
     <row r="57">
@@ -4355,45 +4355,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>464</v>
+        <v>411</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="G57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="I57" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J57" s="9" t="n">
-        <v>300</v>
+        <v>217</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.646551724137931</v>
+        <v>0.6472019464720195</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>447</v>
+        <v>376</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>287</v>
+        <v>243</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6420581655480985</v>
+        <v>0.6462765957446809</v>
       </c>
     </row>
     <row r="59">
@@ -4449,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I59" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>284</v>
+      </c>
+      <c r="K59" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J59" s="9" t="n">
-        <v>278</v>
-      </c>
-      <c r="K59" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" s="9" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6413793103448274</v>
+        <v>0.6420581655480985</v>
       </c>
     </row>
     <row r="60">
@@ -4496,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>376</v>
+        <v>435</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>241</v>
+        <v>279</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6409574468085107</v>
+        <v>0.6413793103448274</v>
       </c>
     </row>
     <row r="61">
@@ -4566,13 +4566,13 @@
         <v>44</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>1</v>
@@ -4604,16 +4604,16 @@
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" s="9" t="n">
         <v>3</v>
@@ -4625,10 +4625,10 @@
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6334405144694534</v>
+        <v>0.632</v>
       </c>
     </row>
     <row r="63">
@@ -4842,13 +4842,13 @@
         <v>500</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I67" s="9" t="n">
         <v>2</v>
@@ -4860,10 +4860,10 @@
         <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.618</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="68">
@@ -4933,16 +4933,16 @@
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I69" s="9" t="n">
         <v>0</v>
@@ -4954,10 +4954,10 @@
         <v>1</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6121495327102804</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="70">
@@ -5083,13 +5083,13 @@
         <v>1</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I72" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>1</v>
@@ -5362,10 +5362,10 @@
         <v>156</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I78" s="9" t="n">
         <v>1</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0.5957894736842105</v>
+        <v>0.5978947368421053</v>
       </c>
     </row>
     <row r="79">
@@ -5483,45 +5483,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>465</v>
+        <v>533</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.5913978494623656</v>
+        <v>0.5928705440900562</v>
       </c>
     </row>
     <row r="82">
@@ -5530,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>533</v>
+        <v>465</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>218</v>
+        <v>183</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>315</v>
+        <v>275</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.5909943714821764</v>
+        <v>0.5913978494623656</v>
       </c>
     </row>
     <row r="83">
@@ -5688,13 +5688,13 @@
         <v>511</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I85" s="9" t="n">
         <v>0</v>
@@ -5706,10 +5706,10 @@
         <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.5831702544031311</v>
+        <v>0.5851272015655578</v>
       </c>
     </row>
     <row r="86">
@@ -5859,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>364</v>
+        <v>475</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="K89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>208</v>
+        <v>272</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5726315789473684</v>
       </c>
     </row>
     <row r="90">
@@ -5906,27 +5906,27 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>475</v>
+        <v>364</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H90" s="9" t="n">
         <v>1</v>
@@ -5935,16 +5935,16 @@
         <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.5705263157894737</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="91">
@@ -6141,45 +6141,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>466</v>
+        <v>427</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.5536480686695279</v>
+        <v>0.5573770491803278</v>
       </c>
     </row>
     <row r="96">
@@ -6188,45 +6188,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>427</v>
+        <v>466</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="G96" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H96" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I96" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H96" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I96" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J96" s="9" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5526932084309133</v>
+        <v>0.5536480686695279</v>
       </c>
     </row>
     <row r="97">
@@ -6252,13 +6252,13 @@
         <v>439</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I97" s="9" t="n">
         <v>0</v>
@@ -6270,10 +6270,10 @@
         <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.55125284738041</v>
+        <v>0.5535307517084282</v>
       </c>
     </row>
     <row r="98">
@@ -6440,13 +6440,13 @@
         <v>426</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I101" s="9" t="n">
         <v>0</v>
@@ -6458,10 +6458,10 @@
         <v>2</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.539906103286385</v>
+        <v>0.5446009389671361</v>
       </c>
     </row>
     <row r="102">
@@ -6846,45 +6846,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>420</v>
+        <v>471</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H110" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I110" s="9" t="n">
-        <v>14</v>
-      </c>
       <c r="J110" s="9" t="n">
-        <v>204</v>
+        <v>244</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.524416135881104</v>
       </c>
     </row>
     <row r="111">
@@ -6893,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>471</v>
+        <v>420</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="K111" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>246</v>
+        <v>220</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5222929936305732</v>
+        <v>0.5238095238095238</v>
       </c>
     </row>
     <row r="112">
@@ -7104,13 +7104,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I115" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>1</v>
@@ -7175,45 +7175,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5011764705882353</v>
+        <v>0.5012345679012346</v>
       </c>
     </row>
     <row r="118">
@@ -7222,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>476</v>
+        <v>425</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5</v>
+        <v>0.5011764705882353</v>
       </c>
     </row>
     <row r="119">
@@ -7269,42 +7269,42 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>404</v>
+        <v>476</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>201</v>
+        <v>229</v>
       </c>
       <c r="G119" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H119" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="I119" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>194</v>
+      </c>
+      <c r="K119" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H119" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I119" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="J119" s="9" t="n">
-        <v>184</v>
-      </c>
-      <c r="K119" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L119" s="9" t="n">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="M119" s="12" t="n">
         <v>0.5</v>
@@ -7389,10 +7389,10 @@
         <v>1</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
@@ -7645,45 +7645,45 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="F127" s="9" t="n">
         <v>215</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.4806763285024155</v>
+        <v>0.4807256235827664</v>
       </c>
     </row>
     <row r="128">
@@ -7692,45 +7692,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="F128" s="9" t="n">
         <v>215</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>196</v>
+        <v>147</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4784580498866213</v>
+        <v>0.4806763285024155</v>
       </c>
     </row>
     <row r="129">
@@ -7739,45 +7739,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>442</v>
+        <v>407</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4660633484162895</v>
+        <v>0.4668304668304668</v>
       </c>
     </row>
     <row r="130">
@@ -7786,45 +7786,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>407</v>
+        <v>442</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4643734643734644</v>
+        <v>0.4660633484162895</v>
       </c>
     </row>
     <row r="131">
@@ -8041,10 +8041,10 @@
         <v>227</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I135" s="9" t="n">
         <v>11</v>
@@ -8056,10 +8056,10 @@
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4466230936819172</v>
+        <v>0.4488017429193899</v>
       </c>
     </row>
     <row r="136">
@@ -8135,7 +8135,7 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.34 WITA</t>
+          <t>Pukul        : 21.08 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8271,13 +8271,13 @@
         <v>2881</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>0</v>
@@ -8315,16 +8315,16 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>27</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>9</v>
@@ -8339,7 +8339,7 @@
         <v>1543</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7597242737567701</v>
+        <v>0.7593503937007874</v>
       </c>
     </row>
     <row r="9">
@@ -8362,16 +8362,16 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2799</v>
+        <v>2801</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>8</v>
@@ -8386,7 +8386,7 @@
         <v>2082</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7438370846730975</v>
+        <v>0.7433059621563727</v>
       </c>
     </row>
     <row r="10">
@@ -8409,16 +8409,16 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2898</v>
+        <v>2899</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>89</v>
@@ -8433,7 +8433,7 @@
         <v>2124</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7329192546583851</v>
+        <v>0.7326664367023112</v>
       </c>
     </row>
     <row r="11">
@@ -8456,16 +8456,16 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
         <v>1791</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.717548076923077</v>
+        <v>0.7169735788630905</v>
       </c>
     </row>
     <row r="12">
@@ -8503,16 +8503,16 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2838</v>
+        <v>2839</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>12</v>
@@ -8527,7 +8527,7 @@
         <v>2006</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7068357998590556</v>
+        <v>0.7065868263473054</v>
       </c>
     </row>
     <row r="13">
@@ -8536,45 +8536,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2767</v>
+        <v>2110</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>928</v>
+        <v>679</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1780</v>
+        <v>1380</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1791</v>
+        <v>1382</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6472714130827611</v>
+        <v>0.6549763033175355</v>
       </c>
     </row>
     <row r="14">
@@ -8583,45 +8583,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2103</v>
+        <v>2767</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>704</v>
+        <v>928</v>
       </c>
       <c r="G14" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="J14" s="9" t="n">
-        <v>1358</v>
+        <v>1781</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1360</v>
+        <v>1792</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6466951973371374</v>
+        <v>0.6476328153234551</v>
       </c>
     </row>
     <row r="15">
@@ -8647,13 +8647,13 @@
         <v>2902</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I15" s="9" t="n">
         <v>8</v>
@@ -8694,7 +8694,7 @@
         <v>2395</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>11</v>
@@ -8703,19 +8703,19 @@
         <v>5</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.630062630480167</v>
+        <v>0.6304801670146137</v>
       </c>
     </row>
     <row r="17">
@@ -8744,10 +8744,10 @@
         <v>793</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>3</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2878</v>
+        <v>2884</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1099</v>
+        <v>1081</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>52</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J18" s="9" t="n">
         <v>1697</v>
@@ -8806,10 +8806,10 @@
         <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1726</v>
+        <v>1720</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.5997220291869354</v>
+        <v>0.5963938973647711</v>
       </c>
     </row>
     <row r="19">
@@ -8832,31 +8832,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2809</v>
+        <v>2816</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1149</v>
+        <v>1130</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1636</v>
+        <v>1632</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1652</v>
+        <v>1666</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.5881096475614097</v>
+        <v>0.5916193181818182</v>
       </c>
     </row>
     <row r="20">
@@ -8865,45 +8865,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2662</v>
+        <v>2448</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1155</v>
+        <v>903</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1480</v>
+        <v>1350</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1481</v>
+        <v>1361</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5563486100676184</v>
+        <v>0.5559640522875817</v>
       </c>
     </row>
     <row r="21">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -8926,31 +8926,31 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2695</v>
+        <v>2664</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1147</v>
+        <v>1152</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1490</v>
+        <v>1480</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1493</v>
+        <v>1481</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5539888682745826</v>
+        <v>0.5559309309309309</v>
       </c>
     </row>
     <row r="22">
@@ -8959,45 +8959,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2312</v>
+        <v>2696</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>960</v>
+        <v>1146</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1235</v>
+        <v>1490</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1261</v>
+        <v>1493</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5454152249134948</v>
+        <v>0.5537833827893175</v>
       </c>
     </row>
     <row r="23">
@@ -9006,45 +9006,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2443</v>
+        <v>2312</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>910</v>
+        <v>959</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>171</v>
+        <v>16</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1321</v>
+        <v>1235</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1332</v>
+        <v>1261</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5452312730249693</v>
+        <v>0.5454152249134948</v>
       </c>
     </row>
     <row r="24">
@@ -9070,28 +9070,28 @@
         <v>1429</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>294</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>746</v>
+        <v>760</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>748</v>
+        <v>762</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.523442967109867</v>
+        <v>0.5332400279916025</v>
       </c>
     </row>
     <row r="25">
@@ -9167,10 +9167,10 @@
         <v>1227</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>5</v>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>996</v>
@@ -9311,7 +9311,7 @@
         <v>20</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>60</v>
@@ -9326,7 +9326,7 @@
         <v>1022</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.4899328859060403</v>
+        <v>0.4896981312889315</v>
       </c>
     </row>
   </sheetData>
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.34 WITA</t>
+          <t>Pukul        : 21.08 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7600882723833543</v>
+        <v>0.7608695652173914</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7422598148739228</v>
+        <v>0.7447351627313339</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7138364779874213</v>
+        <v>0.720666344760985</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7135456017269293</v>
+        <v>0.7150102514298047</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9510,15 +9510,15 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tenggara</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.631219512195122</v>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.632</v>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9528,15 +9528,15 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.6304</v>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.631219512195122</v>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.6180860403863038</v>
+        <v>0.6198419666374012</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.5898896404414382</v>
+        <v>0.59765625</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.5786127167630057</v>
+        <v>0.5827559661277906</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5544962080173348</v>
+        <v>0.556060606060606</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5469079191969265</v>
+        <v>0.5476957383548068</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5367389783065081</v>
+        <v>0.543037088873338</v>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
@@ -9654,15 +9654,15 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.533195020746888</v>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5334109042553191</v>
+      </c>
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9672,15 +9672,15 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.5331670822942643</v>
+        <v>0.533195020746888</v>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-1</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 21.08 WITA</t>
+          <t>Pukul        : 22.01 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -839,7 +839,7 @@
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -894,35 +894,35 @@
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1501</v>
+        <v>1491</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4443</v>
+        <v>4441</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -936,14 +936,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4668</v>
+        <v>4683</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3174</v>
+        <v>3181</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>759</v>
+        <v>739</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,7 +977,7 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
@@ -991,7 +991,7 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -1005,14 +1005,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2415</v>
+        <v>2442</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1039,14 +1039,14 @@
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1074,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1170,7 +1170,7 @@
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
@@ -1184,7 +1184,7 @@
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
@@ -1212,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,34 +1233,34 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6016</v>
+        <v>6017</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2778</v>
+        <v>2774</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
@@ -1281,14 +1281,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3209</v>
+        <v>3213</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1308,21 +1308,21 @@
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3525</v>
+        <v>3519</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
@@ -1350,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4421</v>
+        <v>4429</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1377,21 +1377,21 @@
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
@@ -1419,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3028</v>
+        <v>3041</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1446,7 +1446,7 @@
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
@@ -1460,7 +1460,7 @@
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
@@ -1488,14 +1488,14 @@
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,27 +1509,27 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9267</v>
+        <v>9276</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2552</v>
+        <v>2544</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
@@ -1543,7 +1543,7 @@
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6540</v>
+        <v>6559</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6626</v>
+        <v>6647</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1584,7 +1584,7 @@
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1626,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1653,28 +1653,28 @@
         <v>8</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E20" s="10">
         <f>D20/B20</f>
         <v/>
       </c>
       <c r="F20" s="9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G20" s="10">
         <f>F20/B20</f>
         <v/>
       </c>
       <c r="H20" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I20" s="10">
         <f>H20/B20</f>
         <v/>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K20" s="10">
         <f>J20/B20</f>
@@ -1695,14 +1695,14 @@
         <v/>
       </c>
       <c r="P20" s="9" t="n">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="Q20" s="11">
         <f>P20/B20</f>
         <v/>
       </c>
       <c r="R20" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S20" s="10">
         <f>R20/B20</f>
@@ -1736,21 +1736,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1632</v>
+        <v>1641</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 21.08 WITA</t>
+          <t>Pukul        : 22.01 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2348,16 +2348,16 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>0</v>
@@ -2369,10 +2369,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.854881266490765</v>
+        <v>0.868766404199475</v>
       </c>
     </row>
     <row r="15">
@@ -2448,25 +2448,25 @@
         <v>67</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.8262910798122065</v>
+        <v>0.8333333333333335</v>
       </c>
     </row>
     <row r="17">
@@ -2475,45 +2475,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>399</v>
+        <v>493</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>320</v>
+        <v>392</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>326</v>
+        <v>407</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8170426065162907</v>
+        <v>0.8255578093306287</v>
       </c>
     </row>
     <row r="18">
@@ -2522,21 +2522,21 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>71</v>
@@ -2545,22 +2545,22 @@
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8136482939632547</v>
+        <v>0.8225</v>
       </c>
     </row>
     <row r="19">
@@ -2569,45 +2569,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>477</v>
+        <v>382</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>377</v>
+        <v>298</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>385</v>
+        <v>312</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8071278825995808</v>
+        <v>0.8167539267015707</v>
       </c>
     </row>
     <row r="20">
@@ -2616,45 +2616,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8061224489795918</v>
+        <v>0.8092243186582809</v>
       </c>
     </row>
     <row r="21">
@@ -2680,13 +2680,13 @@
         <v>422</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>2</v>
@@ -2698,10 +2698,10 @@
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8009478672985783</v>
+        <v>0.8033175355450237</v>
       </c>
     </row>
     <row r="22">
@@ -2757,45 +2757,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>499</v>
+        <v>389</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="G23" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="9" t="n">
+      <c r="J23" s="9" t="n">
+        <v>296</v>
+      </c>
+      <c r="K23" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="9" t="n">
-        <v>393</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" s="9" t="n">
-        <v>394</v>
+        <v>308</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.7895791583166333</v>
+        <v>0.7917737789203084</v>
       </c>
     </row>
     <row r="24">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>530</v>
+        <v>499</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H24" s="9" t="n">
         <v>2</v>
@@ -2833,16 +2833,16 @@
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.7849056603773586</v>
+        <v>0.7915831663326653</v>
       </c>
     </row>
     <row r="25">
@@ -2851,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>389</v>
+        <v>430</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>296</v>
+        <v>327</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7840616966580977</v>
+        <v>0.7860465116279071</v>
       </c>
     </row>
     <row r="26">
@@ -2918,7 +2918,7 @@
         <v>93</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H26" s="9" t="n">
         <v>1</v>
@@ -2927,16 +2927,16 @@
         <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.783838383838384</v>
+        <v>0.7858585858585857</v>
       </c>
     </row>
     <row r="27">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -2959,31 +2959,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>430</v>
+        <v>530</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>327</v>
+        <v>414</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>335</v>
+        <v>416</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7790697674418605</v>
+        <v>0.7849056603773586</v>
       </c>
     </row>
     <row r="28">
@@ -3056,28 +3056,28 @@
         <v>485</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>35</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7463917525773196</v>
+        <v>0.7484536082474227</v>
       </c>
     </row>
     <row r="30">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -3103,28 +3103,28 @@
         <v>422</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7417061611374407</v>
+        <v>0.7464454976303316</v>
       </c>
     </row>
     <row r="31">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -3147,7 +3147,7 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>109</v>
@@ -3162,16 +3162,16 @@
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7398568019093079</v>
+        <v>0.7417061611374407</v>
       </c>
     </row>
     <row r="32">
@@ -3180,45 +3180,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>500</v>
+        <v>414</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="G32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>301</v>
+      </c>
+      <c r="K32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H32" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I32" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>356</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" s="9" t="n">
-        <v>366</v>
+        <v>307</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.732</v>
+        <v>0.7415458937198067</v>
       </c>
     </row>
     <row r="33">
@@ -3227,45 +3227,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>556</v>
+        <v>500</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>398</v>
+        <v>356</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>406</v>
+        <v>366</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7302158273381295</v>
+        <v>0.732</v>
       </c>
     </row>
     <row r="34">
@@ -3274,45 +3274,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>414</v>
+        <v>556</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>301</v>
+        <v>398</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>302</v>
+        <v>406</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7294685990338166</v>
+        <v>0.7302158273381295</v>
       </c>
     </row>
     <row r="35">
@@ -3462,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>452</v>
+        <v>512</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>312</v>
+        <v>360</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>322</v>
+        <v>366</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7123893805309734</v>
+        <v>0.71484375</v>
       </c>
     </row>
     <row r="39">
@@ -3509,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>512</v>
+        <v>453</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>360</v>
+        <v>323</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>364</v>
+        <v>323</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7109375</v>
+        <v>0.7130242825607064</v>
       </c>
     </row>
     <row r="40">
@@ -3673,10 +3673,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="9" t="n">
         <v>1</v>
-      </c>
-      <c r="I42" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="J42" s="9" t="n">
         <v>288</v>
@@ -3885,45 +3885,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>289</v>
+        <v>368</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>191</v>
+        <v>241</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>194</v>
+        <v>248</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.671280276816609</v>
+        <v>0.673913043478261</v>
       </c>
     </row>
     <row r="48">
@@ -3932,45 +3932,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>368</v>
+        <v>289</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>241</v>
+        <v>191</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6711956521739131</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="49">
@@ -3979,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>345</v>
+        <v>455</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>230</v>
+        <v>280</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>231</v>
+        <v>305</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6695652173913044</v>
+        <v>0.6703296703296702</v>
       </c>
     </row>
     <row r="50">
@@ -4046,25 +4046,25 @@
         <v>144</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6660194174757281</v>
+        <v>0.6699029126213593</v>
       </c>
     </row>
     <row r="51">
@@ -4073,45 +4073,45 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>455</v>
+        <v>345</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>303</v>
+        <v>231</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6659340659340658</v>
+        <v>0.6695652173913044</v>
       </c>
     </row>
     <row r="52">
@@ -4137,7 +4137,7 @@
         <v>460</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>0</v>
@@ -4149,16 +4149,16 @@
         <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6608695652173913</v>
+        <v>0.6630434782608695</v>
       </c>
     </row>
     <row r="53">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F53" s="9" t="n">
         <v>154</v>
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I53" s="9" t="n">
         <v>2</v>
@@ -4202,10 +4202,10 @@
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6554809843400448</v>
+        <v>0.6570155902004454</v>
       </c>
     </row>
     <row r="54">
@@ -4284,13 +4284,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K55" s="9" t="n">
         <v>2</v>
@@ -4325,13 +4325,13 @@
         <v>464</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I56" s="9" t="n">
         <v>0</v>
@@ -4343,10 +4343,10 @@
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6508620689655173</v>
+        <v>0.6530172413793103</v>
       </c>
     </row>
     <row r="57">
@@ -4472,10 +4472,10 @@
         <v>2</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J59" s="9" t="n">
         <v>284</v>
@@ -4543,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>404</v>
+        <v>625</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>103</v>
+        <v>219</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>249</v>
+        <v>391</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>257</v>
+        <v>399</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6361386138613861</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="62">
@@ -4590,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>625</v>
+        <v>404</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>220</v>
+        <v>103</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="H62" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>249</v>
+      </c>
+      <c r="K62" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I62" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J62" s="9" t="n">
-        <v>391</v>
-      </c>
-      <c r="K62" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L62" s="9" t="n">
-        <v>395</v>
+        <v>257</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.632</v>
+        <v>0.6361386138613861</v>
       </c>
     </row>
     <row r="63">
@@ -4825,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>500</v>
+        <v>429</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H67" s="9" t="n">
         <v>4</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>304</v>
+        <v>261</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>310</v>
+        <v>266</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.62</v>
+        <v>0.62004662004662</v>
       </c>
     </row>
     <row r="68">
@@ -4872,45 +4872,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.6179337231968811</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>429</v>
+        <v>513</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>261</v>
+        <v>301</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>264</v>
+        <v>317</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6179337231968811</v>
       </c>
     </row>
     <row r="70">
@@ -5013,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>467</v>
+        <v>381</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>281</v>
+        <v>230</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.6017130620985011</v>
+        <v>0.6036745406824147</v>
       </c>
     </row>
     <row r="72">
@@ -5060,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>468</v>
+        <v>558</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="G72" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="H72" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H72" s="9" t="n">
-        <v>10</v>
-      </c>
       <c r="I72" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>266</v>
+        <v>335</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>281</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>0.6004273504273504</v>
+        <v>336</v>
+      </c>
+      <c r="M72" s="11" t="n">
+        <v>0.6021505376344086</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>558</v>
+        <v>467</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>335</v>
+        <v>280</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>335</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>0.600358422939068</v>
+        <v>281</v>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>0.6017130620985011</v>
       </c>
     </row>
     <row r="74">
@@ -5154,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>400</v>
+        <v>468</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>240</v>
+        <v>281</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>0.6</v>
+        <v>0.6004273504273504</v>
       </c>
     </row>
     <row r="75">
@@ -5201,42 +5201,42 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>0.6</v>
@@ -5248,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>439</v>
+        <v>360</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>263</v>
+        <v>216</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0.5990888382687927</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="77">
@@ -5295,45 +5295,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>381</v>
+        <v>439</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>228</v>
+        <v>263</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.5984251968503937</v>
+        <v>0.5990888382687927</v>
       </c>
     </row>
     <row r="78">
@@ -5577,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.5856573705179283</v>
+        <v>0.5873015873015873</v>
       </c>
     </row>
     <row r="84">
@@ -5624,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>13</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.5853174603174603</v>
+        <v>0.5856573705179283</v>
       </c>
     </row>
     <row r="85">
@@ -5882,13 +5882,13 @@
         <v>18</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K89" s="9" t="n">
         <v>0</v>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -5967,31 +5967,31 @@
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>470</v>
+        <v>427</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H91" s="9" t="n">
         <v>9</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>267</v>
+        <v>243</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.5680851063829787</v>
+        <v>0.5690866510538641</v>
       </c>
     </row>
     <row r="92">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.5672645739910314</v>
+        <v>0.5680851063829787</v>
       </c>
     </row>
     <row r="93">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -6061,31 +6061,31 @@
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>493</v>
+        <v>446</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I93" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>279</v>
+        <v>253</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.565922920892495</v>
+        <v>0.5672645739910314</v>
       </c>
     </row>
     <row r="94">
@@ -6114,10 +6114,10 @@
         <v>219</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I94" s="9" t="n">
         <v>0</v>
@@ -6129,10 +6129,10 @@
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5622710622710623</v>
+        <v>0.5659340659340659</v>
       </c>
     </row>
     <row r="95">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
@@ -6155,31 +6155,31 @@
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>427</v>
+        <v>493</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>188</v>
+        <v>211</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.5573770491803278</v>
+        <v>0.565922920892495</v>
       </c>
     </row>
     <row r="96">
@@ -6205,13 +6205,13 @@
         <v>466</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I96" s="9" t="n">
         <v>1</v>
@@ -6223,10 +6223,10 @@
         <v>1</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5536480686695279</v>
+        <v>0.5579399141630901</v>
       </c>
     </row>
     <row r="97">
@@ -6252,13 +6252,13 @@
         <v>439</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I97" s="9" t="n">
         <v>0</v>
@@ -6270,10 +6270,10 @@
         <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5535307517084282</v>
+        <v>0.5558086560364465</v>
       </c>
     </row>
     <row r="98">
@@ -6299,13 +6299,13 @@
         <v>396</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I98" s="9" t="n">
         <v>0</v>
@@ -6317,10 +6317,10 @@
         <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5505050505050505</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="99">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
@@ -6343,31 +6343,31 @@
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>399</v>
+        <v>460</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>180</v>
+        <v>206</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>218</v>
+        <v>251</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.5521739130434783</v>
       </c>
     </row>
     <row r="100">
@@ -6376,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>460</v>
+        <v>427</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.5456521739130434</v>
+        <v>0.550351288056206</v>
       </c>
     </row>
     <row r="101">
@@ -6423,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>426</v>
+        <v>399</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5446009389671361</v>
+        <v>0.5463659147869674</v>
       </c>
     </row>
     <row r="102">
@@ -6637,10 +6637,10 @@
         <v>1</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>3</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F109" s="9" t="n">
         <v>197</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I109" s="9" t="n">
         <v>1</v>
@@ -6834,10 +6834,10 @@
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5264423076923077</v>
+        <v>0.5275779376498801</v>
       </c>
     </row>
     <row r="110">
@@ -6866,10 +6866,10 @@
         <v>215</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I110" s="9" t="n">
         <v>2</v>
@@ -6881,10 +6881,10 @@
         <v>0</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.524416135881104</v>
+        <v>0.5265392781316348</v>
       </c>
     </row>
     <row r="111">
@@ -7107,10 +7107,10 @@
         <v>0</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>1</v>
@@ -7477,13 +7477,13 @@
         <v>221</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H123" s="9" t="n">
         <v>3</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J123" s="9" t="n">
         <v>203</v>
@@ -7492,10 +7492,10 @@
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.4920273348519363</v>
+        <v>0.489749430523918</v>
       </c>
     </row>
     <row r="124">
@@ -7756,13 +7756,13 @@
         <v>407</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G129" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I129" s="9" t="n">
         <v>0</v>
@@ -7774,10 +7774,10 @@
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4668304668304668</v>
+        <v>0.4717444717444718</v>
       </c>
     </row>
     <row r="130">
@@ -7806,13 +7806,13 @@
         <v>210</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H130" s="9" t="n">
         <v>8</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J130" s="9" t="n">
         <v>177</v>
@@ -7821,10 +7821,10 @@
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4660633484162895</v>
+        <v>0.4638009049773755</v>
       </c>
     </row>
     <row r="131">
@@ -7974,45 +7974,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>420</v>
+        <v>459</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="K134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.4553376906318083</v>
       </c>
     </row>
     <row r="135">
@@ -8021,45 +8021,45 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>459</v>
+        <v>420</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>186</v>
+        <v>159</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4488017429193899</v>
+        <v>0.4523809523809524</v>
       </c>
     </row>
     <row r="136">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 21.08 WITA</t>
+          <t>Pukul        : 22.01 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8268,16 +8268,16 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2881</v>
+        <v>2886</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>0</v>
@@ -8292,7 +8292,7 @@
         <v>2434</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8448455397431447</v>
+        <v>0.8433818433818433</v>
       </c>
     </row>
     <row r="8">
@@ -8362,31 +8362,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2801</v>
+        <v>2808</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>8</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7433059621563727</v>
+        <v>0.7418091168091168</v>
       </c>
     </row>
     <row r="10">
@@ -8412,28 +8412,28 @@
         <v>2899</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7326664367023112</v>
+        <v>0.7323214901690238</v>
       </c>
     </row>
     <row r="11">
@@ -8456,31 +8456,31 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2498</v>
+        <v>2502</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1791</v>
+        <v>1803</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1791</v>
+        <v>1803</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7169735788630905</v>
+        <v>0.7206235011990407</v>
       </c>
     </row>
     <row r="12">
@@ -8506,16 +8506,16 @@
         <v>2839</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>1994</v>
@@ -8524,10 +8524,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7065868263473054</v>
+        <v>0.7079957731595631</v>
       </c>
     </row>
     <row r="13">
@@ -8600,10 +8600,10 @@
         <v>2767</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H14" s="9" t="n">
         <v>3</v>
@@ -8612,16 +8612,16 @@
         <v>7</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1792</v>
+        <v>1796</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6476328153234551</v>
+        <v>0.6490784242862305</v>
       </c>
     </row>
     <row r="15">
@@ -8647,28 +8647,28 @@
         <v>2902</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6309441764300483</v>
+        <v>0.6316333563059958</v>
       </c>
     </row>
     <row r="16">
@@ -8694,13 +8694,13 @@
         <v>2395</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>11</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>6</v>
@@ -8744,10 +8744,10 @@
         <v>793</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>3</v>
@@ -8771,45 +8771,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2884</v>
+        <v>2816</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1081</v>
+        <v>1130</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="H18" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="I18" s="9" t="n">
-        <v>21</v>
-      </c>
       <c r="J18" s="9" t="n">
-        <v>1697</v>
+        <v>1641</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1720</v>
+        <v>1680</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.5963938973647711</v>
+        <v>0.5965909090909091</v>
       </c>
     </row>
     <row r="19">
@@ -8818,45 +8818,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2816</v>
+        <v>2884</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1130</v>
+        <v>1077</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1632</v>
+        <v>1697</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1666</v>
+        <v>1720</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.5916193181818182</v>
+        <v>0.5963938973647711</v>
       </c>
     </row>
     <row r="20">
@@ -8929,13 +8929,13 @@
         <v>2664</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
@@ -8979,10 +8979,10 @@
         <v>1146</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
@@ -9023,13 +9023,13 @@
         <v>2312</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>24</v>
@@ -9076,22 +9076,22 @@
         <v>294</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5332400279916025</v>
+        <v>0.5346396081175647</v>
       </c>
     </row>
     <row r="25">
@@ -9117,13 +9117,13 @@
         <v>2545</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>2</v>
@@ -9211,13 +9211,13 @@
         <v>2410</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>30</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>44</v>
@@ -9255,19 +9255,19 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="I28" s="9" t="n">
         <v>24</v>
-      </c>
-      <c r="I28" s="9" t="n">
-        <v>25</v>
       </c>
       <c r="J28" s="9" t="n">
         <v>990</v>
@@ -9276,10 +9276,10 @@
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.4917635658914728</v>
+        <v>0.4910411622276029</v>
       </c>
     </row>
     <row r="29">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 21.08 WITA</t>
+          <t>Pukul        : 22.01 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.7802768166089965</v>
+        <v>0.7811418685121108</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.7676831185161899</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7447351627313339</v>
+        <v>0.7471282705807275</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7150102514298047</v>
+        <v>0.7165804225959466</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.632</v>
+        <v>0.6384</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.6198419666374012</v>
+        <v>0.62071992976295</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.5827559661277906</v>
+        <v>0.5852578906851424</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.556060606060606</v>
+        <v>0.5562770562770563</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5476957383548068</v>
+        <v>0.5486868186323092</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9654,15 +9654,15 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5334109042553191</v>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.5344398340248963</v>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9672,15 +9672,15 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.533195020746888</v>
+        <v>0.5339870367292671</v>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-2</t>
         </is>
       </c>
     </row>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 20 Juli 2026</t>
+          <t>Hari/Tanggal : 21 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 22.01 WITA</t>
+          <t>Pukul        : 10.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4142</v>
+        <v>4143</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
@@ -770,42 +770,42 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2908</v>
+        <v>2907</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
         <v/>
       </c>
       <c r="N7" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O7" s="10">
         <f>N7/B7</f>
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2985</v>
+        <v>2993</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -819,13 +819,13 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1429</v>
+        <v>1433</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
@@ -839,7 +839,7 @@
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -853,7 +853,7 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -867,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -888,62 +888,62 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6268</v>
+        <v>6290</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1491</v>
+        <v>1451</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4441</v>
+        <v>4451</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
         <v/>
       </c>
       <c r="N9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O9" s="10">
         <f>N9/B9</f>
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4683</v>
+        <v>4751</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3181</v>
+        <v>3185</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>739</v>
+        <v>725</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -977,42 +977,42 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
         <v/>
       </c>
       <c r="N10" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O10" s="10">
         <f>N10/B10</f>
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2442</v>
+        <v>2460</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1032,7 +1032,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
@@ -1046,7 +1046,7 @@
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1074,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1115,14 +1115,14 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
@@ -1164,27 +1164,27 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4620</v>
+        <v>4624</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>2015</v>
+        <v>1999</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
@@ -1198,7 +1198,7 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2370</v>
+        <v>2414</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1212,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2570</v>
+        <v>2588</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,41 +1233,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6017</v>
+        <v>6028</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2774</v>
+        <v>2770</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3042</v>
+        <v>3051</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1281,14 +1281,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3213</v>
+        <v>3230</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,27 +1302,27 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8072</v>
+        <v>8079</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3519</v>
+        <v>3499</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
@@ -1336,7 +1336,7 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4359</v>
+        <v>4406</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1350,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4429</v>
+        <v>4469</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,41 +1371,41 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5196</v>
+        <v>5204</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2032</v>
+        <v>2023</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2932</v>
+        <v>2985</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1419,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3041</v>
+        <v>3062</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,27 +1440,27 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2410</v>
+        <v>2413</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1092</v>
+        <v>1077</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
@@ -1474,28 +1474,28 @@
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1288</v>
+        <v>1310</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,41 +1509,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9276</v>
+        <v>9298</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2544</v>
+        <v>2481</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6559</v>
+        <v>6675</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1557,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6647</v>
+        <v>6746</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>134</v>
+        <v>233</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1612,7 +1612,7 @@
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1626,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1667,21 +1667,21 @@
         <v/>
       </c>
       <c r="H20" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I20" s="10">
         <f>H20/B20</f>
         <v/>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K20" s="10">
         <f>J20/B20</f>
         <v/>
       </c>
       <c r="L20" s="9" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M20" s="10">
         <f>L20/B20</f>
@@ -1716,13 +1716,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2816</v>
+        <v>2825</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1736,21 +1736,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1641</v>
+        <v>1632</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1764,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1683</v>
+        <v>1697</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1900,7 +1900,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 20 Juli 2026</t>
+          <t>Hari/Tanggal : 21 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 22.01 WITA</t>
+          <t>Pukul        : 10.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2122,13 +2122,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
@@ -2166,25 +2166,25 @@
         <v>33</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.926923076923077</v>
+        <v>0.9307692307692308</v>
       </c>
     </row>
     <row r="11">
@@ -2351,13 +2351,13 @@
         <v>381</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>0</v>
@@ -2369,10 +2369,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.868766404199475</v>
+        <v>0.8713910761154857</v>
       </c>
     </row>
     <row r="15">
@@ -2448,13 +2448,13 @@
         <v>67</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>264</v>
@@ -2463,10 +2463,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.8333333333333335</v>
+        <v>0.8380281690140845</v>
       </c>
     </row>
     <row r="17">
@@ -2475,45 +2475,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>493</v>
+        <v>401</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>392</v>
+        <v>319</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>407</v>
+        <v>333</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8255578093306287</v>
+        <v>0.8304239401496259</v>
       </c>
     </row>
     <row r="18">
@@ -2522,45 +2522,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>400</v>
+        <v>493</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>320</v>
+        <v>392</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>329</v>
+        <v>407</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8225</v>
+        <v>0.8255578093306287</v>
       </c>
     </row>
     <row r="19">
@@ -2583,7 +2583,7 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>70</v>
@@ -2592,22 +2592,22 @@
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8167539267015707</v>
+        <v>0.8177083333333335</v>
       </c>
     </row>
     <row r="20">
@@ -2633,13 +2633,13 @@
         <v>477</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
@@ -2651,10 +2651,10 @@
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8092243186582809</v>
+        <v>0.8155136268343816</v>
       </c>
     </row>
     <row r="21">
@@ -2677,31 +2677,31 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8033175355450237</v>
+        <v>0.8085106382978722</v>
       </c>
     </row>
     <row r="22">
@@ -2710,45 +2710,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.7931873479318735</v>
+        <v>0.7981438515081206</v>
       </c>
     </row>
     <row r="23">
@@ -2757,45 +2757,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>389</v>
+        <v>495</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>296</v>
+        <v>394</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>308</v>
+        <v>394</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.7917737789203084</v>
+        <v>0.795959595959596</v>
       </c>
     </row>
     <row r="24">
@@ -2804,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>499</v>
+        <v>389</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="G24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I24" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" s="9" t="n">
-        <v>393</v>
+        <v>299</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>395</v>
+        <v>309</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.7915831663326653</v>
+        <v>0.7943444730077122</v>
       </c>
     </row>
     <row r="25">
@@ -2851,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7860465116279071</v>
+        <v>0.7931873479318735</v>
       </c>
     </row>
     <row r="26">
@@ -2898,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.7858585858585857</v>
+        <v>0.7915831663326653</v>
       </c>
     </row>
     <row r="27">
@@ -2965,7 +2965,7 @@
         <v>106</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H27" s="9" t="n">
         <v>2</v>
@@ -2974,16 +2974,16 @@
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7849056603773586</v>
+        <v>0.7867924528301887</v>
       </c>
     </row>
     <row r="28">
@@ -3053,31 +3053,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>35</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7484536082474227</v>
+        <v>0.7653061224489796</v>
       </c>
     </row>
     <row r="30">
@@ -3100,7 +3100,7 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>107</v>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>0</v>
@@ -3121,10 +3121,10 @@
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7464454976303316</v>
+        <v>0.7470449172576832</v>
       </c>
     </row>
     <row r="31">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
@@ -3162,16 +3162,16 @@
         <v>0</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7417061611374407</v>
+        <v>0.7463768115942028</v>
       </c>
     </row>
     <row r="32">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
@@ -3194,31 +3194,31 @@
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7415458937198067</v>
+        <v>0.7440758293838863</v>
       </c>
     </row>
     <row r="33">
@@ -3241,16 +3241,16 @@
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I33" s="9" t="n">
         <v>3</v>
@@ -3262,10 +3262,10 @@
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.732</v>
+        <v>0.7390438247011953</v>
       </c>
     </row>
     <row r="34">
@@ -3321,45 +3321,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>402</v>
+        <v>512</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>287</v>
+        <v>360</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>290</v>
+        <v>371</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7213930348258707</v>
+        <v>0.724609375</v>
       </c>
     </row>
     <row r="36">
@@ -3368,45 +3368,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>501</v>
+        <v>539</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>360</v>
+        <v>389</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.718562874251497</v>
+        <v>0.7217068645640075</v>
       </c>
     </row>
     <row r="37">
@@ -3415,45 +3415,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>536</v>
+        <v>402</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>151</v>
+        <v>112</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>385</v>
+        <v>287</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>385</v>
+        <v>290</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7182835820895522</v>
+        <v>0.7213930348258707</v>
       </c>
     </row>
     <row r="38">
@@ -3462,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I38" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>354</v>
+      </c>
+      <c r="K38" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" s="9" t="n">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.71484375</v>
+        <v>0.720558882235529</v>
       </c>
     </row>
     <row r="39">
@@ -3509,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>453</v>
+        <v>347</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>323</v>
+        <v>244</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>323</v>
+        <v>249</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7130242825607064</v>
+        <v>0.7175792507204612</v>
       </c>
     </row>
     <row r="40">
@@ -3556,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>347</v>
+        <v>453</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>244</v>
+        <v>323</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>246</v>
+        <v>323</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7089337175792507</v>
+        <v>0.7130242825607064</v>
       </c>
     </row>
     <row r="41">
@@ -3603,45 +3603,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>252</v>
+        <v>288</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.7</v>
+        <v>0.7095238095238094</v>
       </c>
     </row>
     <row r="42">
@@ -3650,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>417</v>
+        <v>503</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>288</v>
+        <v>335</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>290</v>
+        <v>354</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.6954436450839329</v>
+        <v>0.7037773359840955</v>
       </c>
     </row>
     <row r="43">
@@ -3697,45 +3697,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>503</v>
+        <v>381</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>154</v>
+        <v>114</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>333</v>
+        <v>253</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>348</v>
+        <v>267</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.6918489065606361</v>
+        <v>0.7007874015748031</v>
       </c>
     </row>
     <row r="44">
@@ -3761,28 +3761,28 @@
         <v>504</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.6904761904761905</v>
+        <v>0.6924603174603174</v>
       </c>
     </row>
     <row r="45">
@@ -3838,45 +3838,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>527</v>
+        <v>369</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>353</v>
+        <v>247</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>357</v>
+        <v>251</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.6774193548387096</v>
+        <v>0.6802168021680217</v>
       </c>
     </row>
     <row r="47">
@@ -3885,45 +3885,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>368</v>
+        <v>527</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>241</v>
+        <v>354</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>248</v>
+        <v>358</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.673913043478261</v>
+        <v>0.6793168880455408</v>
       </c>
     </row>
     <row r="48">
@@ -3932,45 +3932,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>289</v>
+        <v>345</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>191</v>
+        <v>230</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.671280276816609</v>
+        <v>0.6782608695652174</v>
       </c>
     </row>
     <row r="49">
@@ -3979,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>455</v>
+        <v>515</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>280</v>
+        <v>342</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>305</v>
+        <v>349</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6703296703296702</v>
+        <v>0.6776699029126214</v>
       </c>
     </row>
     <row r="50">
@@ -4026,45 +4026,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>515</v>
+        <v>455</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H50" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I50" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="I50" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J50" s="9" t="n">
-        <v>342</v>
+        <v>287</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>345</v>
+        <v>306</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6699029126213593</v>
+        <v>0.6725274725274726</v>
       </c>
     </row>
     <row r="51">
@@ -4073,45 +4073,45 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>345</v>
+        <v>289</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I51" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J51" s="9" t="n">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>231</v>
+        <v>194</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6695652173913044</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="52">
@@ -4228,31 +4228,31 @@
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H54" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I54" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>287</v>
+      </c>
+      <c r="K54" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="9" t="n">
-        <v>294</v>
-      </c>
-      <c r="K54" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" s="9" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6534216335540839</v>
+        <v>0.6541850220264317</v>
       </c>
     </row>
     <row r="55">
@@ -4355,45 +4355,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>411</v>
+        <v>448</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>217</v>
+        <v>284</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.6472019464720195</v>
+        <v>0.6495535714285714</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>376</v>
+        <v>411</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="I58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="K58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6462765957446809</v>
+        <v>0.6472019464720195</v>
       </c>
     </row>
     <row r="59">
@@ -4449,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>447</v>
+        <v>376</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>287</v>
+        <v>243</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6420581655480985</v>
+        <v>0.6462765957446809</v>
       </c>
     </row>
     <row r="60">
@@ -4566,13 +4566,13 @@
         <v>7</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
         <v>429</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>0</v>
@@ -4666,16 +4666,16 @@
         <v>0</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.6317016317016317</v>
+        <v>0.634032634032634</v>
       </c>
     </row>
     <row r="64">
@@ -4701,28 +4701,28 @@
         <v>498</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6265060240963856</v>
+        <v>0.6285140562248996</v>
       </c>
     </row>
     <row r="65">
@@ -4731,45 +4731,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>453</v>
+        <v>429</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.6247240618101545</v>
+        <v>0.627039627039627</v>
       </c>
     </row>
     <row r="66">
@@ -4778,45 +4778,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>351</v>
+        <v>453</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>214</v>
+        <v>281</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>219</v>
+        <v>283</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6239316239316239</v>
+        <v>0.6247240618101545</v>
       </c>
     </row>
     <row r="67">
@@ -4825,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>429</v>
+        <v>351</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>163</v>
+        <v>132</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.62004662004662</v>
+        <v>0.6239316239316239</v>
       </c>
     </row>
     <row r="68">
@@ -4872,45 +4872,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>500</v>
+        <v>467</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="K68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.62</v>
+        <v>0.6231263383297645</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6179337231968811</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="70">
@@ -4966,45 +4966,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>414</v>
+        <v>513</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="G70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>301</v>
+      </c>
+      <c r="K70" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H70" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I70" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" s="9" t="n">
-        <v>243</v>
-      </c>
-      <c r="K70" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L70" s="9" t="n">
-        <v>252</v>
+        <v>317</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6179337231968811</v>
       </c>
     </row>
     <row r="71">
@@ -5013,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>381</v>
+        <v>544</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>151</v>
+        <v>208</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="I71" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I71" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="J71" s="9" t="n">
-        <v>224</v>
+        <v>308</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>230</v>
+        <v>336</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.6036745406824147</v>
+        <v>0.6176470588235294</v>
       </c>
     </row>
     <row r="72">
@@ -5060,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>558</v>
+        <v>381</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>335</v>
+        <v>224</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>0.6021505376344086</v>
+        <v>0.6089238845144357</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>467</v>
+        <v>414</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>280</v>
+        <v>243</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="M73" s="11" t="n">
-        <v>0.6017130620985011</v>
+        <v>0.6086956521739131</v>
       </c>
     </row>
     <row r="74">
@@ -5154,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>468</v>
+        <v>426</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>186</v>
+        <v>165</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>281</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>0.6004273504273504</v>
+        <v>259</v>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>0.607981220657277</v>
       </c>
     </row>
     <row r="75">
@@ -5201,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>400</v>
+        <v>558</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>237</v>
+        <v>338</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>240</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0.6</v>
+        <v>338</v>
+      </c>
+      <c r="M75" s="11" t="n">
+        <v>0.6057347670250897</v>
       </c>
     </row>
     <row r="76">
@@ -5248,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>360</v>
+        <v>440</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>210</v>
+        <v>262</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>216</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>0.6</v>
+        <v>266</v>
+      </c>
+      <c r="M76" s="11" t="n">
+        <v>0.6045454545454545</v>
       </c>
     </row>
     <row r="77">
@@ -5295,45 +5295,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>439</v>
+        <v>468</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.5990888382687927</v>
+        <v>0.6004273504273504</v>
       </c>
     </row>
     <row r="78">
@@ -5342,45 +5342,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>475</v>
+        <v>400</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>280</v>
+        <v>237</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>284</v>
+        <v>240</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0.5978947368421053</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="79">
@@ -5389,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>414</v>
+        <v>360</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="K79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.5942028985507246</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="80">
@@ -5436,27 +5436,27 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>426</v>
+        <v>475</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="H80" s="9" t="n">
         <v>0</v>
@@ -5465,16 +5465,16 @@
         <v>1</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.5938967136150235</v>
+        <v>0.5978947368421053</v>
       </c>
     </row>
     <row r="81">
@@ -5483,45 +5483,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I81" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.5928705440900562</v>
+        <v>0.596039603960396</v>
       </c>
     </row>
     <row r="82">
@@ -5530,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>465</v>
+        <v>414</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.5913978494623656</v>
+        <v>0.5942028985507246</v>
       </c>
     </row>
     <row r="83">
@@ -5577,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>504</v>
+        <v>465</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>196</v>
+        <v>183</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.5873015873015873</v>
+        <v>0.5913978494623656</v>
       </c>
     </row>
     <row r="84">
@@ -5638,31 +5638,31 @@
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>13</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I84" s="9" t="n">
         <v>5</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.5856573705179283</v>
+        <v>0.5912698412698413</v>
       </c>
     </row>
     <row r="85">
@@ -5688,28 +5688,28 @@
         <v>511</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.5851272015655578</v>
+        <v>0.5870841487279843</v>
       </c>
     </row>
     <row r="86">
@@ -5718,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="K86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.5822510822510822</v>
+        <v>0.5852631578947368</v>
       </c>
     </row>
     <row r="87">
@@ -5765,45 +5765,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>400</v>
+        <v>470</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>216</v>
+        <v>256</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>232</v>
+        <v>274</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.58</v>
+        <v>0.5829787234042553</v>
       </c>
     </row>
     <row r="88">
@@ -5812,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>440</v>
+        <v>463</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.5727272727272728</v>
+        <v>0.5809935205183585</v>
       </c>
     </row>
     <row r="89">
@@ -5859,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>475</v>
+        <v>400</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>272</v>
+        <v>216</v>
       </c>
       <c r="K89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>272</v>
+        <v>232</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.5726315789473684</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="90">
@@ -5906,45 +5906,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>364</v>
+        <v>440</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5727272727272728</v>
       </c>
     </row>
     <row r="91">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
@@ -5967,31 +5967,31 @@
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>427</v>
+        <v>547</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>183</v>
+        <v>219</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>234</v>
+        <v>313</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>243</v>
+        <v>313</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.5690866510538641</v>
+        <v>0.5722120658135283</v>
       </c>
     </row>
     <row r="92">
@@ -6000,45 +6000,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>470</v>
+        <v>364</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>179</v>
+        <v>156</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>267</v>
+        <v>208</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.5680851063829787</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="93">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -6061,31 +6061,31 @@
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>252</v>
+        <v>234</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.5672645739910314</v>
+        <v>0.5690866510538641</v>
       </c>
     </row>
     <row r="94">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
@@ -6108,31 +6108,31 @@
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>546</v>
+        <v>446</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>219</v>
+        <v>177</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>306</v>
+        <v>252</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>309</v>
+        <v>253</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5659340659340659</v>
+        <v>0.5672645739910314</v>
       </c>
     </row>
     <row r="95">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
@@ -6155,31 +6155,31 @@
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.565922920892495</v>
+        <v>0.5665236051502146</v>
       </c>
     </row>
     <row r="96">
@@ -6188,45 +6188,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5579399141630901</v>
+        <v>0.565922920892495</v>
       </c>
     </row>
     <row r="97">
@@ -6235,45 +6235,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="G97" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H97" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I97" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>246</v>
+      </c>
+      <c r="K97" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H97" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="I97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="9" t="n">
-        <v>240</v>
-      </c>
-      <c r="K97" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L97" s="9" t="n">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5558086560364465</v>
+        <v>0.5653104925053534</v>
       </c>
     </row>
     <row r="98">
@@ -6282,45 +6282,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>396</v>
+        <v>443</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>211</v>
+        <v>244</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5643340857787811</v>
       </c>
     </row>
     <row r="99">
@@ -6329,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>460</v>
+        <v>396</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>206</v>
+        <v>172</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>254</v>
+        <v>222</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5521739130434783</v>
+        <v>0.5606060606060606</v>
       </c>
     </row>
     <row r="100">
@@ -6423,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="G101" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H101" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>195</v>
+      </c>
+      <c r="K101" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="9" t="n">
-        <v>218</v>
-      </c>
-      <c r="K101" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L101" s="9" t="n">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.5483870967741935</v>
       </c>
     </row>
     <row r="102">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
@@ -6484,13 +6484,13 @@
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H102" s="9" t="n">
         <v>0</v>
@@ -6499,16 +6499,16 @@
         <v>0</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5388349514563107</v>
+        <v>0.5463659147869674</v>
       </c>
     </row>
     <row r="103">
@@ -6517,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>325</v>
+        <v>520</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>79</v>
+        <v>234</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>173</v>
+        <v>263</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>175</v>
+        <v>284</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5461538461538461</v>
       </c>
     </row>
     <row r="104">
@@ -6581,13 +6581,13 @@
         <v>455</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G104" s="9" t="n">
         <v>11</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I104" s="9" t="n">
         <v>10</v>
@@ -6599,10 +6599,10 @@
         <v>3</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.5362637362637362</v>
+        <v>0.545054945054945</v>
       </c>
     </row>
     <row r="105">
@@ -6611,45 +6611,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>511</v>
+        <v>456</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="G105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H105" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="I105" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5362035225048923</v>
+        <v>0.5394736842105263</v>
       </c>
     </row>
     <row r="106">
@@ -6658,45 +6658,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>368</v>
+        <v>412</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>195</v>
+        <v>221</v>
       </c>
       <c r="K106" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5353260869565217</v>
+        <v>0.5388349514563107</v>
       </c>
     </row>
     <row r="107">
@@ -6705,45 +6705,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>454</v>
+        <v>325</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>211</v>
+        <v>79</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="H107" s="9" t="n">
         <v>2</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>240</v>
+        <v>173</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>243</v>
+        <v>175</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5352422907488987</v>
+        <v>0.5384615384615384</v>
       </c>
     </row>
     <row r="108">
@@ -6869,13 +6869,13 @@
         <v>8</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I110" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>0</v>
@@ -7034,45 +7034,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>408</v>
+        <v>508</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>198</v>
+        <v>247</v>
       </c>
       <c r="G114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H114" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="I114" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5122549019607843</v>
+        <v>0.5137795275590551</v>
       </c>
     </row>
     <row r="115">
@@ -7081,45 +7081,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>508</v>
+        <v>408</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>248</v>
+        <v>198</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>260</v>
+        <v>209</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5118110236220472</v>
+        <v>0.5122549019607843</v>
       </c>
     </row>
     <row r="116">
@@ -7128,45 +7128,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>454</v>
+        <v>477</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H116" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="I116" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>189</v>
+      </c>
+      <c r="K116" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="I116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="9" t="n">
-        <v>225</v>
-      </c>
-      <c r="K116" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L116" s="9" t="n">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5088105726872246</v>
+        <v>0.5115303983228512</v>
       </c>
     </row>
     <row r="117">
@@ -7175,45 +7175,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>405</v>
+        <v>454</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I117" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>203</v>
+        <v>231</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5012345679012346</v>
+        <v>0.5088105726872246</v>
       </c>
     </row>
     <row r="118">
@@ -7222,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5011764705882353</v>
+        <v>0.5012345679012346</v>
       </c>
     </row>
     <row r="119">
@@ -7269,45 +7269,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>476</v>
+        <v>425</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5</v>
+        <v>0.5011764705882353</v>
       </c>
     </row>
     <row r="120">
@@ -7316,45 +7316,45 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>346</v>
+        <v>399</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.5</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="121">
@@ -7363,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>399</v>
+        <v>345</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I121" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="J121" s="9" t="n">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.4987468671679198</v>
+        <v>0.4985507246376812</v>
       </c>
     </row>
     <row r="122">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
@@ -7424,31 +7424,31 @@
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I122" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J122" s="9" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="K122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.4928229665071771</v>
+        <v>0.4977168949771689</v>
       </c>
     </row>
     <row r="123">
@@ -7457,45 +7457,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.489749430523918</v>
+        <v>0.4928229665071771</v>
       </c>
     </row>
     <row r="124">
@@ -7504,45 +7504,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>450</v>
+        <v>416</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.4866666666666667</v>
+        <v>0.4927884615384615</v>
       </c>
     </row>
     <row r="125">
@@ -7551,45 +7551,45 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.4840182648401827</v>
+        <v>0.4920273348519363</v>
       </c>
     </row>
     <row r="126">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
@@ -7612,31 +7612,31 @@
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>414</v>
+        <v>451</v>
       </c>
       <c r="F126" s="9" t="n">
+        <v>229</v>
+      </c>
+      <c r="G126" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H126" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J126" s="9" t="n">
         <v>213</v>
       </c>
-      <c r="G126" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" s="9" t="n">
-        <v>200</v>
-      </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.4830917874396136</v>
+        <v>0.4878048780487805</v>
       </c>
     </row>
     <row r="127">
@@ -7645,45 +7645,45 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.4807256235827664</v>
+        <v>0.4830917874396136</v>
       </c>
     </row>
     <row r="128">
@@ -7692,45 +7692,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="F128" s="9" t="n">
         <v>215</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>147</v>
+        <v>196</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4806763285024155</v>
+        <v>0.4807256235827664</v>
       </c>
     </row>
     <row r="129">
@@ -7806,25 +7806,25 @@
         <v>210</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H130" s="9" t="n">
         <v>8</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4638009049773755</v>
+        <v>0.4705882352941176</v>
       </c>
     </row>
     <row r="131">
@@ -7833,45 +7833,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>391</v>
+        <v>514</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>210</v>
+        <v>269</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4629156010230179</v>
+        <v>0.4669260700389105</v>
       </c>
     </row>
     <row r="132">
@@ -7880,45 +7880,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>513</v>
+        <v>391</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>272</v>
+        <v>210</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>215</v>
+        <v>181</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4600389863547758</v>
+        <v>0.4629156010230179</v>
       </c>
     </row>
     <row r="133">
@@ -7927,45 +7927,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>417</v>
+        <v>459</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>149</v>
+        <v>198</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4556354916067146</v>
+        <v>0.4596949891067538</v>
       </c>
     </row>
     <row r="134">
@@ -7974,45 +7974,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>459</v>
+        <v>417</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>186</v>
+        <v>149</v>
       </c>
       <c r="K134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.4553376906318083</v>
+        <v>0.4580335731414868</v>
       </c>
     </row>
     <row r="135">
@@ -8035,7 +8035,7 @@
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F135" s="9" t="n">
         <v>228</v>
@@ -8044,22 +8044,22 @@
         <v>2</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I135" s="9" t="n">
         <v>15</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.4549763033175356</v>
       </c>
     </row>
     <row r="136">
@@ -8135,7 +8135,7 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8149,7 +8149,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 20 Juli 2026</t>
+          <t>Hari/Tanggal : 21 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 22.01 WITA</t>
+          <t>Pukul        : 10.25 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8268,31 +8268,31 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2886</v>
+        <v>2898</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>412</v>
+        <v>385</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2427</v>
+        <v>2496</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2434</v>
+        <v>2505</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8433818433818433</v>
+        <v>0.8643892339544513</v>
       </c>
     </row>
     <row r="8">
@@ -8315,16 +8315,16 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>27</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>9</v>
@@ -8333,13 +8333,13 @@
         <v>1528</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7593503937007874</v>
+        <v>0.7584849975405804</v>
       </c>
     </row>
     <row r="9">
@@ -8362,31 +8362,31 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2808</v>
+        <v>2812</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>680</v>
+        <v>666</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2083</v>
+        <v>2088</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7418091168091168</v>
+        <v>0.7425320056899004</v>
       </c>
     </row>
     <row r="10">
@@ -8409,31 +8409,31 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2899</v>
+        <v>2906</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2123</v>
+        <v>2131</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7323214901690238</v>
+        <v>0.7333103922918101</v>
       </c>
     </row>
     <row r="11">
@@ -8456,31 +8456,31 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2502</v>
+        <v>2505</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1803</v>
+        <v>1828</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1803</v>
+        <v>1828</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7206235011990407</v>
+        <v>0.7297405189620758</v>
       </c>
     </row>
     <row r="12">
@@ -8503,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2839</v>
+        <v>2854</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>778</v>
+        <v>755</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1994</v>
+        <v>2007</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7079957731595631</v>
+        <v>0.7060266292922215</v>
       </c>
     </row>
     <row r="13">
@@ -8553,19 +8553,19 @@
         <v>2110</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>7</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>0</v>
@@ -8597,31 +8597,31 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2767</v>
+        <v>2774</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>927</v>
+        <v>913</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6490784242862305</v>
+        <v>0.6470800288392213</v>
       </c>
     </row>
     <row r="15">
@@ -8644,31 +8644,31 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2902</v>
+        <v>2903</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>1012</v>
+        <v>991</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1826</v>
+        <v>1856</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1833</v>
+        <v>1868</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6316333563059958</v>
+        <v>0.6434722700654496</v>
       </c>
     </row>
     <row r="16">
@@ -8691,19 +8691,19 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2395</v>
+        <v>2403</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="G16" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I16" s="9" t="n">
         <v>11</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>6</v>
       </c>
       <c r="J16" s="9" t="n">
         <v>1504</v>
@@ -8712,10 +8712,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6304801670146137</v>
+        <v>0.630461922596754</v>
       </c>
     </row>
     <row r="17">
@@ -8741,16 +8741,16 @@
         <v>2164</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>17</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>1325</v>
@@ -8759,10 +8759,10 @@
         <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.6141404805914972</v>
+        <v>0.6136783733826248</v>
       </c>
     </row>
     <row r="18">
@@ -8771,45 +8771,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2816</v>
+        <v>2890</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1130</v>
+        <v>1072</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1641</v>
+        <v>1730</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1680</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>0.5965909090909091</v>
+        <v>1753</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0.6065743944636678</v>
       </c>
     </row>
     <row r="19">
@@ -8818,45 +8818,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2884</v>
+        <v>2825</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1077</v>
+        <v>1125</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1697</v>
+        <v>1632</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1720</v>
+        <v>1679</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.5963938973647711</v>
+        <v>0.5943362831858408</v>
       </c>
     </row>
     <row r="20">
@@ -8865,45 +8865,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2448</v>
+        <v>2670</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>903</v>
+        <v>1127</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1350</v>
+        <v>1519</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1361</v>
+        <v>1520</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5559640522875817</v>
+        <v>0.5692883895131086</v>
       </c>
     </row>
     <row r="21">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -8926,31 +8926,31 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2664</v>
+        <v>2697</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1480</v>
+        <v>1498</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1481</v>
+        <v>1501</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5559309309309309</v>
+        <v>0.5565443084909159</v>
       </c>
     </row>
     <row r="22">
@@ -8959,45 +8959,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2696</v>
+        <v>2451</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1146</v>
+        <v>897</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1490</v>
+        <v>1350</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1493</v>
+        <v>1359</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5537833827893175</v>
+        <v>0.554467564259486</v>
       </c>
     </row>
     <row r="23">
@@ -9020,31 +9020,31 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1235</v>
+        <v>1255</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1261</v>
+        <v>1279</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5454152249134948</v>
+        <v>0.5527225583405359</v>
       </c>
     </row>
     <row r="24">
@@ -9053,45 +9053,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>1429</v>
+        <v>2546</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>359</v>
+        <v>1161</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>294</v>
+        <v>2</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>762</v>
+        <v>1371</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>764</v>
+        <v>1377</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5346396081175647</v>
+        <v>0.5408483896307934</v>
       </c>
     </row>
     <row r="25">
@@ -9100,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2545</v>
+        <v>1433</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1171</v>
+        <v>356</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>3</v>
+        <v>294</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1327</v>
+        <v>766</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1331</v>
+        <v>768</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5229862475442043</v>
+        <v>0.5359385903698535</v>
       </c>
     </row>
     <row r="26">
@@ -9147,45 +9147,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2712</v>
+        <v>2413</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1227</v>
+        <v>1077</v>
       </c>
       <c r="G26" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>69</v>
+      </c>
+      <c r="I26" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="H26" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="I26" s="9" t="n">
-        <v>5</v>
-      </c>
       <c r="J26" s="9" t="n">
-        <v>1389</v>
+        <v>1186</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1394</v>
+        <v>1241</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5140117994100295</v>
+        <v>0.5142975549108993</v>
       </c>
     </row>
     <row r="27">
@@ -9194,45 +9194,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2410</v>
+        <v>2712</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1092</v>
+        <v>1227</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1179</v>
+        <v>1389</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1229</v>
+        <v>1394</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.5099585062240664</v>
+        <v>0.5140117994100295</v>
       </c>
     </row>
     <row r="28">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Olfira Sicilia Budiman</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -9255,31 +9255,31 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2065</v>
+        <v>2090</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1016</v>
+        <v>996</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>990</v>
+        <v>967</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1014</v>
+        <v>1029</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.4910411622276029</v>
+        <v>0.4923444976076555</v>
       </c>
     </row>
     <row r="29">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Olfira Sicilia Budiman</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
@@ -9302,31 +9302,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2087</v>
+        <v>2065</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>996</v>
+        <v>1016</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>962</v>
+        <v>990</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1022</v>
+        <v>1011</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.4896981312889315</v>
+        <v>0.489588377723971</v>
       </c>
     </row>
   </sheetData>
@@ -9360,7 +9360,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 20 Juli 2026</t>
+          <t>Hari/Tanggal : 21 Juli 2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 22.01 WITA</t>
+          <t>Pukul        : 10.25 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.7811418685121108</v>
+        <v>0.783923941227312</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7676831185161899</v>
+        <v>0.7723704866562009</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7471282705807275</v>
+        <v>0.7553259141494436</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9474,15 +9474,15 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.720666344760985</v>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.7255323725532372</v>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9492,15 +9492,15 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7165804225959466</v>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.7224233647115617</v>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.62071992976295</v>
+        <v>0.6233538191395961</v>
       </c>
       <c r="D14" s="17" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.59765625</v>
+        <v>0.6007079646017699</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.5852578906851424</v>
+        <v>0.5883935434281322</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5562770562770563</v>
+        <v>0.5596885813148789</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -9622,7 +9622,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5486868186323092</v>
+        <v>0.5531625201138755</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.543037088873338</v>
+        <v>0.5464061409630147</v>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5344398340248963</v>
+        <v>0.5428926647326979</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.5339870367292671</v>
+        <v>0.5358327803583278</v>
       </c>
       <c r="D21" s="19" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -611,7 +611,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.59 WITA</t>
+          <t>Pukul        : 21.00 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.59 WITA</t>
+          <t>Pukul        : 21.00 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8161,7 +8161,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.59 WITA</t>
+          <t>Pukul        : 21.00 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9372,7 +9372,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.59 WITA</t>
+          <t>Pukul        : 21.00 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +91,10 @@
     </font>
     <font>
       <color rgb="00595959"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="8">
@@ -163,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -188,6 +192,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -610,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.30 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -744,62 +750,62 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4143</v>
+        <v>4157</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1116</v>
+        <v>1097</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2907</v>
+        <v>2910</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
         <v/>
       </c>
       <c r="N7" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O7" s="10">
         <f>N7/B7</f>
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>2993</v>
+        <v>3032</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -813,41 +819,41 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1433</v>
+        <v>1439</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>356</v>
+        <v>338</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
         <v/>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K8" s="10">
         <f>J8/B8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>766</v>
+        <v>802</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -861,14 +867,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>783</v>
+        <v>826</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -882,62 +888,62 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6290</v>
+        <v>6336</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1451</v>
+        <v>1365</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>109</v>
+        <v>69</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4451</v>
+        <v>4611</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
         <v/>
       </c>
       <c r="N9" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="10">
         <f>N9/B9</f>
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4751</v>
+        <v>4877</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -951,13 +957,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3185</v>
+        <v>3212</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>725</v>
+        <v>680</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -971,42 +977,42 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
         <v/>
       </c>
       <c r="J10" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K10" s="10">
         <f>J10/B10</f>
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2383</v>
+        <v>2477</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
         <v/>
       </c>
       <c r="N10" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O10" s="10">
         <f>N10/B10</f>
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2460</v>
+        <v>2532</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1020,41 +1026,41 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>1139</v>
+        <v>1146</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>412</v>
+        <v>396</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
         <v/>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="K11" s="10">
         <f>J11/B11</f>
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>694</v>
+        <v>718</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1068,14 +1074,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>710</v>
+        <v>739</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1089,13 +1095,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1025</v>
+        <v>1035</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
@@ -1109,14 +1115,14 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
         <v/>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="10">
         <f>J12/B12</f>
@@ -1137,14 +1143,14 @@
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>647</v>
+        <v>678</v>
       </c>
       <c r="Q12" s="11">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1158,13 +1164,13 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4624</v>
+        <v>4650</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1999</v>
+        <v>1946</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
@@ -1178,21 +1184,21 @@
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>164</v>
+        <v>220</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2414</v>
+        <v>2442</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1206,14 +1212,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2588</v>
+        <v>2667</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1227,41 +1233,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6028</v>
+        <v>6081</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2770</v>
+        <v>2686</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3051</v>
+        <v>3149</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1275,14 +1281,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3230</v>
+        <v>3364</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1296,41 +1302,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8079</v>
+        <v>8130</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3499</v>
+        <v>3385</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>54</v>
+        <v>143</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4406</v>
+        <v>4489</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1344,14 +1350,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4469</v>
+        <v>4642</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1365,41 +1371,41 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5204</v>
+        <v>5222</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>2023</v>
+        <v>1949</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>2985</v>
+        <v>3087</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1413,14 +1419,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3062</v>
+        <v>3155</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1434,62 +1440,62 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2413</v>
+        <v>2418</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1077</v>
+        <v>1033</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1310</v>
+        <v>1362</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1503,62 +1509,62 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9298</v>
+        <v>9380</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2481</v>
+        <v>2310</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>46</v>
+        <v>162</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6675</v>
+        <v>6780</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
         <v/>
       </c>
       <c r="N18" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O18" s="10">
         <f>N18/B18</f>
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6746</v>
+        <v>6970</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1572,13 +1578,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1592,7 +1598,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1606,7 +1612,7 @@
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>897</v>
+        <v>907</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1620,14 +1626,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>907</v>
+        <v>932</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1710,13 +1716,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2825</v>
+        <v>2835</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1125</v>
+        <v>1090</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1730,21 +1736,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1632</v>
+        <v>1724</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1758,14 +1764,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1697</v>
+        <v>1742</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1911,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.30 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2060,31 +2066,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>6</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.964200477326969</v>
+        <v>0.9929577464788732</v>
       </c>
     </row>
     <row r="9">
@@ -2107,16 +2113,16 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
@@ -2128,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>534</v>
+        <v>556</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.956989247311828</v>
+        <v>0.9737302977232924</v>
       </c>
     </row>
     <row r="10">
@@ -2154,31 +2160,31 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.9307692307692308</v>
+        <v>0.9358490566037736</v>
       </c>
     </row>
     <row r="11">
@@ -2216,10 +2222,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>283</v>
@@ -2234,45 +2240,45 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Fitria Rianti Gorosita</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8818681318681318</v>
+        <v>0.8932291666666665</v>
       </c>
     </row>
     <row r="13">
@@ -2281,45 +2287,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Alfred Jonathan</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="I13" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" s="9" t="n">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.8726790450928382</v>
+        <v>0.8818681318681318</v>
       </c>
     </row>
     <row r="14">
@@ -2328,45 +2334,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Fitria Rianti Gorosita</t>
+          <t>Alfred Jonathan</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.8713910761154857</v>
+        <v>0.8726790450928382</v>
       </c>
     </row>
     <row r="15">
@@ -2389,19 +2395,19 @@
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" s="9" t="n">
         <v>2</v>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>5</v>
       </c>
       <c r="J15" s="9" t="n">
         <v>307</v>
@@ -2410,10 +2416,10 @@
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.841823056300268</v>
+        <v>0.8567639257294429</v>
       </c>
     </row>
     <row r="16">
@@ -2422,45 +2428,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>426</v>
+        <v>507</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>264</v>
+        <v>420</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>357</v>
+        <v>425</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8382642998027613</v>
       </c>
     </row>
     <row r="17">
@@ -2469,45 +2475,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>401</v>
+        <v>426</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8304239401496259</v>
+        <v>0.8380281690140845</v>
       </c>
     </row>
     <row r="18">
@@ -2516,45 +2522,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>493</v>
+        <v>405</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>392</v>
+        <v>337</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>407</v>
+        <v>339</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8255578093306287</v>
+        <v>0.8370370370370369</v>
       </c>
     </row>
     <row r="19">
@@ -2577,31 +2583,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8177083333333335</v>
+        <v>0.8324742268041238</v>
       </c>
     </row>
     <row r="20">
@@ -2610,45 +2616,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>477</v>
+        <v>415</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>377</v>
+        <v>326</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8155136268343816</v>
+        <v>0.8313253012048193</v>
       </c>
     </row>
     <row r="21">
@@ -2657,45 +2663,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>423</v>
+        <v>499</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>336</v>
+        <v>401</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>342</v>
+        <v>410</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8085106382978722</v>
+        <v>0.8216432865731462</v>
       </c>
     </row>
     <row r="22">
@@ -2704,7 +2710,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -2718,31 +2724,31 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.7981438515081206</v>
+        <v>0.8215962441314554</v>
       </c>
     </row>
     <row r="23">
@@ -2751,45 +2757,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>495</v>
+        <v>431</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>394</v>
+        <v>346</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>394</v>
+        <v>354</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.795959595959596</v>
+        <v>0.8213457076566125</v>
       </c>
     </row>
     <row r="24">
@@ -2798,45 +2804,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Cevin Sander Zon Makapedua</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>389</v>
+        <v>478</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>299</v>
+        <v>377</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>309</v>
+        <v>392</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.7943444730077122</v>
+        <v>0.8200836820083682</v>
       </c>
     </row>
     <row r="25">
@@ -2845,45 +2851,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>411</v>
+        <v>503</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>326</v>
+        <v>398</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>326</v>
+        <v>407</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.7931873479318735</v>
+        <v>0.8091451292246521</v>
       </c>
     </row>
     <row r="26">
@@ -2892,45 +2898,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Cevin Sander Zon Makapedua</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>499</v>
+        <v>392</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>393</v>
+        <v>312</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>395</v>
+        <v>316</v>
       </c>
       <c r="M26" s="11" t="n">
-        <v>0.7915831663326653</v>
+        <v>0.8061224489795918</v>
       </c>
     </row>
     <row r="27">
@@ -2953,31 +2959,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7867924528301887</v>
+        <v>0.7879924953095684</v>
       </c>
     </row>
     <row r="28">
@@ -2986,45 +2992,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>384</v>
+        <v>498</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>296</v>
+        <v>390</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.7708333333333335</v>
+        <v>0.7831325301204819</v>
       </c>
     </row>
     <row r="29">
@@ -3033,45 +3039,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>490</v>
+        <v>386</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>323</v>
+        <v>281</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>375</v>
+        <v>298</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7653061224489796</v>
+        <v>0.7720207253886009</v>
       </c>
     </row>
     <row r="30">
@@ -3080,7 +3086,7 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
@@ -3094,31 +3100,31 @@
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7470449172576832</v>
+        <v>0.7714285714285716</v>
       </c>
     </row>
     <row r="31">
@@ -3127,7 +3133,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
@@ -3141,31 +3147,31 @@
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7463768115942028</v>
+        <v>0.7570754716981132</v>
       </c>
     </row>
     <row r="32">
@@ -3188,31 +3194,31 @@
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7440758293838863</v>
+        <v>0.7570754716981132</v>
       </c>
     </row>
     <row r="33">
@@ -3221,45 +3227,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>502</v>
+        <v>410</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>356</v>
+        <v>291</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>371</v>
+        <v>310</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7390438247011953</v>
+        <v>0.7560975609756098</v>
       </c>
     </row>
     <row r="34">
@@ -3268,45 +3274,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>556</v>
+        <v>503</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>406</v>
+        <v>378</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7302158273381295</v>
+        <v>0.7514910536779325</v>
       </c>
     </row>
     <row r="35">
@@ -3329,31 +3335,31 @@
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>8</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.724609375</v>
+        <v>0.7495183044315994</v>
       </c>
     </row>
     <row r="36">
@@ -3362,45 +3368,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>539</v>
+        <v>560</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>389</v>
+        <v>414</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7217068645640075</v>
+        <v>0.7392857142857143</v>
       </c>
     </row>
     <row r="37">
@@ -3409,45 +3415,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>402</v>
+        <v>350</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7213930348258707</v>
+        <v>0.7371428571428571</v>
       </c>
     </row>
     <row r="38">
@@ -3456,45 +3462,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>501</v>
+        <v>544</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="G38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H38" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="I38" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>354</v>
+        <v>396</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>361</v>
+        <v>400</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.720558882235529</v>
+        <v>0.7352941176470589</v>
       </c>
     </row>
     <row r="39">
@@ -3503,45 +3509,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>347</v>
+        <v>425</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>249</v>
+        <v>312</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7175792507204612</v>
+        <v>0.7341176470588234</v>
       </c>
     </row>
     <row r="40">
@@ -3550,45 +3556,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>453</v>
+        <v>507</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>323</v>
+        <v>370</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7130242825607064</v>
+        <v>0.7297830374753451</v>
       </c>
     </row>
     <row r="41">
@@ -3597,45 +3603,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>420</v>
+        <v>505</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>288</v>
+        <v>349</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>298</v>
+        <v>364</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.7095238095238094</v>
+        <v>0.7207920792079208</v>
       </c>
     </row>
     <row r="42">
@@ -3644,45 +3650,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>503</v>
+        <v>453</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7037773359840955</v>
+        <v>0.7130242825607064</v>
       </c>
     </row>
     <row r="43">
@@ -3705,19 +3711,19 @@
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="9" t="n">
         <v>253</v>
@@ -3726,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.7007874015748031</v>
+        <v>0.711340206185567</v>
       </c>
     </row>
     <row r="44">
@@ -3738,45 +3744,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>504</v>
+        <v>458</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H44" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="I44" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I44" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J44" s="9" t="n">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>349</v>
+        <v>323</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.6924603174603174</v>
+        <v>0.7052401746724891</v>
       </c>
     </row>
     <row r="45">
@@ -3785,45 +3791,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>389</v>
+        <v>505</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="G45" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H45" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>350</v>
+      </c>
+      <c r="K45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="I45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="9" t="n">
-        <v>223</v>
-      </c>
-      <c r="K45" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" s="9" t="n">
-        <v>266</v>
+        <v>354</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.6838046272493572</v>
+        <v>0.7009900990099009</v>
       </c>
     </row>
     <row r="46">
@@ -3846,31 +3852,31 @@
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.6802168021680217</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="47">
@@ -3879,45 +3885,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>527</v>
+        <v>469</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>358</v>
+        <v>327</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.6793168880455408</v>
+        <v>0.697228144989339</v>
       </c>
     </row>
     <row r="48">
@@ -3926,45 +3932,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>345</v>
+        <v>520</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>230</v>
+        <v>341</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>234</v>
+        <v>360</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6782608695652174</v>
+        <v>0.6923076923076923</v>
       </c>
     </row>
     <row r="49">
@@ -3973,45 +3979,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>515</v>
+        <v>347</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>342</v>
+        <v>228</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>349</v>
+        <v>240</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6776699029126214</v>
+        <v>0.69164265129683</v>
       </c>
     </row>
     <row r="50">
@@ -4020,45 +4026,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>455</v>
+        <v>389</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>287</v>
+        <v>223</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>306</v>
+        <v>268</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6725274725274726</v>
+        <v>0.6889460154241646</v>
       </c>
     </row>
     <row r="51">
@@ -4067,7 +4073,7 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
@@ -4081,10 +4087,10 @@
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>289</v>
+        <v>528</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>95</v>
+        <v>166</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0</v>
@@ -4093,19 +4099,19 @@
         <v>0</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>191</v>
+        <v>360</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>194</v>
+        <v>362</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.671280276816609</v>
+        <v>0.6856060606060607</v>
       </c>
     </row>
     <row r="52">
@@ -4114,45 +4120,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>460</v>
+        <v>380</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>305</v>
+        <v>259</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6630434782608695</v>
+        <v>0.6815789473684211</v>
       </c>
     </row>
     <row r="53">
@@ -4161,45 +4167,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>449</v>
+        <v>416</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>9</v>
+        <v>59</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6570155902004454</v>
+        <v>0.673076923076923</v>
       </c>
     </row>
     <row r="54">
@@ -4208,45 +4214,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6541850220264317</v>
+        <v>0.6728971962616822</v>
       </c>
     </row>
     <row r="55">
@@ -4255,45 +4261,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>424</v>
+        <v>458</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6533018867924528</v>
+        <v>0.6724890829694323</v>
       </c>
     </row>
     <row r="56">
@@ -4302,45 +4308,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>464</v>
+        <v>289</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="G56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="I56" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J56" s="9" t="n">
-        <v>300</v>
+        <v>191</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>303</v>
+        <v>194</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6530172413793103</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="57">
@@ -4363,31 +4369,31 @@
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.6495535714285714</v>
+        <v>0.6703539823008849</v>
       </c>
     </row>
     <row r="58">
@@ -4396,45 +4402,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>217</v>
+        <v>260</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6472019464720195</v>
+        <v>0.6674876847290641</v>
       </c>
     </row>
     <row r="59">
@@ -4443,45 +4449,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>376</v>
+        <v>452</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>237</v>
+        <v>284</v>
       </c>
       <c r="K59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6462765957446809</v>
+        <v>0.6637168141592921</v>
       </c>
     </row>
     <row r="60">
@@ -4490,45 +4496,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>129</v>
+        <v>157</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="H60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6413793103448274</v>
+        <v>0.6573275862068965</v>
       </c>
     </row>
     <row r="61">
@@ -4537,45 +4543,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>625</v>
+        <v>459</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>219</v>
+        <v>159</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>394</v>
+        <v>281</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>399</v>
+        <v>300</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6384</v>
+        <v>0.65359477124183</v>
       </c>
     </row>
     <row r="62">
@@ -4584,45 +4590,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>404</v>
+        <v>502</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>249</v>
+        <v>324</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>257</v>
+        <v>328</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6361386138613861</v>
+        <v>0.6533864541832669</v>
       </c>
     </row>
     <row r="63">
@@ -4631,45 +4637,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>157</v>
+        <v>129</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.634032634032634</v>
+        <v>0.6505747126436782</v>
       </c>
     </row>
     <row r="64">
@@ -4678,45 +4684,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6285140562248996</v>
+        <v>0.6447105788423154</v>
       </c>
     </row>
     <row r="65">
@@ -4739,10 +4745,10 @@
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
@@ -4754,16 +4760,16 @@
         <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.627039627039627</v>
+        <v>0.6412037037037037</v>
       </c>
     </row>
     <row r="66">
@@ -4772,45 +4778,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6247240618101545</v>
+        <v>0.639344262295082</v>
       </c>
     </row>
     <row r="67">
@@ -4819,45 +4825,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>351</v>
+        <v>625</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>214</v>
+        <v>394</v>
       </c>
       <c r="K67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>219</v>
+        <v>399</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6239316239316239</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="68">
@@ -4883,28 +4889,28 @@
         <v>467</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="K68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.6231263383297645</v>
+        <v>0.6381156316916489</v>
       </c>
     </row>
     <row r="69">
@@ -4913,45 +4919,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>500</v>
+        <v>386</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>304</v>
+        <v>233</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>310</v>
+        <v>245</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.62</v>
+        <v>0.6347150259067358</v>
       </c>
     </row>
     <row r="70">
@@ -4960,24 +4966,24 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>513</v>
+        <v>429</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>196</v>
+        <v>157</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>0</v>
@@ -4986,19 +4992,19 @@
         <v>0</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>317</v>
+        <v>272</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.6179337231968811</v>
+        <v>0.634032634032634</v>
       </c>
     </row>
     <row r="71">
@@ -5007,45 +5013,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>544</v>
+        <v>352</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>308</v>
+        <v>211</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>336</v>
-      </c>
-      <c r="M71" s="12" t="n">
-        <v>0.6176470588235294</v>
+        <v>223</v>
+      </c>
+      <c r="M71" s="11" t="n">
+        <v>0.6335227272727273</v>
       </c>
     </row>
     <row r="72">
@@ -5054,45 +5060,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>381</v>
+        <v>515</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>224</v>
+        <v>324</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>232</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>0.6089238845144357</v>
+        <v>326</v>
+      </c>
+      <c r="M72" s="11" t="n">
+        <v>0.6330097087378641</v>
       </c>
     </row>
     <row r="73">
@@ -5101,45 +5107,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>414</v>
+        <v>572</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>161</v>
+        <v>201</v>
       </c>
       <c r="G73" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H73" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="I73" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="I73" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="J73" s="9" t="n">
-        <v>243</v>
+        <v>326</v>
       </c>
       <c r="K73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>252</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>0.6086956521739131</v>
+        <v>360</v>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>0.6293706293706294</v>
       </c>
     </row>
     <row r="74">
@@ -5148,45 +5154,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>259</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>0.607981220657277</v>
+        <v>277</v>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>0.6281179138321995</v>
       </c>
     </row>
     <row r="75">
@@ -5195,45 +5201,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>558</v>
+        <v>427</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>338</v>
+        <v>266</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>338</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0.6057347670250897</v>
+        <v>268</v>
+      </c>
+      <c r="M75" s="11" t="n">
+        <v>0.6276346604215457</v>
       </c>
     </row>
     <row r="76">
@@ -5242,45 +5248,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>266</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>0.6045454545454545</v>
+        <v>299</v>
+      </c>
+      <c r="M76" s="11" t="n">
+        <v>0.6255230125523012</v>
       </c>
     </row>
     <row r="77">
@@ -5303,10 +5309,10 @@
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>1</v>
@@ -5315,19 +5321,19 @@
         <v>1</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>281</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>0.6004273504273504</v>
+        <v>293</v>
+      </c>
+      <c r="M77" s="11" t="n">
+        <v>0.6247334754797441</v>
       </c>
     </row>
     <row r="78">
@@ -5336,45 +5342,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>400</v>
+        <v>546</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>160</v>
+        <v>205</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I78" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>237</v>
+        <v>333</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>240</v>
-      </c>
-      <c r="M78" s="12" t="n">
-        <v>0.6</v>
+        <v>341</v>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>0.6245421245421245</v>
       </c>
     </row>
     <row r="79">
@@ -5383,45 +5389,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>216</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>0.6</v>
+        <v>252</v>
+      </c>
+      <c r="M79" s="11" t="n">
+        <v>0.6237623762376238</v>
       </c>
     </row>
     <row r="80">
@@ -5430,45 +5436,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>475</v>
+        <v>415</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>284</v>
-      </c>
-      <c r="M80" s="12" t="n">
-        <v>0.5978947368421053</v>
+        <v>258</v>
+      </c>
+      <c r="M80" s="11" t="n">
+        <v>0.6216867469879518</v>
       </c>
     </row>
     <row r="81">
@@ -5491,31 +5497,31 @@
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="K81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>301</v>
-      </c>
-      <c r="M81" s="12" t="n">
-        <v>0.596039603960396</v>
+        <v>315</v>
+      </c>
+      <c r="M81" s="11" t="n">
+        <v>0.618860510805501</v>
       </c>
     </row>
     <row r="82">
@@ -5524,45 +5530,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.5942028985507246</v>
+        <v>0.6172248803827751</v>
       </c>
     </row>
     <row r="83">
@@ -5571,45 +5577,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.5913978494623656</v>
+        <v>0.6171548117154811</v>
       </c>
     </row>
     <row r="84">
@@ -5618,45 +5624,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>504</v>
+        <v>559</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>288</v>
+        <v>344</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.5912698412698413</v>
+        <v>0.6153846153846154</v>
       </c>
     </row>
     <row r="85">
@@ -5679,31 +5685,31 @@
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.5870841487279843</v>
+        <v>0.6143410852713178</v>
       </c>
     </row>
     <row r="86">
@@ -5712,45 +5718,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="K86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.5852631578947368</v>
+        <v>0.610752688172043</v>
       </c>
     </row>
     <row r="87">
@@ -5759,7 +5765,7 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
@@ -5773,31 +5779,31 @@
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I87" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="9" t="n">
         <v>274</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.5829787234042553</v>
+        <v>0.6088888888888889</v>
       </c>
     </row>
     <row r="88">
@@ -5806,45 +5812,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>463</v>
+        <v>366</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>269</v>
+        <v>222</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.5809935205183585</v>
+        <v>0.6065573770491803</v>
       </c>
     </row>
     <row r="89">
@@ -5853,45 +5859,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="I89" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>216</v>
+        <v>256</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>232</v>
+        <v>260</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.58</v>
+        <v>0.6046511627906976</v>
       </c>
     </row>
     <row r="90">
@@ -5900,45 +5906,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>440</v>
+        <v>361</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>252</v>
+        <v>211</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.5727272727272728</v>
+        <v>0.6011080332409973</v>
       </c>
     </row>
     <row r="91">
@@ -5947,45 +5953,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>547</v>
+        <v>450</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>219</v>
+        <v>180</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>313</v>
+        <v>263</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>313</v>
+        <v>270</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.5722120658135283</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="92">
@@ -5994,45 +6000,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>364</v>
+        <v>402</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="I92" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I92" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J92" s="9" t="n">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>208</v>
+        <v>241</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.599502487562189</v>
       </c>
     </row>
     <row r="93">
@@ -6041,7 +6047,7 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
@@ -6055,31 +6061,31 @@
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>427</v>
+        <v>469</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>234</v>
+        <v>280</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>243</v>
+        <v>280</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.5690866510538641</v>
+        <v>0.5970149253731343</v>
       </c>
     </row>
     <row r="94">
@@ -6088,45 +6094,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>446</v>
+        <v>504</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>253</v>
+        <v>300</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5672645739910314</v>
+        <v>0.5952380952380952</v>
       </c>
     </row>
     <row r="95">
@@ -6135,45 +6141,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.5665236051502146</v>
+        <v>0.594017094017094</v>
       </c>
     </row>
     <row r="96">
@@ -6182,45 +6188,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>493</v>
+        <v>469</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J96" s="9" t="n">
         <v>269</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.565922920892495</v>
+        <v>0.5906183368869936</v>
       </c>
     </row>
     <row r="97">
@@ -6229,45 +6235,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5653104925053534</v>
+        <v>0.5902335456475584</v>
       </c>
     </row>
     <row r="98">
@@ -6276,45 +6282,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>443</v>
+        <v>325</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>244</v>
+        <v>186</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>250</v>
+        <v>191</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5643340857787811</v>
+        <v>0.5876923076923077</v>
       </c>
     </row>
     <row r="99">
@@ -6323,45 +6329,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>396</v>
+        <v>445</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="K99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>222</v>
+        <v>254</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5606060606060606</v>
+        <v>0.5707865168539326</v>
       </c>
     </row>
     <row r="100">
@@ -6370,45 +6376,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>427</v>
+        <v>496</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>235</v>
+        <v>283</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.550351288056206</v>
+        <v>0.5705645161290323</v>
       </c>
     </row>
     <row r="101">
@@ -6417,45 +6423,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>372</v>
+        <v>397</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>195</v>
+        <v>226</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.5692695214105793</v>
       </c>
     </row>
     <row r="102">
@@ -6464,45 +6470,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="G102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>207</v>
+      </c>
+      <c r="K102" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="9" t="n">
-        <v>218</v>
-      </c>
-      <c r="K102" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L102" s="9" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5463659147869674</v>
+        <v>0.5691489361702128</v>
       </c>
     </row>
     <row r="103">
@@ -6511,45 +6517,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>520</v>
+        <v>455</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="G103" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H103" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I103" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>235</v>
+      </c>
+      <c r="K103" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H103" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="I103" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J103" s="9" t="n">
-        <v>263</v>
-      </c>
-      <c r="K103" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="L103" s="9" t="n">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5461538461538461</v>
+        <v>0.567032967032967</v>
       </c>
     </row>
     <row r="104">
@@ -6558,45 +6564,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>455</v>
+        <v>522</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>229</v>
+        <v>287</v>
       </c>
       <c r="K104" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>248</v>
+        <v>292</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.545054945054945</v>
+        <v>0.5593869731800766</v>
       </c>
     </row>
     <row r="105">
@@ -6619,31 +6625,31 @@
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="K105" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5394736842105263</v>
+        <v>0.5577342047930284</v>
       </c>
     </row>
     <row r="106">
@@ -6652,7 +6658,7 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
@@ -6666,13 +6672,13 @@
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H106" s="9" t="n">
         <v>0</v>
@@ -6681,16 +6687,16 @@
         <v>0</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5388349514563107</v>
+        <v>0.5513784461152882</v>
       </c>
     </row>
     <row r="107">
@@ -6699,45 +6705,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>325</v>
+        <v>412</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>173</v>
+        <v>221</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>175</v>
+        <v>227</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5509708737864077</v>
       </c>
     </row>
     <row r="108">
@@ -6746,45 +6752,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5323383084577115</v>
+        <v>0.5458823529411765</v>
       </c>
     </row>
     <row r="109">
@@ -6807,31 +6813,31 @@
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I109" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5275779376498801</v>
+        <v>0.542654028436019</v>
       </c>
     </row>
     <row r="110">
@@ -6840,45 +6846,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>471</v>
+        <v>512</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5265392781316348</v>
+        <v>0.537109375</v>
       </c>
     </row>
     <row r="111">
@@ -6887,45 +6893,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>420</v>
+        <v>479</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>204</v>
+        <v>188</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>220</v>
+        <v>257</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5365344467640919</v>
       </c>
     </row>
     <row r="112">
@@ -6934,7 +6940,7 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Ivan Christian Sasenga</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
@@ -6948,31 +6954,31 @@
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>498</v>
+        <v>402</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>238</v>
+        <v>185</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5220883534136547</v>
+        <v>0.5348258706467661</v>
       </c>
     </row>
     <row r="113">
@@ -6981,7 +6987,7 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Ivan Christian Sasenga</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
@@ -6995,31 +7001,31 @@
         </is>
       </c>
       <c r="E113" s="9" t="n">
-        <v>438</v>
+        <v>503</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>227</v>
+        <v>253</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.5205479452054794</v>
+        <v>0.532803180914513</v>
       </c>
     </row>
     <row r="114">
@@ -7028,45 +7034,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>508</v>
+        <v>408</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="G114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5137795275590551</v>
+        <v>0.5318627450980392</v>
       </c>
     </row>
     <row r="115">
@@ -7075,45 +7081,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>408</v>
+        <v>471</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>209</v>
+        <v>248</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5122549019607843</v>
+        <v>0.5265392781316348</v>
       </c>
     </row>
     <row r="116">
@@ -7122,45 +7128,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>477</v>
+        <v>438</v>
       </c>
       <c r="F116" s="9" t="n">
+        <v>209</v>
+      </c>
+      <c r="G116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>227</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" s="9" t="n">
         <v>229</v>
       </c>
-      <c r="G116" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H116" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="I116" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="J116" s="9" t="n">
-        <v>189</v>
-      </c>
-      <c r="K116" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L116" s="9" t="n">
-        <v>244</v>
-      </c>
       <c r="M116" s="12" t="n">
-        <v>0.5115303983228512</v>
+        <v>0.5228310502283106</v>
       </c>
     </row>
     <row r="117">
@@ -7169,45 +7175,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>454</v>
+        <v>346</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>223</v>
+        <v>166</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>231</v>
+        <v>171</v>
       </c>
       <c r="K117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>231</v>
+        <v>180</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5088105726872246</v>
+        <v>0.5202312138728323</v>
       </c>
     </row>
     <row r="118">
@@ -7216,45 +7222,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>405</v>
+        <v>455</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>184</v>
+        <v>231</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5012345679012346</v>
+        <v>0.5186813186813187</v>
       </c>
     </row>
     <row r="119">
@@ -7263,45 +7269,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="G119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5011764705882353</v>
+        <v>0.5166666666666667</v>
       </c>
     </row>
     <row r="120">
@@ -7310,45 +7316,45 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.4987468671679198</v>
+        <v>0.5135135135135135</v>
       </c>
     </row>
     <row r="121">
@@ -7357,45 +7363,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>345</v>
+        <v>426</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="G121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I121" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.4985507246376812</v>
+        <v>0.5093896713615024</v>
       </c>
     </row>
     <row r="122">
@@ -7404,45 +7410,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G122" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.4977168949771689</v>
+        <v>0.5076586433260394</v>
       </c>
     </row>
     <row r="123">
@@ -7451,45 +7457,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.4928229665071771</v>
+        <v>0.5068181818181818</v>
       </c>
     </row>
     <row r="124">
@@ -7498,7 +7504,7 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
@@ -7512,31 +7518,31 @@
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="I124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.4927884615384615</v>
+        <v>0.5056179775280899</v>
       </c>
     </row>
     <row r="125">
@@ -7545,7 +7551,7 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
@@ -7559,31 +7565,31 @@
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>221</v>
+        <v>207</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I125" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.4920273348519363</v>
+        <v>0.5047619047619047</v>
       </c>
     </row>
     <row r="126">
@@ -7592,45 +7598,45 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>451</v>
+        <v>416</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="I126" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.4878048780487805</v>
+        <v>0.5024038461538461</v>
       </c>
     </row>
     <row r="127">
@@ -7639,7 +7645,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7653,31 +7659,31 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.4830917874396136</v>
+        <v>0.5012224938875306</v>
       </c>
     </row>
     <row r="128">
@@ -7686,45 +7692,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>441</v>
+        <v>399</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>215</v>
+        <v>191</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4807256235827664</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="129">
@@ -7733,45 +7739,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4717444717444718</v>
+        <v>0.4966139954853273</v>
       </c>
     </row>
     <row r="130">
@@ -7780,45 +7786,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4875283446712018</v>
       </c>
     </row>
     <row r="131">
@@ -7827,45 +7833,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>514</v>
+        <v>396</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>269</v>
+        <v>203</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>240</v>
+        <v>193</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4669260700389105</v>
+        <v>0.4873737373737373</v>
       </c>
     </row>
     <row r="132">
@@ -7874,45 +7880,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>391</v>
+        <v>514</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>210</v>
+        <v>260</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4629156010230179</v>
+        <v>0.4844357976653696</v>
       </c>
     </row>
     <row r="133">
@@ -7921,45 +7927,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>459</v>
+        <v>420</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H133" s="9" t="n">
         <v>1</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4596949891067538</v>
+        <v>0.4833333333333333</v>
       </c>
     </row>
     <row r="134">
@@ -7968,45 +7974,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>417</v>
+        <v>459</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="G134" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="H134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="H134" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="I134" s="9" t="n">
-        <v>29</v>
-      </c>
       <c r="J134" s="9" t="n">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="K134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.4580335731414868</v>
+        <v>0.477124183006536</v>
       </c>
     </row>
     <row r="135">
@@ -8029,31 +8035,31 @@
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4549763033175356</v>
+        <v>0.4680851063829787</v>
       </c>
     </row>
     <row r="136">
@@ -8082,25 +8088,25 @@
         <v>8</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="K136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4427710843373494</v>
+        <v>0.4518072289156627</v>
       </c>
     </row>
   </sheetData>
@@ -8160,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.30 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8262,19 +8268,19 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2898</v>
+        <v>2934</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>2496</v>
@@ -8283,10 +8289,10 @@
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8643892339544513</v>
+        <v>0.8534423994546694</v>
       </c>
     </row>
     <row r="8">
@@ -8295,45 +8301,45 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Simson Petiunaung</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2033</v>
+        <v>2835</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>440</v>
+        <v>626</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1528</v>
+        <v>2170</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>1542</v>
+        <v>2186</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7584849975405804</v>
+        <v>0.7710758377425044</v>
       </c>
     </row>
     <row r="9">
@@ -8342,45 +8348,45 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Simson Petiunaung</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2812</v>
+        <v>2038</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>666</v>
+        <v>436</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>2076</v>
+        <v>1530</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>2088</v>
+        <v>1542</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7425320056899004</v>
+        <v>0.7566241413150148</v>
       </c>
     </row>
     <row r="10">
@@ -8389,45 +8395,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Charly Angel Tatontos</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan, Tabukan Utara</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi, Hendri</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2906</v>
+        <v>2519</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>590</v>
+        <v>624</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2034</v>
+        <v>1862</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2131</v>
+        <v>1866</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7333103922918101</v>
+        <v>0.740770146883684</v>
       </c>
     </row>
     <row r="11">
@@ -8436,45 +8442,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Charly Angel Tatontos</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan, Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Alfi, Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2505</v>
+        <v>2936</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>661</v>
+        <v>558</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1828</v>
+        <v>2112</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1828</v>
+        <v>2173</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7297405189620758</v>
+        <v>0.7401226158038147</v>
       </c>
     </row>
     <row r="12">
@@ -8497,31 +8503,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2854</v>
+        <v>2867</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>755</v>
+        <v>710</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>8</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2007</v>
+        <v>2079</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2015</v>
+        <v>2087</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7060266292922215</v>
+        <v>0.7279386117893268</v>
       </c>
     </row>
     <row r="13">
@@ -8530,45 +8536,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Kepulauan Marore, Tabukan Utara</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri, Michael</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2110</v>
+        <v>2911</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>676</v>
+        <v>936</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1379</v>
+        <v>1906</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1382</v>
+        <v>1914</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6549763033175355</v>
+        <v>0.6575060116798351</v>
       </c>
     </row>
     <row r="14">
@@ -8591,31 +8597,31 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2774</v>
+        <v>2803</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>913</v>
+        <v>863</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1786</v>
+        <v>1817</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1795</v>
+        <v>1830</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6470800288392213</v>
+        <v>0.6528719229397075</v>
       </c>
     </row>
     <row r="15">
@@ -8624,45 +8630,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore, Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Hendri, Michael</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2903</v>
+        <v>2119</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>991</v>
+        <v>661</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1856</v>
+        <v>1380</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1868</v>
+        <v>1382</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6434722700654496</v>
+        <v>0.6521944313355357</v>
       </c>
     </row>
     <row r="16">
@@ -8685,31 +8691,31 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2403</v>
+        <v>2428</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>864</v>
+        <v>834</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1504</v>
+        <v>1554</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1515</v>
+        <v>1563</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.630461922596754</v>
+        <v>0.6437397034596376</v>
       </c>
     </row>
     <row r="17">
@@ -8732,31 +8738,31 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2164</v>
+        <v>2181</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>790</v>
+        <v>753</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1325</v>
+        <v>1349</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1328</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>0.6136783733826248</v>
+        <v>1362</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>0.624484181568088</v>
       </c>
     </row>
     <row r="18">
@@ -8779,31 +8785,31 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2890</v>
+        <v>2898</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1072</v>
+        <v>1053</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1730</v>
+        <v>1772</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1753</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>0.6065743944636678</v>
+        <v>1799</v>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0.6207729468599034</v>
       </c>
     </row>
     <row r="19">
@@ -8826,31 +8832,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2825</v>
+        <v>2835</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1125</v>
+        <v>1090</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1632</v>
+        <v>1724</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1679</v>
+        <v>1738</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.5943362831858408</v>
+        <v>0.6130511463844798</v>
       </c>
     </row>
     <row r="20">
@@ -8873,31 +8879,31 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2670</v>
+        <v>2682</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1127</v>
+        <v>1073</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1519</v>
+        <v>1582</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1520</v>
+        <v>1583</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5692883895131086</v>
+        <v>0.5902311707680835</v>
       </c>
     </row>
     <row r="21">
@@ -8906,45 +8912,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2697</v>
+        <v>2324</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>1145</v>
+        <v>896</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1498</v>
+        <v>1315</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1501</v>
+        <v>1339</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5565443084909159</v>
+        <v>0.5761617900172117</v>
       </c>
     </row>
     <row r="22">
@@ -8953,45 +8959,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2451</v>
+        <v>1439</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>897</v>
+        <v>338</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>35</v>
+        <v>275</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>9</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1350</v>
+        <v>802</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1359</v>
+        <v>813</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.554467564259486</v>
+        <v>0.5649756775538568</v>
       </c>
     </row>
     <row r="23">
@@ -9000,45 +9006,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2314</v>
+        <v>2727</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>951</v>
+        <v>1101</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1255</v>
+        <v>1511</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1279</v>
+        <v>1515</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5527225583405359</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="24">
@@ -9047,45 +9053,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2546</v>
+        <v>2465</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1161</v>
+        <v>873</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>6</v>
+        <v>198</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1371</v>
+        <v>1355</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1377</v>
+        <v>1359</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5408483896307934</v>
+        <v>0.5513184584178499</v>
       </c>
     </row>
     <row r="25">
@@ -9094,45 +9100,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1433</v>
+        <v>2562</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>356</v>
+        <v>1127</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>294</v>
+        <v>2</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>766</v>
+        <v>1394</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>768</v>
+        <v>1397</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5359385903698535</v>
+        <v>0.5452771272443404</v>
       </c>
     </row>
     <row r="26">
@@ -9155,31 +9161,31 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2413</v>
+        <v>2418</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1077</v>
+        <v>1033</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1186</v>
+        <v>1208</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1241</v>
+        <v>1268</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5142975549108993</v>
+        <v>0.5244003308519437</v>
       </c>
     </row>
     <row r="27">
@@ -9188,45 +9194,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Olfira Sicilia Budiman</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2712</v>
+        <v>2108</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1227</v>
+        <v>965</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1389</v>
+        <v>1012</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1394</v>
+        <v>1095</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.5140117994100295</v>
+        <v>0.5194497153700189</v>
       </c>
     </row>
     <row r="28">
@@ -9235,45 +9241,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Olfira Sicilia Budiman</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2090</v>
+        <v>2721</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>996</v>
+        <v>1211</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>967</v>
+        <v>1396</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1029</v>
+        <v>1401</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.4923444976076555</v>
+        <v>0.5148842337375965</v>
       </c>
     </row>
     <row r="29">
@@ -9296,31 +9302,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2065</v>
+        <v>2078</v>
       </c>
       <c r="F29" s="9" t="n">
+        <v>984</v>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="9" t="n">
+        <v>74</v>
+      </c>
+      <c r="I29" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>1003</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="9" t="n">
         <v>1016</v>
       </c>
-      <c r="G29" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="H29" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>21</v>
-      </c>
-      <c r="J29" s="9" t="n">
-        <v>990</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="9" t="n">
-        <v>1011</v>
-      </c>
       <c r="M29" s="12" t="n">
-        <v>0.489588377723971</v>
+        <v>0.4889316650625601</v>
       </c>
     </row>
   </sheetData>
@@ -9371,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.30 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9418,7 +9424,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.783923941227312</v>
+        <v>0.802065404475043</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9436,7 +9442,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7723704866562009</v>
+        <v>0.7882938978829389</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9454,7 +9460,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7553259141494436</v>
+        <v>0.7697285353535354</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9472,7 +9478,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7255323725532372</v>
+        <v>0.7430703624733475</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9490,7 +9496,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7224233647115617</v>
+        <v>0.7293721433726245</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9504,15 +9510,15 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.6384</v>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6550724637681159</v>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9522,15 +9528,15 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tenggara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.631219512195122</v>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6448516579406632</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>+1</t>
         </is>
       </c>
     </row>
@@ -9540,15 +9546,15 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.6233538191395961</v>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.6384</v>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>-2</t>
         </is>
       </c>
     </row>
@@ -9562,7 +9568,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.6007079646017699</v>
+        <v>0.6144620811287478</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9580,7 +9586,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.5883935434281322</v>
+        <v>0.6041746457296056</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9594,15 +9600,15 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5596885813148789</v>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5740097289784573</v>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>+2</t>
         </is>
       </c>
     </row>
@@ -9612,15 +9618,15 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5531625201138755</v>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5735483870967742</v>
+      </c>
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9630,15 +9636,15 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5464061409630147</v>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
+        <v>0.5709717097170972</v>
+      </c>
+      <c r="D19" s="19" t="inlineStr">
+        <is>
+          <t>-1</t>
         </is>
       </c>
     </row>
@@ -9652,7 +9658,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5428926647326979</v>
+        <v>0.5632754342431762</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -9670,7 +9676,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.5358327803583278</v>
+        <v>0.553198487090939</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 11.05 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 11.05 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 11.05 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 11.05 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -616,7 +616,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.05 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1917,7 +1917,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.05 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.05 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 11.05 WITA</t>
+          <t>Pukul        : 09.35 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,10 +91,6 @@
     </font>
     <font>
       <color rgb="00595959"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
     </font>
   </fonts>
   <fills count="8">
@@ -167,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -192,8 +188,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -616,32 +610,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 15.40 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-37):</t>
+          <t>Target Hari Ini (H-38):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.79%</t>
+          <t>63.46%</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Hijau &gt;= 61.79%</t>
+          <t>Hijau &gt;= 63.46%</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>Kuning 30.89% - 61.79%</t>
+          <t>Kuning 31.73% - 63.46%</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
-          <t>Merah &lt; 30.89%</t>
+          <t>Merah &lt; 31.73%</t>
         </is>
       </c>
     </row>
@@ -770,21 +764,21 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
         <v/>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2910</v>
+        <v>2912</v>
       </c>
       <c r="M7" s="10">
         <f>L7/B7</f>
@@ -805,7 +799,7 @@
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -819,41 +813,41 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1439</v>
+        <v>1447</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
         <v/>
       </c>
       <c r="J8" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K8" s="10">
         <f>J8/B8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
@@ -867,14 +861,14 @@
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>826</v>
+        <v>839</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -894,7 +888,7 @@
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
@@ -908,21 +902,21 @@
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4611</v>
+        <v>4621</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -936,14 +930,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4877</v>
+        <v>4879</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -1012,7 +1006,7 @@
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1032,7 +1026,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
@@ -1046,7 +1040,7 @@
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1074,14 +1068,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1150,7 +1144,7 @@
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1164,27 +1158,27 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4650</v>
+        <v>4655</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1946</v>
+        <v>1936</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
@@ -1198,7 +1192,7 @@
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2442</v>
+        <v>2446</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1212,14 +1206,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2667</v>
+        <v>2683</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1233,41 +1227,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6081</v>
+        <v>6086</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2686</v>
+        <v>2668</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3149</v>
+        <v>3170</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1281,14 +1275,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3364</v>
+        <v>3394</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1302,27 +1296,27 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8130</v>
+        <v>8133</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3385</v>
+        <v>3378</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
@@ -1336,7 +1330,7 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4489</v>
+        <v>4492</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1350,14 +1344,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4642</v>
+        <v>4659</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>173</v>
+        <v>17</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1371,41 +1365,41 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5222</v>
+        <v>5233</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1949</v>
+        <v>1928</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
         <v/>
       </c>
       <c r="J16" s="9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K16" s="10">
         <f>J16/B16</f>
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3087</v>
+        <v>3089</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1419,14 +1413,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3155</v>
+        <v>3182</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,34 +1434,34 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>2418</v>
+        <v>2422</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1033</v>
+        <v>1019</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
@@ -1481,21 +1475,21 @@
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1362</v>
+        <v>1378</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1509,13 +1503,13 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9380</v>
+        <v>9395</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2310</v>
+        <v>2285</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
@@ -1536,14 +1530,14 @@
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6780</v>
+        <v>6819</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1557,14 +1551,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>6970</v>
+        <v>7010</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,13 +1572,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1598,7 +1592,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1626,14 +1620,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1716,13 +1710,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2835</v>
+        <v>2838</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1736,14 +1730,14 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
@@ -1764,14 +1758,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1742</v>
+        <v>1755</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1917,17 +1911,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 15.40 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-37):</t>
+          <t>Target Hari Ini (H-38):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.79%</t>
+          <t>63.46%</t>
         </is>
       </c>
     </row>
@@ -2116,13 +2110,13 @@
         <v>571</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
@@ -2134,10 +2128,10 @@
         <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.9737302977232924</v>
+        <v>0.9772329246935202</v>
       </c>
     </row>
     <row r="10">
@@ -2163,16 +2157,16 @@
         <v>530</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>6</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J10" s="9" t="n">
         <v>478</v>
@@ -2181,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.9358490566037736</v>
+        <v>0.9377358490566039</v>
       </c>
     </row>
     <row r="11">
@@ -2310,13 +2304,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>2</v>
@@ -2428,45 +2422,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>507</v>
+        <v>416</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>420</v>
+        <v>326</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>425</v>
+        <v>351</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.8382642998027613</v>
+        <v>0.84375</v>
       </c>
     </row>
     <row r="17">
@@ -2475,45 +2469,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>426</v>
+        <v>507</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>269</v>
+        <v>420</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>357</v>
+        <v>425</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8382642998027613</v>
       </c>
     </row>
     <row r="18">
@@ -2522,45 +2516,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>337</v>
+        <v>269</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8370370370370369</v>
+        <v>0.8380281690140845</v>
       </c>
     </row>
     <row r="19">
@@ -2586,13 +2580,13 @@
         <v>388</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>4</v>
@@ -2604,10 +2598,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8324742268041238</v>
+        <v>0.8376288659793815</v>
       </c>
     </row>
     <row r="20">
@@ -2616,45 +2610,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8313253012048193</v>
+        <v>0.8370370370370369</v>
       </c>
     </row>
     <row r="21">
@@ -2683,25 +2677,25 @@
         <v>71</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8216432865731462</v>
+        <v>0.8276553106212425</v>
       </c>
     </row>
     <row r="22">
@@ -2733,13 +2727,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
@@ -2874,10 +2868,10 @@
         <v>4</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" s="9" t="n">
         <v>398</v>
@@ -3291,28 +3285,28 @@
         <v>503</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I34" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.7514910536779325</v>
+        <v>0.753479125248509</v>
       </c>
     </row>
     <row r="35">
@@ -3368,45 +3362,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7392857142857143</v>
+        <v>0.7412844036697248</v>
       </c>
     </row>
     <row r="37">
@@ -3415,45 +3409,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>350</v>
+        <v>560</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>255</v>
+        <v>398</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>258</v>
+        <v>414</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7371428571428571</v>
+        <v>0.7392857142857143</v>
       </c>
     </row>
     <row r="38">
@@ -3462,45 +3456,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>544</v>
+        <v>350</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>396</v>
+        <v>255</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>400</v>
+        <v>258</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.7371428571428571</v>
       </c>
     </row>
     <row r="39">
@@ -3526,7 +3520,7 @@
         <v>425</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>0</v>
@@ -3538,16 +3532,16 @@
         <v>2</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7341176470588234</v>
+        <v>0.7364705882352941</v>
       </c>
     </row>
     <row r="40">
@@ -3573,10 +3567,10 @@
         <v>507</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H40" s="9" t="n">
         <v>1</v>
@@ -3664,16 +3658,16 @@
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I42" s="9" t="n">
         <v>0</v>
@@ -3685,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7130242825607064</v>
+        <v>0.7171052631578947</v>
       </c>
     </row>
     <row r="43">
@@ -3814,13 +3808,13 @@
         <v>5</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>1</v>
@@ -3932,45 +3926,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>520</v>
+        <v>347</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>341</v>
+        <v>228</v>
       </c>
       <c r="K48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6923076923076923</v>
+        <v>0.69164265129683</v>
       </c>
     </row>
     <row r="49">
@@ -3979,45 +3973,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>347</v>
+        <v>389</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="I49" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.69164265129683</v>
+        <v>0.6889460154241646</v>
       </c>
     </row>
     <row r="50">
@@ -4026,45 +4020,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>389</v>
+        <v>526</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>223</v>
+        <v>341</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>268</v>
+        <v>362</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6889460154241646</v>
+        <v>0.688212927756654</v>
       </c>
     </row>
     <row r="51">
@@ -4096,10 +4090,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J51" s="9" t="n">
         <v>360</v>
@@ -4137,13 +4131,13 @@
         <v>380</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G52" s="9" t="n">
         <v>11</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I52" s="9" t="n">
         <v>1</v>
@@ -4155,10 +4149,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6815789473684211</v>
+        <v>0.6842105263157895</v>
       </c>
     </row>
     <row r="53">
@@ -4167,45 +4161,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>221</v>
+        <v>270</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.673076923076923</v>
+        <v>0.6775700934579441</v>
       </c>
     </row>
     <row r="54">
@@ -4214,45 +4208,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>270</v>
+        <v>225</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6728971962616822</v>
+        <v>0.673076923076923</v>
       </c>
     </row>
     <row r="55">
@@ -4369,31 +4363,31 @@
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="K57" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.6703539823008849</v>
+        <v>0.6710816777041942</v>
       </c>
     </row>
     <row r="58">
@@ -4402,45 +4396,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>260</v>
+        <v>324</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>271</v>
+        <v>338</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6674876847290641</v>
+        <v>0.6679841897233202</v>
       </c>
     </row>
     <row r="59">
@@ -4449,45 +4443,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>452</v>
+        <v>406</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6637168141592921</v>
+        <v>0.6674876847290641</v>
       </c>
     </row>
     <row r="60">
@@ -4496,45 +4490,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G60" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I60" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="H60" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J60" s="9" t="n">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6573275862068965</v>
+        <v>0.6637168141592921</v>
       </c>
     </row>
     <row r="61">
@@ -4543,45 +4537,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.65359477124183</v>
+        <v>0.6573275862068965</v>
       </c>
     </row>
     <row r="62">
@@ -4590,45 +4584,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>502</v>
+        <v>458</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>324</v>
+        <v>281</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6533864541832669</v>
+        <v>0.6528384279475984</v>
       </c>
     </row>
     <row r="63">
@@ -4698,16 +4692,16 @@
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I64" s="9" t="n">
         <v>1</v>
@@ -4719,10 +4713,10 @@
         <v>2</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.6447105788423154</v>
+        <v>0.647410358565737</v>
       </c>
     </row>
     <row r="65">
@@ -4748,13 +4742,13 @@
         <v>432</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" s="9" t="n">
         <v>0</v>
@@ -4766,10 +4760,10 @@
         <v>1</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.6412037037037037</v>
+        <v>0.6435185185185185</v>
       </c>
     </row>
     <row r="66">
@@ -4778,45 +4772,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>427</v>
+        <v>469</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="G66" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J66" s="9" t="n">
-        <v>273</v>
+        <v>297</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.639344262295082</v>
+        <v>0.6417910447761195</v>
       </c>
     </row>
     <row r="67">
@@ -4825,45 +4819,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>625</v>
+        <v>429</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>394</v>
+        <v>272</v>
       </c>
       <c r="K67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>399</v>
+        <v>275</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.6384</v>
+        <v>0.641025641025641</v>
       </c>
     </row>
     <row r="68">
@@ -4872,45 +4866,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>467</v>
+        <v>427</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="K68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>298</v>
+        <v>273</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.6381156316916489</v>
+        <v>0.639344262295082</v>
       </c>
     </row>
     <row r="69">
@@ -4919,45 +4913,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>386</v>
+        <v>625</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>141</v>
+        <v>219</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>233</v>
+        <v>394</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>245</v>
+        <v>399</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6347150259067358</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="70">
@@ -4966,45 +4960,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>429</v>
+        <v>386</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="K70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>272</v>
+        <v>245</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.634032634032634</v>
+        <v>0.6347150259067358</v>
       </c>
     </row>
     <row r="71">
@@ -5013,45 +5007,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>352</v>
+        <v>479</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>211</v>
+        <v>294</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>223</v>
+        <v>304</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.6335227272727273</v>
+        <v>0.6346555323590815</v>
       </c>
     </row>
     <row r="72">
@@ -5060,27 +5054,27 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>515</v>
+        <v>478</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H72" s="9" t="n">
         <v>1</v>
@@ -5089,16 +5083,16 @@
         <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>326</v>
-      </c>
-      <c r="M72" s="11" t="n">
-        <v>0.6330097087378641</v>
+        <v>303</v>
+      </c>
+      <c r="M72" s="12" t="n">
+        <v>0.6338912133891214</v>
       </c>
     </row>
     <row r="73">
@@ -5107,45 +5101,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>572</v>
+        <v>516</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="I73" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>324</v>
+      </c>
+      <c r="K73" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="9" t="n">
-        <v>326</v>
-      </c>
-      <c r="K73" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L73" s="9" t="n">
-        <v>360</v>
-      </c>
-      <c r="M73" s="11" t="n">
-        <v>0.6293706293706294</v>
+        <v>327</v>
+      </c>
+      <c r="M73" s="12" t="n">
+        <v>0.6337209302325582</v>
       </c>
     </row>
     <row r="74">
@@ -5154,24 +5148,24 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>441</v>
+        <v>352</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>0</v>
@@ -5180,19 +5174,19 @@
         <v>4</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>272</v>
+        <v>211</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>277</v>
-      </c>
-      <c r="M74" s="11" t="n">
-        <v>0.6281179138321995</v>
+        <v>223</v>
+      </c>
+      <c r="M74" s="12" t="n">
+        <v>0.6335227272727273</v>
       </c>
     </row>
     <row r="75">
@@ -5201,45 +5195,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>268</v>
-      </c>
-      <c r="M75" s="11" t="n">
-        <v>0.6276346604215457</v>
+        <v>256</v>
+      </c>
+      <c r="M75" s="12" t="n">
+        <v>0.6320987654320988</v>
       </c>
     </row>
     <row r="76">
@@ -5248,7 +5242,7 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -5262,31 +5256,31 @@
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>478</v>
+        <v>428</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>299</v>
-      </c>
-      <c r="M76" s="11" t="n">
-        <v>0.6255230125523012</v>
+        <v>270</v>
+      </c>
+      <c r="M76" s="12" t="n">
+        <v>0.6308411214953271</v>
       </c>
     </row>
     <row r="77">
@@ -5295,45 +5289,45 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>469</v>
+        <v>444</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>293</v>
-      </c>
-      <c r="M77" s="11" t="n">
-        <v>0.6247334754797441</v>
+        <v>280</v>
+      </c>
+      <c r="M77" s="12" t="n">
+        <v>0.6306306306306306</v>
       </c>
     </row>
     <row r="78">
@@ -5342,45 +5336,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>546</v>
+        <v>416</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>205</v>
+        <v>148</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>333</v>
+        <v>258</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>341</v>
-      </c>
-      <c r="M78" s="11" t="n">
-        <v>0.6245421245421245</v>
+        <v>262</v>
+      </c>
+      <c r="M78" s="12" t="n">
+        <v>0.6298076923076923</v>
       </c>
     </row>
     <row r="79">
@@ -5389,45 +5383,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>404</v>
+        <v>572</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>152</v>
+        <v>201</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>237</v>
+        <v>326</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>252</v>
-      </c>
-      <c r="M79" s="11" t="n">
-        <v>0.6237623762376238</v>
+        <v>360</v>
+      </c>
+      <c r="M79" s="12" t="n">
+        <v>0.6293706293706294</v>
       </c>
     </row>
     <row r="80">
@@ -5436,45 +5430,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>258</v>
-      </c>
-      <c r="M80" s="11" t="n">
-        <v>0.6216867469879518</v>
+        <v>263</v>
+      </c>
+      <c r="M80" s="12" t="n">
+        <v>0.6291866028708134</v>
       </c>
     </row>
     <row r="81">
@@ -5483,45 +5477,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>509</v>
+        <v>469</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>315</v>
-      </c>
-      <c r="M81" s="11" t="n">
-        <v>0.618860510805501</v>
+        <v>294</v>
+      </c>
+      <c r="M81" s="12" t="n">
+        <v>0.6268656716417911</v>
       </c>
     </row>
     <row r="82">
@@ -5530,45 +5524,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>418</v>
+        <v>546</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="G82" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="H82" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="I82" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>251</v>
+        <v>333</v>
       </c>
       <c r="K82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>258</v>
+        <v>341</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.6172248803827751</v>
+        <v>0.6245421245421245</v>
       </c>
     </row>
     <row r="83">
@@ -5577,45 +5571,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>478</v>
+        <v>509</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="H83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.6171548117154811</v>
+        <v>0.6227897838899804</v>
       </c>
     </row>
     <row r="84">
@@ -5624,45 +5618,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>559</v>
+        <v>517</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="K84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>344</v>
+        <v>319</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.6170212765957447</v>
       </c>
     </row>
     <row r="85">
@@ -5671,45 +5665,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>516</v>
+        <v>450</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>199</v>
+        <v>155</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>313</v>
+        <v>251</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>317</v>
+        <v>277</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.6143410852713178</v>
+        <v>0.6155555555555555</v>
       </c>
     </row>
     <row r="86">
@@ -5718,45 +5712,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>465</v>
+        <v>560</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>262</v>
+        <v>344</v>
       </c>
       <c r="K86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.610752688172043</v>
+        <v>0.6142857142857143</v>
       </c>
     </row>
     <row r="87">
@@ -5765,45 +5759,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>450</v>
+        <v>465</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.6088888888888889</v>
+        <v>0.610752688172043</v>
       </c>
     </row>
     <row r="88">
@@ -5812,45 +5806,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>366</v>
+        <v>504</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>144</v>
+        <v>190</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>207</v>
+        <v>296</v>
       </c>
       <c r="K88" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.6071428571428571</v>
       </c>
     </row>
     <row r="89">
@@ -5876,13 +5870,13 @@
         <v>430</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I89" s="9" t="n">
         <v>0</v>
@@ -5894,10 +5888,10 @@
         <v>2</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.6046511627906976</v>
+        <v>0.6069767441860465</v>
       </c>
     </row>
     <row r="90">
@@ -5906,21 +5900,21 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="F90" s="9" t="n">
         <v>144</v>
@@ -5929,22 +5923,22 @@
         <v>0</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="K90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.6011080332409973</v>
+        <v>0.6065573770491803</v>
       </c>
     </row>
     <row r="91">
@@ -5953,45 +5947,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>450</v>
+        <v>325</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>263</v>
+        <v>186</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>270</v>
+        <v>197</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.6</v>
+        <v>0.6061538461538462</v>
       </c>
     </row>
     <row r="92">
@@ -6000,7 +5994,7 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -6014,31 +6008,31 @@
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>402</v>
+        <v>450</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>217</v>
+        <v>268</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>241</v>
+        <v>271</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.599502487562189</v>
+        <v>0.6022222222222222</v>
       </c>
     </row>
     <row r="93">
@@ -6047,45 +6041,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>469</v>
+        <v>361</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>189</v>
+        <v>144</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>280</v>
+        <v>211</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>280</v>
+        <v>217</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.5970149253731343</v>
+        <v>0.6011080332409973</v>
       </c>
     </row>
     <row r="94">
@@ -6094,45 +6088,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>504</v>
+        <v>471</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H94" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I94" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I94" s="9" t="n">
-        <v>4</v>
-      </c>
       <c r="J94" s="9" t="n">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.5952380952380952</v>
+        <v>0.6008492569002123</v>
       </c>
     </row>
     <row r="95">
@@ -6141,45 +6135,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>468</v>
+        <v>402</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I95" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>260</v>
+        <v>217</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>278</v>
+        <v>241</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.594017094017094</v>
+        <v>0.599502487562189</v>
       </c>
     </row>
     <row r="96">
@@ -6188,17 +6182,17 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
@@ -6208,25 +6202,25 @@
         <v>189</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5906183368869936</v>
+        <v>0.5970149253731343</v>
       </c>
     </row>
     <row r="97">
@@ -6235,45 +6229,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5902335456475584</v>
+        <v>0.5970149253731343</v>
       </c>
     </row>
     <row r="98">
@@ -6282,45 +6276,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>325</v>
+        <v>472</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>186</v>
+        <v>259</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L98" s="9" t="n">
-        <v>191</v>
+        <v>280</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5876923076923077</v>
+        <v>0.5932203389830508</v>
       </c>
     </row>
     <row r="99">
@@ -6329,45 +6323,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>445</v>
+        <v>379</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="G99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="I99" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>207</v>
+      </c>
+      <c r="K99" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H99" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="9" t="n">
-        <v>253</v>
-      </c>
-      <c r="K99" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L99" s="9" t="n">
-        <v>254</v>
+        <v>219</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5707865168539326</v>
+        <v>0.5778364116094987</v>
       </c>
     </row>
     <row r="100">
@@ -6376,45 +6370,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>496</v>
+        <v>524</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I100" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>287</v>
+      </c>
+      <c r="K100" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J100" s="9" t="n">
-        <v>269</v>
-      </c>
-      <c r="K100" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L100" s="9" t="n">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.5705645161290323</v>
+        <v>0.5763358778625954</v>
       </c>
     </row>
     <row r="101">
@@ -6423,45 +6417,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>397</v>
+        <v>446</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>226</v>
+        <v>255</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5692695214105793</v>
+        <v>0.5739910313901345</v>
       </c>
     </row>
     <row r="102">
@@ -6470,45 +6464,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>376</v>
+        <v>496</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>207</v>
+        <v>269</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>214</v>
+        <v>283</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5691489361702128</v>
+        <v>0.5705645161290323</v>
       </c>
     </row>
     <row r="103">
@@ -6517,45 +6511,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>455</v>
+        <v>397</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>258</v>
+        <v>226</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.567032967032967</v>
+        <v>0.5692695214105793</v>
       </c>
     </row>
     <row r="104">
@@ -6564,45 +6558,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>522</v>
+        <v>455</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>228</v>
+        <v>186</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>287</v>
+        <v>235</v>
       </c>
       <c r="K104" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.5593869731800766</v>
+        <v>0.567032967032967</v>
       </c>
     </row>
     <row r="105">
@@ -6658,45 +6652,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5513784461152882</v>
+        <v>0.5526932084309133</v>
       </c>
     </row>
     <row r="107">
@@ -6705,7 +6699,7 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
@@ -6719,31 +6713,31 @@
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5509708737864077</v>
+        <v>0.5513784461152882</v>
       </c>
     </row>
     <row r="108">
@@ -6752,45 +6746,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5458823529411765</v>
+        <v>0.5509708737864077</v>
       </c>
     </row>
     <row r="109">
@@ -6816,16 +6810,16 @@
         <v>422</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J109" s="9" t="n">
         <v>222</v>
@@ -6834,10 +6828,10 @@
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.542654028436019</v>
+        <v>0.5450236966824644</v>
       </c>
     </row>
     <row r="110">
@@ -6846,45 +6840,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>271</v>
+        <v>188</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.537109375</v>
+        <v>0.5407098121085595</v>
       </c>
     </row>
     <row r="111">
@@ -6893,45 +6887,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>479</v>
+        <v>512</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5365344467640919</v>
+        <v>0.5390625</v>
       </c>
     </row>
     <row r="112">
@@ -7095,16 +7089,16 @@
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F115" s="9" t="n">
         <v>213</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115" s="9" t="n">
         <v>2</v>
@@ -7116,10 +7110,10 @@
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5265392781316348</v>
+        <v>0.523109243697479</v>
       </c>
     </row>
     <row r="116">
@@ -7128,45 +7122,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5228310502283106</v>
+        <v>0.5230769230769231</v>
       </c>
     </row>
     <row r="117">
@@ -7175,45 +7169,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Mabelkhan Ladorang</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>346</v>
+        <v>438</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>166</v>
+        <v>209</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>180</v>
+        <v>229</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5202312138728323</v>
+        <v>0.5228310502283106</v>
       </c>
     </row>
     <row r="118">
@@ -7222,7 +7216,7 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
@@ -7236,31 +7230,31 @@
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>455</v>
+        <v>420</v>
       </c>
       <c r="F118" s="9" t="n">
+        <v>201</v>
+      </c>
+      <c r="G118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="I118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>206</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="9" t="n">
         <v>219</v>
       </c>
-      <c r="G118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="I118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="9" t="n">
-        <v>231</v>
-      </c>
-      <c r="K118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" s="9" t="n">
-        <v>236</v>
-      </c>
       <c r="M118" s="12" t="n">
-        <v>0.5186813186813187</v>
+        <v>0.5214285714285715</v>
       </c>
     </row>
     <row r="119">
@@ -7269,45 +7263,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="G119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I119" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J119" s="9" t="n">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="K119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5166666666666667</v>
+        <v>0.5208845208845209</v>
       </c>
     </row>
     <row r="120">
@@ -7316,7 +7310,7 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
@@ -7330,31 +7324,31 @@
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>407</v>
+        <v>457</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>184</v>
+        <v>224</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>209</v>
+        <v>238</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.5135135135135135</v>
+        <v>0.5207877461706784</v>
       </c>
     </row>
     <row r="121">
@@ -7363,45 +7357,45 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Mabelkhan Ladorang</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D121" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E121" s="9" t="n">
-        <v>426</v>
+        <v>346</v>
       </c>
       <c r="F121" s="9" t="n">
-        <v>209</v>
+        <v>166</v>
       </c>
       <c r="G121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J121" s="9" t="n">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="9" t="n">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="M121" s="12" t="n">
-        <v>0.5093896713615024</v>
+        <v>0.5202312138728323</v>
       </c>
     </row>
     <row r="122">
@@ -7410,45 +7404,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>457</v>
+        <v>416</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="G122" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>221</v>
+        <v>147</v>
       </c>
       <c r="K122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.5076586433260394</v>
+        <v>0.5096153846153846</v>
       </c>
     </row>
     <row r="123">
@@ -7457,45 +7451,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>440</v>
+        <v>426</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.5068181818181818</v>
+        <v>0.5093896713615024</v>
       </c>
     </row>
     <row r="124">
@@ -7504,45 +7498,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.5056179775280899</v>
+        <v>0.5068181818181818</v>
       </c>
     </row>
     <row r="125">
@@ -7551,45 +7545,45 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.5047619047619047</v>
+        <v>0.5067873303167421</v>
       </c>
     </row>
     <row r="126">
@@ -7598,7 +7592,7 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
@@ -7612,31 +7606,31 @@
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>416</v>
+        <v>445</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="G126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>62</v>
+        <v>3</v>
       </c>
       <c r="I126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>147</v>
+        <v>222</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.5024038461538461</v>
+        <v>0.5056179775280899</v>
       </c>
     </row>
     <row r="127">
@@ -7645,7 +7639,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7659,31 +7653,31 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="I127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.5012224938875306</v>
+        <v>0.5047619047619047</v>
       </c>
     </row>
     <row r="128">
@@ -7692,45 +7686,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.4987468671679198</v>
+        <v>0.5012224938875306</v>
       </c>
     </row>
     <row r="129">
@@ -7739,45 +7733,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>443</v>
+        <v>399</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4966139954853273</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="130">
@@ -7786,45 +7780,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="H130" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="I130" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="I130" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J130" s="9" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4875283446712018</v>
+        <v>0.4954954954954955</v>
       </c>
     </row>
     <row r="131">
@@ -7833,45 +7827,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>396</v>
+        <v>515</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4873737373737373</v>
+        <v>0.4912621359223301</v>
       </c>
     </row>
     <row r="132">
@@ -7880,45 +7874,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>514</v>
+        <v>420</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>260</v>
+        <v>201</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>249</v>
+        <v>206</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4844357976653696</v>
+        <v>0.4904761904761905</v>
       </c>
     </row>
     <row r="133">
@@ -7927,45 +7921,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4833333333333333</v>
+        <v>0.4873737373737373</v>
       </c>
     </row>
     <row r="134">
@@ -8044,13 +8038,13 @@
         <v>1</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I135" s="9" t="n">
         <v>22</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
@@ -8082,16 +8076,16 @@
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="F136" s="9" t="n">
         <v>8</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I136" s="9" t="n">
         <v>0</v>
@@ -8103,10 +8097,10 @@
         <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4518072289156627</v>
+        <v>0.4510385756676558</v>
       </c>
     </row>
   </sheetData>
@@ -8166,17 +8160,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 15.40 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-37):</t>
+          <t>Target Hari Ini (H-38):</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>61.79%</t>
+          <t>63.46%</t>
         </is>
       </c>
     </row>
@@ -8271,13 +8265,13 @@
         <v>2934</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>1</v>
@@ -8371,22 +8365,22 @@
         <v>23</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7566241413150148</v>
+        <v>0.7561334641805693</v>
       </c>
     </row>
     <row r="10">
@@ -8409,16 +8403,16 @@
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2519</v>
+        <v>2524</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="I10" s="9" t="n">
         <v>4</v>
@@ -8433,7 +8427,7 @@
         <v>1866</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.740770146883684</v>
+        <v>0.7393026941362916</v>
       </c>
     </row>
     <row r="11">
@@ -8459,16 +8453,16 @@
         <v>2936</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>74</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>2112</v>
@@ -8477,10 +8471,10 @@
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>2173</v>
+        <v>2169</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7401226158038147</v>
+        <v>0.7387602179836512</v>
       </c>
     </row>
     <row r="12">
@@ -8506,28 +8500,28 @@
         <v>2867</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2079</v>
+        <v>2089</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2087</v>
+        <v>2095</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7279386117893268</v>
+        <v>0.730728985001744</v>
       </c>
     </row>
     <row r="13">
@@ -8550,31 +8544,31 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2911</v>
+        <v>2915</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>936</v>
+        <v>929</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1906</v>
+        <v>1929</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1914</v>
+        <v>1938</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6575060116798351</v>
+        <v>0.6648370497427101</v>
       </c>
     </row>
     <row r="14">
@@ -8597,31 +8591,31 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2803</v>
+        <v>2810</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>863</v>
+        <v>852</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>9</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1817</v>
+        <v>1833</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1830</v>
+        <v>1846</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6528719229397075</v>
+        <v>0.6569395017793594</v>
       </c>
     </row>
     <row r="15">
@@ -8691,31 +8685,31 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>834</v>
+        <v>824</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>19</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1554</v>
+        <v>1570</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1563</v>
+        <v>1581</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6437397034596376</v>
+        <v>0.6503496503496503</v>
       </c>
     </row>
     <row r="17">
@@ -8741,13 +8735,13 @@
         <v>2181</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>11</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>12</v>
@@ -8761,7 +8755,7 @@
       <c r="L17" s="9" t="n">
         <v>1362</v>
       </c>
-      <c r="M17" s="11" t="n">
+      <c r="M17" s="12" t="n">
         <v>0.624484181568088</v>
       </c>
     </row>
@@ -8788,28 +8782,28 @@
         <v>2898</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1799</v>
-      </c>
-      <c r="M18" s="11" t="n">
-        <v>0.6207729468599034</v>
+        <v>1800</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>0.6211180124223602</v>
       </c>
     </row>
     <row r="19">
@@ -8832,19 +8826,19 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2835</v>
+        <v>2838</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1090</v>
+        <v>1080</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H19" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I19" s="9" t="n">
         <v>4</v>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>6</v>
       </c>
       <c r="J19" s="9" t="n">
         <v>1724</v>
@@ -8853,10 +8847,10 @@
         <v>8</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.6130511463844798</v>
+        <v>0.6116983791402396</v>
       </c>
     </row>
     <row r="20">
@@ -8879,31 +8873,31 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1582</v>
+        <v>1586</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1583</v>
+        <v>1587</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5902311707680835</v>
+        <v>0.5915020499440924</v>
       </c>
     </row>
     <row r="21">
@@ -8926,16 +8920,16 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2324</v>
+        <v>2335</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>896</v>
+        <v>878</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>22</v>
@@ -8950,7 +8944,7 @@
         <v>1339</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5761617900172117</v>
+        <v>0.5734475374732334</v>
       </c>
     </row>
     <row r="22">
@@ -8973,22 +8967,22 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1439</v>
+        <v>1447</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>802</v>
+        <v>811</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>2</v>
@@ -8997,7 +8991,7 @@
         <v>813</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5649756775538568</v>
+        <v>0.5618521078092605</v>
       </c>
     </row>
     <row r="23">
@@ -9023,19 +9017,19 @@
         <v>2727</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>3</v>
@@ -9067,31 +9061,31 @@
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="K24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5513184584178499</v>
+        <v>0.5527169505271695</v>
       </c>
     </row>
     <row r="25">
@@ -9114,16 +9108,16 @@
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2562</v>
+        <v>2566</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1127</v>
+        <v>1120</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>1</v>
@@ -9138,7 +9132,7 @@
         <v>1397</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5452771272443404</v>
+        <v>0.5444271239282931</v>
       </c>
     </row>
     <row r="26">
@@ -9161,31 +9155,31 @@
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2418</v>
+        <v>2422</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1033</v>
+        <v>1019</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J26" s="9" t="n">
         <v>1208</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.5244003308519437</v>
+        <v>0.523121387283237</v>
       </c>
     </row>
     <row r="27">
@@ -9208,31 +9202,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.5194497153700189</v>
+        <v>0.5208530805687204</v>
       </c>
     </row>
     <row r="28">
@@ -9255,19 +9249,19 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2721</v>
+        <v>2723</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>1211</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J28" s="9" t="n">
         <v>1396</v>
@@ -9276,10 +9270,10 @@
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.5148842337375965</v>
+        <v>0.5141388174807198</v>
       </c>
     </row>
     <row r="29">
@@ -9305,13 +9299,13 @@
         <v>2078</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>4</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I29" s="9" t="n">
         <v>13</v>
@@ -9377,17 +9371,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 09.35 WITA</t>
+          <t>Pukul        : 15.40 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Target Hari Ini (H-37):</t>
+          <t>Target Hari Ini (H-38):</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>61.79%</t>
+          <t>63.46%</t>
         </is>
       </c>
     </row>
@@ -9424,7 +9418,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.802065404475043</v>
+        <v>0.8073946689595872</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9460,7 +9454,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7697285353535354</v>
+        <v>0.7700441919191919</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9478,7 +9472,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7430703624733475</v>
+        <v>0.7461415646620543</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9516,9 +9510,9 @@
       <c r="C12" s="11" t="n">
         <v>0.6550724637681159</v>
       </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9532,11 +9526,11 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.6448516579406632</v>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>+1</t>
+        <v>0.6457242582897034</v>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9552,9 +9546,9 @@
       <c r="C14" s="11" t="n">
         <v>0.6384</v>
       </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>-2</t>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9568,7 +9562,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.6144620811287478</v>
+        <v>0.6183932346723044</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9586,7 +9580,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.6041746457296056</v>
+        <v>0.608064207911332</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9604,11 +9598,11 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5740097289784573</v>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>+2</t>
+        <v>0.5798203178991016</v>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9622,11 +9616,11 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5735483870967742</v>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.5763694951664876</v>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9640,11 +9634,11 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5709717097170972</v>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>-1</t>
+        <v>0.5728513463666544</v>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9658,7 +9652,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5632754342431762</v>
+        <v>0.5689512799339389</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -9676,7 +9670,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.553198487090939</v>
+        <v>0.5576733486690766</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15.40 WITA</t>
+          <t>Pukul        : 16.17 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15.40 WITA</t>
+          <t>Pukul        : 16.17 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15.40 WITA</t>
+          <t>Pukul        : 16.17 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15.40 WITA</t>
+          <t>Pukul        : 16.17 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15.40 WITA</t>
+          <t>Pukul        : 20.54 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -744,13 +744,13 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4157</v>
+        <v>4160</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
@@ -764,14 +764,14 @@
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
         <v/>
       </c>
       <c r="J7" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K7" s="10">
         <f>J7/B7</f>
@@ -792,14 +792,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>3032</v>
+        <v>3040</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -813,62 +813,62 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1447</v>
+        <v>1452</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
         <v/>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8" s="10">
         <f>J8/B8</f>
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>811</v>
+        <v>856</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
         <v/>
       </c>
       <c r="N8" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O8" s="10">
         <f>N8/B8</f>
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>839</v>
+        <v>879</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -882,34 +882,34 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6336</v>
+        <v>6338</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1363</v>
+        <v>1353</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
         <v/>
       </c>
       <c r="F9" s="9" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G9" s="10">
         <f>F9/B9</f>
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
@@ -930,14 +930,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4879</v>
+        <v>4892</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -957,7 +957,7 @@
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -971,7 +971,7 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
@@ -999,14 +999,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2532</v>
+        <v>2536</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1026,7 +1026,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
@@ -1040,7 +1040,7 @@
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1068,14 +1068,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1089,7 +1089,7 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>23</v>
@@ -1109,7 +1109,7 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
@@ -1137,14 +1137,14 @@
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="Q12" s="11">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4655</v>
+        <v>4658</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1936</v>
+        <v>1927</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
@@ -1178,21 +1178,21 @@
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2446</v>
+        <v>2510</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1206,14 +1206,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2683</v>
+        <v>2695</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1227,41 +1227,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6086</v>
+        <v>6099</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2668</v>
+        <v>2644</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3170</v>
+        <v>3201</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1275,14 +1275,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3394</v>
+        <v>3424</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1296,41 +1296,41 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8133</v>
+        <v>8154</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3378</v>
+        <v>3349</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>157</v>
+        <v>95</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
         <v/>
       </c>
       <c r="J15" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="10">
         <f>J15/B15</f>
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4492</v>
+        <v>4590</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1344,14 +1344,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4659</v>
+        <v>4696</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1365,27 +1365,27 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5233</v>
+        <v>5243</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1928</v>
+        <v>1878</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
@@ -1399,7 +1399,7 @@
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3089</v>
+        <v>3110</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1413,14 +1413,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3182</v>
+        <v>3223</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,7 +1440,7 @@
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
@@ -1468,7 +1468,7 @@
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
@@ -1482,14 +1482,14 @@
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1503,41 +1503,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9395</v>
+        <v>9417</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2285</v>
+        <v>2247</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6819</v>
+        <v>6827</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1551,14 +1551,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>7010</v>
+        <v>7051</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1578,7 +1578,7 @@
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1592,7 +1592,7 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
@@ -1620,14 +1620,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>939</v>
+        <v>944</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1668,14 +1668,14 @@
         <v/>
       </c>
       <c r="J20" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K20" s="10">
         <f>J20/B20</f>
         <v/>
       </c>
       <c r="L20" s="9" t="n">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M20" s="10">
         <f>L20/B20</f>
@@ -1710,13 +1710,13 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2838</v>
+        <v>2848</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1080</v>
+        <v>1060</v>
       </c>
       <c r="E21" s="10">
         <f>D21/B21</f>
@@ -1730,21 +1730,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1724</v>
+        <v>1772</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1758,14 +1758,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1755</v>
+        <v>1785</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15.40 WITA</t>
+          <t>Pukul        : 20.54 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2345,13 +2345,13 @@
         <v>377</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.8726790450928382</v>
+        <v>0.8779840848806366</v>
       </c>
     </row>
     <row r="15">
@@ -2375,45 +2375,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Clara Patricia Pangandaheng</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>377</v>
+        <v>511</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>307</v>
+        <v>420</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>323</v>
+        <v>443</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.8567639257294429</v>
+        <v>0.8669275929549901</v>
       </c>
     </row>
     <row r="16">
@@ -2422,45 +2422,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Ahmad Risandi Karim</t>
+          <t>Clara Patricia Pangandaheng</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>416</v>
+        <v>377</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.84375</v>
+        <v>0.8567639257294429</v>
       </c>
     </row>
     <row r="17">
@@ -2469,45 +2469,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Ahmad Risandi Karim</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>507</v>
+        <v>416</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>420</v>
+        <v>326</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>425</v>
+        <v>354</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8382642998027613</v>
+        <v>0.8509615384615384</v>
       </c>
     </row>
     <row r="18">
@@ -2516,45 +2516,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>426</v>
+        <v>389</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>84</v>
+        <v>7</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>269</v>
+        <v>319</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8380462724935732</v>
       </c>
     </row>
     <row r="19">
@@ -2563,45 +2563,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>388</v>
+        <v>426</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>2</v>
+        <v>84</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>4</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>319</v>
+        <v>269</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8376288659793815</v>
+        <v>0.8380281690140845</v>
       </c>
     </row>
     <row r="20">
@@ -2671,22 +2671,22 @@
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>413</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.8276553106212425</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="22">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Glenn Christi Palembang</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -2718,31 +2718,31 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>426</v>
+        <v>505</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="I22" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>348</v>
+        <v>398</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>350</v>
+        <v>417</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.8215962441314554</v>
+        <v>0.8257425742574257</v>
       </c>
     </row>
     <row r="23">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Glenn Christi Palembang</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
@@ -2765,31 +2765,31 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.8213457076566125</v>
+        <v>0.823943661971831</v>
       </c>
     </row>
     <row r="24">
@@ -2812,16 +2812,16 @@
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G24" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I24" s="9" t="n">
         <v>0</v>
@@ -2833,10 +2833,10 @@
         <v>1</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.8200836820083682</v>
+        <v>0.8225469728601253</v>
       </c>
     </row>
     <row r="25">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
@@ -2859,31 +2859,31 @@
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>503</v>
+        <v>431</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
         <v>8</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>398</v>
+        <v>346</v>
       </c>
       <c r="K25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>407</v>
+        <v>354</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.8091451292246521</v>
+        <v>0.8213457076566125</v>
       </c>
     </row>
     <row r="26">
@@ -3033,45 +3033,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>386</v>
+        <v>420</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>318</v>
+      </c>
+      <c r="K29" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="9" t="n">
-        <v>281</v>
-      </c>
-      <c r="K29" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" s="9" t="n">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7720207253886009</v>
+        <v>0.7809523809523811</v>
       </c>
     </row>
     <row r="30">
@@ -3080,45 +3080,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7714285714285716</v>
+        <v>0.7720207253886009</v>
       </c>
     </row>
     <row r="31">
@@ -3362,45 +3362,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>545</v>
+        <v>408</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>141</v>
+        <v>60</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I36" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>403</v>
+        <v>291</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>404</v>
+        <v>304</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7412844036697248</v>
+        <v>0.7450980392156863</v>
       </c>
     </row>
     <row r="37">
@@ -3409,45 +3409,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="K37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7392857142857143</v>
+        <v>0.7435897435897436</v>
       </c>
     </row>
     <row r="38">
@@ -3456,45 +3456,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>350</v>
+        <v>560</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>255</v>
+        <v>398</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>258</v>
+        <v>415</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7371428571428571</v>
+        <v>0.7410714285714286</v>
       </c>
     </row>
     <row r="39">
@@ -3503,45 +3503,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>425</v>
+        <v>508</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>291</v>
+        <v>364</v>
       </c>
       <c r="K39" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>313</v>
+        <v>375</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7364705882352941</v>
+        <v>0.7381889763779528</v>
       </c>
     </row>
     <row r="40">
@@ -3550,45 +3550,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>507</v>
+        <v>350</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>364</v>
+        <v>255</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>370</v>
+        <v>258</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7297830374753451</v>
+        <v>0.7371428571428571</v>
       </c>
     </row>
     <row r="41">
@@ -3597,45 +3597,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>505</v>
+        <v>425</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="G41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="I41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>291</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>349</v>
-      </c>
-      <c r="K41" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" s="9" t="n">
-        <v>364</v>
+        <v>313</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.7207920792079208</v>
+        <v>0.7364705882352941</v>
       </c>
     </row>
     <row r="42">
@@ -3658,19 +3658,19 @@
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" s="9" t="n">
         <v>323</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7171052631578947</v>
+        <v>0.7270742358078602</v>
       </c>
     </row>
     <row r="43">
@@ -3691,45 +3691,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>388</v>
+        <v>505</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J43" s="9" t="n">
-        <v>253</v>
+        <v>349</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>276</v>
+        <v>364</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.711340206185567</v>
+        <v>0.7207920792079208</v>
       </c>
     </row>
     <row r="44">
@@ -3738,45 +3738,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>458</v>
+        <v>390</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>323</v>
+        <v>278</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.7052401746724891</v>
+        <v>0.7128205128205128</v>
       </c>
     </row>
     <row r="45">
@@ -3785,45 +3785,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>505</v>
+        <v>458</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H45" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="I45" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I45" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J45" s="9" t="n">
-        <v>351</v>
+        <v>290</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>354</v>
+        <v>323</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.7009900990099009</v>
+        <v>0.7052401746724891</v>
       </c>
     </row>
     <row r="46">
@@ -3832,45 +3832,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>252</v>
+        <v>228</v>
       </c>
       <c r="K46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.7</v>
+        <v>0.7020057306590259</v>
       </c>
     </row>
     <row r="47">
@@ -3879,45 +3879,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>469</v>
+        <v>370</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>312</v>
+        <v>252</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>327</v>
+        <v>259</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.697228144989339</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="48">
@@ -3926,45 +3926,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>347</v>
+        <v>507</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>107</v>
+        <v>137</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>353</v>
+      </c>
+      <c r="K48" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="9" t="n">
-        <v>228</v>
-      </c>
-      <c r="K48" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" s="9" t="n">
-        <v>240</v>
+        <v>354</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.69164265129683</v>
+        <v>0.6982248520710059</v>
       </c>
     </row>
     <row r="49">
@@ -3973,45 +3973,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>389</v>
+        <v>469</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>223</v>
+        <v>312</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.6889460154241646</v>
+        <v>0.697228144989339</v>
       </c>
     </row>
     <row r="50">
@@ -4034,16 +4034,16 @@
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I50" s="9" t="n">
         <v>0</v>
@@ -4055,10 +4055,10 @@
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.688212927756654</v>
+        <v>0.6944971537001898</v>
       </c>
     </row>
     <row r="51">
@@ -4081,31 +4081,31 @@
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6856060606060607</v>
+        <v>0.6943396226415094</v>
       </c>
     </row>
     <row r="52">
@@ -4114,45 +4114,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="I52" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6889460154241646</v>
       </c>
     </row>
     <row r="53">
@@ -4161,45 +4161,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>428</v>
+        <v>380</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6775700934579441</v>
+        <v>0.6842105263157895</v>
       </c>
     </row>
     <row r="54">
@@ -4208,45 +4208,45 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>225</v>
+        <v>270</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.673076923076923</v>
+        <v>0.6775700934579441</v>
       </c>
     </row>
     <row r="55">
@@ -4255,45 +4255,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>458</v>
+        <v>416</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>93</v>
+        <v>136</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>305</v>
+        <v>267</v>
       </c>
       <c r="K55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>308</v>
+        <v>280</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.6724890829694323</v>
+        <v>0.673076923076923</v>
       </c>
     </row>
     <row r="56">
@@ -4302,45 +4302,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>289</v>
+        <v>458</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>191</v>
+        <v>305</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>194</v>
+        <v>308</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.671280276816609</v>
+        <v>0.6724890829694323</v>
       </c>
     </row>
     <row r="57">
@@ -4349,27 +4349,27 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>453</v>
+        <v>289</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="G57" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H57" s="9" t="n">
         <v>0</v>
@@ -4378,16 +4378,16 @@
         <v>1</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>302</v>
+        <v>191</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>304</v>
+        <v>194</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.6710816777041942</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="58">
@@ -4396,45 +4396,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>506</v>
+        <v>453</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6679841897233202</v>
+        <v>0.6710816777041942</v>
       </c>
     </row>
     <row r="59">
@@ -4443,45 +4443,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>406</v>
+        <v>506</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>91</v>
+        <v>164</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>269</v>
+        <v>324</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>271</v>
+        <v>338</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6674876847290641</v>
+        <v>0.6679841897233202</v>
       </c>
     </row>
     <row r="60">
@@ -4537,45 +4537,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>464</v>
+        <v>432</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6573275862068965</v>
+        <v>0.6620370370370371</v>
       </c>
     </row>
     <row r="62">
@@ -4584,45 +4584,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>281</v>
+        <v>305</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6528384279475984</v>
+        <v>0.6573275862068965</v>
       </c>
     </row>
     <row r="63">
@@ -4631,45 +4631,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.6505747126436782</v>
+        <v>0.655011655011655</v>
       </c>
     </row>
     <row r="64">
@@ -4678,45 +4678,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>502</v>
+        <v>459</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I64" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.647410358565737</v>
+        <v>0.65359477124183</v>
       </c>
     </row>
     <row r="65">
@@ -4725,45 +4725,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>432</v>
+        <v>481</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H65" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I65" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I65" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J65" s="9" t="n">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>278</v>
+        <v>313</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.6435185185185185</v>
+        <v>0.6507276507276507</v>
       </c>
     </row>
     <row r="66">
@@ -4772,45 +4772,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>469</v>
+        <v>435</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="K66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>301</v>
+        <v>283</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6417910447761195</v>
+        <v>0.6505747126436782</v>
       </c>
     </row>
     <row r="67">
@@ -4819,45 +4819,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>429</v>
+        <v>502</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.641025641025641</v>
+        <v>0.649402390438247</v>
       </c>
     </row>
     <row r="68">
@@ -4866,24 +4866,24 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1</v>
@@ -4892,19 +4892,19 @@
         <v>0</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>273</v>
+        <v>302</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.639344262295082</v>
+        <v>0.6454352441613588</v>
       </c>
     </row>
     <row r="69">
@@ -4913,45 +4913,45 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E69" s="9" t="n">
-        <v>625</v>
+        <v>416</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>219</v>
+        <v>142</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>394</v>
+        <v>258</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>399</v>
+        <v>268</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6384</v>
+        <v>0.6442307692307694</v>
       </c>
     </row>
     <row r="70">
@@ -4960,45 +4960,45 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>386</v>
+        <v>469</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="K70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>245</v>
+        <v>301</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.6347150259067358</v>
+        <v>0.6417910447761195</v>
       </c>
     </row>
     <row r="71">
@@ -5007,45 +5007,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>479</v>
+        <v>427</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="H71" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>304</v>
+        <v>273</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.6346555323590815</v>
+        <v>0.639344262295082</v>
       </c>
     </row>
     <row r="72">
@@ -5054,45 +5054,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>478</v>
+        <v>625</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>300</v>
+        <v>395</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>303</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>0.6338912133891214</v>
+        <v>399</v>
+      </c>
+      <c r="M72" s="11" t="n">
+        <v>0.6384</v>
       </c>
     </row>
     <row r="73">
@@ -5101,45 +5101,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>516</v>
+        <v>352</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>189</v>
+        <v>128</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>324</v>
+        <v>211</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>327</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>0.6337209302325582</v>
+        <v>224</v>
+      </c>
+      <c r="M73" s="11" t="n">
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="74">
@@ -5148,45 +5148,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>352</v>
+        <v>386</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>223</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>0.6335227272727273</v>
+        <v>245</v>
+      </c>
+      <c r="M74" s="11" t="n">
+        <v>0.6347150259067358</v>
       </c>
     </row>
     <row r="75">
@@ -5195,45 +5195,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>405</v>
+        <v>516</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>237</v>
+        <v>326</v>
       </c>
       <c r="K75" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>256</v>
+        <v>327</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>0.6320987654320988</v>
+        <v>0.6337209302325582</v>
       </c>
     </row>
     <row r="76">
@@ -5242,45 +5242,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>0.6308411214953271</v>
+        <v>0.6337078651685393</v>
       </c>
     </row>
     <row r="77">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -5303,31 +5303,31 @@
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>444</v>
+        <v>405</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>272</v>
+        <v>237</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0.6306306306306306</v>
+        <v>0.6320987654320988</v>
       </c>
     </row>
     <row r="78">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Asiantina Maniku</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -5350,31 +5350,31 @@
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0.6298076923076923</v>
+        <v>0.6317016317016317</v>
       </c>
     </row>
     <row r="79">
@@ -5397,16 +5397,16 @@
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I79" s="9" t="n">
         <v>1</v>
@@ -5418,10 +5418,10 @@
         <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.6293706293706294</v>
+        <v>0.6309523809523809</v>
       </c>
     </row>
     <row r="80">
@@ -5453,13 +5453,13 @@
         <v>3</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
@@ -5477,45 +5477,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>469</v>
+        <v>546</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="G81" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="I81" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H81" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I81" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J81" s="9" t="n">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>294</v>
+        <v>343</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.6268656716417911</v>
+        <v>0.6282051282051282</v>
       </c>
     </row>
     <row r="82">
@@ -5524,45 +5524,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>546</v>
+        <v>484</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>205</v>
+        <v>164</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="9" t="n">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>341</v>
+        <v>304</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.6245421245421245</v>
+        <v>0.628099173553719</v>
       </c>
     </row>
     <row r="83">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
@@ -5585,31 +5585,31 @@
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.6227897838899804</v>
+        <v>0.626204238921002</v>
       </c>
     </row>
     <row r="84">
@@ -5618,45 +5618,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>517</v>
+        <v>325</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>198</v>
+        <v>74</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>313</v>
+        <v>200</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>319</v>
+        <v>203</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.6170212765957447</v>
+        <v>0.6246153846153846</v>
       </c>
     </row>
     <row r="85">
@@ -5665,45 +5665,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>450</v>
+        <v>514</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="I85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>251</v>
+        <v>317</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>277</v>
+        <v>319</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.6155555555555555</v>
+        <v>0.6206225680933852</v>
       </c>
     </row>
     <row r="86">
@@ -5712,45 +5712,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>560</v>
+        <v>505</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>344</v>
+        <v>305</v>
       </c>
       <c r="K86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>344</v>
+        <v>313</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.6142857142857143</v>
+        <v>0.6198019801980198</v>
       </c>
     </row>
     <row r="87">
@@ -5759,45 +5759,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Jeklin Andris</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>465</v>
+        <v>561</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="9" t="n">
-        <v>262</v>
+        <v>344</v>
       </c>
       <c r="K87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="9" t="n">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.610752688172043</v>
+        <v>0.6167557932263814</v>
       </c>
     </row>
     <row r="88">
@@ -5806,45 +5806,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>504</v>
+        <v>453</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>306</v>
+        <v>279</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.6158940397350994</v>
       </c>
     </row>
     <row r="89">
@@ -5853,45 +5853,45 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Jeklin Andris</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E89" s="9" t="n">
-        <v>430</v>
+        <v>465</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="I89" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="9" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.6069767441860465</v>
+        <v>0.610752688172043</v>
       </c>
     </row>
     <row r="90">
@@ -5900,45 +5900,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>366</v>
+        <v>430</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>207</v>
+        <v>256</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.6093023255813953</v>
       </c>
     </row>
     <row r="91">
@@ -5947,45 +5947,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>325</v>
+        <v>366</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="K91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.6061538461538462</v>
+        <v>0.6065573770491803</v>
       </c>
     </row>
     <row r="92">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
@@ -6008,31 +6008,31 @@
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.6022222222222222</v>
+        <v>0.6044776119402985</v>
       </c>
     </row>
     <row r="93">
@@ -6041,45 +6041,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>361</v>
+        <v>469</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>144</v>
+        <v>186</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>211</v>
+        <v>283</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>217</v>
+        <v>283</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.6011080332409973</v>
+        <v>0.6034115138592751</v>
       </c>
     </row>
     <row r="94">
@@ -6088,45 +6088,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.6008492569002123</v>
+        <v>0.6022222222222222</v>
       </c>
     </row>
     <row r="95">
@@ -6135,45 +6135,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>402</v>
+        <v>361</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J95" s="9" t="n">
+        <v>211</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="9" t="n">
         <v>217</v>
       </c>
-      <c r="K95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="9" t="n">
-        <v>241</v>
-      </c>
       <c r="M95" s="12" t="n">
-        <v>0.599502487562189</v>
+        <v>0.6011080332409973</v>
       </c>
     </row>
     <row r="96">
@@ -6182,45 +6182,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.5970149253731343</v>
+        <v>0.6008492569002123</v>
       </c>
     </row>
     <row r="97">
@@ -6243,16 +6243,16 @@
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>24</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I97" s="9" t="n">
         <v>1</v>
@@ -6264,10 +6264,10 @@
         <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.5970149253731343</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="98">
@@ -6299,13 +6299,13 @@
         <v>13</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I98" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>0</v>
@@ -6323,45 +6323,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>379</v>
+        <v>461</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>160</v>
+        <v>192</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>207</v>
+        <v>266</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>219</v>
+        <v>269</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5778364116094987</v>
+        <v>0.5835140997830802</v>
       </c>
     </row>
     <row r="100">
@@ -6384,31 +6384,31 @@
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>2</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I100" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="K100" s="9" t="n">
         <v>3</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.5763358778625954</v>
+        <v>0.5828571428571429</v>
       </c>
     </row>
     <row r="101">
@@ -6434,7 +6434,7 @@
         <v>446</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>1</v>
@@ -6446,16 +6446,16 @@
         <v>0</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5739910313901345</v>
+        <v>0.5807174887892377</v>
       </c>
     </row>
     <row r="102">
@@ -6464,45 +6464,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>496</v>
+        <v>398</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I102" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="K102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>283</v>
+        <v>231</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5705645161290323</v>
+        <v>0.5804020100502513</v>
       </c>
     </row>
     <row r="103">
@@ -6511,45 +6511,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5692695214105793</v>
+        <v>0.5789473684210527</v>
       </c>
     </row>
     <row r="104">
@@ -6558,45 +6558,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Rendy Julio Bangonang</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>455</v>
+        <v>497</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I104" s="9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="J104" s="9" t="n">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L104" s="9" t="n">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.567032967032967</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="105">
@@ -6605,45 +6605,45 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Rendy Julio Bangonang</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E105" s="9" t="n">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H105" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I105" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J105" s="9" t="n">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.5577342047930284</v>
+        <v>0.567032967032967</v>
       </c>
     </row>
     <row r="106">
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I106" s="9" t="n">
         <v>12</v>
@@ -6687,10 +6687,10 @@
         <v>0</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5526932084309133</v>
+        <v>0.5584112149532711</v>
       </c>
     </row>
     <row r="107">
@@ -6699,45 +6699,45 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5513784461152882</v>
+        <v>0.5552941176470588</v>
       </c>
     </row>
     <row r="108">
@@ -6746,45 +6746,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>412</v>
+        <v>517</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>221</v>
+        <v>284</v>
       </c>
       <c r="K108" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>227</v>
+        <v>286</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5509708737864077</v>
+        <v>0.5531914893617021</v>
       </c>
     </row>
     <row r="109">
@@ -6793,45 +6793,45 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D109" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>422</v>
+        <v>399</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5450236966824644</v>
+        <v>0.5513784461152882</v>
       </c>
     </row>
     <row r="110">
@@ -6840,45 +6840,45 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E110" s="9" t="n">
-        <v>479</v>
+        <v>412</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>216</v>
+        <v>170</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>259</v>
+        <v>227</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5407098121085595</v>
+        <v>0.5509708737864077</v>
       </c>
     </row>
     <row r="111">
@@ -6887,45 +6887,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>512</v>
+        <v>479</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>271</v>
+        <v>189</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5390625</v>
+        <v>0.5407098121085595</v>
       </c>
     </row>
     <row r="112">
@@ -6957,13 +6957,13 @@
         <v>2</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0</v>
@@ -7004,13 +7004,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J113" s="9" t="n">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="K113" s="9" t="n">
         <v>0</v>
@@ -7051,13 +7051,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="K114" s="9" t="n">
         <v>0</v>
@@ -7075,45 +7075,45 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Svidania Kundiman</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D115" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>476</v>
+        <v>420</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="I115" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J115" s="9" t="n">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="K115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.523109243697479</v>
+        <v>0.5285714285714286</v>
       </c>
     </row>
     <row r="116">
@@ -7122,45 +7122,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>455</v>
+        <v>477</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5230769230769231</v>
+        <v>0.5262054507337526</v>
       </c>
     </row>
     <row r="117">
@@ -7169,45 +7169,45 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D117" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E117" s="9" t="n">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J117" s="9" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5228310502283106</v>
+        <v>0.5230769230769231</v>
       </c>
     </row>
     <row r="118">
@@ -7216,45 +7216,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Svidania Kundiman</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="G118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5214285714285715</v>
+        <v>0.5228310502283106</v>
       </c>
     </row>
     <row r="119">
@@ -7277,16 +7277,16 @@
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" s="9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I119" s="9" t="n">
         <v>12</v>
@@ -7298,10 +7298,10 @@
         <v>0</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5208845208845209</v>
+        <v>0.5220588235294118</v>
       </c>
     </row>
     <row r="120">
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F120" s="9" t="n">
         <v>217</v>
@@ -7333,7 +7333,7 @@
         <v>2</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I120" s="9" t="n">
         <v>10</v>
@@ -7345,10 +7345,10 @@
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.5207877461706784</v>
+        <v>0.5218340611353712</v>
       </c>
     </row>
     <row r="121">
@@ -7404,45 +7404,45 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="G122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="I122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J122" s="9" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="K122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.5096153846153846</v>
+        <v>0.5136363636363637</v>
       </c>
     </row>
     <row r="123">
@@ -7451,45 +7451,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.5093896713615024</v>
+        <v>0.5119047619047619</v>
       </c>
     </row>
     <row r="124">
@@ -7498,45 +7498,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.5068181818181818</v>
+        <v>0.5096153846153846</v>
       </c>
     </row>
     <row r="125">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
@@ -7559,31 +7559,31 @@
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="F125" s="9" t="n">
+        <v>209</v>
+      </c>
+      <c r="G125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I125" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="9" t="n">
         <v>213</v>
       </c>
-      <c r="G125" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H125" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="I125" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J125" s="9" t="n">
-        <v>196</v>
-      </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.5067873303167421</v>
+        <v>0.5093896713615024</v>
       </c>
     </row>
     <row r="126">
@@ -7592,36 +7592,36 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
         <v>225</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.5056179775280899</v>
+        <v>0.5090497737556561</v>
       </c>
     </row>
     <row r="127">
@@ -7639,45 +7639,45 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>420</v>
+        <v>445</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.5047619047619047</v>
+        <v>0.5056179775280899</v>
       </c>
     </row>
     <row r="128">
@@ -7686,45 +7686,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.5012224938875306</v>
+        <v>0.5044843049327354</v>
       </c>
     </row>
     <row r="129">
@@ -7733,45 +7733,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.4987468671679198</v>
+        <v>0.5036674816625917</v>
       </c>
     </row>
     <row r="130">
@@ -7780,45 +7780,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>444</v>
+        <v>399</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="K130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4954954954954955</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="131">
@@ -7844,13 +7844,13 @@
         <v>515</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G131" s="9" t="n">
         <v>5</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I131" s="9" t="n">
         <v>14</v>
@@ -7862,10 +7862,10 @@
         <v>1</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4912621359223301</v>
+        <v>0.4932038834951457</v>
       </c>
     </row>
     <row r="132">
@@ -7874,45 +7874,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="F132" s="9" t="n">
         <v>201</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="K132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4904761904761905</v>
+        <v>0.4924242424242424</v>
       </c>
     </row>
     <row r="133">
@@ -7921,45 +7921,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>193</v>
+        <v>161</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4873737373737373</v>
+        <v>0.4894117647058824</v>
       </c>
     </row>
     <row r="134">
@@ -8029,31 +8029,31 @@
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G135" s="9" t="n">
         <v>1</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4680851063829787</v>
+        <v>0.4716981132075472</v>
       </c>
     </row>
     <row r="136">
@@ -8076,31 +8076,31 @@
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F136" s="9" t="n">
         <v>8</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I136" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" s="9" t="n">
         <v>152</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4510385756676558</v>
+        <v>0.4483775811209439</v>
       </c>
     </row>
   </sheetData>
@@ -8129,7 +8129,7 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15.40 WITA</t>
+          <t>Pukul        : 20.54 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8262,16 +8262,16 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2934</v>
+        <v>2938</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>1</v>
@@ -8286,7 +8286,7 @@
         <v>2504</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.8534423994546694</v>
+        <v>0.852280462899932</v>
       </c>
     </row>
     <row r="8">
@@ -8312,13 +8312,13 @@
         <v>2835</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>14</v>
@@ -8356,16 +8356,16 @@
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>23</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>5</v>
@@ -8380,7 +8380,7 @@
         <v>1541</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7561334641805693</v>
+        <v>0.7557626287395781</v>
       </c>
     </row>
     <row r="10">
@@ -8389,45 +8389,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Charly Angel Tatontos</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan, Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Alfi, Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2524</v>
+        <v>2936</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>614</v>
+        <v>557</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>44</v>
+        <v>136</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1862</v>
+        <v>2112</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>1866</v>
+        <v>2169</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7393026941362916</v>
+        <v>0.7387602179836512</v>
       </c>
     </row>
     <row r="11">
@@ -8436,45 +8436,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Charly Angel Tatontos</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan, Tabukan Utara</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi, Hendri</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2936</v>
+        <v>2528</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>557</v>
+        <v>599</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>74</v>
+        <v>2</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>2112</v>
+        <v>1863</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>2169</v>
+        <v>1864</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7387602179836512</v>
+        <v>0.7373417721518988</v>
       </c>
     </row>
     <row r="12">
@@ -8497,19 +8497,19 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2867</v>
+        <v>2869</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>2089</v>
@@ -8518,10 +8518,10 @@
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.730728985001744</v>
+        <v>0.7298710352039037</v>
       </c>
     </row>
     <row r="13">
@@ -8544,31 +8544,31 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2915</v>
+        <v>2923</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>929</v>
+        <v>919</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="H13" s="9" t="n">
         <v>10</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1929</v>
+        <v>1937</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1938</v>
+        <v>1945</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6648370497427101</v>
+        <v>0.6654122476907287</v>
       </c>
     </row>
     <row r="14">
@@ -8591,16 +8591,16 @@
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2810</v>
+        <v>2816</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>9</v>
@@ -8615,7 +8615,7 @@
         <v>1846</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6569395017793594</v>
+        <v>0.6555397727272727</v>
       </c>
     </row>
     <row r="15">
@@ -8624,45 +8624,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Manganitu, Tamako</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike, Mega</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2119</v>
+        <v>2433</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>661</v>
+        <v>819</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1380</v>
+        <v>1578</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1382</v>
+        <v>1588</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6521944313355357</v>
+        <v>0.6526921496095356</v>
       </c>
     </row>
     <row r="16">
@@ -8671,45 +8671,45 @@
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Manganitu, Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Erike, Mega</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2431</v>
+        <v>2121</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>824</v>
+        <v>657</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1570</v>
+        <v>1380</v>
       </c>
       <c r="K16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1581</v>
+        <v>1381</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6503496503496503</v>
+        <v>0.6511079679396511</v>
       </c>
     </row>
     <row r="17">
@@ -8718,45 +8718,45 @@
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2181</v>
+        <v>2904</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>752</v>
+        <v>1005</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1349</v>
+        <v>1795</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1362</v>
+        <v>1821</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.624484181568088</v>
+        <v>0.6270661157024794</v>
       </c>
     </row>
     <row r="18">
@@ -8765,45 +8765,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2898</v>
+        <v>2848</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1774</v>
+        <v>1772</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>1800</v>
+        <v>1785</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.6211180124223602</v>
+        <v>0.6267556179775281</v>
       </c>
     </row>
     <row r="19">
@@ -8812,45 +8812,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2838</v>
+        <v>2183</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>1080</v>
+        <v>751</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1724</v>
+        <v>1349</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1736</v>
+        <v>1362</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.6116983791402396</v>
+        <v>0.6239120476408612</v>
       </c>
     </row>
     <row r="20">
@@ -8873,31 +8873,31 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2683</v>
+        <v>2684</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1069</v>
+        <v>1052</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1586</v>
+        <v>1597</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1587</v>
+        <v>1598</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5915020499440924</v>
+        <v>0.5953800298062594</v>
       </c>
     </row>
     <row r="21">
@@ -8906,45 +8906,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>2335</v>
+        <v>1452</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>878</v>
+        <v>302</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>85</v>
+        <v>271</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1315</v>
+        <v>856</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1339</v>
+        <v>864</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5734475374732334</v>
+        <v>0.5950413223140496</v>
       </c>
     </row>
     <row r="22">
@@ -8953,45 +8953,45 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Selatan, Tabukan Tengah</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis, Lusine</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>1447</v>
+        <v>2467</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>334</v>
+        <v>869</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>274</v>
+        <v>34</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>811</v>
+        <v>1423</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>813</v>
+        <v>1457</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5618521078092605</v>
+        <v>0.5905958654235914</v>
       </c>
     </row>
     <row r="23">
@@ -9000,45 +9000,45 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2727</v>
+        <v>2339</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1098</v>
+        <v>873</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="I23" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>1315</v>
+      </c>
+      <c r="K23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="9" t="n">
-        <v>1510</v>
-      </c>
-      <c r="K23" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="L23" s="9" t="n">
-        <v>1515</v>
+        <v>1339</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5724668661821292</v>
       </c>
     </row>
     <row r="24">
@@ -9047,45 +9047,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan, Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Kharis, Lusine</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>2466</v>
+        <v>2746</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>870</v>
+        <v>1088</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>199</v>
+        <v>89</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>1359</v>
+        <v>1510</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1363</v>
+        <v>1515</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.5527169505271695</v>
+        <v>0.5517115804806992</v>
       </c>
     </row>
     <row r="25">
@@ -9094,45 +9094,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>2566</v>
+        <v>2724</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>1120</v>
+        <v>1209</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>1394</v>
+        <v>1483</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>1397</v>
+        <v>1488</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.5444271239282931</v>
+        <v>0.5462555066079295</v>
       </c>
     </row>
     <row r="26">
@@ -9141,45 +9141,45 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>2422</v>
+        <v>2568</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>1019</v>
+        <v>1112</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>1208</v>
+        <v>1394</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>1267</v>
+        <v>1397</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.523121387283237</v>
+        <v>0.5440031152647975</v>
       </c>
     </row>
     <row r="27">
@@ -9202,31 +9202,31 @@
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>2110</v>
+        <v>2120</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1017</v>
+        <v>1035</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>1099</v>
+        <v>1121</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.5208530805687204</v>
+        <v>0.5287735849056604</v>
       </c>
     </row>
     <row r="28">
@@ -9235,45 +9235,45 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>2723</v>
+        <v>2422</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1211</v>
+        <v>1017</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1396</v>
+        <v>1210</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>1400</v>
+        <v>1269</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.5141388174807198</v>
+        <v>0.5239471511147812</v>
       </c>
     </row>
     <row r="29">
@@ -9296,31 +9296,31 @@
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>981</v>
+        <v>971</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1003</v>
+        <v>1008</v>
       </c>
       <c r="K29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>1016</v>
+        <v>1028</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.4889316650625601</v>
+        <v>0.4944684944684944</v>
       </c>
     </row>
   </sheetData>
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 15.40 WITA</t>
+          <t>Pukul        : 20.54 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0.8073946689595872</v>
+        <v>0.8116938950988822</v>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>0.7882938978829389</v>
+        <v>0.7895392278953923</v>
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0.7700441919191919</v>
+        <v>0.7718523193436415</v>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         </is>
       </c>
       <c r="C10" s="11" t="n">
-        <v>0.7461415646620543</v>
+        <v>0.7487522565572902</v>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0.7293721433726245</v>
+        <v>0.7307692307692306</v>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.6550724637681159</v>
+        <v>0.6557377049180327</v>
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.6457242582897034</v>
+        <v>0.6465968586387434</v>
       </c>
       <c r="D13" s="17" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.6183932346723044</v>
+        <v>0.6267556179775281</v>
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
@@ -9580,7 +9580,7 @@
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.608064207911332</v>
+        <v>0.6147243944306695</v>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.5798203178991016</v>
+        <v>0.6053719008264463</v>
       </c>
       <c r="D17" s="17" t="inlineStr">
         <is>
@@ -9616,7 +9616,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.5763694951664876</v>
+        <v>0.5785744954916273</v>
       </c>
       <c r="D18" s="17" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.5728513463666544</v>
+        <v>0.5759136620063773</v>
       </c>
       <c r="D19" s="17" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>0.5689512799339389</v>
+        <v>0.5697770437654831</v>
       </c>
       <c r="D20" s="17" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>0.5576733486690766</v>
+        <v>0.5614035087719298</v>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.54 WITA</t>
+          <t>Pukul        : 21.09 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.54 WITA</t>
+          <t>Pukul        : 21.09 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.54 WITA</t>
+          <t>Pukul        : 21.09 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.54 WITA</t>
+          <t>Pukul        : 21.09 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring Kecamatan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PPL" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard PML" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leaderboard Kecamatan" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 21.09 WITA</t>
+          <t>Pukul        : 20.54 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 21.09 WITA</t>
+          <t>Pukul        : 20.54 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 21.09 WITA</t>
+          <t>Pukul        : 20.54 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 21.09 WITA</t>
+          <t>Pukul        : 20.54 WITA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">

--- a/dashboard/public/Report_Dashboard_Latest.xlsx
+++ b/dashboard/public/Report_Dashboard_Latest.xlsx
@@ -588,7 +588,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 22 Juli 2026</t>
+          <t>Hari/Tanggal : 23 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -610,7 +610,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.54 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -744,27 +744,27 @@
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>4160</v>
+        <v>4163</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>48</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1092</v>
+        <v>1079</v>
       </c>
       <c r="E7" s="10">
         <f>D7/B7</f>
         <v/>
       </c>
       <c r="F7" s="9" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="G7" s="10">
         <f>F7/B7</f>
         <v/>
       </c>
       <c r="H7" s="9" t="n">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="I7" s="10">
         <f>H7/B7</f>
@@ -792,14 +792,14 @@
         <v/>
       </c>
       <c r="P7" s="9" t="n">
-        <v>3040</v>
+        <v>3065</v>
       </c>
       <c r="Q7" s="11">
         <f>P7/B7</f>
         <v/>
       </c>
       <c r="R7" s="9" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="S7" s="10">
         <f>R7/B7</f>
@@ -813,27 +813,27 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>1452</v>
+        <v>1456</v>
       </c>
       <c r="C8" s="9" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="E8" s="10">
         <f>D8/B8</f>
         <v/>
       </c>
       <c r="F8" s="9" t="n">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="G8" s="10">
         <f>F8/B8</f>
         <v/>
       </c>
       <c r="H8" s="9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I8" s="10">
         <f>H8/B8</f>
@@ -847,28 +847,28 @@
         <v/>
       </c>
       <c r="L8" s="9" t="n">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="M8" s="10">
         <f>L8/B8</f>
         <v/>
       </c>
       <c r="N8" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O8" s="10">
         <f>N8/B8</f>
         <v/>
       </c>
       <c r="P8" s="9" t="n">
-        <v>879</v>
+        <v>901</v>
       </c>
       <c r="Q8" s="12">
         <f>P8/B8</f>
         <v/>
       </c>
       <c r="R8" s="9" t="n">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="S8" s="10">
         <f>R8/B8</f>
@@ -882,13 +882,13 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>6338</v>
+        <v>6341</v>
       </c>
       <c r="C9" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1353</v>
+        <v>1340</v>
       </c>
       <c r="E9" s="10">
         <f>D9/B9</f>
@@ -902,21 +902,21 @@
         <v/>
       </c>
       <c r="H9" s="9" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I9" s="10">
         <f>H9/B9</f>
         <v/>
       </c>
       <c r="J9" s="9" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K9" s="10">
         <f>J9/B9</f>
         <v/>
       </c>
       <c r="L9" s="9" t="n">
-        <v>4621</v>
+        <v>4636</v>
       </c>
       <c r="M9" s="10">
         <f>L9/B9</f>
@@ -930,14 +930,14 @@
         <v/>
       </c>
       <c r="P9" s="9" t="n">
-        <v>4892</v>
+        <v>4908</v>
       </c>
       <c r="Q9" s="11">
         <f>P9/B9</f>
         <v/>
       </c>
       <c r="R9" s="9" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="S9" s="10">
         <f>R9/B9</f>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>3212</v>
+        <v>3218</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>42</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>676</v>
+        <v>657</v>
       </c>
       <c r="E10" s="10">
         <f>D10/B10</f>
@@ -971,7 +971,7 @@
         <v/>
       </c>
       <c r="H10" s="9" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="I10" s="10">
         <f>H10/B10</f>
@@ -985,7 +985,7 @@
         <v/>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2477</v>
+        <v>2482</v>
       </c>
       <c r="M10" s="10">
         <f>L10/B10</f>
@@ -999,14 +999,14 @@
         <v/>
       </c>
       <c r="P10" s="9" t="n">
-        <v>2536</v>
+        <v>2561</v>
       </c>
       <c r="Q10" s="11">
         <f>P10/B10</f>
         <v/>
       </c>
       <c r="R10" s="9" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="S10" s="10">
         <f>R10/B10</f>
@@ -1026,21 +1026,21 @@
         <v>27</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E11" s="10">
         <f>D11/B11</f>
         <v/>
       </c>
       <c r="F11" s="9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G11" s="10">
         <f>F11/B11</f>
         <v/>
       </c>
       <c r="H11" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I11" s="10">
         <f>H11/B11</f>
@@ -1054,7 +1054,7 @@
         <v/>
       </c>
       <c r="L11" s="9" t="n">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="M11" s="10">
         <f>L11/B11</f>
@@ -1068,14 +1068,14 @@
         <v/>
       </c>
       <c r="P11" s="9" t="n">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="Q11" s="11">
         <f>P11/B11</f>
         <v/>
       </c>
       <c r="R11" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="S11" s="10">
         <f>R11/B11</f>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="B12" s="9" t="n">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>23</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E12" s="10">
         <f>D12/B12</f>
@@ -1109,7 +1109,7 @@
         <v/>
       </c>
       <c r="H12" s="9" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I12" s="10">
         <f>H12/B12</f>
@@ -1137,14 +1137,14 @@
         <v/>
       </c>
       <c r="P12" s="9" t="n">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="Q12" s="11">
         <f>P12/B12</f>
         <v/>
       </c>
       <c r="R12" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="S12" s="10">
         <f>R12/B12</f>
@@ -1158,41 +1158,41 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>4658</v>
+        <v>4665</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>59</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1927</v>
+        <v>1909</v>
       </c>
       <c r="E13" s="10">
         <f>D13/B13</f>
         <v/>
       </c>
       <c r="F13" s="9" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G13" s="10">
         <f>F13/B13</f>
         <v/>
       </c>
       <c r="H13" s="9" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="I13" s="10">
         <f>H13/B13</f>
         <v/>
       </c>
       <c r="J13" s="9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K13" s="10">
         <f>J13/B13</f>
         <v/>
       </c>
       <c r="L13" s="9" t="n">
-        <v>2510</v>
+        <v>2519</v>
       </c>
       <c r="M13" s="10">
         <f>L13/B13</f>
@@ -1206,14 +1206,14 @@
         <v/>
       </c>
       <c r="P13" s="9" t="n">
-        <v>2695</v>
+        <v>2725</v>
       </c>
       <c r="Q13" s="12">
         <f>P13/B13</f>
         <v/>
       </c>
       <c r="R13" s="9" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="S13" s="10">
         <f>R13/B13</f>
@@ -1227,41 +1227,41 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>6099</v>
+        <v>6108</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>76</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>2644</v>
+        <v>2628</v>
       </c>
       <c r="E14" s="10">
         <f>D14/B14</f>
         <v/>
       </c>
       <c r="F14" s="9" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G14" s="10">
         <f>F14/B14</f>
         <v/>
       </c>
       <c r="H14" s="9" t="n">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="I14" s="10">
         <f>H14/B14</f>
         <v/>
       </c>
       <c r="J14" s="9" t="n">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="K14" s="10">
         <f>J14/B14</f>
         <v/>
       </c>
       <c r="L14" s="9" t="n">
-        <v>3201</v>
+        <v>3263</v>
       </c>
       <c r="M14" s="10">
         <f>L14/B14</f>
@@ -1275,14 +1275,14 @@
         <v/>
       </c>
       <c r="P14" s="9" t="n">
-        <v>3424</v>
+        <v>3454</v>
       </c>
       <c r="Q14" s="12">
         <f>P14/B14</f>
         <v/>
       </c>
       <c r="R14" s="9" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="S14" s="10">
         <f>R14/B14</f>
@@ -1296,27 +1296,27 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>8154</v>
+        <v>8167</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>84</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>3349</v>
+        <v>3303</v>
       </c>
       <c r="E15" s="10">
         <f>D15/B15</f>
         <v/>
       </c>
       <c r="F15" s="9" t="n">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G15" s="10">
         <f>F15/B15</f>
         <v/>
       </c>
       <c r="H15" s="9" t="n">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="I15" s="10">
         <f>H15/B15</f>
@@ -1330,7 +1330,7 @@
         <v/>
       </c>
       <c r="L15" s="9" t="n">
-        <v>4590</v>
+        <v>4643</v>
       </c>
       <c r="M15" s="10">
         <f>L15/B15</f>
@@ -1344,14 +1344,14 @@
         <v/>
       </c>
       <c r="P15" s="9" t="n">
-        <v>4696</v>
+        <v>4770</v>
       </c>
       <c r="Q15" s="12">
         <f>P15/B15</f>
         <v/>
       </c>
       <c r="R15" s="9" t="n">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="S15" s="10">
         <f>R15/B15</f>
@@ -1365,27 +1365,27 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>5243</v>
+        <v>5251</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>67</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1878</v>
+        <v>1853</v>
       </c>
       <c r="E16" s="10">
         <f>D16/B16</f>
         <v/>
       </c>
       <c r="F16" s="9" t="n">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="G16" s="10">
         <f>F16/B16</f>
         <v/>
       </c>
       <c r="H16" s="9" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I16" s="10">
         <f>H16/B16</f>
@@ -1399,7 +1399,7 @@
         <v/>
       </c>
       <c r="L16" s="9" t="n">
-        <v>3110</v>
+        <v>3165</v>
       </c>
       <c r="M16" s="10">
         <f>L16/B16</f>
@@ -1413,14 +1413,14 @@
         <v/>
       </c>
       <c r="P16" s="9" t="n">
-        <v>3223</v>
+        <v>3280</v>
       </c>
       <c r="Q16" s="12">
         <f>P16/B16</f>
         <v/>
       </c>
       <c r="R16" s="9" t="n">
-        <v>68</v>
+        <v>125</v>
       </c>
       <c r="S16" s="10">
         <f>R16/B16</f>
@@ -1440,56 +1440,56 @@
         <v>40</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1017</v>
+        <v>999</v>
       </c>
       <c r="E17" s="10">
         <f>D17/B17</f>
         <v/>
       </c>
       <c r="F17" s="9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G17" s="10">
         <f>F17/B17</f>
         <v/>
       </c>
       <c r="H17" s="9" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I17" s="10">
         <f>H17/B17</f>
         <v/>
       </c>
       <c r="J17" s="9" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K17" s="10">
         <f>J17/B17</f>
         <v/>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1210</v>
+        <v>1219</v>
       </c>
       <c r="M17" s="10">
         <f>L17/B17</f>
         <v/>
       </c>
       <c r="N17" s="9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O17" s="10">
         <f>N17/B17</f>
         <v/>
       </c>
       <c r="P17" s="9" t="n">
-        <v>1380</v>
+        <v>1399</v>
       </c>
       <c r="Q17" s="12">
         <f>P17/B17</f>
         <v/>
       </c>
       <c r="R17" s="9" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="S17" s="10">
         <f>R17/B17</f>
@@ -1503,41 +1503,41 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>9417</v>
+        <v>9424</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>96</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2247</v>
+        <v>2227</v>
       </c>
       <c r="E18" s="10">
         <f>D18/B18</f>
         <v/>
       </c>
       <c r="F18" s="9" t="n">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="G18" s="10">
         <f>F18/B18</f>
         <v/>
       </c>
       <c r="H18" s="9" t="n">
-        <v>198</v>
+        <v>162</v>
       </c>
       <c r="I18" s="10">
         <f>H18/B18</f>
         <v/>
       </c>
       <c r="J18" s="9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K18" s="10">
         <f>J18/B18</f>
         <v/>
       </c>
       <c r="L18" s="9" t="n">
-        <v>6827</v>
+        <v>6933</v>
       </c>
       <c r="M18" s="10">
         <f>L18/B18</f>
@@ -1551,14 +1551,14 @@
         <v/>
       </c>
       <c r="P18" s="9" t="n">
-        <v>7051</v>
+        <v>7119</v>
       </c>
       <c r="Q18" s="11">
         <f>P18/B18</f>
         <v/>
       </c>
       <c r="R18" s="9" t="n">
-        <v>81</v>
+        <v>149</v>
       </c>
       <c r="S18" s="10">
         <f>R18/B18</f>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>26</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E19" s="10">
         <f>D19/B19</f>
@@ -1592,21 +1592,21 @@
         <v/>
       </c>
       <c r="H19" s="9" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="I19" s="10">
         <f>H19/B19</f>
         <v/>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K19" s="10">
         <f>J19/B19</f>
         <v/>
       </c>
       <c r="L19" s="9" t="n">
-        <v>907</v>
+        <v>953</v>
       </c>
       <c r="M19" s="10">
         <f>L19/B19</f>
@@ -1620,14 +1620,14 @@
         <v/>
       </c>
       <c r="P19" s="9" t="n">
-        <v>944</v>
+        <v>959</v>
       </c>
       <c r="Q19" s="11">
         <f>P19/B19</f>
         <v/>
       </c>
       <c r="R19" s="9" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="S19" s="10">
         <f>R19/B19</f>
@@ -1710,7 +1710,7 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>39</v>
@@ -1730,21 +1730,21 @@
         <v/>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" s="10">
         <f>H21/B21</f>
         <v/>
       </c>
       <c r="J21" s="9" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="K21" s="10">
         <f>J21/B21</f>
         <v/>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1772</v>
+        <v>1743</v>
       </c>
       <c r="M21" s="10">
         <f>L21/B21</f>
@@ -1758,14 +1758,14 @@
         <v/>
       </c>
       <c r="P21" s="9" t="n">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="Q21" s="12">
         <f>P21/B21</f>
         <v/>
       </c>
       <c r="R21" s="9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S21" s="10">
         <f>R21/B21</f>
@@ -1880,7 +1880,7 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1894,7 +1894,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 22 Juli 2026</t>
+          <t>Hari/Tanggal : 23 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.54 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2116,13 +2116,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="K9" s="9" t="n">
         <v>0</v>
@@ -2201,16 +2201,16 @@
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I11" s="9" t="n">
         <v>0</v>
@@ -2222,10 +2222,10 @@
         <v>1</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.9158576051779935</v>
+        <v>0.9196141479099679</v>
       </c>
     </row>
     <row r="12">
@@ -2234,45 +2234,45 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Fitria Rianti Gorosita</t>
+          <t>Avricilya Ester Rangian</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>384</v>
+        <v>511</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>338</v>
+        <v>466</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>343</v>
+        <v>466</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.8932291666666665</v>
+        <v>0.9119373776908023</v>
       </c>
     </row>
     <row r="13">
@@ -2281,45 +2281,45 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Alfred Jonathan</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.8818681318681318</v>
+        <v>0.8947368421052632</v>
       </c>
     </row>
     <row r="14">
@@ -2328,45 +2328,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Alfred Jonathan</t>
+          <t>Fitria Rianti Gorosita</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.8779840848806366</v>
+        <v>0.8932291666666665</v>
       </c>
     </row>
     <row r="15">
@@ -2375,45 +2375,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Avricilya Ester Rangian</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>511</v>
+        <v>364</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>43</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>420</v>
+        <v>313</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>443</v>
+        <v>321</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.8669275929549901</v>
+        <v>0.8818681318681318</v>
       </c>
     </row>
     <row r="16">
@@ -2439,13 +2439,13 @@
         <v>377</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>2</v>
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.8567639257294429</v>
+        <v>0.870026525198939</v>
       </c>
     </row>
     <row r="17">
@@ -2486,28 +2486,28 @@
         <v>416</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M17" s="11" t="n">
-        <v>0.8509615384615384</v>
+        <v>0.8533653846153846</v>
       </c>
     </row>
     <row r="18">
@@ -2516,45 +2516,45 @@
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Sandy Anggriawan Makangiras</t>
+          <t>Meisye Fransiska Samau</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>389</v>
+        <v>406</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="M18" s="11" t="n">
-        <v>0.8380462724935732</v>
+        <v>0.8472906403940886</v>
       </c>
     </row>
     <row r="19">
@@ -2563,45 +2563,45 @@
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Asari Prisilia Antari</t>
+          <t>Rubiani Mamuka</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>426</v>
+        <v>500</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>269</v>
+        <v>412</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="M19" s="11" t="n">
-        <v>0.8380281690140845</v>
+        <v>0.8420000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -2610,45 +2610,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Meisye Fransiska Samau</t>
+          <t>Sandy Anggriawan Makangiras</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>405</v>
+        <v>389</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="M20" s="11" t="n">
-        <v>0.8370370370370369</v>
+        <v>0.8406169665809768</v>
       </c>
     </row>
     <row r="21">
@@ -2657,45 +2657,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Rubiani Mamuka</t>
+          <t>Asari Prisilia Antari</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>500</v>
+        <v>426</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>412</v>
+        <v>269</v>
       </c>
       <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>413</v>
+        <v>357</v>
       </c>
       <c r="M21" s="11" t="n">
-        <v>0.826</v>
+        <v>0.8380281690140845</v>
       </c>
     </row>
     <row r="22">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Puteri Teratai Timuhingide</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
@@ -2718,31 +2718,31 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>505</v>
+        <v>434</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>398</v>
+        <v>346</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>417</v>
+        <v>361</v>
       </c>
       <c r="M22" s="11" t="n">
-        <v>0.8257425742574257</v>
+        <v>0.8317972350230414</v>
       </c>
     </row>
     <row r="23">
@@ -2768,28 +2768,28 @@
         <v>426</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M23" s="11" t="n">
-        <v>0.823943661971831</v>
+        <v>0.8262910798122065</v>
       </c>
     </row>
     <row r="24">
@@ -2798,45 +2798,45 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Puteri Teratai Timuhingide</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>479</v>
+        <v>505</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>85</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="M24" s="11" t="n">
-        <v>0.8225469728601253</v>
+        <v>0.8257425742574257</v>
       </c>
     </row>
     <row r="25">
@@ -2845,45 +2845,45 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="C25" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E25" s="9" t="n">
-        <v>431</v>
+        <v>479</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="G25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I25" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>346</v>
+        <v>377</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>354</v>
+        <v>394</v>
       </c>
       <c r="M25" s="11" t="n">
-        <v>0.8213457076566125</v>
+        <v>0.8225469728601253</v>
       </c>
     </row>
     <row r="26">
@@ -2939,45 +2939,45 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Meychindy Riane Takaheghesang</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E27" s="9" t="n">
-        <v>533</v>
+        <v>425</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I27" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>420</v>
+        <v>318</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>420</v>
+        <v>336</v>
       </c>
       <c r="M27" s="11" t="n">
-        <v>0.7879924953095684</v>
+        <v>0.7905882352941176</v>
       </c>
     </row>
     <row r="28">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Sheryl Jessica Tatontos</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -3000,31 +3000,31 @@
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>498</v>
+        <v>533</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>336</v>
+        <v>420</v>
       </c>
       <c r="K28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="M28" s="11" t="n">
-        <v>0.7831325301204819</v>
+        <v>0.7879924953095684</v>
       </c>
     </row>
     <row r="29">
@@ -3033,45 +3033,45 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Meychindy Riane Takaheghesang</t>
+          <t>Sheryl Jessica Tatontos</t>
         </is>
       </c>
       <c r="C29" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E29" s="9" t="n">
-        <v>420</v>
+        <v>498</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>328</v>
+        <v>390</v>
       </c>
       <c r="M29" s="11" t="n">
-        <v>0.7809523809523811</v>
+        <v>0.7831325301204819</v>
       </c>
     </row>
     <row r="30">
@@ -3080,45 +3080,45 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Veronika Saletia</t>
+          <t>Fiona F. Adrian</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I30" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J30" s="9" t="n">
-        <v>281</v>
+        <v>313</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="9" t="n">
-        <v>298</v>
+        <v>328</v>
       </c>
       <c r="M30" s="11" t="n">
-        <v>0.7720207253886009</v>
+        <v>0.7735849056603774</v>
       </c>
     </row>
     <row r="31">
@@ -3127,45 +3127,45 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Tia Ivanca Christy Pangandaheng</t>
+          <t>Veronika Saletia</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D31" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E31" s="9" t="n">
-        <v>424</v>
+        <v>386</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J31" s="9" t="n">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="K31" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="9" t="n">
-        <v>321</v>
+        <v>298</v>
       </c>
       <c r="M31" s="11" t="n">
-        <v>0.7570754716981132</v>
+        <v>0.7720207253886009</v>
       </c>
     </row>
     <row r="32">
@@ -3174,45 +3174,45 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>Fiona F. Adrian</t>
+          <t>Juldrike Tuwohingide</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>424</v>
+        <v>503</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>313</v>
+        <v>375</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>321</v>
+        <v>382</v>
       </c>
       <c r="M32" s="11" t="n">
-        <v>0.7570754716981132</v>
+        <v>0.7594433399602386</v>
       </c>
     </row>
     <row r="33">
@@ -3221,45 +3221,45 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Nurhayati Mangentiku</t>
+          <t>Sigfried Erik Hontong</t>
         </is>
       </c>
       <c r="C33" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E33" s="9" t="n">
-        <v>410</v>
+        <v>561</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="9" t="n">
-        <v>291</v>
+        <v>398</v>
       </c>
       <c r="K33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="9" t="n">
-        <v>310</v>
+        <v>425</v>
       </c>
       <c r="M33" s="11" t="n">
-        <v>0.7560975609756098</v>
+        <v>0.7575757575757575</v>
       </c>
     </row>
     <row r="34">
@@ -3268,45 +3268,45 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>Juldrike Tuwohingide</t>
+          <t>Tia Ivanca Christy Pangandaheng</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>503</v>
+        <v>424</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>374</v>
+        <v>319</v>
       </c>
       <c r="K34" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="9" t="n">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="M34" s="11" t="n">
-        <v>0.753479125248509</v>
+        <v>0.7570754716981132</v>
       </c>
     </row>
     <row r="35">
@@ -3315,45 +3315,45 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>Christian Megawe</t>
+          <t>Nurhayati Mangentiku</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E35" s="9" t="n">
-        <v>519</v>
+        <v>410</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" s="9" t="n">
-        <v>375</v>
+        <v>291</v>
       </c>
       <c r="K35" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="9" t="n">
-        <v>389</v>
+        <v>310</v>
       </c>
       <c r="M35" s="11" t="n">
-        <v>0.7495183044315994</v>
+        <v>0.7560975609756098</v>
       </c>
     </row>
     <row r="36">
@@ -3362,45 +3362,45 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>Feybe Ayuninsi Patandra</t>
+          <t>Christian Megawe</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>408</v>
+        <v>519</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>291</v>
+        <v>375</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>304</v>
+        <v>389</v>
       </c>
       <c r="M36" s="11" t="n">
-        <v>0.7450980392156863</v>
+        <v>0.7495183044315994</v>
       </c>
     </row>
     <row r="37">
@@ -3409,45 +3409,45 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Anace Diamanis</t>
+          <t>Arianti Adahati</t>
         </is>
       </c>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E37" s="9" t="n">
-        <v>546</v>
+        <v>508</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H37" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J37" s="9" t="n">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="M37" s="11" t="n">
-        <v>0.7435897435897436</v>
+        <v>0.7480314960629921</v>
       </c>
     </row>
     <row r="38">
@@ -3456,45 +3456,45 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Sigfried Erik Hontong</t>
+          <t>Feybe Ayuninsi Patandra</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>560</v>
+        <v>408</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>398</v>
+        <v>302</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="9" t="n">
-        <v>415</v>
+        <v>304</v>
       </c>
       <c r="M38" s="11" t="n">
-        <v>0.7410714285714286</v>
+        <v>0.7450980392156863</v>
       </c>
     </row>
     <row r="39">
@@ -3503,45 +3503,45 @@
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>Arianti Adahati</t>
+          <t>Anace Diamanis</t>
         </is>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E39" s="9" t="n">
-        <v>508</v>
+        <v>547</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J39" s="9" t="n">
-        <v>364</v>
+        <v>406</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>375</v>
+        <v>407</v>
       </c>
       <c r="M39" s="11" t="n">
-        <v>0.7381889763779528</v>
+        <v>0.7440585009140768</v>
       </c>
     </row>
     <row r="40">
@@ -3550,45 +3550,45 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>Meyilandriane Herung</t>
+          <t>Rofia Pandawa</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>350</v>
+        <v>425</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I40" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>255</v>
+        <v>291</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L40" s="9" t="n">
-        <v>258</v>
+        <v>314</v>
       </c>
       <c r="M40" s="11" t="n">
-        <v>0.7371428571428571</v>
+        <v>0.7388235294117647</v>
       </c>
     </row>
     <row r="41">
@@ -3597,45 +3597,45 @@
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>Rofia Pandawa</t>
+          <t>Meyilandriane Herung</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E41" s="9" t="n">
-        <v>425</v>
+        <v>350</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I41" s="9" t="n">
         <v>2</v>
       </c>
       <c r="J41" s="9" t="n">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="K41" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L41" s="9" t="n">
-        <v>313</v>
+        <v>258</v>
       </c>
       <c r="M41" s="11" t="n">
-        <v>0.7364705882352941</v>
+        <v>0.7371428571428571</v>
       </c>
     </row>
     <row r="42">
@@ -3644,45 +3644,45 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>Muvidah Kaehe</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>458</v>
+        <v>392</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I42" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>323</v>
+        <v>253</v>
       </c>
       <c r="K42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>333</v>
+        <v>286</v>
       </c>
       <c r="M42" s="11" t="n">
-        <v>0.7270742358078602</v>
+        <v>0.7295918367346939</v>
       </c>
     </row>
     <row r="43">
@@ -3691,45 +3691,45 @@
       </c>
       <c r="B43" s="9" t="inlineStr">
         <is>
-          <t>Roberto Lahapo</t>
+          <t>Muvidah Kaehe</t>
         </is>
       </c>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E43" s="9" t="n">
-        <v>505</v>
+        <v>458</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="G43" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H43" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="I43" s="9" t="n">
-        <v>7</v>
-      </c>
       <c r="J43" s="9" t="n">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>364</v>
+        <v>333</v>
       </c>
       <c r="M43" s="11" t="n">
-        <v>0.7207920792079208</v>
+        <v>0.7270742358078602</v>
       </c>
     </row>
     <row r="44">
@@ -3738,45 +3738,45 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Roberto Lahapo</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>390</v>
+        <v>505</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J44" s="9" t="n">
-        <v>253</v>
+        <v>349</v>
       </c>
       <c r="K44" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>278</v>
+        <v>364</v>
       </c>
       <c r="M44" s="11" t="n">
-        <v>0.7128205128205128</v>
+        <v>0.7207920792079208</v>
       </c>
     </row>
     <row r="45">
@@ -3785,45 +3785,45 @@
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Virchow Keynes Sahabat</t>
+          <t>Ruslan Ginoga</t>
         </is>
       </c>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Nusa Tabukan</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Alfi</t>
         </is>
       </c>
       <c r="E45" s="9" t="n">
-        <v>458</v>
+        <v>371</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J45" s="9" t="n">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="K45" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>323</v>
+        <v>264</v>
       </c>
       <c r="M45" s="11" t="n">
-        <v>0.7052401746724891</v>
+        <v>0.7115902964959568</v>
       </c>
     </row>
     <row r="46">
@@ -3832,45 +3832,45 @@
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Ritmawati Siliwire</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>349</v>
+        <v>508</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H46" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>228</v>
+        <v>359</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>245</v>
+        <v>360</v>
       </c>
       <c r="M46" s="11" t="n">
-        <v>0.7020057306590259</v>
+        <v>0.7086614173228347</v>
       </c>
     </row>
     <row r="47">
@@ -3879,45 +3879,45 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>Ruslan Ginoga</t>
+          <t>Virchow Keynes Sahabat</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
-          <t>Alfi</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E47" s="9" t="n">
-        <v>370</v>
+        <v>458</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J47" s="9" t="n">
-        <v>252</v>
+        <v>291</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="M47" s="11" t="n">
-        <v>0.7</v>
+        <v>0.7052401746724891</v>
       </c>
     </row>
     <row r="48">
@@ -3926,45 +3926,45 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>Ritmawati Siliwire</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>507</v>
+        <v>349</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="9" t="n">
-        <v>353</v>
+        <v>228</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" s="9" t="n">
-        <v>354</v>
+        <v>246</v>
       </c>
       <c r="M48" s="11" t="n">
-        <v>0.6982248520710059</v>
+        <v>0.7048710601719198</v>
       </c>
     </row>
     <row r="49">
@@ -3973,45 +3973,45 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Alfrets Getah</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E49" s="9" t="n">
-        <v>469</v>
+        <v>380</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" s="9" t="n">
-        <v>312</v>
+        <v>259</v>
       </c>
       <c r="K49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="9" t="n">
-        <v>327</v>
+        <v>267</v>
       </c>
       <c r="M49" s="11" t="n">
-        <v>0.697228144989339</v>
+        <v>0.7026315789473684</v>
       </c>
     </row>
     <row r="50">
@@ -4020,45 +4020,45 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>Novatania Makagansa</t>
+          <t>Linda Yunice Amal</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>527</v>
+        <v>390</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" s="9" t="n">
-        <v>341</v>
+        <v>223</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>366</v>
+        <v>273</v>
       </c>
       <c r="M50" s="11" t="n">
-        <v>0.6944971537001898</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="51">
@@ -4067,36 +4067,36 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>Voni Fience Sarah Dien</t>
+          <t>Novatania Makagansa</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E51" s="9" t="n">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="9" t="n">
-        <v>368</v>
+        <v>341</v>
       </c>
       <c r="K51" s="9" t="n">
         <v>0</v>
@@ -4105,7 +4105,7 @@
         <v>368</v>
       </c>
       <c r="M51" s="11" t="n">
-        <v>0.6943396226415094</v>
+        <v>0.6982922201138519</v>
       </c>
     </row>
     <row r="52">
@@ -4114,45 +4114,45 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>Linda Yunice Amal</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>389</v>
+        <v>469</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" s="9" t="n">
-        <v>223</v>
+        <v>312</v>
       </c>
       <c r="K52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="9" t="n">
-        <v>268</v>
+        <v>327</v>
       </c>
       <c r="M52" s="11" t="n">
-        <v>0.6889460154241646</v>
+        <v>0.697228144989339</v>
       </c>
     </row>
     <row r="53">
@@ -4161,45 +4161,45 @@
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>Alfrets Getah</t>
+          <t>Voni Fience Sarah Dien</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E53" s="9" t="n">
-        <v>380</v>
+        <v>510</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J53" s="9" t="n">
-        <v>253</v>
+        <v>339</v>
       </c>
       <c r="K53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>260</v>
+        <v>348</v>
       </c>
       <c r="M53" s="11" t="n">
-        <v>0.6842105263157895</v>
+        <v>0.6823529411764706</v>
       </c>
     </row>
     <row r="54">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>Misye Yosevin Pulumbara</t>
+          <t>Novianty Key</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
@@ -4222,31 +4222,31 @@
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J54" s="9" t="n">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="9" t="n">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="M54" s="11" t="n">
-        <v>0.6775700934579441</v>
+        <v>0.6791208791208792</v>
       </c>
     </row>
     <row r="55">
@@ -4255,45 +4255,45 @@
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>Meisye Miranti Salendeho</t>
+          <t>Misye Yosevin Pulumbara</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D55" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E55" s="9" t="n">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J55" s="9" t="n">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="M55" s="11" t="n">
-        <v>0.673076923076923</v>
+        <v>0.6790697674418604</v>
       </c>
     </row>
     <row r="56">
@@ -4302,45 +4302,45 @@
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>Nicky Jacson Taidi</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="H56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J56" s="9" t="n">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="K56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="9" t="n">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="M56" s="11" t="n">
-        <v>0.6724890829694323</v>
+        <v>0.6767241379310345</v>
       </c>
     </row>
     <row r="57">
@@ -4349,45 +4349,45 @@
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>Srirahayu Durumias</t>
+          <t>Meisye Miranti Salendeho</t>
         </is>
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E57" s="9" t="n">
-        <v>289</v>
+        <v>416</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L57" s="9" t="n">
-        <v>194</v>
+        <v>280</v>
       </c>
       <c r="M57" s="11" t="n">
-        <v>0.671280276816609</v>
+        <v>0.673076923076923</v>
       </c>
     </row>
     <row r="58">
@@ -4396,45 +4396,45 @@
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>Novianty Key</t>
+          <t>Nicky Jacson Taidi</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="H58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="9" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="M58" s="11" t="n">
-        <v>0.6710816777041942</v>
+        <v>0.6724890829694323</v>
       </c>
     </row>
     <row r="59">
@@ -4443,45 +4443,45 @@
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E59" s="9" t="n">
-        <v>506</v>
+        <v>289</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" s="9" t="n">
-        <v>324</v>
+        <v>191</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>338</v>
+        <v>194</v>
       </c>
       <c r="M59" s="11" t="n">
-        <v>0.6679841897233202</v>
+        <v>0.671280276816609</v>
       </c>
     </row>
     <row r="60">
@@ -4490,45 +4490,45 @@
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>Kesya Syalomita Pangeke</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>452</v>
+        <v>506</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>284</v>
+        <v>324</v>
       </c>
       <c r="K60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="9" t="n">
-        <v>300</v>
+        <v>339</v>
       </c>
       <c r="M60" s="11" t="n">
-        <v>0.6637168141592921</v>
+        <v>0.6699604743083004</v>
       </c>
     </row>
     <row r="61">
@@ -4537,45 +4537,45 @@
       </c>
       <c r="B61" s="9" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Fernando Bielly Sindua</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D61" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E61" s="9" t="n">
-        <v>432</v>
+        <v>482</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" s="9" t="n">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>286</v>
+        <v>322</v>
       </c>
       <c r="M61" s="11" t="n">
-        <v>0.6620370370370371</v>
+        <v>0.6680497925311202</v>
       </c>
     </row>
     <row r="62">
@@ -4584,45 +4584,45 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>464</v>
+        <v>435</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="G62" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H62" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="H62" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="I62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62" s="9" t="n">
-        <v>305</v>
+        <v>278</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="M62" s="11" t="n">
-        <v>0.6573275862068965</v>
+        <v>0.6666666666666665</v>
       </c>
     </row>
     <row r="63">
@@ -4631,45 +4631,45 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>Claudia Angelia Adam</t>
+          <t>Kesya Syalomita Pangeke</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E63" s="9" t="n">
-        <v>429</v>
+        <v>452</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J63" s="9" t="n">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="K63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="9" t="n">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="M63" s="11" t="n">
-        <v>0.655011655011655</v>
+        <v>0.6637168141592921</v>
       </c>
     </row>
     <row r="64">
@@ -4678,45 +4678,45 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>Fadli Samalam</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
-        <v>459</v>
+        <v>432</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" s="9" t="n">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K64" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L64" s="9" t="n">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="M64" s="11" t="n">
-        <v>0.65359477124183</v>
+        <v>0.6620370370370371</v>
       </c>
     </row>
     <row r="65">
@@ -4725,45 +4725,45 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>Fernando Bielly Sindua</t>
+          <t>Claudia Angelia Adam</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D65" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E65" s="9" t="n">
-        <v>481</v>
+        <v>429</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="K65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="M65" s="11" t="n">
-        <v>0.6507276507276507</v>
+        <v>0.6620046620046619</v>
       </c>
     </row>
     <row r="66">
@@ -4772,45 +4772,45 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Fadli Samalam</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I66" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="M66" s="11" t="n">
-        <v>0.6505747126436782</v>
+        <v>0.65359477124183</v>
       </c>
     </row>
     <row r="67">
@@ -4819,45 +4819,45 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>Eugenia Ariani Tamakaenge</t>
+          <t>Maknany Sasiang</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E67" s="9" t="n">
-        <v>502</v>
+        <v>429</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L67" s="9" t="n">
-        <v>326</v>
+        <v>280</v>
       </c>
       <c r="M67" s="11" t="n">
-        <v>0.649402390438247</v>
+        <v>0.6526806526806527</v>
       </c>
     </row>
     <row r="68">
@@ -4866,45 +4866,45 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Eugenia Ariani Tamakaenge</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
-        <v>471</v>
+        <v>502</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="I68" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K68" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="M68" s="11" t="n">
-        <v>0.6454352441613588</v>
+        <v>0.649402390438247</v>
       </c>
     </row>
     <row r="69">
@@ -4930,28 +4930,28 @@
         <v>416</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="9" t="n">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="K69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L69" s="9" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M69" s="11" t="n">
-        <v>0.6442307692307694</v>
+        <v>0.6466346153846154</v>
       </c>
     </row>
     <row r="70">
@@ -4960,27 +4960,27 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>Amna Maneking</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="9" t="n">
         <v>0</v>
@@ -4989,16 +4989,16 @@
         <v>1</v>
       </c>
       <c r="J70" s="9" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="9" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M70" s="11" t="n">
-        <v>0.6417910447761195</v>
+        <v>0.6454352441613588</v>
       </c>
     </row>
     <row r="71">
@@ -5007,45 +5007,45 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>Maknany Sasiang</t>
+          <t>Amna Maneking</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E71" s="9" t="n">
-        <v>427</v>
+        <v>470</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="G71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H71" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="I71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" s="9" t="n">
-        <v>273</v>
+        <v>301</v>
       </c>
       <c r="K71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>273</v>
+        <v>303</v>
       </c>
       <c r="M71" s="11" t="n">
-        <v>0.639344262295082</v>
+        <v>0.6446808510638298</v>
       </c>
     </row>
     <row r="72">
@@ -5054,45 +5054,45 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>Iramaya Sasiang</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Kepulauan Marore</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>625</v>
+        <v>520</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H72" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J72" s="9" t="n">
-        <v>395</v>
+        <v>329</v>
       </c>
       <c r="K72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L72" s="9" t="n">
-        <v>399</v>
+        <v>334</v>
       </c>
       <c r="M72" s="11" t="n">
-        <v>0.6384</v>
+        <v>0.6423076923076924</v>
       </c>
     </row>
     <row r="73">
@@ -5101,45 +5101,45 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>Titien Kurniawati Lamorahan</t>
+          <t>Dayan Abdullah</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E73" s="9" t="n">
-        <v>352</v>
+        <v>484</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J73" s="9" t="n">
-        <v>211</v>
+        <v>303</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="9" t="n">
-        <v>224</v>
+        <v>309</v>
       </c>
       <c r="M73" s="11" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6384297520661157</v>
       </c>
     </row>
     <row r="74">
@@ -5148,45 +5148,45 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>Sry Ayu Permatasari Tamamile Manake</t>
+          <t>Iramaya Sasiang</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan</t>
+          <t>Kepulauan Marore</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>Lusine</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
-        <v>386</v>
+        <v>625</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>141</v>
+        <v>219</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J74" s="9" t="n">
-        <v>233</v>
+        <v>395</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>245</v>
+        <v>399</v>
       </c>
       <c r="M74" s="11" t="n">
-        <v>0.6347150259067358</v>
+        <v>0.6384</v>
       </c>
     </row>
     <row r="75">
@@ -5195,45 +5195,45 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>Eka Saputri Rusmain</t>
+          <t>Billy Amstrong Tempolenehe</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E75" s="9" t="n">
-        <v>516</v>
+        <v>546</v>
       </c>
       <c r="F75" s="9" t="n">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="9" t="n">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" s="9" t="n">
-        <v>327</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0.6337209302325582</v>
+        <v>348</v>
+      </c>
+      <c r="M75" s="11" t="n">
+        <v>0.6373626373626373</v>
       </c>
     </row>
     <row r="76">
@@ -5242,45 +5242,45 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>Yustin Durian</t>
+          <t>Titien Kurniawati Lamorahan</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tabukan Selatan Tengah</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
-        <v>445</v>
+        <v>352</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J76" s="9" t="n">
-        <v>272</v>
+        <v>211</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="9" t="n">
-        <v>282</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>0.6337078651685393</v>
+        <v>224</v>
+      </c>
+      <c r="M76" s="11" t="n">
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="77">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>Jeisy Dolongseda</t>
+          <t>Yustin Durian</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -5303,31 +5303,31 @@
         </is>
       </c>
       <c r="E77" s="9" t="n">
-        <v>405</v>
+        <v>445</v>
       </c>
       <c r="F77" s="9" t="n">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>237</v>
+        <v>272</v>
       </c>
       <c r="K77" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L77" s="9" t="n">
-        <v>256</v>
-      </c>
-      <c r="M77" s="12" t="n">
-        <v>0.6320987654320988</v>
+        <v>283</v>
+      </c>
+      <c r="M77" s="11" t="n">
+        <v>0.6359550561797753</v>
       </c>
     </row>
     <row r="78">
@@ -5336,45 +5336,45 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>Andini Safitri Makaminan</t>
+          <t>Eka Saputri Rusmain</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
-        <v>429</v>
+        <v>518</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>156</v>
+        <v>189</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" s="9" t="n">
-        <v>271</v>
+        <v>326</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>271</v>
-      </c>
-      <c r="M78" s="12" t="n">
-        <v>0.6317016317016317</v>
+        <v>329</v>
+      </c>
+      <c r="M78" s="11" t="n">
+        <v>0.6351351351351351</v>
       </c>
     </row>
     <row r="79">
@@ -5383,45 +5383,45 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Sry Ayu Permatasari Tamamile Manake</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tabukan Selatan</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Lusine</t>
         </is>
       </c>
       <c r="E79" s="9" t="n">
-        <v>588</v>
+        <v>386</v>
       </c>
       <c r="F79" s="9" t="n">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="I79" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>326</v>
+        <v>233</v>
       </c>
       <c r="K79" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L79" s="9" t="n">
-        <v>371</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>0.6309523809523809</v>
+        <v>245</v>
+      </c>
+      <c r="M79" s="11" t="n">
+        <v>0.6347150259067358</v>
       </c>
     </row>
     <row r="80">
@@ -5430,45 +5430,45 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>Marisye Silpia Limpong</t>
+          <t>Andini Safitri Makaminan</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E80" s="9" t="n">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I80" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J80" s="9" t="n">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="K80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0.6291866028708134</v>
+        <v>0.634032634032634</v>
       </c>
     </row>
     <row r="81">
@@ -5477,45 +5477,45 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>Billy Amstrong Tempolenehe</t>
+          <t>Jeisy Dolongseda</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E81" s="9" t="n">
-        <v>546</v>
+        <v>405</v>
       </c>
       <c r="F81" s="9" t="n">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I81" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>333</v>
+        <v>241</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="9" t="n">
-        <v>343</v>
+        <v>256</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0.6282051282051282</v>
+        <v>0.6320987654320988</v>
       </c>
     </row>
     <row r="82">
@@ -5524,45 +5524,45 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>Dayan Abdullah</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E82" s="9" t="n">
-        <v>484</v>
+        <v>588</v>
       </c>
       <c r="F82" s="9" t="n">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H82" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="I82" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="I82" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="J82" s="9" t="n">
-        <v>301</v>
+        <v>335</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>304</v>
+        <v>371</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0.628099173553719</v>
+        <v>0.6309523809523809</v>
       </c>
     </row>
     <row r="83">
@@ -5571,45 +5571,45 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Marisye Silpia Limpong</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D83" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E83" s="9" t="n">
-        <v>519</v>
+        <v>418</v>
       </c>
       <c r="F83" s="9" t="n">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I83" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J83" s="9" t="n">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c r="K83" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="9" t="n">
-        <v>325</v>
+        <v>263</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>0.626204238921002</v>
+        <v>0.6291866028708134</v>
       </c>
     </row>
     <row r="84">
@@ -5618,45 +5618,45 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>Nofri Markus Taidi</t>
+          <t>Fitriani Mandalurang</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E84" s="9" t="n">
-        <v>325</v>
+        <v>514</v>
       </c>
       <c r="F84" s="9" t="n">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="9" t="n">
-        <v>200</v>
+        <v>316</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="9" t="n">
-        <v>203</v>
+        <v>323</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.6246153846153846</v>
+        <v>0.6284046692607004</v>
       </c>
     </row>
     <row r="85">
@@ -5665,45 +5665,45 @@
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>Fitriani Mandalurang</t>
+          <t>Vera Angelita Tangkabiringan</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E85" s="9" t="n">
-        <v>514</v>
+        <v>562</v>
       </c>
       <c r="F85" s="9" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="9" t="n">
-        <v>317</v>
+        <v>352</v>
       </c>
       <c r="K85" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>319</v>
+        <v>352</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>0.6206225680933852</v>
+        <v>0.6263345195729537</v>
       </c>
     </row>
     <row r="86">
@@ -5712,45 +5712,45 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Nofri Markus Taidi</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E86" s="9" t="n">
-        <v>505</v>
+        <v>325</v>
       </c>
       <c r="F86" s="9" t="n">
-        <v>184</v>
+        <v>74</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I86" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>305</v>
+        <v>202</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>313</v>
+        <v>203</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0.6198019801980198</v>
+        <v>0.6246153846153846</v>
       </c>
     </row>
     <row r="87">
@@ -5759,45 +5759,45 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>Vera Angelita Tangkabiringan</t>
+          <t>Nolvi Sanggel</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E87" s="9" t="n">
-        <v>561</v>
+        <v>431</v>
       </c>
       <c r="F87" s="9" t="n">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H87" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>264</v>
+      </c>
+      <c r="K87" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="9" t="n">
-        <v>344</v>
-      </c>
-      <c r="K87" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L87" s="9" t="n">
-        <v>346</v>
+        <v>269</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0.6167557932263814</v>
+        <v>0.6241299303944315</v>
       </c>
     </row>
     <row r="88">
@@ -5806,45 +5806,45 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>Nalla Aulya Ponto</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E88" s="9" t="n">
-        <v>453</v>
+        <v>505</v>
       </c>
       <c r="F88" s="9" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="I88" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>251</v>
+        <v>311</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" s="9" t="n">
-        <v>279</v>
+        <v>315</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0.6158940397350994</v>
+        <v>0.6237623762376238</v>
       </c>
     </row>
     <row r="89">
@@ -5870,13 +5870,13 @@
         <v>465</v>
       </c>
       <c r="F89" s="9" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I89" s="9" t="n">
         <v>0</v>
@@ -5888,10 +5888,10 @@
         <v>0</v>
       </c>
       <c r="L89" s="9" t="n">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>0.610752688172043</v>
+        <v>0.6193548387096774</v>
       </c>
     </row>
     <row r="90">
@@ -5900,45 +5900,45 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>Nolvi Sanggel</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E90" s="9" t="n">
-        <v>430</v>
+        <v>475</v>
       </c>
       <c r="F90" s="9" t="n">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I90" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="9" t="n">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>0.6093023255813953</v>
+        <v>0.6189473684210526</v>
       </c>
     </row>
     <row r="91">
@@ -5947,45 +5947,45 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>Elan Chrisye Ansar</t>
+          <t>Nalla Aulya Ponto</t>
         </is>
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D91" s="9" t="inlineStr">
         <is>
-          <t>Erwin, Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E91" s="9" t="n">
-        <v>366</v>
+        <v>453</v>
       </c>
       <c r="F91" s="9" t="n">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="9" t="n">
-        <v>207</v>
+        <v>252</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="9" t="n">
-        <v>222</v>
+        <v>280</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>0.6065573770491803</v>
+        <v>0.6181015452538632</v>
       </c>
     </row>
     <row r="92">
@@ -5994,45 +5994,45 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>Nefi Anet Wawanda</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E92" s="9" t="n">
-        <v>402</v>
+        <v>472</v>
       </c>
       <c r="F92" s="9" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H92" s="9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I92" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" s="9" t="n">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="K92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L92" s="9" t="n">
-        <v>243</v>
+        <v>290</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>0.6044776119402985</v>
+        <v>0.614406779661017</v>
       </c>
     </row>
     <row r="93">
@@ -6041,45 +6041,45 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Deisye Reine Budiman</t>
         </is>
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E93" s="9" t="n">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="F93" s="9" t="n">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H93" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J93" s="9" t="n">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="K93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L93" s="9" t="n">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>0.6034115138592751</v>
+        <v>0.6088888888888889</v>
       </c>
     </row>
     <row r="94">
@@ -6088,45 +6088,45 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>Deisye Reine Budiman</t>
+          <t>Elan Chrisye Ansar</t>
         </is>
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Selatan Tengah, Tabukan Selatan Tenggara</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Erwin, Lalu</t>
         </is>
       </c>
       <c r="E94" s="9" t="n">
-        <v>450</v>
+        <v>366</v>
       </c>
       <c r="F94" s="9" t="n">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H94" s="9" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J94" s="9" t="n">
-        <v>270</v>
+        <v>207</v>
       </c>
       <c r="K94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>271</v>
+        <v>222</v>
       </c>
       <c r="M94" s="12" t="n">
-        <v>0.6022222222222222</v>
+        <v>0.6065573770491803</v>
       </c>
     </row>
     <row r="95">
@@ -6135,45 +6135,45 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>Juanric Eben Misarios Rakinaung</t>
+          <t>Nefi Anet Wawanda</t>
         </is>
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E95" s="9" t="n">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="9" t="n">
-        <v>217</v>
+        <v>243</v>
       </c>
       <c r="M95" s="12" t="n">
-        <v>0.6011080332409973</v>
+        <v>0.6044776119402985</v>
       </c>
     </row>
     <row r="96">
@@ -6182,45 +6182,45 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E96" s="9" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F96" s="9" t="n">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I96" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J96" s="9" t="n">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M96" s="12" t="n">
-        <v>0.6008492569002123</v>
+        <v>0.6016949152542372</v>
       </c>
     </row>
     <row r="97">
@@ -6229,45 +6229,45 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Juanric Eben Misarios Rakinaung</t>
         </is>
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D97" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E97" s="9" t="n">
-        <v>470</v>
+        <v>361</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97" s="9" t="n">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="K97" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>282</v>
+        <v>217</v>
       </c>
       <c r="M97" s="12" t="n">
-        <v>0.6</v>
+        <v>0.6011080332409973</v>
       </c>
     </row>
     <row r="98">
@@ -6276,45 +6276,45 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E98" s="9" t="n">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H98" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>269</v>
+      </c>
+      <c r="K98" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="J98" s="9" t="n">
-        <v>278</v>
-      </c>
-      <c r="K98" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L98" s="9" t="n">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M98" s="12" t="n">
-        <v>0.5932203389830508</v>
+        <v>0.6008492569002123</v>
       </c>
     </row>
     <row r="99">
@@ -6323,45 +6323,45 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>Asyer Claudio Maralending</t>
+          <t>Satrio Prasetya Braid Dalantang</t>
         </is>
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E99" s="9" t="n">
-        <v>461</v>
+        <v>384</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" s="9" t="n">
-        <v>266</v>
+        <v>219</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>269</v>
+        <v>230</v>
       </c>
       <c r="M99" s="12" t="n">
-        <v>0.5835140997830802</v>
+        <v>0.5989583333333334</v>
       </c>
     </row>
     <row r="100">
@@ -6370,45 +6370,45 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Yesika Angelin Guwaunaung</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E100" s="9" t="n">
-        <v>525</v>
+        <v>448</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>217</v>
+        <v>180</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I100" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J100" s="9" t="n">
-        <v>301</v>
+        <v>259</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="M100" s="12" t="n">
-        <v>0.5828571428571429</v>
+        <v>0.5959821428571429</v>
       </c>
     </row>
     <row r="101">
@@ -6417,45 +6417,45 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>Yesika Angelin Guwaunaung</t>
+          <t>Junisye Ignes Boham</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D101" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E101" s="9" t="n">
-        <v>446</v>
+        <v>500</v>
       </c>
       <c r="F101" s="9" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J101" s="9" t="n">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="9" t="n">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="M101" s="12" t="n">
-        <v>0.5807174887892377</v>
+        <v>0.594</v>
       </c>
     </row>
     <row r="102">
@@ -6464,45 +6464,45 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>Allan Christovel Sapeti</t>
+          <t>Asyer Claudio Maralending</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E102" s="9" t="n">
-        <v>398</v>
+        <v>461</v>
       </c>
       <c r="F102" s="9" t="n">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J102" s="9" t="n">
-        <v>226</v>
+        <v>273</v>
       </c>
       <c r="K102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L102" s="9" t="n">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="M102" s="12" t="n">
-        <v>0.5804020100502513</v>
+        <v>0.5921908893709328</v>
       </c>
     </row>
     <row r="103">
@@ -6511,45 +6511,45 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>Satrio Prasetya Braid Dalantang</t>
+          <t>Allan Christovel Sapeti</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E103" s="9" t="n">
-        <v>380</v>
+        <v>399</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I103" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" s="9" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L103" s="9" t="n">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="M103" s="12" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5864661654135338</v>
       </c>
     </row>
     <row r="104">
@@ -6558,45 +6558,45 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>Junisye Ignes Boham</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E104" s="9" t="n">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="F104" s="9" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H104" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>301</v>
+      </c>
+      <c r="K104" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J104" s="9" t="n">
-        <v>281</v>
-      </c>
-      <c r="K104" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L104" s="9" t="n">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="M104" s="12" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5828571428571429</v>
       </c>
     </row>
     <row r="105">
@@ -6622,13 +6622,13 @@
         <v>455</v>
       </c>
       <c r="F105" s="9" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G105" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H105" s="9" t="n">
         <v>11</v>
-      </c>
-      <c r="H105" s="9" t="n">
-        <v>5</v>
       </c>
       <c r="I105" s="9" t="n">
         <v>14</v>
@@ -6640,10 +6640,10 @@
         <v>3</v>
       </c>
       <c r="L105" s="9" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="M105" s="12" t="n">
-        <v>0.567032967032967</v>
+        <v>0.5802197802197803</v>
       </c>
     </row>
     <row r="106">
@@ -6652,45 +6652,45 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>Regina Kesya Dumumpe</t>
+          <t>Nur Alifah Kasilialang</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Kendahe</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="E106" s="9" t="n">
-        <v>428</v>
+        <v>536</v>
       </c>
       <c r="F106" s="9" t="n">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I106" s="9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J106" s="9" t="n">
-        <v>219</v>
+        <v>284</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>239</v>
+        <v>305</v>
       </c>
       <c r="M106" s="12" t="n">
-        <v>0.5584112149532711</v>
+        <v>0.5690298507462687</v>
       </c>
     </row>
     <row r="107">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>Priskila Bawotong</t>
+          <t>Regina Kesya Dumumpe</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
@@ -6713,31 +6713,31 @@
         </is>
       </c>
       <c r="E107" s="9" t="n">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="F107" s="9" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I107" s="9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J107" s="9" t="n">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L107" s="9" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="M107" s="12" t="n">
-        <v>0.5552941176470588</v>
+        <v>0.5661252900232019</v>
       </c>
     </row>
     <row r="108">
@@ -6746,45 +6746,45 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>Nur Alifah Kasilialang</t>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>Kendahe</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E108" s="9" t="n">
-        <v>517</v>
+        <v>399</v>
       </c>
       <c r="F108" s="9" t="n">
-        <v>231</v>
+        <v>176</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J108" s="9" t="n">
-        <v>284</v>
+        <v>221</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="M108" s="12" t="n">
-        <v>0.5531914893617021</v>
+        <v>0.5588972431077694</v>
       </c>
     </row>
     <row r="109">
@@ -6793,7 +6793,7 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Leonardo Rio Patras</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
@@ -6807,31 +6807,31 @@
         </is>
       </c>
       <c r="E109" s="9" t="n">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K109" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="M109" s="12" t="n">
-        <v>0.5513784461152882</v>
+        <v>0.5588235294117647</v>
       </c>
     </row>
     <row r="110">
@@ -6860,13 +6860,13 @@
         <v>170</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" s="9" t="n">
         <v>221</v>
@@ -6875,10 +6875,10 @@
         <v>1</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="M110" s="12" t="n">
-        <v>0.5509708737864077</v>
+        <v>0.558252427184466</v>
       </c>
     </row>
     <row r="111">
@@ -6887,45 +6887,45 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>Evita Beatrix Nanlohy</t>
+          <t>Priskila Bawotong</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D111" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E111" s="9" t="n">
-        <v>479</v>
+        <v>425</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="G111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="H111" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="I111" s="9" t="n">
-        <v>15</v>
-      </c>
       <c r="J111" s="9" t="n">
-        <v>189</v>
+        <v>232</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L111" s="9" t="n">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="M111" s="12" t="n">
-        <v>0.5407098121085595</v>
+        <v>0.5576470588235294</v>
       </c>
     </row>
     <row r="112">
@@ -6934,45 +6934,45 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>Bayu Sutiyono Dujoh</t>
+          <t>Evita Beatrix Nanlohy</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E112" s="9" t="n">
-        <v>402</v>
+        <v>479</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L112" s="9" t="n">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="M112" s="12" t="n">
-        <v>0.5348258706467661</v>
+        <v>0.5511482254697286</v>
       </c>
     </row>
     <row r="113">
@@ -6998,13 +6998,13 @@
         <v>503</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I113" s="9" t="n">
         <v>0</v>
@@ -7016,10 +7016,10 @@
         <v>0</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>0.532803180914513</v>
+        <v>0.5407554671968191</v>
       </c>
     </row>
     <row r="114">
@@ -7028,45 +7028,45 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>Leonardo Rio Patras</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E114" s="9" t="n">
-        <v>408</v>
+        <v>481</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J114" s="9" t="n">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="K114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="M114" s="12" t="n">
-        <v>0.5318627450980392</v>
+        <v>0.5363825363825364</v>
       </c>
     </row>
     <row r="115">
@@ -7089,16 +7089,16 @@
         </is>
       </c>
       <c r="E115" s="9" t="n">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I115" s="9" t="n">
         <v>0</v>
@@ -7110,10 +7110,10 @@
         <v>0</v>
       </c>
       <c r="L115" s="9" t="n">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M115" s="12" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.5355450236966824</v>
       </c>
     </row>
     <row r="116">
@@ -7122,45 +7122,45 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Bayu Sutiyono Dujoh</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E116" s="9" t="n">
-        <v>477</v>
+        <v>402</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J116" s="9" t="n">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="K116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L116" s="9" t="n">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="M116" s="12" t="n">
-        <v>0.5262054507337526</v>
+        <v>0.5348258706467661</v>
       </c>
     </row>
     <row r="117">
@@ -7186,13 +7186,13 @@
         <v>455</v>
       </c>
       <c r="F117" s="9" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I117" s="9" t="n">
         <v>0</v>
@@ -7204,10 +7204,10 @@
         <v>0</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M117" s="12" t="n">
-        <v>0.5230769230769231</v>
+        <v>0.5274725274725275</v>
       </c>
     </row>
     <row r="118">
@@ -7216,45 +7216,45 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>Septian Gilbert Wuisan</t>
+          <t>Vania Gavrila Lakada</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E118" s="9" t="n">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="F118" s="9" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I118" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J118" s="9" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="M118" s="12" t="n">
-        <v>0.5228310502283106</v>
+        <v>0.527114967462039</v>
       </c>
     </row>
     <row r="119">
@@ -7263,45 +7263,45 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>Ardi Brian Silas Saul</t>
+          <t>Septian Gilbert Wuisan</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D119" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E119" s="9" t="n">
-        <v>408</v>
+        <v>438</v>
       </c>
       <c r="F119" s="9" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="G119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>228</v>
+      </c>
+      <c r="K119" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="H119" s="9" t="n">
-        <v>17</v>
-      </c>
-      <c r="I119" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="J119" s="9" t="n">
-        <v>184</v>
-      </c>
-      <c r="K119" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="L119" s="9" t="n">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="M119" s="12" t="n">
-        <v>0.5220588235294118</v>
+        <v>0.5228310502283106</v>
       </c>
     </row>
     <row r="120">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>Vania Gavrila Lakada</t>
+          <t>Ardi Brian Silas Saul</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
@@ -7324,31 +7324,31 @@
         </is>
       </c>
       <c r="E120" s="9" t="n">
-        <v>458</v>
+        <v>408</v>
       </c>
       <c r="F120" s="9" t="n">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I120" s="9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J120" s="9" t="n">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="M120" s="12" t="n">
-        <v>0.5218340611353712</v>
+        <v>0.5220588235294118</v>
       </c>
     </row>
     <row r="121">
@@ -7404,33 +7404,33 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>Julianty Thesa Takaredase</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E122" s="9" t="n">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F122" s="9" t="n">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="G122" s="9" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H122" s="9" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I122" s="9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J122" s="9" t="n">
         <v>203</v>
@@ -7439,10 +7439,10 @@
         <v>0</v>
       </c>
       <c r="L122" s="9" t="n">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="M122" s="12" t="n">
-        <v>0.5136363636363637</v>
+        <v>0.5179372197309418</v>
       </c>
     </row>
     <row r="123">
@@ -7451,45 +7451,45 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Jeklen Malage Dalita</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D123" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E123" s="9" t="n">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="F123" s="9" t="n">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J123" s="9" t="n">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="K123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="9" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="M123" s="12" t="n">
-        <v>0.5119047619047619</v>
+        <v>0.5179372197309418</v>
       </c>
     </row>
     <row r="124">
@@ -7498,45 +7498,45 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>Marwesley Iverson Matheos</t>
+          <t>Julianty Thesa Takaredase</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E124" s="9" t="n">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="F124" s="9" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="G124" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H124" s="9" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I124" s="9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J124" s="9" t="n">
-        <v>169</v>
+        <v>213</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="M124" s="12" t="n">
-        <v>0.5096153846153846</v>
+        <v>0.5159090909090909</v>
       </c>
     </row>
     <row r="125">
@@ -7545,45 +7545,45 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>Aditya Christovel Hangau</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D125" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E125" s="9" t="n">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F125" s="9" t="n">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J125" s="9" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M125" s="12" t="n">
-        <v>0.5093896713615024</v>
+        <v>0.5119047619047619</v>
       </c>
     </row>
     <row r="126">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Adriano Arga Takahopekang</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
@@ -7606,13 +7606,13 @@
         </is>
       </c>
       <c r="E126" s="9" t="n">
-        <v>442</v>
+        <v>397</v>
       </c>
       <c r="F126" s="9" t="n">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H126" s="9" t="n">
         <v>0</v>
@@ -7621,16 +7621,16 @@
         <v>0</v>
       </c>
       <c r="J126" s="9" t="n">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="K126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="M126" s="12" t="n">
-        <v>0.5090497737556561</v>
+        <v>0.5113350125944585</v>
       </c>
     </row>
     <row r="127">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>Jeklen Malage Dalita</t>
+          <t>Marwesley Iverson Matheos</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
@@ -7653,31 +7653,31 @@
         </is>
       </c>
       <c r="E127" s="9" t="n">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="F127" s="9" t="n">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="G127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I127" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J127" s="9" t="n">
-        <v>222</v>
+        <v>176</v>
       </c>
       <c r="K127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L127" s="9" t="n">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="M127" s="12" t="n">
-        <v>0.5056179775280899</v>
+        <v>0.5096153846153846</v>
       </c>
     </row>
     <row r="128">
@@ -7686,45 +7686,45 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Aditya Christovel Hangau</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E128" s="9" t="n">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="F128" s="9" t="n">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I128" s="9" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J128" s="9" t="n">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="K128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="M128" s="12" t="n">
-        <v>0.5044843049327354</v>
+        <v>0.5093896713615024</v>
       </c>
     </row>
     <row r="129">
@@ -7733,45 +7733,45 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>Amels Wisye Margareth Sasauw</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E129" s="9" t="n">
-        <v>409</v>
+        <v>442</v>
       </c>
       <c r="F129" s="9" t="n">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I129" s="9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J129" s="9" t="n">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="K129" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>206</v>
+        <v>225</v>
       </c>
       <c r="M129" s="12" t="n">
-        <v>0.5036674816625917</v>
+        <v>0.5090497737556561</v>
       </c>
     </row>
     <row r="130">
@@ -7780,45 +7780,45 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>Arfando Pieter Tampilang</t>
+          <t>Ratna Sari Tumuwe</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Tengah</t>
+          <t>Tahuna Barat</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="E130" s="9" t="n">
-        <v>399</v>
+        <v>515</v>
       </c>
       <c r="F130" s="9" t="n">
-        <v>191</v>
+        <v>250</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="I130" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J130" s="9" t="n">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>199</v>
+        <v>262</v>
       </c>
       <c r="M130" s="12" t="n">
-        <v>0.4987468671679198</v>
+        <v>0.5087378640776699</v>
       </c>
     </row>
     <row r="131">
@@ -7827,45 +7827,45 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>Ratna Sari Tumuwe</t>
+          <t>Amels Wisye Margareth Sasauw</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Barat</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D131" s="9" t="inlineStr">
         <is>
-          <t>Begin</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E131" s="9" t="n">
-        <v>515</v>
+        <v>409</v>
       </c>
       <c r="F131" s="9" t="n">
-        <v>256</v>
+        <v>200</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H131" s="9" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="I131" s="9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J131" s="9" t="n">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>254</v>
+        <v>207</v>
       </c>
       <c r="M131" s="12" t="n">
-        <v>0.4932038834951457</v>
+        <v>0.5061124694376528</v>
       </c>
     </row>
     <row r="132">
@@ -7874,45 +7874,45 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>Adriano Arga Takahopekang</t>
+          <t>Nevivania Liopenne Kakauhe</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E132" s="9" t="n">
-        <v>396</v>
+        <v>425</v>
       </c>
       <c r="F132" s="9" t="n">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" s="9" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="J132" s="9" t="n">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="K132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="M132" s="12" t="n">
-        <v>0.4924242424242424</v>
+        <v>0.5035294117647059</v>
       </c>
     </row>
     <row r="133">
@@ -7921,45 +7921,45 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>Nevivania Liopenne Kakauhe</t>
+          <t>Arfando Pieter Tampilang</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tabukan Tengah</t>
         </is>
       </c>
       <c r="D133" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="E133" s="9" t="n">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="F133" s="9" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I133" s="9" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J133" s="9" t="n">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="K133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L133" s="9" t="n">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="M133" s="12" t="n">
-        <v>0.4894117647058824</v>
+        <v>0.5012531328320802</v>
       </c>
     </row>
     <row r="134">
@@ -7968,45 +7968,45 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>Dince Lahaube</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>Tahuna Timur</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E134" s="9" t="n">
-        <v>459</v>
+        <v>339</v>
       </c>
       <c r="F134" s="9" t="n">
-        <v>222</v>
+        <v>7</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>18</v>
+        <v>168</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I134" s="9" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J134" s="9" t="n">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L134" s="9" t="n">
-        <v>219</v>
+        <v>164</v>
       </c>
       <c r="M134" s="12" t="n">
-        <v>0.477124183006536</v>
+        <v>0.4837758112094395</v>
       </c>
     </row>
     <row r="135">
@@ -8015,45 +8015,45 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>Yosias Budiman Monok</t>
+          <t>Jessica Juanita Lombontari</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>Manganitu</t>
+          <t>Tahuna Timur</t>
         </is>
       </c>
       <c r="D135" s="9" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="E135" s="9" t="n">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="F135" s="9" t="n">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I135" s="9" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J135" s="9" t="n">
-        <v>170</v>
+        <v>203</v>
       </c>
       <c r="K135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L135" s="9" t="n">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="M135" s="12" t="n">
-        <v>0.4716981132075472</v>
+        <v>0.477124183006536</v>
       </c>
     </row>
     <row r="136">
@@ -8062,45 +8062,45 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>Dince Lahaube</t>
+          <t>Yosias Budiman Monok</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Manganitu</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="E136" s="9" t="n">
-        <v>339</v>
+        <v>424</v>
       </c>
       <c r="F136" s="9" t="n">
-        <v>8</v>
+        <v>223</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>179</v>
+        <v>1</v>
       </c>
       <c r="H136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136" s="9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="J136" s="9" t="n">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L136" s="9" t="n">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="M136" s="12" t="n">
-        <v>0.4483775811209439</v>
+        <v>0.4716981132075472</v>
       </c>
     </row>
   </sheetData>
@@ -8143,7 +8143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hari/Tanggal : 22 Juli 2026</t>
+          <t>Hari/Tanggal : 23 Juli 2026</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pukul        : 20.54 WITA</t>
+          <t>Pukul        : 08.16 WITA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -8265,28 +8265,28 @@
         <v>2938</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>2496</v>
+        <v>2560</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>7</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>2504</v>
+        <v>2568</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.852280462899932</v>
+        <v>0.874063989108237</v>
       </c>
     </row>
     <row r="8">
@@ -8309,31 +8309,31 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>2835</v>
+        <v>2841</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>622</v>
+        <v>608</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>14</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>2170</v>
+        <v>2175</v>
       </c>
       <c r="K8" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2186</v>
+        <v>2191</v>
       </c>
       <c r="M8" s="11" t="n">
-        <v>0.7710758377425044</v>
+        <v>0.7712073213657163</v>
       </c>
     </row>
     <row r="9">
@@ -8342,45 +8342,45 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Manganitu Selatan</t>
+          <t>Nusa Tabukan, Tabukan Utara</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Alfi, Hendri</t>
         </is>
       </c>
       <c r="E9" s="9" t="n">
-        <v>2039</v>
+        <v>2534</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>435</v>
+        <v>579</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1532</v>
+        <v>1939</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>1541</v>
+        <v>1943</v>
       </c>
       <c r="M9" s="11" t="n">
-        <v>0.7557626287395781</v>
+        <v>0.7667719021310182</v>
       </c>
     </row>
     <row r="10">
@@ -8389,45 +8389,45 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Charly Angel Tatontos</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Tamako</t>
+          <t>Manganitu Selatan</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>2936</v>
+        <v>2041</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>557</v>
+        <v>433</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>2112</v>
+        <v>1532</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>2169</v>
+        <v>1541</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>0.7387602179836512</v>
+        <v>0.7550220480156785</v>
       </c>
     </row>
     <row r="11">
@@ -8436,45 +8436,45 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Charly Angel Tatontos</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Nusa Tabukan, Tabukan Utara</t>
+          <t>Tamako</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Alfi, Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="E11" s="9" t="n">
-        <v>2528</v>
+        <v>2936</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>599</v>
+        <v>557</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1863</v>
+        <v>2112</v>
       </c>
       <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>1864</v>
+        <v>2168</v>
       </c>
       <c r="M11" s="11" t="n">
-        <v>0.7373417721518988</v>
+        <v>0.7384196185286104</v>
       </c>
     </row>
     <row r="12">
@@ -8497,31 +8497,31 @@
         </is>
       </c>
       <c r="E12" s="9" t="n">
-        <v>2869</v>
+        <v>2872</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>3</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>2089</v>
+        <v>2104</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>2094</v>
+        <v>2114</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>0.7298710352039037</v>
+        <v>0.7360724233983287</v>
       </c>
     </row>
     <row r="13">
@@ -8544,31 +8544,31 @@
         </is>
       </c>
       <c r="E13" s="9" t="n">
-        <v>2923</v>
+        <v>2924</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1937</v>
+        <v>1950</v>
       </c>
       <c r="K13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1945</v>
+        <v>1957</v>
       </c>
       <c r="M13" s="11" t="n">
-        <v>0.6654122476907287</v>
+        <v>0.6692886456908345</v>
       </c>
     </row>
     <row r="14">
@@ -8577,45 +8577,45 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>Tabukan Utara</t>
+          <t>Manganitu, Tamako</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike, Mega</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
-        <v>2816</v>
+        <v>2439</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>849</v>
+        <v>809</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>1833</v>
+        <v>1585</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>1846</v>
+        <v>1599</v>
       </c>
       <c r="M14" s="11" t="n">
-        <v>0.6555397727272727</v>
+        <v>0.6555965559655597</v>
       </c>
     </row>
     <row r="15">
@@ -8624,45 +8624,45 @@
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Manganitu, Tamako</t>
+          <t>Tabukan Utara</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Erike, Mega</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="E15" s="9" t="n">
-        <v>2433</v>
+        <v>2820</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>819</v>
+        <v>844</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="H15" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="I15" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>10</v>
-      </c>
       <c r="J15" s="9" t="n">
-        <v>1578</v>
+        <v>1832</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1588</v>
+        <v>1843</v>
       </c>
       <c r="M15" s="11" t="n">
-        <v>0.6526921496095356</v>
+        <v>0.6535460992907801</v>
       </c>
     </row>
     <row r="16">
@@ -8685,16 +8685,16 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="I16" s="9" t="n">
         <v>1</v>
@@ -8709,7 +8709,7 @@
         <v>1381</v>
       </c>
       <c r="M16" s="11" t="n">
-        <v>0.6511079679396511</v>
+        <v>0.6508011310084825</v>
       </c>
     </row>
     <row r="17">
@@ -8732,31 +8732,31 @@
         </is>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2904</v>
+        <v>2905</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>1005</v>
+        <v>994</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I17" s="9" t="n">
         <v>24</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1795</v>
+        <v>1834</v>
       </c>
       <c r="K17" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>1821</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>0.6270661157024794</v>
+        <v>1860</v>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>0.6402753872633391</v>
       </c>
     </row>
     <row r="18">
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="E18" s="9" t="n">
-        <v>2848</v>
+        <v>2849</v>
       </c>
       <c r="F18" s="9" t="n">
         <v>1060</v>
@@ -8788,13 +8788,13 @@
         <v>3</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>1772</v>
+        <v>1743</v>
       </c>
       <c r="K18" s="9" t="n">
         <v>8</v>
@@ -8803,7 +8803,7 @@
         <v>1785</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.6267556179775281</v>
+        <v>0.6265356265356266</v>
       </c>
     </row>
     <row r="19">
@@ -8826,31 +8826,31 @@
         </is>
       </c>
       <c r="E19" s="9" t="n">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>751</v>
+        <v>743</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="I19" s="9" t="n">
         <v>12</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1349</v>
+        <v>1355</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1362</v>
+        <v>1368</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.6239120476408612</v>
+        <v>0.6260869565217392</v>
       </c>
     </row>
     <row r="20">
@@ -8859,45 +8859,45 @@
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Kezia Maralending</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>Tahuna</t>
+          <t>Tatoareng</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Sutriwati</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>2684</v>
+        <v>1456</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1052</v>
+        <v>295</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>29</v>
+        <v>260</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1597</v>
+        <v>876</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1598</v>
+        <v>882</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.5953800298062594</v>
+        <v>0.6057692307692307</v>
       </c>
     </row>
     <row r="21">
@@ -8906,45 +8906,45 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>Kezia Maralending</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Tatoareng</t>
+          <t>Tahuna</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Sutriwati</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="E21" s="9" t="n">
-        <v>1452</v>
+        <v>2694</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>302</v>
+        <v>1031</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>271</v>
+        <v>25</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>856</v>
+        <v>1630</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>864</v>
+        <v>1631</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.5950413223140496</v>
+        <v>0.605419450631032</v>
       </c>
     </row>
     <row r="22">
@@ -8967,31 +8967,31 @@
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>869</v>
+        <v>858</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>1423</v>
+        <v>1428</v>
       </c>
       <c r="K22" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>1457</v>
+        <v>1466</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.5905958654235914</v>
+        <v>0.5935222672064777</v>
       </c>
     </row>
     <row r="23">
@@ -9014,31 +9014,31 @@
         </is>
       </c>
       <c r="E23" s="9" t="n">
-        <v>2339</v>
+        <v>2346</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>873</v>
+        <v>859</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="I23" s="9" t="n">
         <v>22</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>1315</v>
+        <v>1331</v>
       </c>
       <c r="K23" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1339</v>
+        <v>1355</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.5724668661821292</v>
+        <v>0.5775788576300085</v>
       </c>
     </row>
     <row r="24">
@@ -9064,28 +9064,28 @@
         <v>2746</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="G24" s="9" t="n">
- 